--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-04T22:20:16</t>
+          <t>CreatedAt: 2026-03-04T23:21:24</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46.8</v>
+        <v>44.72</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.33</v>
+        <v>40.62</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>35.02</v>
+        <v>35.29</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>35.4</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>35.68</v>
-      </c>
       <c r="H4" s="3" t="n">
-        <v>35.33</v>
+        <v>35.1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>48.25</v>
+        <v>40.14</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>42.04</v>
+        <v>47</v>
       </c>
       <c r="K4" s="3" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>37.12</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>35.05</v>
-      </c>
       <c r="N4" s="3" t="n">
-        <v>40.33</v>
+        <v>37.24</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>36.89</v>
+        <v>35.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>40.1</v>
+        <v>37.19</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>37.19</v>
+        <v>37.15</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>40.13</v>
+        <v>36.93</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>55.05</v>
+        <v>51.67</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>50.73</v>
+        <v>50.54</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>45.16</v>
+        <v>50.63</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>60.42</v>
+        <v>63.25</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>65.38</v>
+        <v>64.56</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>54.16</v>
+        <v>55.22</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>50.9</v>
+        <v>48.75</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>40.49</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="5">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.35</v>
+        <v>0.04</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>-0.14</v>
@@ -836,58 +836,58 @@
         <v>-0.25</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.36</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.8</v>
       </c>
       <c r="K6" s="3" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>-0.59</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>-0.63</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.5</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.59</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.72</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.82</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.42</v>
+        <v>-2.59</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.62</v>
+        <v>-2.52</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.78</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="7">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>48.4</v>
+        <v>46.25</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>36.6</v>
+        <v>41.79</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>36.32</v>
+        <v>36.67</v>
       </c>
       <c r="F9" s="3" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>36.83</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>37.12</v>
-      </c>
       <c r="H9" s="3" t="n">
-        <v>36.49</v>
+        <v>36.17</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>49.52</v>
+        <v>41.12</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>42.42</v>
+        <v>47.32</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>37.86</v>
+        <v>42.59</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>36.68</v>
+        <v>37.71</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>35.86</v>
+        <v>38.09</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>41.47</v>
+        <v>38.33</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>38.13</v>
+        <v>36.55</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>41.24</v>
+        <v>38.29</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>38.29</v>
+        <v>38.25</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>41.57</v>
+        <v>38.24</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>56.65</v>
+        <v>53.16</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>50.73</v>
+        <v>50.54</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>45.74</v>
+        <v>51.23</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>60.83</v>
+        <v>63.68</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>67.45</v>
+        <v>66.48</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>55.84</v>
+        <v>56.88</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>52.49</v>
+        <v>50.24</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.9</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="10">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.91</v>
+        <v>1.21</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="F11" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="H11" s="3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2.01</v>
+        <v>-2.17</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="12">
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>48.4</v>
+        <v>46.25</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>36.64</v>
+        <v>41.79</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>36.36</v>
+        <v>36.67</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>36.83</v>
+        <v>37.02</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>37.16</v>
+        <v>36.87</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>36.49</v>
+        <v>36.21</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>49.52</v>
+        <v>41.12</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>42.42</v>
+        <v>47.32</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>37.86</v>
+        <v>42.63</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>36.68</v>
+        <v>37.71</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>35.86</v>
+        <v>38.13</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>41.51</v>
+        <v>38.37</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>38.13</v>
+        <v>36.55</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>41.28</v>
+        <v>38.29</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>38.29</v>
+        <v>38.25</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>41.57</v>
+        <v>38.24</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>56.71</v>
+        <v>140.9</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>50.73</v>
+        <v>50.54</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>45.74</v>
+        <v>51.23</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>60.89</v>
+        <v>63.68</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>67.45</v>
+        <v>66.48</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>55.9</v>
+        <v>56.94</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>52.55</v>
+        <v>50.24</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>41.9</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="15">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0</v>
+        <v>87.73</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.95</v>
+        <v>1.21</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.72</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.95</v>
+        <v>-2.17</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="17">
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46.52</v>
+        <v>44.5</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>35.12</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>34.85</v>
-      </c>
       <c r="F19" s="3" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>35.22</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>35.5</v>
-      </c>
       <c r="H19" s="3" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="O19" s="3" t="n">
         <v>35.19</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>41.84</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>40.13</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>36.78</v>
-      </c>
       <c r="P19" s="3" t="n">
-        <v>39.94</v>
+        <v>37.01</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>37.08</v>
+        <v>36.97</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>39.98</v>
+        <v>36.75</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>54.68</v>
+        <v>51.22</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>50.34</v>
+        <v>50.06</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>44.78</v>
+        <v>50.15</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>59.84</v>
+        <v>62.65</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>64.88</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>53.69</v>
+        <v>54.8</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>50.55</v>
+        <v>48.42</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>40.25</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="20">
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.13</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>-0.5600000000000001</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.52</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>-0.32</v>
@@ -2093,61 +2093,61 @@
         <v>-0.32</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.03</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>-0.78</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>-0.84</v>
-      </c>
       <c r="N21" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.78</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.67</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.88</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.95</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.01</v>
+        <v>-2.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.31</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.99</v>
+        <v>-3.2</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-3.11</v>
+        <v>-3.01</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.04</v>
+        <v>-2.03</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.11</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="22">
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>46.52</v>
+        <v>44.5</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>35.12</v>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>34.85</v>
-      </c>
       <c r="F24" s="3" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>35.22</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>35.5</v>
-      </c>
       <c r="H24" s="3" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="O24" s="3" t="n">
         <v>35.19</v>
       </c>
-      <c r="I24" s="3" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>41.84</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>40.13</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>36.78</v>
-      </c>
       <c r="P24" s="3" t="n">
-        <v>39.94</v>
+        <v>37.01</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>37.08</v>
+        <v>36.97</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>39.98</v>
+        <v>36.75</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>54.68</v>
+        <v>51.22</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>50.34</v>
+        <v>50.06</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>44.78</v>
+        <v>50.15</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>59.84</v>
+        <v>62.65</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>64.88</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>53.69</v>
+        <v>54.8</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>50.55</v>
+        <v>48.42</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>40.25</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="25">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.13</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>-0.5600000000000001</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-0.52</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>-0.32</v>
@@ -2513,61 +2513,61 @@
         <v>-0.32</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.03</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>-0.78</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>-0.84</v>
-      </c>
       <c r="N26" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.78</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.67</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.88</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.95</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.01</v>
+        <v>-2.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.31</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.99</v>
+        <v>-3.2</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-3.11</v>
+        <v>-3.01</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.04</v>
+        <v>-2.03</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.11</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="27">
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>46.07</v>
+        <v>44.01</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>34.78</v>
+        <v>39.9</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>34.58</v>
+        <v>34.85</v>
       </c>
       <c r="F29" s="3" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="G29" s="3" t="n">
         <v>34.91</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>35.22</v>
-      </c>
       <c r="H29" s="3" t="n">
-        <v>34.91</v>
+        <v>34.61</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>47.64</v>
+        <v>39.67</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>41.51</v>
+        <v>46.45</v>
       </c>
       <c r="K29" s="3" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>36.61</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>34.48</v>
-      </c>
       <c r="N29" s="3" t="n">
-        <v>39.78</v>
+        <v>36.62</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>36.49</v>
+        <v>34.81</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>39.67</v>
+        <v>36.65</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>36.83</v>
+        <v>36.65</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>39.7</v>
+        <v>36.39</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>54.11</v>
+        <v>50.54</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>49.86</v>
+        <v>49.54</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>44.31</v>
+        <v>49.58</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>59.11</v>
+        <v>61.94</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>64.14</v>
+        <v>63.28</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>53.07</v>
+        <v>54.12</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>49.96</v>
+        <v>47.86</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>39.82</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="30">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.62</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.68</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.84</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.73</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.83</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.35</v>
       </c>
       <c r="K31" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M31" s="3" t="n">
         <v>-1.1</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>-1.21</v>
-      </c>
       <c r="N31" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.17</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.84</v>
+        <v>-1.04</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.1</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.88</v>
+        <v>-1.1</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.24</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-2.43</v>
+        <v>-2.63</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.72</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.88</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.9</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.85</v>
+        <v>-3.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.65</v>
+        <v>-2.71</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.68</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="32">
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>49.11</v>
+        <v>46.98</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>36.94</v>
+        <v>42.23</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>36.62</v>
+        <v>37.02</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>37.22</v>
+        <v>37.44</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>37.55</v>
+        <v>37.29</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>36.79</v>
+        <v>36.43</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>49.62</v>
+        <v>41.16</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>42.8</v>
+        <v>47.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>37.79</v>
+        <v>42.55</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>36.79</v>
+        <v>37.87</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>35.83</v>
+        <v>38.09</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>41.68</v>
+        <v>38.61</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>38.37</v>
+        <v>36.89</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>41.32</v>
+        <v>38.44</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>38.36</v>
+        <v>38.4</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>41.91</v>
+        <v>38.63</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>57</v>
+        <v>77.23</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>50.88</v>
+        <v>50.79</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>45.74</v>
+        <v>51.28</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>61.48</v>
+        <v>64.36</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>68.75</v>
+        <v>67.69</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>53.08</v>
+        <v>50.54</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>42.2</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="35">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0</v>
+        <v>23.69</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="S36" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="X36" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="Y36" s="3" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="37">
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>46.8</v>
+        <v>44.72</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>35.33</v>
+        <v>40.62</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>35.02</v>
+        <v>35.29</v>
       </c>
       <c r="F39" s="3" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="G39" s="3" t="n">
         <v>35.4</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>35.68</v>
-      </c>
       <c r="H39" s="3" t="n">
-        <v>35.33</v>
+        <v>35.1</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>48.25</v>
+        <v>40.14</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>42.04</v>
+        <v>47</v>
       </c>
       <c r="K39" s="3" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>37.12</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>35.05</v>
-      </c>
       <c r="N39" s="3" t="n">
-        <v>40.33</v>
+        <v>37.24</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>36.89</v>
+        <v>35.36</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>40.1</v>
+        <v>37.19</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>37.19</v>
+        <v>37.15</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>40.13</v>
+        <v>36.93</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>55.05</v>
+        <v>51.67</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>50.73</v>
+        <v>50.54</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>45.16</v>
+        <v>50.63</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>60.42</v>
+        <v>63.25</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>65.38</v>
+        <v>64.56</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>54.16</v>
+        <v>55.22</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>50.9</v>
+        <v>48.75</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>40.49</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="40">
@@ -3758,16 +3758,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.35</v>
+        <v>0.04</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>-0.14</v>
@@ -3776,58 +3776,58 @@
         <v>-0.25</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.36</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.8</v>
       </c>
       <c r="K41" s="3" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>-0.59</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>-0.63</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.5</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.59</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.72</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.82</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.42</v>
+        <v>-2.59</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.62</v>
+        <v>-2.52</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.78</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="42">
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>48</v>
+        <v>45.77</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>36.56</v>
       </c>
-      <c r="E44" s="3" t="n">
-        <v>36.24</v>
-      </c>
       <c r="F44" s="3" t="n">
-        <v>36.49</v>
+        <v>36.6</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>36.74</v>
+        <v>36.42</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>36.42</v>
+        <v>36.17</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>50.03</v>
+        <v>41.58</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>43.67</v>
+        <v>48.77</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>38.25</v>
+        <v>43.15</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>36.6</v>
+        <v>37.67</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>35.97</v>
+        <v>38.05</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>41.35</v>
+        <v>38.22</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>37.71</v>
+        <v>36.18</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>41.07</v>
+        <v>38.17</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>38.13</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>41.27</v>
+        <v>38.09</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>57.75</v>
+        <v>54.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>53.53</v>
+        <v>53.44</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>47.84</v>
+        <v>53.58</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>64.05</v>
+        <v>67.05</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>69.31</v>
+        <v>68.38</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>56.87</v>
+        <v>57.99</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>53.03</v>
+        <v>50.65</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>42.03</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="45">
@@ -4178,73 +4178,73 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>0.88</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.87</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O46" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="P46" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.42</v>
-      </c>
       <c r="R46" s="3" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>1.18</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>1.18</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>46.43</v>
+        <v>44.19</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>35.9</v>
+        <v>40.86</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>35.52</v>
+        <v>35.83</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>35.68</v>
+        <v>35.79</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>35.43</v>
+        <v>35.05</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>33.85</v>
+        <v>33.59</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>44.67</v>
+        <v>37.05</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>38.73</v>
+        <v>43.26</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>34.1</v>
+        <v>38.5</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>34.28</v>
+        <v>35.25</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>35.83</v>
+        <v>37.86</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>40.97</v>
+        <v>37.87</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>37.26</v>
+        <v>35.79</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>40.66</v>
+        <v>37.79</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>37.75</v>
+        <v>37.79</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>40.94</v>
+        <v>37.82</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>54.63</v>
+        <v>51.42</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>47.68</v>
+        <v>47.64</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>42.81</v>
+        <v>47.9</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>57.49</v>
+        <v>60.13</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>65.19</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>53.84</v>
+        <v>54.9</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>52.71</v>
+        <v>50.24</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>41.43</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="50">
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.44</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>0.14</v>
@@ -4610,25 +4610,25 @@
         <v>0.14</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.49</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.75</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-4.11</v>
+        <v>-3.45</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-4.03</v>
+        <v>-4.54</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-3.61</v>
+        <v>-4.04</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-1.95</v>
+        <v>-2.04</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>0.08</v>
@@ -4643,28 +4643,28 @@
         <v>0.04</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.91</v>
+        <v>-1.75</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-4.67</v>
+        <v>-4.62</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-4.02</v>
+        <v>-4.55</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.35</v>
+        <v>-5.71</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.8</v>
+        <v>-2.77</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.88</v>
+        <v>-1.92</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>0.58</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>48.75</v>
+        <v>46.34</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>37.13</v>
+        <v>42.23</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>36.36</v>
+        <v>36.75</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>36.79</v>
+        <v>36.94</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>36.44</v>
+        <v>36.12</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>35.65</v>
+        <v>35.38</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>46.95</v>
+        <v>38.98</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>40.92</v>
+        <v>45.83</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>35.92</v>
+        <v>40.68</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>35.35</v>
+        <v>36.53</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>35.19</v>
+        <v>37.34</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>40.41</v>
+        <v>37.57</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>36.67</v>
+        <v>35.43</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>39.63</v>
+        <v>37.01</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>36.83</v>
+        <v>37.05</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>39.7</v>
+        <v>36.86</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>55.32</v>
+        <v>52.07</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>51.23</v>
+        <v>51.24</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>44.52</v>
+        <v>49.82</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>62.21</v>
+        <v>65.13</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>67.58</v>
+        <v>66.61</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>55.51</v>
+        <v>56.6</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>52.02</v>
+        <v>49.39</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>40.77</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="55">
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.52</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.87</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.77</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.37</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.23</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.43</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.74</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.7</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.77</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.09</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.02</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.64</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.72</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="57">
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>49.37</v>
+        <v>47.08</v>
       </c>
       <c r="D59" s="3" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E59" s="3" t="n">
         <v>37.68</v>
       </c>
-      <c r="E59" s="3" t="n">
-        <v>37.35</v>
-      </c>
       <c r="F59" s="3" t="n">
-        <v>37.57</v>
+        <v>37.72</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>37.83</v>
+        <v>37.49</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>37.49</v>
+        <v>37.24</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>51.62</v>
+        <v>42.86</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>45.1</v>
+        <v>50.37</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>39.66</v>
+        <v>44.74</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>37.98</v>
+        <v>39.1</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>37.36</v>
+        <v>39.53</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>43</v>
+        <v>39.74</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>39.13</v>
+        <v>37.59</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>42.71</v>
+        <v>39.65</v>
       </c>
       <c r="Q59" s="3" t="n">
         <v>39.61</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>42.83</v>
+        <v>39.53</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>59.83</v>
+        <v>56.26</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>55.46</v>
+        <v>55.36</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>49.56</v>
+        <v>55.51</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>71.87</v>
+        <v>70.91</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>58.85</v>
+        <v>60.01</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>54.77</v>
+        <v>52.25</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>43.32</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="60">
@@ -5438,73 +5438,73 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J61" s="3" t="n">
         <v>2.57</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>2.35</v>
-      </c>
       <c r="K61" s="3" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q61" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R61" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R61" s="3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S61" s="3" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>2.47</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>50.06</v>
+        <v>47.73</v>
       </c>
       <c r="D64" s="3" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>38.2</v>
       </c>
-      <c r="E64" s="3" t="n">
-        <v>37.87</v>
-      </c>
       <c r="F64" s="3" t="n">
-        <v>38.09</v>
+        <v>38.25</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>38.35</v>
+        <v>38.01</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>38.05</v>
+        <v>37.8</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>52.4</v>
+        <v>43.5</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>45.83</v>
+        <v>51.18</v>
       </c>
       <c r="K64" s="3" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="P64" s="3" t="n">
         <v>40.29</v>
       </c>
-      <c r="L64" s="3" t="n">
-        <v>38.59</v>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>43.69</v>
-      </c>
-      <c r="O64" s="3" t="n">
-        <v>39.72</v>
-      </c>
-      <c r="P64" s="3" t="n">
-        <v>43.35</v>
-      </c>
       <c r="Q64" s="3" t="n">
-        <v>40.25</v>
+        <v>40.24</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>43.47</v>
+        <v>40.16</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>60.86</v>
+        <v>57.29</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>56.48</v>
+        <v>56.38</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>50.47</v>
+        <v>56.53</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>73.19</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>59.86</v>
+        <v>61.04</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>55.65</v>
+        <v>53.09</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>43.97</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="D66" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>2.52</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="F66" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q66" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="G66" s="3" t="n">
+      <c r="R66" s="3" t="n">
         <v>2.53</v>
       </c>
-      <c r="H66" s="3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Q66" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R66" s="3" t="n">
-        <v>2.74</v>
-      </c>
       <c r="S66" s="3" t="n">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>4.12</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.63</v>
+        <v>4.07</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.66</v>
+        <v>4.88</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>5.2</v>
+        <v>5.13</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>4.13</v>
+        <v>4.21</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="67">
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>50.6</v>
+        <v>48.3</v>
       </c>
       <c r="D69" s="3" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="E69" s="3" t="n">
         <v>38.66</v>
       </c>
-      <c r="E69" s="3" t="n">
-        <v>38.33</v>
-      </c>
       <c r="F69" s="3" t="n">
-        <v>38.55</v>
+        <v>38.66</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>38.81</v>
+        <v>38.42</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>38.46</v>
+        <v>38.21</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>52.97</v>
+        <v>43.97</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>46.27</v>
+        <v>51.67</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>40.77</v>
+        <v>46</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>39.01</v>
+        <v>40.15</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>38.37</v>
+        <v>40.59</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>44.21</v>
+        <v>40.86</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>40.19</v>
+        <v>38.6</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>43.91</v>
+        <v>40.81</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>40.68</v>
+        <v>40.72</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>43.94</v>
+        <v>40.59</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>61.52</v>
+        <v>57.85</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>56.97</v>
+        <v>56.93</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>50.91</v>
+        <v>57.02</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>68.15000000000001</v>
+        <v>71.34</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>72.83</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>60.44</v>
+        <v>61.63</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>56.19</v>
+        <v>53.61</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>44.45</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="D71" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E71" s="3" t="n">
         <v>2.98</v>
       </c>
-      <c r="E71" s="3" t="n">
-        <v>2.95</v>
-      </c>
       <c r="F71" s="3" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="H71" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M71" s="3" t="n">
         <v>2.88</v>
       </c>
-      <c r="I71" s="3" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="K71" s="3" t="n">
+      <c r="N71" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="L71" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>3.32</v>
-      </c>
       <c r="O71" s="3" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.29</v>
+        <v>3.06</v>
       </c>
       <c r="Q71" s="3" t="n">
         <v>2.97</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>4.98</v>
+        <v>4.69</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="U71" s="3" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="Y71" s="3" t="n">
         <v>4.07</v>
       </c>
-      <c r="V71" s="3" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="W71" s="3" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="X71" s="3" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="Y71" s="3" t="n">
-        <v>4.33</v>
-      </c>
       <c r="Z71" s="3" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="72">
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>48.8</v>
+        <v>46.54</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>37.29</v>
+        <v>42.49</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>37.08</v>
+        <v>37.4</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>37.26</v>
+        <v>37.37</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>37.39</v>
+        <v>37.02</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>37.06</v>
+        <v>36.81</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>50.87</v>
+        <v>42.23</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>44.63</v>
+        <v>49.69</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>39.12</v>
+        <v>44.18</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>37.63</v>
+        <v>38.69</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>37.17</v>
+        <v>39.32</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>42.77</v>
+        <v>39.54</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>38.81</v>
+        <v>37.27</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>42.31</v>
+        <v>39.32</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>39.37</v>
+        <v>39.4</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>42.43</v>
+        <v>39.2</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>59.27</v>
+        <v>55.79</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>54.88</v>
+        <v>54.78</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>48.99</v>
+        <v>54.87</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>65.59</v>
+        <v>68.66</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>71.34</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>58.29</v>
+        <v>59.44</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>54.42</v>
+        <v>51.92</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>43</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="75">
@@ -6698,73 +6698,73 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="L76" s="3" t="n">
         <v>1.39</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="Q76" s="3" t="n">
         <v>1.65</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>2.52</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>2.15</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>46.8</v>
+        <v>44.63</v>
       </c>
       <c r="D79" s="3" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="E79" s="3" t="n">
         <v>35.68</v>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>35.38</v>
-      </c>
       <c r="F79" s="3" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="G79" s="3" t="n">
         <v>35.54</v>
       </c>
-      <c r="G79" s="3" t="n">
-        <v>35.82</v>
-      </c>
       <c r="H79" s="3" t="n">
-        <v>35.58</v>
+        <v>35.34</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>48.78</v>
+        <v>40.5</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>42.76</v>
+        <v>47.8</v>
       </c>
       <c r="K79" s="3" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="M79" s="3" t="n">
         <v>37.71</v>
       </c>
-      <c r="L79" s="3" t="n">
-        <v>36.24</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>35.68</v>
-      </c>
       <c r="N79" s="3" t="n">
-        <v>40.89</v>
+        <v>37.8</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>37.33</v>
+        <v>35.86</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>40.62</v>
+        <v>37.75</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>37.71</v>
+        <v>37.75</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>40.74</v>
+        <v>37.63</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>56.54</v>
+        <v>53.16</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>52.35</v>
+        <v>52.26</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>46.84</v>
+        <v>52.46</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>62.83</v>
+        <v>65.84</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>67.98999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>55.73</v>
+        <v>56.83</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>51.86</v>
+        <v>49.53</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="80">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>49.9</v>
+        <v>47.18</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>38.08</v>
+        <v>43.26</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>36.54</v>
+        <v>37.05</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>37.45</v>
+        <v>37.64</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>36.41</v>
+        <v>36.08</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>35.94</v>
+        <v>35.59</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>45.8</v>
+        <v>38.03</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>39.33</v>
+        <v>44.18</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>34.44</v>
+        <v>39.21</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>34.45</v>
+        <v>35.86</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34.61</v>
+        <v>36.86</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>39.39</v>
+        <v>36.91</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>35.39</v>
+        <v>34.48</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>14.5</v>
+        <v>35.45</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>12.9</v>
+        <v>35.68</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>12.75</v>
+        <v>35.6</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>52.99</v>
+        <v>49.97</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>49.39</v>
+        <v>49.44</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>17.31</v>
+        <v>46.05</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>59.84</v>
+        <v>62.71</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>64.81</v>
+        <v>23.55</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>53.18</v>
+        <v>54.33</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>19.98</v>
+        <v>47.22</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>39.13</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="85">
@@ -7493,13 +7493,13 @@
         <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>-23.21</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>-22.28</v>
+        <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>-25.28</v>
+        <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
         <v>0</v>
@@ -7508,19 +7508,19 @@
         <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-23.85</v>
+        <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>0</v>
+        <v>-40.21</v>
       </c>
       <c r="X85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>-29.65</v>
+        <v>0</v>
       </c>
       <c r="Z85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>3.09</v>
+        <v>2.55</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-2.98</v>
+        <v>-2.47</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-3.42</v>
+        <v>-3.62</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.33</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.43</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-1.07</v>
+        <v>-0.85</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-1.5</v>
+        <v>-0.89</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-1.95</v>
+        <v>-1.38</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-2.9</v>
+        <v>-2.3</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.07</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-2.7</v>
+        <v>-2.03</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-3.55</v>
+        <v>-3.2</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.96</v>
+        <v>-2.82</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-5.68</v>
+        <v>-6.4</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.99</v>
+        <v>-3.14</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.18</v>
+        <v>-3.32</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-2.55</v>
+        <v>-2.5</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-2.23</v>
+        <v>-2.31</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="87">
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>46.07</v>
+        <v>44.01</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>34.78</v>
+        <v>39.9</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>34.58</v>
+        <v>34.85</v>
       </c>
       <c r="F89" s="3" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="G89" s="3" t="n">
         <v>34.91</v>
       </c>
-      <c r="G89" s="3" t="n">
-        <v>35.22</v>
-      </c>
       <c r="H89" s="3" t="n">
-        <v>34.91</v>
+        <v>34.61</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>47.64</v>
+        <v>39.67</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>41.51</v>
+        <v>46.45</v>
       </c>
       <c r="K89" s="3" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="M89" s="3" t="n">
         <v>36.61</v>
       </c>
-      <c r="L89" s="3" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>34.48</v>
-      </c>
       <c r="N89" s="3" t="n">
-        <v>39.78</v>
+        <v>36.62</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>36.49</v>
+        <v>34.81</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>39.67</v>
+        <v>36.65</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>36.83</v>
+        <v>36.65</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>39.7</v>
+        <v>36.39</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>54.11</v>
+        <v>50.54</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>49.86</v>
+        <v>49.54</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>44.27</v>
+        <v>49.58</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>59.11</v>
+        <v>61.88</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>64.14</v>
+        <v>63.28</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>53.02</v>
+        <v>54.12</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>49.96</v>
+        <v>47.86</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>39.82</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="90">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.62</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.68</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.84</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.73</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.83</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.35</v>
       </c>
       <c r="K91" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M91" s="3" t="n">
         <v>-1.1</v>
       </c>
-      <c r="L91" s="3" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>-1.21</v>
-      </c>
       <c r="N91" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.17</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.84</v>
+        <v>-1.04</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.1</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.88</v>
+        <v>-1.1</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.24</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-2.43</v>
+        <v>-2.63</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.72</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.88</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.96</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.85</v>
+        <v>-3.8</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.7</v>
+        <v>-2.71</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.68</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-06T06:12:33</t>
+          <t>CreatedAt: 2026-03-06T07:11:13</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -674,52 +674,52 @@
         <v>79.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>60.84</v>
+        <v>60.96</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>37.47</v>
+        <v>61.02</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>56.87</v>
+        <v>54.15</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>60.25</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>60.6</v>
-      </c>
       <c r="P4" s="3" t="n">
-        <v>57.79</v>
+        <v>51.87</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>51.92</v>
+        <v>50.64</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>56.32</v>
+        <v>52.02</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>39.39</v>
+        <v>47.22</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>50.31</v>
+        <v>49.8</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>47.8</v>
+        <v>39.69</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>38.9</v>
+        <v>38.94</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>37.04</v>
+        <v>37.03</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>36.65</v>
+        <v>36.61</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>33</v>
+        <v>33.99</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>37.17</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="5">
@@ -842,37 +842,37 @@
         <v>-1.82</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.58</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.46</v>
       </c>
       <c r="M6" s="3" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>-1.76</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-1.96</v>
-      </c>
       <c r="Q6" s="3" t="n">
-        <v>-1.71</v>
+        <v>-1.67</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.66</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.64</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.19</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-0.97</v>
@@ -884,7 +884,7 @@
         <v>-1.17</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.78</v>
@@ -1094,52 +1094,52 @@
         <v>78.75</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>60.03</v>
+        <v>60.14</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>36.97</v>
+        <v>59.85</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>56.99</v>
+        <v>53.78</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>61.74</v>
+        <v>53</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>62.86</v>
+        <v>61.93</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>59.81</v>
+        <v>53.15</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>53.63</v>
+        <v>51.9</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>58.48</v>
+        <v>53.52</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>40.86</v>
+        <v>48.92</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>51.31</v>
+        <v>50.73</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48.99</v>
+        <v>40.68</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>40.6</v>
+        <v>40.64</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>38.81</v>
+        <v>38.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>38.24</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>34.48</v>
+        <v>35.51</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>38.89</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="10">
@@ -1262,37 +1262,37 @@
         <v>-2.13</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.52</v>
+        <v>-2.41</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.59</v>
+        <v>-2.63</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.65</v>
+        <v>-2.1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.49</v>
+        <v>-1.01</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.44</v>
+        <v>-0.25</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.48</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.41</v>
+        <v>-0.16</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>0.73</v>
@@ -1301,10 +1301,10 @@
         <v>0.62</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.93</v>
@@ -1514,52 +1514,52 @@
         <v>78.75</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>60.03</v>
+        <v>60.14</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>36.97</v>
+        <v>59.85</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>56.99</v>
+        <v>53.78</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>61.74</v>
+        <v>53</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>62.86</v>
+        <v>61.93</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>59.81</v>
+        <v>53.21</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>53.69</v>
+        <v>51.9</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>58.48</v>
+        <v>53.57</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>40.86</v>
+        <v>48.97</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>51.31</v>
+        <v>50.73</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>48.99</v>
+        <v>40.72</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>40.65</v>
+        <v>40.69</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>38.85</v>
+        <v>38.84</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>38.28</v>
+        <v>38.24</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>34.48</v>
+        <v>35.54</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>38.89</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="15">
@@ -1682,37 +1682,37 @@
         <v>-2.13</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.52</v>
+        <v>-2.41</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.59</v>
+        <v>-2.63</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.65</v>
+        <v>-2.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.49</v>
+        <v>-1.01</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.44</v>
+        <v>-0.25</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.43</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.42</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.41</v>
+        <v>-0.11</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>0.77</v>
@@ -1724,7 +1724,7 @@
         <v>0.46</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>0.93</v>
@@ -1934,52 +1934,52 @@
         <v>78.22</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>60.2</v>
+        <v>60.31</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>37.15</v>
+        <v>60.31</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>56.27</v>
+        <v>53.52</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>59.67</v>
+        <v>51.68</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>60.02</v>
+        <v>59.61</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>57.29</v>
+        <v>51.37</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>51.42</v>
+        <v>50.21</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>55.78</v>
+        <v>51.52</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>39.09</v>
+        <v>46.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>49.78</v>
+        <v>49.28</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>47.29</v>
+        <v>39.31</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>38.6</v>
+        <v>38.67</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>36.75</v>
+        <v>36.74</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>36.37</v>
+        <v>36.33</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>32.75</v>
+        <v>33.72</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>36.85</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="20">
@@ -2102,40 +2102,40 @@
         <v>-2.66</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.23</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-1.41</v>
+        <v>-2.17</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-2.36</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.33</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-2.4</v>
+        <v>-2.56</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2.26</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.11</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.16</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.83</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.17</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.84</v>
+        <v>-1.57</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.24</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>-1.43</v>
@@ -2144,7 +2144,7 @@
         <v>-1.45</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.21</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>-1.11</v>
@@ -2354,52 +2354,52 @@
         <v>78.22</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>60.2</v>
+        <v>60.31</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>37.15</v>
+        <v>60.31</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>56.27</v>
+        <v>53.52</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>59.67</v>
+        <v>51.68</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>60.02</v>
+        <v>59.61</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>57.29</v>
+        <v>51.37</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>51.42</v>
+        <v>50.21</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>55.78</v>
+        <v>51.52</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>39.09</v>
+        <v>46.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>49.78</v>
+        <v>49.28</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>47.29</v>
+        <v>39.31</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>38.6</v>
+        <v>38.67</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>36.75</v>
+        <v>36.74</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>36.37</v>
+        <v>36.33</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>32.75</v>
+        <v>33.72</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>36.85</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="25">
@@ -2522,40 +2522,40 @@
         <v>-2.66</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.23</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.41</v>
+        <v>-2.17</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>-2.36</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.33</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-2.4</v>
+        <v>-2.56</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2.26</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.11</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.16</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.83</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.17</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.84</v>
+        <v>-1.57</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.24</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>-1.43</v>
@@ -2564,7 +2564,7 @@
         <v>-1.45</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.21</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>-1.11</v>
@@ -2774,52 +2774,52 @@
         <v>77.03</v>
       </c>
       <c r="K29" s="3" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>59.34</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>36.76</v>
-      </c>
       <c r="M29" s="3" t="n">
-        <v>55.37</v>
+        <v>52.67</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>58.77</v>
+        <v>50.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>59.11</v>
+        <v>58.66</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>56.42</v>
+        <v>50.6</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>50.64</v>
+        <v>49.49</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>54.89</v>
+        <v>50.69</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>38.61</v>
+        <v>46.36</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>49.03</v>
+        <v>48.53</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>46.53</v>
+        <v>38.71</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>38.12</v>
+        <v>38.19</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>36.26</v>
+        <v>36.25</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>35.89</v>
+        <v>35.85</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.31</v>
+        <v>33.27</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>36.32</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="30">
@@ -2942,40 +2942,40 @@
         <v>-3.85</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-3.2</v>
+        <v>-3.04</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.8</v>
+        <v>-3.14</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.21</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-3.47</v>
+        <v>-3.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3.52</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-3.33</v>
+        <v>-3.04</v>
       </c>
       <c r="Q31" s="3" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>-2.99</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>-3.18</v>
-      </c>
       <c r="S31" s="3" t="n">
-        <v>-2.05</v>
+        <v>-2.36</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.89</v>
+        <v>-2.91</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.17</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>-1.92</v>
@@ -2984,10 +2984,10 @@
         <v>-1.94</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.66</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="32">
@@ -3194,52 +3194,52 @@
         <v>78.83</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>59.68</v>
+        <v>59.74</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>36.94</v>
+        <v>59.85</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>57.66</v>
+        <v>54.04</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>62.68</v>
+        <v>53.47</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>63.7</v>
+        <v>62.3</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>60.17</v>
+        <v>53.1</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>54.01</v>
+        <v>51.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>59.13</v>
+        <v>53.68</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>41.06</v>
+        <v>49.17</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>51.36</v>
+        <v>50.78</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>49.33</v>
+        <v>40.96</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>41.23</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>39.45</v>
+        <v>39.4</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>38.71</v>
+        <v>38.72</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>34.94</v>
+        <v>35.98</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>39.45</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="35">
@@ -3362,49 +3362,49 @@
         <v>-2.05</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-2.86</v>
+        <v>-2.81</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.63</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.98</v>
+        <v>-1.84</v>
       </c>
       <c r="N36" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="O36" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>0.41</v>
-      </c>
       <c r="T36" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.5</v>
@@ -3614,52 +3614,52 @@
         <v>79.06</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>60.84</v>
+        <v>60.96</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>37.47</v>
+        <v>61.02</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>56.87</v>
+        <v>54.15</v>
       </c>
       <c r="N39" s="3" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="O39" s="3" t="n">
         <v>60.25</v>
       </c>
-      <c r="O39" s="3" t="n">
-        <v>60.6</v>
-      </c>
       <c r="P39" s="3" t="n">
-        <v>57.79</v>
+        <v>51.87</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>51.92</v>
+        <v>50.64</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>56.32</v>
+        <v>52.02</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>39.39</v>
+        <v>47.22</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>50.31</v>
+        <v>49.8</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>47.8</v>
+        <v>39.69</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>38.9</v>
+        <v>38.94</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>37.04</v>
+        <v>37.03</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>36.65</v>
+        <v>36.61</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>33</v>
+        <v>33.99</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>37.17</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="40">
@@ -3782,37 +3782,37 @@
         <v>-1.82</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.58</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.46</v>
       </c>
       <c r="M41" s="3" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="P41" s="3" t="n">
         <v>-1.76</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>-1.96</v>
-      </c>
       <c r="Q41" s="3" t="n">
-        <v>-1.71</v>
+        <v>-1.67</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.66</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.64</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.19</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-0.97</v>
@@ -3824,7 +3824,7 @@
         <v>-1.17</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.78</v>
@@ -4034,52 +4034,52 @@
         <v>81.7</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>62.92</v>
+        <v>63.11</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>38.48</v>
+        <v>62.74</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>58.35</v>
+        <v>55.55</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>61.93</v>
+        <v>53.73</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>62.24</v>
+        <v>61.99</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>59.75</v>
+        <v>53.63</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>53.63</v>
+        <v>52.32</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>58.19</v>
+        <v>53.79</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>40.94</v>
+        <v>49.07</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>52.55</v>
+        <v>52.02</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>49.73</v>
+        <v>41.33</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>40.32</v>
+        <v>40.36</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>38.42</v>
+        <v>38.41</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>38.01</v>
+        <v>37.94</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>33.99</v>
+        <v>35.08</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>38.53</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="45">
@@ -4202,16 +4202,16 @@
         <v>0.82</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.25</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>-0.19</v>
@@ -4223,16 +4223,16 @@
         <v>0</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.44</v>
@@ -4241,10 +4241,10 @@
         <v>0.23</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>0.58</v>
@@ -4454,49 +4454,49 @@
         <v>77.77</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>59.62</v>
+        <v>60.08</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>36.55</v>
+        <v>59.28</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>55.32</v>
+        <v>52.67</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>59.73</v>
+        <v>51.78</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>59.91</v>
+        <v>59.61</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>57.56</v>
+        <v>51.62</v>
       </c>
       <c r="Q49" s="3" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="R49" s="3" t="n">
         <v>51.77</v>
       </c>
-      <c r="R49" s="3" t="n">
-        <v>56</v>
-      </c>
       <c r="S49" s="3" t="n">
-        <v>39.39</v>
+        <v>47.22</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>49.97</v>
+        <v>49.47</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>47.29</v>
+        <v>39.31</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>38.38</v>
+        <v>38.41</v>
       </c>
       <c r="W49" s="3" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="X49" s="3" t="n">
         <v>36.54</v>
       </c>
-      <c r="X49" s="3" t="n">
-        <v>36.65</v>
-      </c>
       <c r="Y49" s="3" t="n">
-        <v>32.65</v>
+        <v>33.72</v>
       </c>
       <c r="Z49" s="3" t="n">
         <v>36.6</v>
@@ -4622,37 +4622,37 @@
         <v>-3.11</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-2.92</v>
+        <v>-2.46</v>
       </c>
       <c r="L51" s="3" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="P51" s="3" t="n">
         <v>-2.01</v>
       </c>
-      <c r="M51" s="3" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>-2.19</v>
-      </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.87</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.07</v>
+        <v>-1.92</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-1.95</v>
+        <v>-1.98</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-1.84</v>
+        <v>-1.57</v>
       </c>
       <c r="V51" s="3" t="n">
         <v>-1.5</v>
@@ -4661,13 +4661,13 @@
         <v>-1.64</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.24</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.21</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="52">
@@ -4874,52 +4874,52 @@
         <v>76.95999999999999</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>59.62</v>
+        <v>59.34</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>36.55</v>
+        <v>59.23</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>58.06</v>
+        <v>55.33</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>61.62</v>
+        <v>53.52</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>62.17</v>
+        <v>61.99</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>59.34</v>
+        <v>53.26</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>53.1</v>
+        <v>51.85</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>57.78</v>
+        <v>53.47</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>40.33</v>
+        <v>48.39</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>51.11</v>
+        <v>50.89</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>46.97</v>
+        <v>39.23</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>38.34</v>
+        <v>38.45</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>37.73</v>
+        <v>37.84</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>37.52</v>
+        <v>37.49</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>33.79</v>
+        <v>34.83</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>37.43</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="55">
@@ -5042,43 +5042,43 @@
         <v>-3.92</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-2.92</v>
+        <v>-3.2</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-2.01</v>
+        <v>-3.26</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.48</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.19</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.21</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-2.16</v>
+        <v>-1.65</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.34</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>-0.3</v>
@@ -5294,52 +5294,52 @@
         <v>83.73</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>64.68000000000001</v>
+        <v>64.75</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>39.55</v>
+        <v>64.48</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>60.02</v>
+        <v>57.2</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>63.83</v>
+        <v>55.33</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>64.16</v>
+        <v>63.84</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>61.6</v>
+        <v>55.29</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>55.35</v>
+        <v>53.99</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>59.93</v>
+        <v>55.4</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>42.13</v>
+        <v>50.49</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>54.03</v>
+        <v>53.48</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>51.13</v>
+        <v>42.49</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>41.45</v>
+        <v>41.49</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>39.53</v>
+        <v>39.52</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>39.11</v>
+        <v>39.04</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>34.98</v>
+        <v>36.09</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>39.62</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="60">
@@ -5462,37 +5462,37 @@
         <v>2.85</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.99</v>
+        <v>2</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="Q61" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R61" s="3" t="n">
         <v>1.72</v>
       </c>
-      <c r="R61" s="3" t="n">
-        <v>1.86</v>
-      </c>
       <c r="S61" s="3" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1.58</v>
@@ -5501,13 +5501,13 @@
         <v>1.34</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="62">
@@ -5714,52 +5714,52 @@
         <v>85.14</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>65.77</v>
+        <v>65.84</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>40.21</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>60.95</v>
+        <v>58.09</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>64.83</v>
+        <v>56.25</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>65.16</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>62.63</v>
+        <v>56.22</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>56.22</v>
+        <v>54.84</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>60.87</v>
+        <v>56.27</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>42.84</v>
+        <v>51.34</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>54.95</v>
+        <v>54.44</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>52.05</v>
+        <v>43.26</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>42.19</v>
+        <v>42.24</v>
       </c>
       <c r="W64" s="3" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="Y64" s="3" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="Z64" s="3" t="n">
         <v>40.24</v>
-      </c>
-      <c r="X64" s="3" t="n">
-        <v>39.81</v>
-      </c>
-      <c r="Y64" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="Z64" s="3" t="n">
-        <v>40.2</v>
       </c>
     </row>
     <row r="65">
@@ -5882,37 +5882,37 @@
         <v>4.26</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.65</v>
+        <v>3.08</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="N66" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P66" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="O66" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Q66" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R66" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="R66" s="3" t="n">
-        <v>2.8</v>
-      </c>
       <c r="S66" s="3" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.91</v>
+        <v>2.38</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>2.32</v>
@@ -5921,10 +5921,10 @@
         <v>2.05</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>2.25</v>
@@ -6134,52 +6134,52 @@
         <v>86.04000000000001</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66.47</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>40.51</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>61.47</v>
+        <v>58.51</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>65.38</v>
+        <v>56.73</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>63.3</v>
+        <v>56.81</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>56.87</v>
+        <v>55.48</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>61.58</v>
+        <v>56.93</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>43.29</v>
+        <v>51.89</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>55.47</v>
+        <v>54.96</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>52.49</v>
+        <v>43.67</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>42.55</v>
+        <v>42.6</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>40.62</v>
+        <v>40.61</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>40.19</v>
+        <v>40.11</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>35.94</v>
+        <v>37.09</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>40.68</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="70">
@@ -6302,37 +6302,37 @@
         <v>5.16</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.94</v>
+        <v>3.78</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>3.14</v>
+        <v>2.72</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="Q71" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R71" s="3" t="n">
         <v>3.24</v>
       </c>
-      <c r="R71" s="3" t="n">
-        <v>3.51</v>
-      </c>
       <c r="S71" s="3" t="n">
-        <v>2.64</v>
+        <v>3.17</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>2.68</v>
@@ -6341,10 +6341,10 @@
         <v>2.44</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>2.73</v>
@@ -6554,52 +6554,52 @@
         <v>83.20999999999999</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>64.28</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>39.35</v>
+        <v>64.09</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>59.71</v>
+        <v>56.9</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>63.51</v>
+        <v>55.11</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>63.83</v>
+        <v>63.58</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>61.28</v>
+        <v>55.01</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>55.18</v>
+        <v>53.82</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>59.8</v>
+        <v>55.23</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>41.91</v>
+        <v>50.23</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>50.81</v>
+        <v>42.27</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>41.19</v>
+        <v>41.23</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>39.33</v>
+        <v>39.32</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>39.03</v>
+        <v>38.83</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>34.76</v>
+        <v>35.94</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>39.45</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="75">
@@ -6722,37 +6722,37 @@
         <v>2.33</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.79</v>
+        <v>1.6</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>1.32</v>
@@ -6761,10 +6761,10 @@
         <v>1.14</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>1.5</v>
@@ -6977,49 +6977,49 @@
         <v>62.55</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>38.56</v>
+        <v>62.48</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>58.64</v>
+        <v>55.88</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>62.24</v>
+        <v>54</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>62.42</v>
+        <v>62.18</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>59.75</v>
+        <v>53.63</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>53.63</v>
+        <v>52.32</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>58.07</v>
+        <v>53.68</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>40.65</v>
+        <v>48.73</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>51.92</v>
+        <v>51.44</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>49.13</v>
+        <v>40.88</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>39.87</v>
+        <v>39.91</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>38.19</v>
+        <v>38.18</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>37.82</v>
+        <v>37.79</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>33.89</v>
+        <v>34.94</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>37.95</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="80">
@@ -7394,52 +7394,52 @@
         <v>72.28</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>55.99</v>
+        <v>55.45</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>33.83</v>
+        <v>54.81</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>55.58</v>
+        <v>52.97</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>59.22</v>
+        <v>51.43</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>60.14</v>
+        <v>59.96</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>57.4</v>
+        <v>51.57</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>51.27</v>
+        <v>50.06</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>56</v>
+        <v>51.82</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>39.09</v>
+        <v>47.03</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>49.64</v>
+        <v>49.51</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>43.83</v>
+        <v>36.66</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>35.92</v>
+        <v>36.25</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>36.75</v>
+        <v>36.99</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>36.54</v>
+        <v>36.51</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>32.59</v>
+        <v>33.59</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>35.94</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="85">
@@ -7562,49 +7562,49 @@
         <v>-8.6</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-6.55</v>
+        <v>-7.1</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-4.74</v>
+        <v>-7.67</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-3.06</v>
+        <v>-2.91</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-3.02</v>
+        <v>-2.57</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.22</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.06</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.25</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-2.07</v>
+        <v>-1.87</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.69</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.28</v>
+        <v>-1.93</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-5.3</v>
+        <v>-4.22</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-3.95</v>
+        <v>-3.66</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.18</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-1.28</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.34</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>-2.01</v>
@@ -7814,52 +7814,52 @@
         <v>77.03</v>
       </c>
       <c r="K89" s="3" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="L89" s="3" t="n">
         <v>59.34</v>
       </c>
-      <c r="L89" s="3" t="n">
-        <v>36.76</v>
-      </c>
       <c r="M89" s="3" t="n">
-        <v>55.37</v>
+        <v>52.67</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>58.77</v>
+        <v>50.85</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>59.06</v>
+        <v>58.66</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>56.42</v>
+        <v>50.6</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>50.64</v>
+        <v>49.49</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>54.89</v>
+        <v>50.69</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>38.61</v>
+        <v>46.36</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>49.03</v>
+        <v>48.53</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>46.53</v>
+        <v>38.71</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>38.12</v>
+        <v>38.19</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>36.23</v>
+        <v>36.25</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>35.89</v>
+        <v>35.85</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>32.31</v>
+        <v>33.27</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>36.32</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="90">
@@ -7982,52 +7982,52 @@
         <v>-3.85</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-3.2</v>
+        <v>-3.04</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.8</v>
+        <v>-3.14</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.21</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-3.47</v>
+        <v>-3.15</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.52</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-3.33</v>
+        <v>-3.04</v>
       </c>
       <c r="Q91" s="3" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="R91" s="3" t="n">
         <v>-2.99</v>
       </c>
-      <c r="R91" s="3" t="n">
-        <v>-3.18</v>
-      </c>
       <c r="S91" s="3" t="n">
-        <v>-2.05</v>
+        <v>-2.36</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.89</v>
+        <v>-2.91</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.17</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.92</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>-1.94</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.66</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-07T03:13:33</t>
+          <t>CreatedAt: 2026-03-07T04:11:33</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -665,61 +665,61 @@
         <v>45.14</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>38.61</v>
+        <v>35.45</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>80.36</v>
+        <v>34.09</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>33.73</v>
+        <v>33.77</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>17.65</v>
+        <v>17.72</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="M4" s="3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>25.68</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>25.68</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>33.03</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>33.05</v>
-      </c>
       <c r="U4" s="3" t="n">
-        <v>34.73</v>
+        <v>34.44</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>40.5</v>
+        <v>40.62</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>40.7</v>
+        <v>40.46</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>40.65</v>
+        <v>40.62</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.38</v>
+        <v>33.77</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>40.9</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="5">
@@ -833,61 +833,61 @@
         <v>0.72</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.17</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>-0.34</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.82</v>
+        <v>-1.05</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.85</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.95</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.51</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.67</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-0.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.97</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.05</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.93</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.41</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="7">
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0</v>
@@ -1085,61 +1085,61 @@
         <v>47.45</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>40.15</v>
+        <v>36.75</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>81.56</v>
+        <v>35.67</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>35.34</v>
+        <v>35.38</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>18.42</v>
+        <v>18.52</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>18.4</v>
+        <v>18.48</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>26.83</v>
       </c>
       <c r="N9" s="3" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="O9" s="3" t="n">
         <v>27.13</v>
       </c>
-      <c r="O9" s="3" t="n">
-        <v>34.76</v>
-      </c>
       <c r="P9" s="3" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>34.58</v>
+        <v>34.34</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>27.07</v>
+        <v>27.05</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>18.38</v>
+        <v>18.29</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>33.81</v>
+        <v>26.27</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>35.45</v>
+        <v>35.2</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>41.85</v>
+        <v>41.97</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>42.57</v>
+        <v>42.36</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>42.44</v>
+        <v>42.4</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>35.83</v>
+        <v>35.16</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>42.93</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="10">
@@ -1253,31 +1253,31 @@
         <v>3.04</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>1.27</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.35</v>
       </c>
       <c r="N11" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O11" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="O11" s="3" t="n">
-        <v>0.83</v>
-      </c>
       <c r="P11" s="3" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0.62</v>
@@ -1289,13 +1289,13 @@
         <v>0.24</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>0.85</v>
@@ -1304,10 +1304,10 @@
         <v>0.85</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>0</v>
@@ -1505,61 +1505,61 @@
         <v>108.88</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>79.23</v>
+        <v>36.79</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>47.75</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>35.34</v>
+        <v>118.16</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.42</v>
+        <v>18.52</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>26.85</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>116.97</v>
+        <v>34.52</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>34.76</v>
+        <v>27.16</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>34.84</v>
+        <v>34.54</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>34.61</v>
+        <v>34.34</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>27.07</v>
+        <v>116.19</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>18.38</v>
+        <v>18.29</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>33.81</v>
+        <v>26.27</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>35.49</v>
+        <v>35.2</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>41.85</v>
+        <v>41.97</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>42.57</v>
+        <v>42.36</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>42.44</v>
+        <v>118.15</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>35.83</v>
+        <v>35.19</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>42.97</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="15">
@@ -1589,13 +1589,13 @@
         <v>61.38</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>39.07</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>12.08</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>82.75</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>89.84</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>0</v>
@@ -1673,34 +1673,34 @@
         <v>3.09</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0.38</v>
       </c>
       <c r="N16" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>0.62</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0.66</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>0.62</v>
@@ -1709,25 +1709,25 @@
         <v>0.24</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>-0.14</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0.85</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="17">
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
@@ -1925,61 +1925,61 @@
         <v>45.32</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>38.73</v>
+        <v>35.59</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>34.34</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>33.87</v>
+        <v>33.94</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>17.72</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>17.63</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>25.71</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>25.73</v>
+        <v>32.74</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.9</v>
+        <v>25.68</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>33.14</v>
+        <v>32.86</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>33.06</v>
+        <v>32.81</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>25.81</v>
+        <v>25.78</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>17.65</v>
+        <v>17.54</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>33.08</v>
+        <v>25.7</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>34.73</v>
+        <v>34.44</v>
       </c>
       <c r="V19" s="3" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>40.54</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>40.78</v>
-      </c>
       <c r="X19" s="3" t="n">
-        <v>40.73</v>
+        <v>40.7</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.41</v>
+        <v>33.77</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>40.9</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="20">
@@ -2093,43 +2093,43 @@
         <v>0.91</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.03</v>
+        <v>0.42</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-0.77</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.82</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.64</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>-0.9</v>
@@ -2138,16 +2138,16 @@
         <v>-0.97</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.97</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.85</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>-0.41</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0</v>
@@ -2345,61 +2345,61 @@
         <v>45.32</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>38.73</v>
+        <v>35.59</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>34.34</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>33.87</v>
+        <v>33.94</v>
       </c>
       <c r="K24" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>17.72</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>17.63</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>25.71</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>25.73</v>
+        <v>32.74</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>32.9</v>
+        <v>25.68</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>33.14</v>
+        <v>32.86</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>33.06</v>
+        <v>32.81</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>25.81</v>
+        <v>25.78</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>17.65</v>
+        <v>17.54</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>33.08</v>
+        <v>25.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>34.73</v>
+        <v>34.44</v>
       </c>
       <c r="V24" s="3" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>40.54</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>40.78</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>40.73</v>
+        <v>40.7</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.41</v>
+        <v>33.77</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>40.9</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="25">
@@ -2513,43 +2513,43 @@
         <v>0.91</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.03</v>
+        <v>0.42</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>-0.77</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.82</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.64</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>-0.9</v>
@@ -2558,16 +2558,16 @@
         <v>-0.97</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.97</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.85</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>-0.41</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="27">
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -2765,61 +2765,61 @@
         <v>45.37</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>38.73</v>
+        <v>35.66</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>34.59</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>34</v>
+        <v>34.07</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>17.79</v>
+        <v>17.89</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>17.67</v>
+        <v>17.75</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>25.73</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>25.73</v>
+        <v>32.74</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>32.87</v>
+        <v>25.68</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>33.14</v>
+        <v>32.86</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.06</v>
+        <v>32.81</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>25.83</v>
+        <v>25.81</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>17.65</v>
+        <v>17.56</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>33.18</v>
+        <v>25.78</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>34.76</v>
+        <v>34.48</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>40.54</v>
+        <v>40.66</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>40.82</v>
+        <v>40.58</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>40.81</v>
+        <v>40.78</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.38</v>
+        <v>33.73</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>40.78</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="30">
@@ -2933,34 +2933,34 @@
         <v>0.95</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.03</v>
+        <v>0.67</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0.75</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.82</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-0.62</v>
@@ -2969,25 +2969,25 @@
         <v>-0.49</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.57</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.93</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="32">
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>0</v>
@@ -3185,61 +3185,61 @@
         <v>109.34</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>79.44</v>
+        <v>36.87</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>81.52</v>
+        <v>47.22</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>35.53</v>
+        <v>118.31</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>18.52</v>
+        <v>18.56</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>18.48</v>
+        <v>18.57</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>26.99</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>117.34</v>
+        <v>34.98</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>35.3</v>
+        <v>27.58</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>35.2</v>
+        <v>34.93</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>34.9</v>
+        <v>34.66</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>27.33</v>
+        <v>116.42</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>18.38</v>
+        <v>18.29</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>33.54</v>
+        <v>26.08</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>35.28</v>
+        <v>35.02</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>41.93</v>
+        <v>42.1</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>42.83</v>
+        <v>42.62</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>42.7</v>
+        <v>118.36</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>36.05</v>
+        <v>35.38</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>43.65</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="35">
@@ -3269,13 +3269,13 @@
         <v>61.38</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>39.07</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>12.08</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>82.75</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>89.84</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0</v>
@@ -3353,10 +3353,10 @@
         <v>3.55</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1.46</v>
@@ -3365,37 +3365,37 @@
         <v>0.52</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.51</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>1.11</v>
@@ -3404,10 +3404,10 @@
         <v>1.11</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="37">
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>0</v>
@@ -3605,61 +3605,61 @@
         <v>45.14</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>38.61</v>
+        <v>35.45</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>80.36</v>
+        <v>34.09</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>33.73</v>
+        <v>33.77</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>17.65</v>
+        <v>17.72</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="M39" s="3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="T39" s="3" t="n">
         <v>25.68</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>25.68</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>33.03</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>33.05</v>
-      </c>
       <c r="U39" s="3" t="n">
-        <v>34.73</v>
+        <v>34.44</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>40.5</v>
+        <v>40.62</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>40.7</v>
+        <v>40.46</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>40.65</v>
+        <v>40.62</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.38</v>
+        <v>33.77</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>40.9</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="40">
@@ -3773,61 +3773,61 @@
         <v>0.72</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.17</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>-0.34</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.82</v>
+        <v>-1.05</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.85</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.95</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.51</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.67</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>-0.9</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.97</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.05</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.93</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.41</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="42">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>0</v>
@@ -4025,61 +4025,61 @@
         <v>45.09</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>38.65</v>
+        <v>35.41</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>80.77</v>
+        <v>34.3</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>34.35</v>
+        <v>34.38</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>18.09</v>
+        <v>18.13</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>18.07</v>
+        <v>18.13</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>26.35</v>
+        <v>26.32</v>
       </c>
       <c r="N44" s="3" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="O44" s="3" t="n">
         <v>26.29</v>
       </c>
-      <c r="O44" s="3" t="n">
-        <v>33.62</v>
-      </c>
       <c r="P44" s="3" t="n">
-        <v>33.8</v>
+        <v>33.55</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>33.72</v>
+        <v>33.49</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>26.37</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>18.18</v>
+        <v>18.09</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>34.08</v>
+        <v>26.53</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>35.84</v>
+        <v>35.55</v>
       </c>
       <c r="V44" s="3" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="X44" s="3" t="n">
         <v>41.72</v>
       </c>
-      <c r="W44" s="3" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>41.76</v>
-      </c>
       <c r="Y44" s="3" t="n">
-        <v>35.11</v>
+        <v>34.45</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>42.02</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="45">
@@ -4193,13 +4193,13 @@
         <v>0.68</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0.09</v>
@@ -4208,37 +4208,37 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="N46" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="O46" s="3" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-0.3</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>-0.3</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.17</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -4445,61 +4445,61 @@
         <v>44.37</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>38.07</v>
+        <v>34.67</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>78.84999999999999</v>
+        <v>32.36</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>32.2</v>
+        <v>32.24</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>16.98</v>
+        <v>17.01</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>17.11</v>
+        <v>17.18</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>25.12</v>
+        <v>25.07</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>25.53</v>
+        <v>32.46</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>32.93</v>
+        <v>25.76</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>32.7</v>
+        <v>32.45</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>32.52</v>
+        <v>32.27</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>25.26</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>17.35</v>
+        <v>17.26</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>30.36</v>
+        <v>23.63</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>32.39</v>
+        <v>32.13</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>37.6</v>
+        <v>37.68</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>37.72</v>
+        <v>37.54</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>39.38</v>
+        <v>39.39</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>35.04</v>
+        <v>34.41</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>41.72</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="50">
@@ -4613,10 +4613,10 @@
         <v>-0.04</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.56</v>
       </c>
       <c r="J51" s="3" t="n">
         <v>-1.87</v>
@@ -4625,46 +4625,46 @@
         <v>-1.02</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.4</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.27</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.75</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.45</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.52</v>
+        <v>-2.72</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.24</v>
+        <v>-3.21</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.91</v>
+        <v>-3.92</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-4</v>
+        <v>-3.98</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.17</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>0.13</v>
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>0</v>
@@ -4865,61 +4865,61 @@
         <v>43.97</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>37.4</v>
+        <v>33.93</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>80.05</v>
+        <v>33.61</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>33.37</v>
+        <v>33.4</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>17.56</v>
+        <v>17.6</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>17.58</v>
+        <v>17.63</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>26.21</v>
+        <v>26.14</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>26.14</v>
+        <v>33.23</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>33.75</v>
+        <v>26.35</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>33.73</v>
+        <v>33.45</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.72</v>
+        <v>33.46</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>25.68</v>
+        <v>25.65</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>32.05</v>
+        <v>24.9</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>33.61</v>
+        <v>33.34</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>39.28</v>
+        <v>39.35</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>41.02</v>
+        <v>40.82</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>41.18</v>
+        <v>41.1</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>34.48</v>
+        <v>33.83</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>41.06</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="55">
@@ -5033,10 +5033,10 @@
         <v>-0.44</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.95</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>-0.7</v>
@@ -5048,46 +5048,46 @@
         <v>-0.49</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.5</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>-0.77</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.44</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-2.02</v>
+        <v>-2</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>-2.24</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.45</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>-0.34</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="57">
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>0</v>
@@ -5285,61 +5285,61 @@
         <v>46.12</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>39.57</v>
+        <v>36.22</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>81.67</v>
+        <v>35.18</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>35.27</v>
+        <v>35.31</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>18.63</v>
+        <v>18.67</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>18.65</v>
+        <v>18.71</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>27.3</v>
+        <v>27.27</v>
       </c>
       <c r="N59" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="O59" s="3" t="n">
         <v>27.27</v>
       </c>
-      <c r="O59" s="3" t="n">
-        <v>34.86</v>
-      </c>
       <c r="P59" s="3" t="n">
-        <v>35.05</v>
+        <v>34.79</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>34.93</v>
+        <v>34.7</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>27.27</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>18.78</v>
+        <v>18.67</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>35.11</v>
+        <v>27.33</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>36.88</v>
+        <v>36.62</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>42.98</v>
+        <v>43.06</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>43.14</v>
+        <v>42.93</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>42.96</v>
+        <v>42.97</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>36.09</v>
+        <v>35.45</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>43.24</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="60">
@@ -5453,10 +5453,10 @@
         <v>1.71</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>1.2</v>
@@ -5468,31 +5468,31 @@
         <v>0.58</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="N61" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O61" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="P61" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="P61" s="3" t="n">
-        <v>0.95</v>
-      </c>
       <c r="Q61" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T61" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="R61" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>1.23</v>
-      </c>
       <c r="U61" s="3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1.46</v>
@@ -5501,13 +5501,13 @@
         <v>1.42</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="62">
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J63" s="3" t="n">
         <v>0</v>
@@ -5705,61 +5705,61 @@
         <v>46.7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>40.07</v>
+        <v>36.68</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>82.16</v>
+        <v>35.67</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>35.79</v>
+        <v>35.82</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>18.93</v>
+        <v>18.96</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>18.96</v>
+        <v>19.02</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>27.75</v>
+        <v>27.72</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>27.75</v>
+        <v>35.31</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>35.45</v>
+        <v>27.72</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>35.64</v>
+        <v>35.37</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>35.52</v>
+        <v>35.28</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>27.73</v>
+        <v>27.7</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>19.08</v>
+        <v>18.98</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>35.7</v>
+        <v>27.76</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>37.54</v>
+        <v>37.24</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>43.7</v>
+        <v>43.78</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>43.82</v>
+        <v>43.65</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>43.69</v>
+        <v>43.65</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.62</v>
+        <v>35.97</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>43.88</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="65">
@@ -5873,10 +5873,10 @@
         <v>2.29</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="J66" s="3" t="n">
         <v>1.72</v>
@@ -5888,46 +5888,46 @@
         <v>0.89</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="O66" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P66" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="P66" s="3" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Q66" s="3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S66" s="3" t="n">
         <v>0.93</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="67">
@@ -6044,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0</v>
@@ -6125,61 +6125,61 @@
         <v>115.1</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>40.63</v>
+        <v>37.19</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>82.62</v>
+        <v>36.13</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>36.25</v>
+        <v>36.28</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>19.15</v>
+        <v>19.19</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>19.18</v>
+        <v>19.24</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>28.08</v>
+        <v>28.05</v>
       </c>
       <c r="N69" s="3" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="O69" s="3" t="n">
         <v>28.05</v>
       </c>
-      <c r="O69" s="3" t="n">
-        <v>35.9</v>
-      </c>
       <c r="P69" s="3" t="n">
-        <v>36.05</v>
+        <v>35.82</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>35.97</v>
+        <v>35.69</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>28.05</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>19.3</v>
+        <v>19.21</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>36.08</v>
+        <v>28.09</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>37.9</v>
+        <v>37.63</v>
       </c>
       <c r="V69" s="3" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="W69" s="3" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="X69" s="3" t="n">
         <v>44.16</v>
       </c>
-      <c r="W69" s="3" t="n">
-        <v>44.33</v>
-      </c>
-      <c r="X69" s="3" t="n">
-        <v>44.15</v>
-      </c>
       <c r="Y69" s="3" t="n">
-        <v>37.09</v>
+        <v>36.39</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>44.44</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="70">
@@ -6293,61 +6293,61 @@
         <v>2.94</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>1.15</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="N71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="O71" s="3" t="n">
+      <c r="P71" s="3" t="n">
         <v>1.97</v>
       </c>
-      <c r="P71" s="3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Q71" s="3" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="72">
@@ -6464,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J73" s="3" t="n">
         <v>0</v>
@@ -6545,61 +6545,61 @@
         <v>45.79</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>39.21</v>
+        <v>35.85</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>81.31</v>
+        <v>34.81</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>34.94</v>
+        <v>34.98</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>18.48</v>
+        <v>18.52</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>18.52</v>
+        <v>18.57</v>
       </c>
       <c r="M74" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="O74" s="3" t="n">
         <v>27.13</v>
       </c>
-      <c r="N74" s="3" t="n">
-        <v>27.13</v>
-      </c>
-      <c r="O74" s="3" t="n">
-        <v>34.69</v>
-      </c>
       <c r="P74" s="3" t="n">
-        <v>34.84</v>
+        <v>34.61</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>34.72</v>
+        <v>34.48</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>18.65</v>
+        <v>18.55</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>34.82</v>
+        <v>27.08</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>36.58</v>
+        <v>36.32</v>
       </c>
       <c r="V74" s="3" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="X74" s="3" t="n">
         <v>42.62</v>
       </c>
-      <c r="W74" s="3" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="X74" s="3" t="n">
-        <v>42.66</v>
-      </c>
       <c r="Y74" s="3" t="n">
-        <v>35.94</v>
+        <v>35.27</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>43.02</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="75">
@@ -6713,10 +6713,10 @@
         <v>1.37</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.87</v>
@@ -6725,49 +6725,49 @@
         <v>0.48</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="N76" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O76" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="O76" s="3" t="n">
+      <c r="P76" s="3" t="n">
         <v>0.76</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>0.73</v>
       </c>
       <c r="Q76" s="3" t="n">
         <v>0.76</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="S76" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>1.11</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>1.07</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="77">
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>0</v>
@@ -6965,61 +6965,61 @@
         <v>44.41</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>38.15</v>
+        <v>34.88</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>80.39</v>
+        <v>33.92</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>34.07</v>
+        <v>34.1</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>18</v>
+        <v>18.04</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>18.07</v>
+        <v>18.13</v>
       </c>
       <c r="M79" s="3" t="n">
         <v>26.48</v>
       </c>
       <c r="N79" s="3" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="O79" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="O79" s="3" t="n">
-        <v>33.92</v>
-      </c>
       <c r="P79" s="3" t="n">
-        <v>34.1</v>
+        <v>33.85</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>33.96</v>
+        <v>33.73</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>26.45</v>
+        <v>26.42</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>18.14</v>
+        <v>18.05</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>33.88</v>
+        <v>26.35</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>35.63</v>
+        <v>35.34</v>
       </c>
       <c r="V79" s="3" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="W79" s="3" t="n">
         <v>41.51</v>
       </c>
-      <c r="W79" s="3" t="n">
+      <c r="X79" s="3" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="Z79" s="3" t="n">
         <v>41.72</v>
-      </c>
-      <c r="X79" s="3" t="n">
-        <v>41.59</v>
-      </c>
-      <c r="Y79" s="3" t="n">
-        <v>34.83</v>
-      </c>
-      <c r="Z79" s="3" t="n">
-        <v>41.6</v>
       </c>
     </row>
     <row r="80">
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0</v>
@@ -7385,61 +7385,61 @@
         <v>42.75</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>36.09</v>
+        <v>32.51</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>32.62</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>32.6</v>
+        <v>32.64</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>17.06</v>
+        <v>17.1</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>16.9</v>
+        <v>16.94</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>25.43</v>
+        <v>25.36</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>25.39</v>
+        <v>32.27</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>32.52</v>
+        <v>25.36</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>32.36</v>
+        <v>32.05</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>32.59</v>
+        <v>32.24</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>24.33</v>
+        <v>24.29</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>16.74</v>
+        <v>16.65</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>29.59</v>
+        <v>22.97</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>30.85</v>
+        <v>30.57</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>36.23</v>
+        <v>36.26</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>39.36</v>
+        <v>39.13</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>39.24</v>
+        <v>39.17</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>32.95</v>
+        <v>32.33</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>39.13</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="85">
@@ -7553,10 +7553,10 @@
         <v>-1.67</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.37</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-1.29</v>
+        <v>-1.3</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>-1.47</v>
@@ -7565,49 +7565,49 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.19</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.12</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.45</v>
       </c>
       <c r="O86" s="3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="S86" s="3" t="n">
         <v>-1.4</v>
       </c>
-      <c r="P86" s="3" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>-1.41</v>
-      </c>
       <c r="T86" s="3" t="n">
-        <v>-4.29</v>
+        <v>-3.38</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-4.78</v>
+        <v>-4.77</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-5.29</v>
+        <v>-5.33</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.39</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.39</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-1.88</v>
+        <v>-1.84</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-2.47</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="87">
@@ -7724,7 +7724,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>0</v>
@@ -7805,61 +7805,61 @@
         <v>45.37</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>38.73</v>
+        <v>35.66</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>34.59</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>34</v>
+        <v>34.07</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>17.79</v>
+        <v>17.89</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>17.67</v>
+        <v>17.75</v>
       </c>
       <c r="M89" s="3" t="n">
         <v>25.73</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>25.73</v>
+        <v>32.74</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>32.87</v>
+        <v>25.68</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>33.14</v>
+        <v>32.86</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>33.06</v>
+        <v>32.81</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>25.83</v>
+        <v>25.81</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>17.65</v>
+        <v>17.56</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>33.18</v>
+        <v>25.78</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>34.76</v>
+        <v>34.48</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>40.54</v>
+        <v>40.66</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>40.82</v>
+        <v>40.58</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>40.81</v>
+        <v>40.78</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>34.38</v>
+        <v>33.73</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>40.78</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="90">
@@ -7973,34 +7973,34 @@
         <v>0.95</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.03</v>
+        <v>0.67</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="M91" s="3" t="n">
         <v>-0.75</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.82</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>-0.62</v>
@@ -8009,25 +8009,25 @@
         <v>-0.49</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.57</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.93</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="92">
@@ -8144,7 +8144,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>46.13</v>
+        <v>-0.79</v>
       </c>
       <c r="J93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-07T15:08:24</t>
+          <t>CreatedAt: 2026-03-07T16:08:03</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -701,25 +701,25 @@
         <v>40</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>45.61</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>34.38</v>
+        <v>59.02</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>34.54</v>
+        <v>34.44</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>34.3</v>
+        <v>25.78</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>25.83</v>
+        <v>17.29</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.5</v>
+        <v>26.1</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>40.06</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="5">
@@ -869,25 +869,25 @@
         <v>-0.76</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.68</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-0.83</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.64</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>0</v>
@@ -1121,25 +1121,25 @@
         <v>55.52</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>66.76000000000001</v>
+        <v>47.48</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>35.52</v>
+        <v>60.34</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>36.1</v>
+        <v>36.06</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>35.8</v>
+        <v>26.96</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>26.99</v>
+        <v>18.04</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>35.99</v>
+        <v>27.19</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.88</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="10">
@@ -1289,22 +1289,22 @@
         <v>1.17</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.57</v>
+        <v>0.34</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.01</v>
+        <v>0.68</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1.3</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>0</v>
@@ -1541,25 +1541,25 @@
         <v>55.56</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>66.81</v>
+        <v>47.48</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>35.55</v>
+        <v>60.34</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>36.13</v>
+        <v>36.06</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>35.8</v>
+        <v>26.96</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>26.99</v>
+        <v>116.23</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>36.03</v>
+        <v>27.19</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>41.92</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="15">
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>98.17</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>0</v>
@@ -1709,25 +1709,25 @@
         <v>1.22</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.57</v>
+        <v>0.36</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.04</v>
+        <v>0.68</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="17">
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>0</v>
@@ -1961,25 +1961,25 @@
         <v>40.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>65.27</v>
+        <v>45.84</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>34.41</v>
+        <v>59.15</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>34.58</v>
+        <v>34.51</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>34.36</v>
+        <v>25.83</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>25.88</v>
+        <v>17.32</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.54</v>
+        <v>26.12</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>40.1</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="20">
@@ -2129,25 +2129,25 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.46</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.82</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.76</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.59</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.38</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.39</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="22">
@@ -2297,10 +2297,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>0</v>
@@ -2381,25 +2381,25 @@
         <v>40.2</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.27</v>
+        <v>45.84</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>34.41</v>
+        <v>59.15</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>34.58</v>
+        <v>34.51</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>34.36</v>
+        <v>25.83</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>25.88</v>
+        <v>17.32</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.54</v>
+        <v>26.12</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>40.1</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="25">
@@ -2549,25 +2549,25 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.46</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.82</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.76</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.59</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.38</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.39</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="27">
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>0</v>
@@ -2801,25 +2801,25 @@
         <v>40.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>65.53</v>
+        <v>46.07</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>34.44</v>
+        <v>59.33</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>34.58</v>
+        <v>34.51</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>34.43</v>
+        <v>25.88</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>25.93</v>
+        <v>17.35</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.5</v>
+        <v>26.1</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>40.06</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="30">
@@ -2969,25 +2969,25 @@
         <v>-0.36</v>
       </c>
       <c r="T31" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="X31" s="3" t="n">
         <v>-0.35</v>
       </c>
-      <c r="U31" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>-0.49</v>
-      </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3137,10 +3137,10 @@
         <v>0</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>0</v>
@@ -3221,25 +3221,25 @@
         <v>42.02</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>66.63</v>
+        <v>47.24</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>35.52</v>
+        <v>60.34</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>36.43</v>
+        <v>36.36</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>36.02</v>
+        <v>27.16</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>27.16</v>
+        <v>116.36</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>36.37</v>
+        <v>27.39</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>42.36</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="35">
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>0</v>
+        <v>98.17</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0</v>
@@ -3389,22 +3389,22 @@
         <v>1.26</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.78</v>
@@ -3557,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
         <v>40</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>45.61</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>34.38</v>
+        <v>59.02</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>34.54</v>
+        <v>34.44</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>34.3</v>
+        <v>25.78</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>25.83</v>
+        <v>17.29</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.5</v>
+        <v>26.1</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>40.06</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="40">
@@ -3809,25 +3809,25 @@
         <v>-0.76</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.68</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-0.83</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.64</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3977,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>0</v>
@@ -4061,25 +4061,25 @@
         <v>40.84</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>66.14</v>
+        <v>46.62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>35.45</v>
+        <v>60.25</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>35.52</v>
+        <v>35.41</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>35.19</v>
+        <v>26.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>26.56</v>
+        <v>17.79</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>35.16</v>
+        <v>26.65</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>40.91</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="45">
@@ -4229,25 +4229,25 @@
         <v>0.08</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="X46" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>0.18</v>
-      </c>
       <c r="Z46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="47">
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>0</v>
@@ -4481,25 +4481,25 @@
         <v>38.97</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>61.9</v>
+        <v>42.28</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>32.03</v>
+        <v>55.76</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>32.01</v>
+        <v>31.89</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>31.64</v>
+        <v>23.85</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>25.38</v>
+        <v>17</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>35.06</v>
+        <v>26.57</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>40.58</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="50">
@@ -4649,25 +4649,25 @@
         <v>-1.79</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.97</v>
+        <v>-4.02</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.24</v>
+        <v>-4.21</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.36</v>
+        <v>-3.38</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-3.45</v>
+        <v>-2.58</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.7</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="52">
@@ -4817,10 +4817,10 @@
         <v>0</v>
       </c>
       <c r="T53" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>0</v>
@@ -4901,25 +4901,25 @@
         <v>40.8</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>64.72</v>
+        <v>45.12</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>34.11</v>
+        <v>57.93</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>34.28</v>
+        <v>34.21</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>34.1</v>
+        <v>25.7</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>25.33</v>
+        <v>17.15</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>34.92</v>
+        <v>26.78</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>40.38</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="55">
@@ -5069,25 +5069,25 @@
         <v>0.04</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.17</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.16</v>
+        <v>-2.04</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.06</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.72</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.55</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="57">
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V58" s="3" t="n">
         <v>0</v>
@@ -5321,25 +5321,25 @@
         <v>42.11</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>67.41</v>
+        <v>47.97</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>36.47</v>
+        <v>61.6</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>36.54</v>
+        <v>36.44</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>36.25</v>
+        <v>27.3</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>27.33</v>
+        <v>18.32</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>36.14</v>
+        <v>27.39</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>42.1</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="60">
@@ -5489,25 +5489,25 @@
         <v>1.35</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1.17</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.16</v>
+        <v>0.87</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.16</v>
+        <v>0.88</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="62">
@@ -5657,10 +5657,10 @@
         <v>0</v>
       </c>
       <c r="T63" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V63" s="3" t="n">
         <v>0</v>
@@ -5741,25 +5741,25 @@
         <v>42.77</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>68.17</v>
+        <v>48.78</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>37.13</v>
+        <v>62.41</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>37.16</v>
+        <v>37.09</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>36.85</v>
+        <v>27.76</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>27.76</v>
+        <v>18.59</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.67</v>
+        <v>27.79</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>42.63</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="65">
@@ -5909,25 +5909,25 @@
         <v>2.01</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.86</v>
+        <v>2.44</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="67">
@@ -6077,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V68" s="3" t="n">
         <v>0</v>
@@ -6164,22 +6164,22 @@
         <v>120</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>37.48</v>
+        <v>75</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>37.55</v>
+        <v>37.44</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>37.25</v>
+        <v>28.05</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>28.08</v>
+        <v>18.83</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>37.14</v>
+        <v>28.15</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>43.26</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="70">
@@ -6329,25 +6329,25 @@
         <v>2.51</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.21</v>
+        <v>2.96</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="72">
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>51.34</v>
+        <v>70.75</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>0</v>
+        <v>12.07</v>
       </c>
       <c r="V72" s="3" t="n">
         <v>0</v>
@@ -6497,10 +6497,10 @@
         <v>0</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V73" s="3" t="n">
         <v>0</v>
@@ -6581,25 +6581,25 @@
         <v>41.81</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>47.53</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>36.17</v>
+        <v>61.21</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>36.24</v>
+        <v>36.14</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>35.91</v>
+        <v>27.07</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>27.21</v>
+        <v>18.23</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>35.88</v>
+        <v>27.19</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>41.75</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="75">
@@ -6749,25 +6749,25 @@
         <v>1.05</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.53</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="77">
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V78" s="3" t="n">
         <v>0</v>
@@ -7001,25 +7001,25 @@
         <v>40.76</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>65.87</v>
+        <v>46.3</v>
       </c>
       <c r="U79" s="3" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="V79" s="3" t="n">
         <v>35.27</v>
       </c>
-      <c r="V79" s="3" t="n">
-        <v>35.37</v>
-      </c>
       <c r="W79" s="3" t="n">
-        <v>35.09</v>
+        <v>26.42</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>26.42</v>
+        <v>17.7</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>34.99</v>
+        <v>26.51</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>40.58</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="80">
@@ -7337,10 +7337,10 @@
         <v>0</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V83" s="3" t="n">
         <v>0</v>
@@ -7421,25 +7421,25 @@
         <v>40.12</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>62.52</v>
+        <v>43.07</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>32.9</v>
+        <v>55.41</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>33.25</v>
+        <v>33.18</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>33.22</v>
+        <v>25.07</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>24.24</v>
+        <v>16.78</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>34.71</v>
+        <v>27.22</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>39.82</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="85">
@@ -7589,25 +7589,25 @@
         <v>-0.64</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.35</v>
+        <v>-3.23</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.37</v>
+        <v>-4.55</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.09</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.35</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-2.18</v>
+        <v>-0.92</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-0.28</v>
+        <v>0.71</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-0.76</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="87">
@@ -7757,10 +7757,10 @@
         <v>0</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V88" s="3" t="n">
         <v>0</v>
@@ -7841,25 +7841,25 @@
         <v>40.4</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>65.53</v>
+        <v>46.11</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>34.44</v>
+        <v>59.33</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>34.58</v>
+        <v>34.51</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>34.43</v>
+        <v>25.88</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>25.93</v>
+        <v>17.35</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>34.5</v>
+        <v>26.1</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>40.06</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="90">
@@ -8009,25 +8009,25 @@
         <v>-0.36</v>
       </c>
       <c r="T91" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="X91" s="3" t="n">
         <v>-0.35</v>
       </c>
-      <c r="U91" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="X91" s="3" t="n">
-        <v>-0.49</v>
-      </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="V93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-11T06:11:43</t>
+          <t>CreatedAt: 2026-03-11T07:10:44</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -674,52 +674,52 @@
         <v>45.29</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>36.58</v>
+        <v>45.74</v>
       </c>
       <c r="L4" s="3" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>35.03</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>39.46</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>45.59</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>45.29</v>
-      </c>
       <c r="R4" s="3" t="n">
-        <v>46.8</v>
+        <v>35.31</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>47.9</v>
+        <v>36.9</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>46.99</v>
+        <v>39.38</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>43.13</v>
+        <v>42.87</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>43.17</v>
+        <v>41.98</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>39.3</v>
+        <v>46.75</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>34.62</v>
+        <v>34.56</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>31.7</v>
+        <v>27.62</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>31.64</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="5">
@@ -842,52 +842,52 @@
         <v>-1.27</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.74</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.83</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.81</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.91</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>-1.26</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.19</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.19</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.06</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.92</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.87</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="X6" s="3" t="n">
         <v>-0.73</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>-0.66</v>
-      </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.47</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="7">
@@ -1094,52 +1094,52 @@
         <v>47.03</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>37.34</v>
+        <v>46.59</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>35.87</v>
+        <v>50.66</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>36.34</v>
+        <v>48.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>41.1</v>
+        <v>49.77</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>41.35</v>
+        <v>36.56</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>47.58</v>
+        <v>36.66</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>47.26</v>
+        <v>36.59</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>49.19</v>
+        <v>37.07</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>49.7</v>
+        <v>38.32</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.16</v>
+        <v>40.33</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>44.52</v>
+        <v>44.26</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>45.12</v>
+        <v>43.88</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>41.54</v>
+        <v>49.42</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>36.3</v>
+        <v>36.19</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>33.37</v>
+        <v>29.02</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>33.59</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="10">
@@ -1262,52 +1262,52 @@
         <v>0.47</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.89</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.76</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>1.03</v>
+        <v>0.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.13</v>
+        <v>0.93</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -1514,52 +1514,52 @@
         <v>47.03</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>37.34</v>
+        <v>46.59</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>35.87</v>
+        <v>50.71</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36.34</v>
+        <v>48.25</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>41.14</v>
+        <v>49.77</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>115.31</v>
+        <v>36.56</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>47.58</v>
+        <v>36.66</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>47.26</v>
+        <v>36.59</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>49.19</v>
+        <v>37.11</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>49.7</v>
+        <v>38.32</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>48.16</v>
+        <v>40.33</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>44.52</v>
+        <v>44.26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>45.17</v>
+        <v>43.88</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>41.58</v>
+        <v>49.42</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>36.3</v>
+        <v>36.22</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>33.41</v>
+        <v>29.05</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>114.73</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="15">
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>73.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>81.15000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1682,52 +1682,52 @@
         <v>0.47</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.89</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.71</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -1934,52 +1934,52 @@
         <v>45.51</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>36.76</v>
+        <v>45.87</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>35.21</v>
+        <v>49.78</v>
       </c>
       <c r="M19" s="3" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>35.24</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>45.56</v>
-      </c>
       <c r="R19" s="3" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>47.08</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>43.43</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>39.57</v>
-      </c>
       <c r="X19" s="3" t="n">
-        <v>34.86</v>
+        <v>34.79</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>31.95</v>
+        <v>27.78</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>31.92</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="20">
@@ -2102,52 +2102,52 @@
         <v>-1.05</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.61</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.64</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.63</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.78</v>
       </c>
       <c r="O21" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>-0.99</v>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>-1.15</v>
-      </c>
       <c r="Q21" s="3" t="n">
-        <v>-1.18</v>
+        <v>-0.99</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.89</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.78</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.66</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="22">
@@ -2354,52 +2354,52 @@
         <v>45.51</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>36.76</v>
+        <v>45.87</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>35.21</v>
+        <v>49.78</v>
       </c>
       <c r="M24" s="3" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>35.24</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>45.56</v>
-      </c>
       <c r="R24" s="3" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>47.08</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>43.43</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>39.57</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>34.86</v>
+        <v>34.79</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>31.95</v>
+        <v>27.78</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>31.92</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="25">
@@ -2522,52 +2522,52 @@
         <v>-1.05</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.61</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.64</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.63</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.78</v>
       </c>
       <c r="O26" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>-0.99</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>-1.15</v>
-      </c>
       <c r="Q26" s="3" t="n">
-        <v>-1.18</v>
+        <v>-0.99</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.89</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.78</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.66</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="27">
@@ -2774,52 +2774,52 @@
         <v>45.78</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>36.94</v>
+        <v>46</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>35.38</v>
+        <v>50.02</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>35.41</v>
+        <v>46.89</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>39.97</v>
+        <v>48.14</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>39.93</v>
+        <v>35.27</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>46.13</v>
+        <v>35.52</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>45.83</v>
+        <v>35.48</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>47.36</v>
+        <v>35.69</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>48.14</v>
+        <v>37.15</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.59</v>
+        <v>39.85</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>43.73</v>
+        <v>43.43</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>43.69</v>
+        <v>42.44</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>39.85</v>
+        <v>47.4</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>35.14</v>
+        <v>35.04</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.21</v>
+        <v>27.98</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.17</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="30">
@@ -2942,49 +2942,49 @@
         <v>-0.78</v>
       </c>
       <c r="K31" s="3" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="P31" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>-0.68</v>
       </c>
-      <c r="O31" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="S31" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.67</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.39</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.33</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>0.03</v>
@@ -3194,52 +3194,52 @@
         <v>47.46</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>37.38</v>
+        <v>46.77</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>35.8</v>
+        <v>50.61</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>36.08</v>
+        <v>47.96</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>41.01</v>
+        <v>49.72</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>115.27</v>
+        <v>36.56</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>47.34</v>
+        <v>36.52</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>46.98</v>
+        <v>36.37</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>49.19</v>
+        <v>37.11</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>49.45</v>
+        <v>38.09</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.88</v>
+        <v>40.13</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>44.48</v>
+        <v>44.22</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>45.4</v>
+        <v>44.11</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>42.06</v>
+        <v>49.99</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>36.41</v>
+        <v>36.33</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>33.65</v>
+        <v>29.26</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>115.12</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="35">
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>73.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>81.15000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3362,52 +3362,52 @@
         <v>0.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.7</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.05</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="S36" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>0.44</v>
-      </c>
       <c r="V36" s="3" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="37">
@@ -3614,52 +3614,52 @@
         <v>45.29</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>36.58</v>
+        <v>45.74</v>
       </c>
       <c r="L39" s="3" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>35.03</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>39.46</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>45.59</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>45.29</v>
-      </c>
       <c r="R39" s="3" t="n">
-        <v>46.8</v>
+        <v>35.31</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>47.9</v>
+        <v>36.9</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>46.99</v>
+        <v>39.38</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>43.13</v>
+        <v>42.87</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>43.17</v>
+        <v>41.98</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>39.3</v>
+        <v>46.75</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>34.62</v>
+        <v>34.56</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>31.7</v>
+        <v>27.62</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>31.64</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="40">
@@ -3782,52 +3782,52 @@
         <v>-1.27</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.74</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.83</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.81</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.91</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>-1.26</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.19</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.19</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.06</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.92</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.87</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="V41" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>-0.73</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>-0.66</v>
-      </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.47</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="42">
@@ -4034,52 +4034,52 @@
         <v>46.56</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>37.45</v>
+        <v>47.19</v>
       </c>
       <c r="L44" s="3" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="Q44" s="3" t="n">
         <v>35.76</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>35.66</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>40.08</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>46.19</v>
-      </c>
       <c r="R44" s="3" t="n">
-        <v>47.78</v>
+        <v>36.08</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>49.15</v>
+        <v>37.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>48.16</v>
+        <v>40.41</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>44.17</v>
+        <v>43.95</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>44.13</v>
+        <v>42.91</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>40.21</v>
+        <v>47.83</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>35.25</v>
+        <v>35.21</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>32.3</v>
+        <v>28.17</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>32.27</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="45">
@@ -4202,52 +4202,52 @@
         <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="L46" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>-0.46</v>
       </c>
-      <c r="M46" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>-0.55</v>
-      </c>
       <c r="R46" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="W46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>0.08</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>0.06</v>
-      </c>
       <c r="Z46" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="47">
@@ -4454,52 +4454,52 @@
         <v>41.79</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>33.89</v>
+        <v>42.54</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>33.95</v>
+        <v>48.24</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>33.73</v>
+        <v>45.1</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>39.73</v>
+        <v>48.61</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>39.69</v>
+        <v>35.24</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>45.95</v>
+        <v>35.48</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>45.65</v>
+        <v>35.38</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>47.4</v>
+        <v>35.76</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>46.23</v>
+        <v>35.65</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>45.34</v>
+        <v>38.08</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>41.66</v>
+        <v>41.45</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>42.13</v>
+        <v>41.01</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>40.25</v>
+        <v>47.88</v>
       </c>
       <c r="X49" s="3" t="n">
         <v>35.14</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>32.05</v>
+        <v>27.95</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>31.76</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="50">
@@ -4622,52 +4622,52 @@
         <v>-4.76</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-3.9</v>
+        <v>-4.93</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.27</v>
+        <v>-3.18</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-2.43</v>
+        <v>-3.25</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.17</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.88</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.82</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.1</v>
+        <v>-0.85</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.61</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-2.82</v>
+        <v>-2.17</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.63</v>
+        <v>-2.17</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.36</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-1.77</v>
+        <v>-1.68</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="X51" s="3" t="n">
         <v>-0.14</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="52">
@@ -4874,52 +4874,52 @@
         <v>46.05</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>37.94</v>
+        <v>47.76</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>36.01</v>
+        <v>51.17</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>35.9</v>
+        <v>48.01</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>40.4</v>
+        <v>49.48</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>40.93</v>
+        <v>36.34</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>47.29</v>
+        <v>36.52</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>47.03</v>
+        <v>36.44</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>48.45</v>
+        <v>36.59</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>47.72</v>
+        <v>36.83</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>46.94</v>
+        <v>39.42</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>43.3</v>
+        <v>43.09</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>43.17</v>
+        <v>41.98</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>40.74</v>
+        <v>48.46</v>
       </c>
       <c r="X54" s="3" t="n">
         <v>35.93</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>32.7</v>
+        <v>28.49</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>32.8</v>
+        <v>31.79</v>
       </c>
     </row>
     <row r="55">
@@ -5042,52 +5042,52 @@
         <v>-0.51</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.26</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.34</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.3</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.34</v>
+        <v>-0.99</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.83</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.71</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="57">
@@ -5294,52 +5294,52 @@
         <v>47.8</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>38.64</v>
+        <v>48.59</v>
       </c>
       <c r="L59" s="3" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="Q59" s="3" t="n">
         <v>36.97</v>
       </c>
-      <c r="M59" s="3" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="N59" s="3" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="O59" s="3" t="n">
-        <v>41.47</v>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>47.96</v>
-      </c>
-      <c r="Q59" s="3" t="n">
-        <v>47.75</v>
-      </c>
       <c r="R59" s="3" t="n">
-        <v>49.35</v>
+        <v>37.22</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>50.52</v>
+        <v>38.95</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>49.4</v>
+        <v>41.45</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>45.35</v>
+        <v>45.08</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>45.22</v>
+        <v>43.97</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>41.28</v>
+        <v>49.06</v>
       </c>
       <c r="X59" s="3" t="n">
         <v>36.15</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>33.17</v>
+        <v>28.93</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>33.17</v>
+        <v>32.15</v>
       </c>
     </row>
     <row r="60">
@@ -5462,52 +5462,52 @@
         <v>1.24</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.85</v>
+        <v>1.12</v>
       </c>
       <c r="L61" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P61" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="M61" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>0.96</v>
-      </c>
       <c r="Q61" s="3" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.18</v>
+        <v>0.86</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="U61" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W61" s="3" t="n">
         <v>1.32</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>1.16</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -5714,52 +5714,52 @@
         <v>48.55</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>39.24</v>
+        <v>49.35</v>
       </c>
       <c r="L64" s="3" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="Q64" s="3" t="n">
         <v>37.54</v>
       </c>
-      <c r="M64" s="3" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="O64" s="3" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="P64" s="3" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="Q64" s="3" t="n">
-        <v>48.49</v>
-      </c>
       <c r="R64" s="3" t="n">
-        <v>50.06</v>
+        <v>37.81</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>51.31</v>
+        <v>39.56</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>50.23</v>
+        <v>42.14</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>46.06</v>
+        <v>45.83</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>45.93</v>
+        <v>44.66</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>41.89</v>
+        <v>49.88</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>36.71</v>
+        <v>36.67</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>33.62</v>
+        <v>29.32</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>33.62</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="65">
@@ -5882,52 +5882,52 @@
         <v>1.99</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="L66" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q66" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="M66" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="N66" s="3" t="n">
+      <c r="R66" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Y66" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z66" s="3" t="n">
         <v>1.43</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q66" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R66" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S66" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X66" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Y66" s="3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z66" s="3" t="n">
-        <v>1.48</v>
       </c>
     </row>
     <row r="67">
@@ -6134,52 +6134,52 @@
         <v>49.06</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>39.69</v>
+        <v>49.92</v>
       </c>
       <c r="L69" s="3" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="Q69" s="3" t="n">
         <v>38.01</v>
       </c>
-      <c r="M69" s="3" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>42.65</v>
-      </c>
-      <c r="O69" s="3" t="n">
-        <v>42.65</v>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>49.1</v>
-      </c>
       <c r="R69" s="3" t="n">
-        <v>50.7</v>
+        <v>38.28</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>51.85</v>
+        <v>39.98</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>50.76</v>
+        <v>42.59</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>46.55</v>
+        <v>46.32</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>46.41</v>
+        <v>45.13</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>42.37</v>
+        <v>50.41</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>37.14</v>
+        <v>37.1</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>34.04</v>
+        <v>29.69</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>34.05</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -6302,52 +6302,52 @@
         <v>2.5</v>
       </c>
       <c r="K71" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R71" s="3" t="n">
         <v>1.91</v>
       </c>
-      <c r="L71" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>2.53</v>
-      </c>
       <c r="S71" s="3" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="72">
@@ -6554,52 +6554,52 @@
         <v>47.46</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>38.4</v>
+        <v>48.3</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>36.82</v>
+        <v>52.26</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>36.71</v>
+        <v>49.03</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>41.31</v>
+        <v>50.53</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>41.35</v>
+        <v>36.67</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>47.82</v>
+        <v>36.89</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>47.55</v>
+        <v>36.85</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>49.14</v>
+        <v>37.11</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>50.21</v>
+        <v>38.71</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>49.1</v>
+        <v>41.2</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>45.07</v>
+        <v>44.8</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>44.94</v>
+        <v>43.7</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>41.07</v>
+        <v>48.86</v>
       </c>
       <c r="X74" s="3" t="n">
         <v>35.96</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>32.96</v>
+        <v>28.75</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>32.93</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="75">
@@ -6722,52 +6722,52 @@
         <v>0.9</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="L76" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P76" s="3" t="n">
         <v>0.59</v>
       </c>
-      <c r="M76" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="Q76" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.98</v>
+        <v>0.74</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.13</v>
+        <v>0.95</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="77">
@@ -6974,52 +6974,52 @@
         <v>46.56</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>37.79</v>
+        <v>47.48</v>
       </c>
       <c r="L79" s="3" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="Q79" s="3" t="n">
         <v>36.23</v>
       </c>
-      <c r="M79" s="3" t="n">
-        <v>36.15</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>40.65</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>47.01</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>46.74</v>
-      </c>
       <c r="R79" s="3" t="n">
-        <v>48.16</v>
+        <v>36.37</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>49.05</v>
+        <v>37.82</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>47.97</v>
+        <v>40.25</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>44.03</v>
+        <v>43.82</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>43.9</v>
+        <v>42.7</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>40.13</v>
+        <v>47.74</v>
       </c>
       <c r="X79" s="3" t="n">
         <v>35.28</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>32.24</v>
+        <v>28.09</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>32.14</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="80">
@@ -7394,52 +7394,52 @@
         <v>44.98</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>38.01</v>
+        <v>47.96</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>35.97</v>
+        <v>51.12</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35.94</v>
+        <v>48.06</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>40.44</v>
+        <v>49.53</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>40.93</v>
+        <v>36.34</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>47.19</v>
+        <v>36.44</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>46.98</v>
+        <v>36.41</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>48.5</v>
+        <v>36.59</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>46.63</v>
+        <v>35.99</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>45.91</v>
+        <v>38.55</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>42.38</v>
+        <v>42.21</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>42.34</v>
+        <v>41.17</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>40.95</v>
+        <v>48.76</v>
       </c>
       <c r="X84" s="3" t="n">
         <v>35.93</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>32.7</v>
+        <v>28.49</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>32.76</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="85">
@@ -7562,52 +7562,52 @@
         <v>-1.57</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.23</v>
+        <v>0.48</v>
       </c>
       <c r="L86" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="N86" s="3" t="n">
         <v>-0.25</v>
       </c>
-      <c r="M86" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="O86" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.42</v>
+        <v>-1.84</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.07</v>
+        <v>-1.7</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-1.65</v>
+        <v>-1.6</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.52</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="87">
@@ -7814,52 +7814,52 @@
         <v>45.78</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>36.94</v>
+        <v>46</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>35.38</v>
+        <v>50.02</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>35.41</v>
+        <v>46.89</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>39.97</v>
+        <v>48.14</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>39.93</v>
+        <v>35.27</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>46.13</v>
+        <v>35.52</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>45.83</v>
+        <v>35.48</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>47.36</v>
+        <v>35.69</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>48.14</v>
+        <v>37.15</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>47.59</v>
+        <v>39.85</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>43.73</v>
+        <v>43.43</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>43.69</v>
+        <v>42.44</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>39.85</v>
+        <v>47.4</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>35.14</v>
+        <v>35.04</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>32.21</v>
+        <v>27.98</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.21</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="90">
@@ -7982,52 +7982,52 @@
         <v>-0.78</v>
       </c>
       <c r="K91" s="3" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="O91" s="3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="L91" s="3" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="N91" s="3" t="n">
+      <c r="P91" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="R91" s="3" t="n">
         <v>-0.68</v>
       </c>
-      <c r="O91" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="S91" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.67</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.39</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.33</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-12T01:14:13</t>
+          <t>CreatedAt: 2026-03-12T02:14:54</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -659,67 +659,67 @@
         <v>66.11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>66.38</v>
+        <v>66.31</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>53.67</v>
+        <v>53.69</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>68.11</v>
+        <v>74.44</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>54.1</v>
+        <v>68.59</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>47.42</v>
+        <v>49.49</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>37.54</v>
+        <v>37.78</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>47.7</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>34.37</v>
+        <v>37.17</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>37.24</v>
+        <v>39.53</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>34.17</v>
+        <v>34.59</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>33.24</v>
+        <v>33.25</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>33.81</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>33.65</v>
+        <v>33.21</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>34.21</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>61.15</v>
+        <v>60.97</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>60.74</v>
+        <v>60.98</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>61.16</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>50.48</v>
+        <v>52.68</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>34.59</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>47</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="5">
@@ -827,34 +827,34 @@
         <v>-0.46</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>-0.54</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>-0.76</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.71</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>-0.93</v>
@@ -863,22 +863,22 @@
         <v>-0.88</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.96</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>-0.58</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.52</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-1.35</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.26</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>-0.62</v>
@@ -887,7 +887,7 @@
         <v>-0.65</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="7">
@@ -1079,67 +1079,67 @@
         <v>68.84999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>70.22</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56.94</v>
+        <v>56.08</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>71.3</v>
+        <v>77.84</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>56.92</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>50.07</v>
+        <v>52.26</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>38.68</v>
+        <v>38.96</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>49.91</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>36</v>
+        <v>38.97</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>39.29</v>
+        <v>41.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>36.07</v>
+        <v>36.52</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>35.01</v>
+        <v>35.02</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>35.55</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>35.55</v>
+        <v>35.09</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>35.8</v>
+        <v>35.65</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>62</v>
+        <v>61.76</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>61.94</v>
+        <v>62.19</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>63.07</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>52.37</v>
+        <v>54.71</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>35.71</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>49.05</v>
+        <v>49.01</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>49.73</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="10">
@@ -1247,34 +1247,34 @@
         <v>2.27</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.73</v>
+        <v>1.85</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>1.45</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.84</v>
@@ -1283,31 +1283,31 @@
         <v>0.85</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.31</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>0.57</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -1502,64 +1502,64 @@
         <v>70.29000000000001</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>163.84</v>
+        <v>56.08</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>71.37</v>
+        <v>77.84</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>56.92</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>50.07</v>
+        <v>52.26</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>38.68</v>
+        <v>38.96</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>49.91</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36</v>
+        <v>38.97</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>39.29</v>
+        <v>41.74</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>36.11</v>
+        <v>36.52</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>35.01</v>
+        <v>35.02</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>35.55</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>35.59</v>
+        <v>35.13</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>35.8</v>
+        <v>35.69</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>62</v>
+        <v>61.76</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>61.94</v>
+        <v>62.19</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>63.07</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>52.42</v>
+        <v>54.71</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>35.75</v>
+        <v>35.71</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>49.05</v>
+        <v>49.01</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>49.73</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="15">
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0</v>
@@ -1670,31 +1670,31 @@
         <v>3.51</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.73</v>
+        <v>1.85</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>1.45</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.84</v>
@@ -1703,31 +1703,31 @@
         <v>0.85</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.31</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>0.57</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17">
@@ -1919,67 +1919,67 @@
         <v>66.23999999999999</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>66.70999999999999</v>
+        <v>66.58</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>53.94</v>
+        <v>53.96</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>68.59</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>54.48</v>
+        <v>69.14</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>47.75</v>
+        <v>49.83</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>37.8</v>
+        <v>38.04</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>47.93</v>
+        <v>47.89</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>34.47</v>
+        <v>37.32</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>37.39</v>
+        <v>39.68</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>34.3</v>
+        <v>34.73</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>33.4</v>
+        <v>33.41</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>33.98</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>33.81</v>
+        <v>33.38</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>34.32</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>61.27</v>
+        <v>61.03</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>60.86</v>
+        <v>61.1</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>61.28</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>50.63</v>
+        <v>52.89</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>34.72</v>
+        <v>34.69</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>46.82</v>
+        <v>46.77</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>47.18</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="20">
@@ -2087,7 +2087,7 @@
         <v>-0.33</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>-0.27</v>
@@ -2096,25 +2096,25 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="J21" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>-0.53</v>
-      </c>
       <c r="M21" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>-0.77</v>
@@ -2123,16 +2123,16 @@
         <v>-0.71</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>-0.48</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.34</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.41</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>-1.23</v>
@@ -2141,13 +2141,13 @@
         <v>-1.06</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="22">
@@ -2339,67 +2339,67 @@
         <v>66.23999999999999</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>66.70999999999999</v>
+        <v>66.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>53.94</v>
+        <v>53.96</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>68.59</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>54.48</v>
+        <v>69.14</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>47.75</v>
+        <v>49.83</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>37.8</v>
+        <v>38.04</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>47.93</v>
+        <v>47.89</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>34.47</v>
+        <v>37.32</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>37.39</v>
+        <v>39.68</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.3</v>
+        <v>34.73</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>33.4</v>
+        <v>33.41</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>33.98</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>33.81</v>
+        <v>33.38</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>34.32</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>61.27</v>
+        <v>61.03</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>60.86</v>
+        <v>61.1</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>61.28</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>50.63</v>
+        <v>52.89</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>34.72</v>
+        <v>34.69</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>46.82</v>
+        <v>46.77</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>47.18</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="25">
@@ -2507,7 +2507,7 @@
         <v>-0.33</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>-0.27</v>
@@ -2516,25 +2516,25 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="J26" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="L26" s="3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>-0.53</v>
-      </c>
       <c r="M26" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>-0.77</v>
@@ -2543,16 +2543,16 @@
         <v>-0.71</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>-0.48</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.34</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.41</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>-1.23</v>
@@ -2561,13 +2561,13 @@
         <v>-1.06</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="27">
@@ -2759,67 +2759,67 @@
         <v>66.38</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>66.91</v>
+        <v>66.78</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.1</v>
+        <v>54.12</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>54.92</v>
+        <v>69.62</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>48.03</v>
+        <v>50.13</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>38.06</v>
+        <v>38.31</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>48.03</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.54</v>
+        <v>37.39</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>37.43</v>
+        <v>39.72</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>34.34</v>
+        <v>34.76</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>33.5</v>
+        <v>33.51</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>34.11</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>33.91</v>
+        <v>33.51</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>34.42</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>61.33</v>
+        <v>61.09</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>60.97</v>
+        <v>61.21</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>61.34</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>50.73</v>
+        <v>52.99</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>34.83</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>46.96</v>
+        <v>46.91</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>47.32</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="30">
@@ -2927,19 +2927,19 @@
         <v>-0.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0.11</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0.19</v>
@@ -2948,13 +2948,13 @@
         <v>-0.43</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.59</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0.67</v>
@@ -2963,22 +2963,22 @@
         <v>-0.58</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>-0.38</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.28</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.29</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>-1.17</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>-0.38</v>
@@ -2987,7 +2987,7 @@
         <v>-0.33</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="32">
@@ -3179,67 +3179,67 @@
         <v>70.23</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>71.27</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>164.94</v>
+        <v>57.38</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>72.12</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>57.4</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>50.92</v>
+        <v>53.14</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>39.11</v>
+        <v>39.36</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>50.32</v>
+        <v>50.37</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>36.22</v>
+        <v>39.21</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>39.74</v>
+        <v>42.22</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>36.6</v>
+        <v>37.02</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>35.33</v>
+        <v>35.34</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>35.77</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>35.95</v>
+        <v>35.49</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>36.02</v>
+        <v>35.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>62.38</v>
+        <v>62.19</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>62.56</v>
+        <v>62.75</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>64.23999999999999</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>53.34</v>
+        <v>55.73</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>36.04</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>49.62</v>
+        <v>49.57</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>50.62</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="35">
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0</v>
@@ -3347,34 +3347,34 @@
         <v>3.65</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>4.49</v>
+        <v>4.72</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.83</v>
+        <v>3.16</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3.46</v>
+        <v>3.62</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.76</v>
+        <v>3.26</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.17</v>
@@ -3383,22 +3383,22 @@
         <v>1.07</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.19</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>1.73</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>0.83</v>
@@ -3407,7 +3407,7 @@
         <v>2.33</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="37">
@@ -3599,67 +3599,67 @@
         <v>66.11</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>66.38</v>
+        <v>66.31</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>53.67</v>
+        <v>53.69</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>68.11</v>
+        <v>74.44</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>54.1</v>
+        <v>68.59</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>47.42</v>
+        <v>49.49</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>37.54</v>
+        <v>37.78</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>47.7</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>34.37</v>
+        <v>37.17</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>37.24</v>
+        <v>39.53</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>34.17</v>
+        <v>34.59</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>33.24</v>
+        <v>33.25</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>33.81</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>33.65</v>
+        <v>33.21</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>34.21</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.15</v>
+        <v>60.97</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>60.74</v>
+        <v>60.98</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>61.16</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>50.48</v>
+        <v>52.68</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>34.59</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>46.64</v>
+        <v>46.59</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>47</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="40">
@@ -3767,34 +3767,34 @@
         <v>-0.46</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>-0.54</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>-0.76</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.71</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>-0.93</v>
@@ -3803,22 +3803,22 @@
         <v>-0.88</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.96</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>-0.58</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.4</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.52</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-1.35</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.26</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>-0.62</v>
@@ -3827,7 +3827,7 @@
         <v>-0.65</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="42">
@@ -4019,67 +4019,67 @@
         <v>67.11</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>67.31</v>
+        <v>67.25</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>54.75</v>
+        <v>54.77</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>54.92</v>
+        <v>69.62</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>48.42</v>
+        <v>50.53</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>38.14</v>
+        <v>38.38</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>48.36</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>34.85</v>
+        <v>37.65</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>37.73</v>
+        <v>40</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>34.61</v>
+        <v>35</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>33.83</v>
+        <v>33.84</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>34.45</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>34.45</v>
+        <v>34.01</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>34.97</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>62.81</v>
+        <v>62.69</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>62.31</v>
+        <v>62.44</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>62.56</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>51.59</v>
+        <v>53.84</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>35.35</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>47.53</v>
+        <v>47.48</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>48.37</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="45">
@@ -4187,31 +4187,31 @@
         <v>0.54</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>0.55</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>-0.1</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.23</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.24</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>-0.35</v>
@@ -4238,7 +4238,7 @@
         <v>0.06</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.14</v>
@@ -4247,7 +4247,7 @@
         <v>0.24</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="47">
@@ -4442,64 +4442,64 @@
         <v>66.44</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>54.2</v>
+        <v>54.23</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>64.95999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>51.89</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>45.93</v>
+        <v>47.94</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>38.02</v>
+        <v>38.31</v>
       </c>
       <c r="L49" s="3" t="n">
         <v>47.98</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>34.61</v>
+        <v>37.43</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>37.5</v>
+        <v>39.8</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>34.44</v>
+        <v>34.83</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>33.6</v>
+        <v>33.61</v>
       </c>
       <c r="Q49" s="3" t="n">
         <v>34.25</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>34.32</v>
+        <v>33.87</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>32.95</v>
+        <v>32.98</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>56.56</v>
+        <v>56.45</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>56.5</v>
+        <v>56.66</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>56.66</v>
+        <v>56.72</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>46.61</v>
+        <v>48.69</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>33.25</v>
+        <v>33.28</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>44.49</v>
+        <v>44.44</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>47.61</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="50">
@@ -4613,25 +4613,25 @@
         <v>0</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-3.7</v>
+        <v>-3.98</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-2.75</v>
+        <v>-3.49</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-2.39</v>
+        <v>-2.49</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="L51" s="3" t="n">
         <v>-0.48</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>-0.52</v>
@@ -4643,31 +4643,31 @@
         <v>-0.45</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.81</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-5.94</v>
+        <v>-5.93</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.88</v>
+        <v>-5.84</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.84</v>
+        <v>-5.79</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.08</v>
+        <v>-5.26</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.93</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>-2.8</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="52">
@@ -4859,67 +4859,67 @@
         <v>68.70999999999999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>68.91</v>
+        <v>68.98</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>56.35</v>
+        <v>56.43</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>75.56</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>56.1</v>
+        <v>70.98</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>48.22</v>
+        <v>50.33</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>37.91</v>
+        <v>38.15</v>
       </c>
       <c r="L54" s="3" t="n">
         <v>49.05</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>35.31</v>
+        <v>38.22</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>38.41</v>
+        <v>40.85</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>35.82</v>
+        <v>36.22</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>35.12</v>
+        <v>35.16</v>
       </c>
       <c r="Q54" s="3" t="n">
         <v>35.44</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>35.19</v>
+        <v>34.45</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>34.21</v>
+        <v>34.18</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>61.1</v>
+        <v>60.97</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>61.03</v>
+        <v>61.16</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>61.4</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>50.78</v>
+        <v>52.94</v>
       </c>
       <c r="X54" s="3" t="n">
         <v>34.69</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>47.01</v>
+        <v>46.96</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>48.72</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="55">
@@ -5027,16 +5027,16 @@
         <v>2.13</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>-0.1</v>
@@ -5048,37 +5048,37 @@
         <v>0.59</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>0.74</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.62</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.35</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>-1.11</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.01</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>-0.52</v>
@@ -5087,7 +5087,7 @@
         <v>-0.28</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5282,64 +5282,64 @@
         <v>68.91</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>56.11</v>
+        <v>56.13</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>70.56999999999999</v>
+        <v>77.12</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>56.04</v>
+        <v>71.05</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>49.66</v>
+        <v>51.83</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>39.27</v>
+        <v>39.52</v>
       </c>
       <c r="L59" s="3" t="n">
         <v>49.75</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>35.92</v>
+        <v>38.81</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>38.85</v>
+        <v>41.19</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>35.71</v>
+        <v>36.11</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>34.9</v>
+        <v>34.91</v>
       </c>
       <c r="Q59" s="3" t="n">
         <v>35.55</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>35.44</v>
+        <v>34.98</v>
       </c>
       <c r="S59" s="3" t="n">
         <v>35.83</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>64.37</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>63.65</v>
+        <v>63.84</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>63.91</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>52.75</v>
+        <v>55.05</v>
       </c>
       <c r="X59" s="3" t="n">
         <v>36.19</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>48.6</v>
+        <v>48.55</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>49.68</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="60">
@@ -5453,28 +5453,28 @@
         <v>1.91</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="I61" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J61" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="J61" s="3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="K61" s="3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>1.29</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0.73</v>
@@ -5483,22 +5483,22 @@
         <v>0.85</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="S61" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1.41</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>0.98</v>
@@ -5507,7 +5507,7 @@
         <v>1.31</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="62">
@@ -5699,67 +5699,67 @@
         <v>69.56999999999999</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>69.84999999999999</v>
+        <v>69.78</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>56.88</v>
+        <v>56.9</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>56.86</v>
+        <v>72.09</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>50.44</v>
+        <v>52.64</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>39.89</v>
+        <v>40.14</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>50.48</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>36.48</v>
+        <v>39.42</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>39.41</v>
+        <v>41.83</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>36.26</v>
+        <v>36.63</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>35.44</v>
+        <v>35.45</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>35.99</v>
+        <v>35.56</v>
       </c>
       <c r="S64" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>65.38</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>64.97</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>53.62</v>
+        <v>55.96</v>
       </c>
       <c r="X64" s="3" t="n">
         <v>36.75</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>49.31</v>
+        <v>49.26</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>50.36</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="65">
@@ -5867,34 +5867,34 @@
         <v>2.99</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>2.67</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="L66" s="3" t="n">
         <v>2.02</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P66" s="3" t="n">
         <v>1.28</v>
@@ -5903,22 +5903,22 @@
         <v>1.41</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S66" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>2.47</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>1.54</v>
@@ -5927,7 +5927,7 @@
         <v>2.02</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="67">
@@ -6122,64 +6122,64 @@
         <v>70.73999999999999</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>57.6</v>
+        <v>57.63</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>72.34999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>57.28</v>
+        <v>72.62</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>51.02</v>
+        <v>53.25</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>40.31</v>
+        <v>40.57</v>
       </c>
       <c r="L69" s="3" t="n">
         <v>51.12</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>36.95</v>
+        <v>39.91</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>39.91</v>
+        <v>42.36</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>36.72</v>
+        <v>37.13</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>35.89</v>
+        <v>35.9</v>
       </c>
       <c r="Q69" s="3" t="n">
         <v>36.52</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>36.29</v>
+        <v>35.82</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>36.7</v>
+        <v>36.67</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>65.86</v>
+        <v>65.73</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>64.84</v>
+        <v>64.97</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>65.04000000000001</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>53.73</v>
+        <v>56.08</v>
       </c>
       <c r="X69" s="3" t="n">
         <v>37.03</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>49.83</v>
+        <v>49.78</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>51</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="70">
@@ -6293,28 +6293,28 @@
         <v>3.4</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>3.69</v>
+        <v>4.03</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="L71" s="3" t="n">
         <v>2.66</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>1.72</v>
@@ -6323,22 +6323,22 @@
         <v>1.83</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>2.54</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>1.81</v>
@@ -6347,7 +6347,7 @@
         <v>2.54</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="72">
@@ -6539,67 +6539,67 @@
         <v>68.42</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>68.63</v>
+        <v>68.56</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>55.88</v>
+        <v>55.9</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>70.06</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>55.7</v>
+        <v>70.62</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>49.35</v>
+        <v>51.51</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>39.07</v>
+        <v>39.32</v>
       </c>
       <c r="L74" s="3" t="n">
         <v>49.5</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>35.78</v>
+        <v>38.65</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>38.65</v>
+        <v>41.02</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>35.56</v>
+        <v>35.96</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>34.76</v>
+        <v>34.77</v>
       </c>
       <c r="Q74" s="3" t="n">
         <v>35.4</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>35.3</v>
+        <v>34.84</v>
       </c>
       <c r="S74" s="3" t="n">
         <v>35.58</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>63.84</v>
+        <v>63.72</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>63.26</v>
+        <v>63.39</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>63.45</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>52.37</v>
+        <v>54.66</v>
       </c>
       <c r="X74" s="3" t="n">
         <v>35.93</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>48.2</v>
+        <v>48.16</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>49.32</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="75">
@@ -6707,34 +6707,34 @@
         <v>1.85</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>1.68</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L76" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="P76" s="3" t="n">
         <v>0.59</v>
@@ -6743,7 +6743,7 @@
         <v>0.71</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S76" s="3" t="n">
         <v>0.78</v>
@@ -6758,16 +6758,16 @@
         <v>0.95</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>0.72</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="77">
@@ -6962,64 +6962,64 @@
         <v>66.78</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>54.2</v>
+        <v>54.23</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>68.66</v>
+        <v>75.03</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>54.64</v>
+        <v>69.28</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>48.32</v>
+        <v>50.43</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>38.25</v>
+        <v>38.5</v>
       </c>
       <c r="L79" s="3" t="n">
         <v>48.46</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>35.03</v>
+        <v>37.88</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>37.92</v>
+        <v>40.24</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>34.96</v>
+        <v>35.35</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>34.17</v>
+        <v>34.18</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>34.69</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>34.62</v>
+        <v>34.18</v>
       </c>
       <c r="S79" s="3" t="n">
         <v>34.8</v>
       </c>
       <c r="T79" s="3" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="U79" s="3" t="n">
         <v>62.5</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>62.38</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>62.5</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>51.69</v>
+        <v>53.95</v>
       </c>
       <c r="X79" s="3" t="n">
         <v>35.21</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>47.29</v>
+        <v>47.24</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>47.94</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="80">
@@ -7379,67 +7379,67 @@
         <v>68.78</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>68.91</v>
+        <v>68.98</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>56.58</v>
+        <v>56.66</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>67.98</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>56.57</v>
+        <v>71.64</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>47.46</v>
+        <v>49.54</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>37.24</v>
+        <v>37.52</v>
       </c>
       <c r="L84" s="3" t="n">
         <v>49.4</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35.59</v>
+        <v>38.53</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>38.61</v>
+        <v>41.06</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>35.89</v>
+        <v>36.33</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>35.26</v>
+        <v>35.31</v>
       </c>
       <c r="Q84" s="3" t="n">
         <v>35.58</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>35.37</v>
+        <v>34.73</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>33.68</v>
+        <v>33.65</v>
       </c>
       <c r="T84" s="3" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="U84" s="3" t="n">
         <v>60.33</v>
-      </c>
-      <c r="U84" s="3" t="n">
-        <v>60.27</v>
       </c>
       <c r="V84" s="3" t="n">
         <v>60.39</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>49.94</v>
+        <v>52.02</v>
       </c>
       <c r="X84" s="3" t="n">
         <v>34.05</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>46.27</v>
+        <v>46.22</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>49.02</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="85">
@@ -7547,58 +7547,58 @@
         <v>2.2</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.89</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.98</v>
       </c>
       <c r="L86" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Q86" s="3" t="n">
         <v>0.89</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
       <c r="T86" s="3" t="n">
         <v>-2.17</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.11</v>
+        <v>-2.17</v>
       </c>
       <c r="V86" s="3" t="n">
         <v>-2.11</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.92</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-1.16</v>
@@ -7607,7 +7607,7 @@
         <v>-1.02</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="87">
@@ -7799,67 +7799,67 @@
         <v>66.38</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>66.91</v>
+        <v>66.78</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>54.1</v>
+        <v>54.12</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>69.06999999999999</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>54.92</v>
+        <v>69.62</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>48.03</v>
+        <v>50.13</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>38.06</v>
+        <v>38.31</v>
       </c>
       <c r="L89" s="3" t="n">
         <v>48.03</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>34.54</v>
+        <v>37.39</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>37.43</v>
+        <v>39.72</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>34.34</v>
+        <v>34.76</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>33.5</v>
+        <v>33.51</v>
       </c>
       <c r="Q89" s="3" t="n">
         <v>34.11</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>33.91</v>
+        <v>33.51</v>
       </c>
       <c r="S89" s="3" t="n">
         <v>34.42</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>61.33</v>
+        <v>61.09</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>60.97</v>
+        <v>61.21</v>
       </c>
       <c r="V89" s="3" t="n">
         <v>61.34</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>50.73</v>
+        <v>52.99</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>34.83</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>46.96</v>
+        <v>46.91</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>47.32</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="90">
@@ -7967,19 +7967,19 @@
         <v>-0.2</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>-0.11</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>-0.19</v>
@@ -7988,13 +7988,13 @@
         <v>-0.43</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.59</v>
       </c>
       <c r="P91" s="3" t="n">
         <v>-0.67</v>
@@ -8003,22 +8003,22 @@
         <v>-0.58</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="S91" s="3" t="n">
         <v>-0.38</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.28</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.29</v>
       </c>
       <c r="V91" s="3" t="n">
         <v>-1.17</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>-0.38</v>
@@ -8027,7 +8027,7 @@
         <v>-0.33</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-12T16:08:03</t>
+          <t>CreatedAt: 2026-03-12T17:09:33</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -704,22 +704,22 @@
         <v>60.87</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>116.92</v>
+        <v>116.68</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>51.02</v>
+        <v>103.08</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>34.15</v>
+        <v>34.12</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>34.26</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.59</v>
+        <v>34.55</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>34.33</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="5">
@@ -872,13 +872,13 @@
         <v>-1.7</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.86</v>
+        <v>-3.97</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.58</v>
+        <v>-3.4</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.09</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>-0.75</v>
@@ -887,7 +887,7 @@
         <v>-0.55</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="7">
@@ -1124,10 +1124,10 @@
         <v>59.82</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>115.13</v>
+        <v>115.12</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>51.92</v>
+        <v>102.58</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>34.93</v>
@@ -1136,10 +1136,10 @@
         <v>35.12</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>36.23</v>
+        <v>36.19</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>36.17</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="10">
@@ -1292,10 +1292,10 @@
         <v>-2.75</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-5.64</v>
+        <v>-5.53</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.67</v>
+        <v>-3.9</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>-0.28</v>
@@ -1307,7 +1307,7 @@
         <v>1.09</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="12">
@@ -1544,22 +1544,22 @@
         <v>59.82</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>115.13</v>
+        <v>115.12</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>51.92</v>
+        <v>102.58</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>34.97</v>
+        <v>34.93</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>35.12</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>36.23</v>
+        <v>36.19</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>36.21</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="15">
@@ -1712,13 +1712,13 @@
         <v>-2.75</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-5.64</v>
+        <v>-5.53</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.67</v>
+        <v>-3.9</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>0.11</v>
@@ -1727,7 +1727,7 @@
         <v>1.09</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
@@ -1964,22 +1964,22 @@
         <v>60.81</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>116.8</v>
+        <v>116.57</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>50.92</v>
+        <v>102.78</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>34.15</v>
+        <v>34.12</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>34.29</v>
+        <v>34.33</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.66</v>
+        <v>34.62</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>34.4</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="20">
@@ -2132,22 +2132,22 @@
         <v>-1.76</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.97</v>
+        <v>-4.08</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.68</v>
+        <v>-3.7</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.09</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2384,22 +2384,22 @@
         <v>60.81</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>116.8</v>
+        <v>116.57</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>50.92</v>
+        <v>102.78</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>34.15</v>
+        <v>34.12</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>34.29</v>
+        <v>34.33</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.66</v>
+        <v>34.62</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>34.4</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="25">
@@ -2552,22 +2552,22 @@
         <v>-1.76</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.97</v>
+        <v>-4.08</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.68</v>
+        <v>-3.7</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.09</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2804,22 +2804,22 @@
         <v>60.87</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>116.92</v>
+        <v>116.57</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>50.82</v>
+        <v>102.39</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>34.12</v>
+        <v>34.09</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>34.33</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.66</v>
+        <v>34.62</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>34.4</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="30">
@@ -2972,22 +2972,22 @@
         <v>-1.7</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-3.86</v>
+        <v>-4.08</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.78</v>
+        <v>-4.1</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.12</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="32">
@@ -3224,10 +3224,10 @@
         <v>59.42</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>114.7</v>
+        <v>114.69</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>52.65</v>
+        <v>103.48</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>35.46</v>
@@ -3236,10 +3236,10 @@
         <v>35.33</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>36.64</v>
+        <v>36.61</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>36.74</v>
+        <v>36.77</v>
       </c>
     </row>
     <row r="35">
@@ -3392,10 +3392,10 @@
         <v>-3.15</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-6.08</v>
+        <v>-5.96</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.05</v>
+        <v>-3</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0.25</v>
@@ -3644,22 +3644,22 @@
         <v>60.87</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>116.92</v>
+        <v>116.68</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>51.02</v>
+        <v>103.08</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>34.15</v>
+        <v>34.12</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>34.26</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.59</v>
+        <v>34.55</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>34.33</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="40">
@@ -3812,13 +3812,13 @@
         <v>-1.7</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.86</v>
+        <v>-3.97</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.58</v>
+        <v>-3.4</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.09</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>-0.75</v>
@@ -3827,7 +3827,7 @@
         <v>-0.55</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="42">
@@ -4064,10 +4064,10 @@
         <v>63.02</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>121.26</v>
+        <v>121.01</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>52.65</v>
+        <v>107.23</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>35.18</v>
@@ -4076,10 +4076,10 @@
         <v>35.23</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>35.42</v>
+        <v>35.39</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>35.4</v>
+        <v>35.43</v>
       </c>
     </row>
     <row r="45">
@@ -4232,10 +4232,10 @@
         <v>0.44</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>-0.04</v>
@@ -4484,22 +4484,22 @@
         <v>59.77</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>115.58</v>
+        <v>115.67</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>50.33</v>
+        <v>102.09</v>
       </c>
       <c r="W49" s="3" t="n">
         <v>33.47</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>33.16</v>
+        <v>33.13</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>34.83</v>
+        <v>34.79</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>35.37</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="50">
@@ -4652,16 +4652,16 @@
         <v>-2.81</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.2</v>
+        <v>-4.97</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-2.26</v>
+        <v>-4.39</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>-1.74</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.89</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>-0.31</v>
@@ -4904,10 +4904,10 @@
         <v>61.17</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>116.24</v>
+        <v>116.23</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>51.36</v>
+        <v>103.48</v>
       </c>
       <c r="W54" s="3" t="n">
         <v>34.59</v>
@@ -4916,10 +4916,10 @@
         <v>34.43</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>36.12</v>
+        <v>35.79</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>36.13</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="55">
@@ -5072,10 +5072,10 @@
         <v>-1.41</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-4.53</v>
+        <v>-4.42</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.23</v>
+        <v>-3</v>
       </c>
       <c r="W56" s="3" t="n">
         <v>-0.62</v>
@@ -5084,7 +5084,7 @@
         <v>-0.59</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="Z56" s="3" t="n">
         <v>1.12</v>
@@ -5324,10 +5324,10 @@
         <v>64.70999999999999</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>124.26</v>
+        <v>124.12</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>53.84</v>
+        <v>109.89</v>
       </c>
       <c r="W59" s="3" t="n">
         <v>36</v>
@@ -5339,7 +5339,7 @@
         <v>36.23</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>36.32</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="60">
@@ -5495,7 +5495,7 @@
         <v>3.48</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.24</v>
+        <v>3.41</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>0.79</v>
@@ -5504,10 +5504,10 @@
         <v>1.05</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="62">
@@ -5744,10 +5744,10 @@
         <v>65.87</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>126.33</v>
+        <v>126.2</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>54.79</v>
+        <v>111.85</v>
       </c>
       <c r="W64" s="3" t="n">
         <v>36.56</v>
@@ -5756,10 +5756,10 @@
         <v>36.66</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.8</v>
+        <v>36.76</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>36.86</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="65">
@@ -5912,10 +5912,10 @@
         <v>3.29</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.19</v>
+        <v>5.37</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>1.35</v>
@@ -5924,7 +5924,7 @@
         <v>1.65</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>1.84</v>
@@ -6167,19 +6167,19 @@
         <v>127</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>54.85</v>
+        <v>112.56</v>
       </c>
       <c r="W69" s="3" t="n">
         <v>36.68</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>36.93</v>
+        <v>36.94</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>37.15</v>
+        <v>37.11</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>37.33</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="70">
@@ -6332,10 +6332,10 @@
         <v>3.85</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>6.22</v>
+        <v>6.35</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.25</v>
+        <v>6.08</v>
       </c>
       <c r="W71" s="3" t="n">
         <v>1.47</v>
@@ -6344,10 +6344,10 @@
         <v>1.92</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="72">
@@ -6587,7 +6587,7 @@
         <v>123.62</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>53.62</v>
+        <v>109.32</v>
       </c>
       <c r="W74" s="3" t="n">
         <v>35.82</v>
@@ -6596,10 +6596,10 @@
         <v>35.84</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>36.04</v>
+        <v>36.01</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>36.13</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="75">
@@ -6752,10 +6752,10 @@
         <v>1.8</v>
       </c>
       <c r="U76" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V76" s="3" t="n">
         <v>2.84</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>1.02</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0.61</v>
@@ -7004,10 +7004,10 @@
         <v>62.57</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>120.78</v>
+        <v>120.65</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>52.6</v>
+        <v>106.48</v>
       </c>
       <c r="W79" s="3" t="n">
         <v>35.21</v>
@@ -7016,10 +7016,10 @@
         <v>35.01</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>35.14</v>
+        <v>35.11</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>35.01</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="80">
@@ -7424,22 +7424,22 @@
         <v>60.05</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>115.35</v>
+        <v>115.12</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>50.53</v>
+        <v>101.51</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>33.95</v>
+        <v>33.92</v>
       </c>
       <c r="X84" s="3" t="n">
         <v>33.67</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>36.27</v>
+        <v>36.01</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>36.13</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="85">
@@ -7592,19 +7592,19 @@
         <v>-2.52</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-5.42</v>
+        <v>-5.53</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.07</v>
+        <v>-4.97</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.29</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-1.35</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>1.12</v>
@@ -7844,22 +7844,22 @@
         <v>60.87</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>116.92</v>
+        <v>116.57</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>50.82</v>
+        <v>102.39</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>34.12</v>
+        <v>34.09</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>34.33</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>34.66</v>
+        <v>34.62</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>34.4</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="90">
@@ -8012,22 +8012,22 @@
         <v>-1.7</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-3.86</v>
+        <v>-4.08</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.78</v>
+        <v>-4.1</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.12</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-14T07:10:04</t>
+          <t>CreatedAt: 2026-03-14T08:09:53</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -677,49 +677,49 @@
         <v>49.36</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>48.25</v>
+        <v>46.97</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>34.19</v>
+        <v>50.03</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>34.22</v>
+        <v>34.18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>34.08</v>
       </c>
       <c r="P4" s="3" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>34.05</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>34.08</v>
-      </c>
       <c r="R4" s="3" t="n">
-        <v>35.29</v>
+        <v>34.67</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.33</v>
+        <v>43.01</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>45.42</v>
+        <v>44.16</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>52.18</v>
+        <v>52.13</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>50.78</v>
+        <v>48.98</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>45.37</v>
+        <v>45.15</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>35.41</v>
+        <v>35.4</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>35.41</v>
+        <v>35.44</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>45.82</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="5">
@@ -845,10 +845,10 @@
         <v>-0.79</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.75</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>-0.82</v>
@@ -857,34 +857,34 @@
         <v>-0.75</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-0.68</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1</v>
+        <v>-1.03</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.32</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.82</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.57</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.06</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-1.19</v>
@@ -1097,49 +1097,49 @@
         <v>52.57</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>51.18</v>
+        <v>49.77</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>36.28</v>
+        <v>53.06</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>36.05</v>
+        <v>36.01</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>35.83</v>
+        <v>35.86</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>35.73</v>
+        <v>35.69</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>35.69</v>
+        <v>35.66</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>37.03</v>
+        <v>36.38</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>44.59</v>
+        <v>44.3</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>46.5</v>
+        <v>45.21</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>53.1</v>
+        <v>53.05</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>52.19</v>
+        <v>50.35</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>46.18</v>
+        <v>45.91</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>36.7</v>
+        <v>36.69</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>37.25</v>
+        <v>37.29</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>48.62</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="10">
@@ -1265,46 +1265,46 @@
         <v>2.42</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>1.01</v>
       </c>
       <c r="O11" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0.96</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0.93</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>-0.9</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.73</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>0.37</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1.6</v>
@@ -1517,49 +1517,49 @@
         <v>173.95</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>51.18</v>
+        <v>49.82</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36.28</v>
+        <v>132.43</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>36.05</v>
+        <v>36.01</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>35.87</v>
+        <v>35.86</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>35.73</v>
+        <v>35.69</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>35.69</v>
+        <v>35.7</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>37.07</v>
+        <v>36.42</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>44.64</v>
+        <v>44.3</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>46.5</v>
+        <v>45.21</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>53.1</v>
+        <v>53.05</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>52.19</v>
+        <v>50.35</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>46.18</v>
+        <v>45.91</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>36.7</v>
+        <v>36.73</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>37.29</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>48.67</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="15">
@@ -1604,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0</v>
+        <v>79.31</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
@@ -1685,10 +1685,10 @@
         <v>2.47</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.27</v>
+        <v>2.34</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1.01</v>
@@ -1697,31 +1697,31 @@
         <v>1.04</v>
       </c>
       <c r="P16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="Q16" s="3" t="n">
-        <v>0.93</v>
-      </c>
       <c r="R16" s="3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>-0.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.73</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>0.78</v>
@@ -1937,49 +1937,49 @@
         <v>49.75</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>48.54</v>
+        <v>47.25</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>34.39</v>
+        <v>50.33</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>34.39</v>
+        <v>34.38</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>34.31</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>34.29</v>
+        <v>34.21</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>34.29</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>35.49</v>
+        <v>34.88</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>43.54</v>
+        <v>43.22</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>45.46</v>
+        <v>44.25</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>52.08</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>50.73</v>
+        <v>48.94</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>45.29</v>
+        <v>45.06</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>35.31</v>
+        <v>35.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>35.34</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>45.73</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="20">
@@ -2105,13 +2105,13 @@
         <v>-0.4</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="M21" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N21" s="3" t="n">
         <v>-0.62</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>-0.65</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>-0.51</v>
@@ -2120,25 +2120,25 @@
         <v>-0.48</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.82</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.93</v>
+        <v>-1.87</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.61</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.58</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>-1.02</v>
@@ -2357,49 +2357,49 @@
         <v>49.75</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>48.54</v>
+        <v>47.25</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>34.39</v>
+        <v>50.33</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>34.39</v>
+        <v>34.38</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>34.31</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>34.29</v>
+        <v>34.21</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>34.29</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>35.49</v>
+        <v>34.88</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>43.54</v>
+        <v>43.22</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>45.46</v>
+        <v>44.25</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>52.08</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>50.73</v>
+        <v>48.94</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>45.29</v>
+        <v>45.06</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>35.31</v>
+        <v>35.3</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>35.34</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>45.73</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="25">
@@ -2525,13 +2525,13 @@
         <v>-0.4</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="M26" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>-0.62</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>-0.65</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>-0.51</v>
@@ -2540,25 +2540,25 @@
         <v>-0.48</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.82</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.93</v>
+        <v>-1.87</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.61</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.58</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>-1.02</v>
@@ -2777,49 +2777,49 @@
         <v>50.05</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>48.78</v>
+        <v>47.48</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.56</v>
+        <v>50.53</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>34.56</v>
+        <v>34.51</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>34.48</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>34.49</v>
+        <v>34.45</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>34.49</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>35.67</v>
+        <v>35.02</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>43.71</v>
+        <v>43.39</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>45.46</v>
+        <v>44.25</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>51.88</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>50.58</v>
+        <v>48.75</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>45.15</v>
+        <v>44.85</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>35.1</v>
+        <v>35.06</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>35.14</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>45.46</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="30">
@@ -2945,10 +2945,10 @@
         <v>-0.1</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0.48</v>
@@ -2957,37 +2957,37 @@
         <v>-0.34</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.39</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.65</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.08</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.87</v>
+        <v>-1.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.79</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.26</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>-1.37</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="32">
@@ -3197,49 +3197,49 @@
         <v>175.02</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>51.39</v>
+        <v>50.03</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>36.77</v>
+        <v>132.48</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>36.65</v>
+        <v>36.57</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>36.28</v>
+        <v>36.31</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>36.18</v>
+        <v>36.13</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>36.07</v>
+        <v>36.03</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>37.49</v>
+        <v>36.88</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>45.05</v>
+        <v>44.71</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.11</v>
+        <v>45.81</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>53.84</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>53.25</v>
+        <v>51.32</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>46.73</v>
+        <v>46.45</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>37.27</v>
+        <v>37.25</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>38.27</v>
+        <v>38.31</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>50.17</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="35">
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>79.31</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3365,46 +3365,46 @@
         <v>3.54</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.77</v>
+        <v>2.39</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O36" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>1.45</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>1.41</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>0.93</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>3.16</v>
@@ -3617,49 +3617,49 @@
         <v>49.36</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>48.25</v>
+        <v>46.97</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>34.19</v>
+        <v>50.03</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>34.22</v>
+        <v>34.18</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>34.08</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>34.05</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>34.08</v>
-      </c>
       <c r="R39" s="3" t="n">
-        <v>35.29</v>
+        <v>34.67</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>43.33</v>
+        <v>43.01</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>45.42</v>
+        <v>44.16</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>52.18</v>
+        <v>52.13</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>50.78</v>
+        <v>48.98</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>45.37</v>
+        <v>45.15</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>35.41</v>
+        <v>35.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>35.41</v>
+        <v>35.44</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>45.82</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="40">
@@ -3785,10 +3785,10 @@
         <v>-0.79</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.75</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>-0.82</v>
@@ -3797,34 +3797,34 @@
         <v>-0.75</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>-0.68</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1</v>
+        <v>-1.03</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.32</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.82</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.57</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.06</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-1.19</v>
@@ -4037,49 +4037,49 @@
         <v>50.25</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>48.98</v>
+        <v>47.67</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>34.76</v>
+        <v>50.58</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>34.73</v>
+        <v>34.68</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>34.41</v>
+        <v>34.45</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>34.46</v>
+        <v>34.38</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>34.56</v>
+        <v>34.52</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>35.81</v>
+        <v>35.23</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>43.93</v>
+        <v>43.65</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>46.36</v>
+        <v>45.08</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>53.47</v>
+        <v>53.42</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>51.99</v>
+        <v>50.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>46.36</v>
+        <v>46.13</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>36.33</v>
+        <v>36.32</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>36.25</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>47.01</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="45">
@@ -4205,16 +4205,16 @@
         <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>-0.31</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>-0.31</v>
@@ -4226,19 +4226,19 @@
         <v>-0.18</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>-0.53</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.45</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.51</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0</v>
@@ -4457,49 +4457,49 @@
         <v>47.54</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>46.21</v>
+        <v>45.06</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>33.09</v>
+        <v>48.04</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>32.96</v>
+        <v>32.92</v>
       </c>
       <c r="O49" s="3" t="n">
         <v>32.82</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>34.39</v>
+        <v>34.31</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>34.32</v>
+        <v>34.29</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>33.92</v>
+        <v>33.37</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>41.97</v>
+        <v>41.7</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>44.42</v>
+        <v>43.2</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>51.24</v>
+        <v>51.19</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>49.62</v>
+        <v>47.82</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>44.43</v>
+        <v>44.21</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>34.37</v>
+        <v>34.36</v>
       </c>
       <c r="Y49" s="3" t="n">
         <v>36</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="50">
@@ -4625,13 +4625,13 @@
         <v>-2.61</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.77</v>
+        <v>-2.57</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.74</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-2.08</v>
+        <v>-2.07</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>-2</v>
@@ -4643,22 +4643,22 @@
         <v>-0.45</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.04</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.34</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.29</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.77</v>
+        <v>-2.76</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-2.83</v>
+        <v>-2.73</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.4</v>
+        <v>-2.43</v>
       </c>
       <c r="X51" s="3" t="n">
         <v>-1.96</v>
@@ -4667,7 +4667,7 @@
         <v>-0.5</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="52">
@@ -4877,49 +4877,49 @@
         <v>50.76</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>48.93</v>
+        <v>47.87</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>34.83</v>
+        <v>50.58</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>34.69</v>
+        <v>34.62</v>
       </c>
       <c r="O54" s="3" t="n">
         <v>34.14</v>
       </c>
       <c r="P54" s="3" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="Q54" s="3" t="n">
         <v>33.05</v>
       </c>
-      <c r="Q54" s="3" t="n">
-        <v>33.08</v>
-      </c>
       <c r="R54" s="3" t="n">
-        <v>34.21</v>
+        <v>33.65</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>42.54</v>
+        <v>42.26</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>45.24</v>
+        <v>43.99</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>52.28</v>
+        <v>52.23</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>50.48</v>
+        <v>48.65</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>44.94</v>
+        <v>44.76</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>36.33</v>
+        <v>36.32</v>
       </c>
       <c r="Y54" s="3" t="n">
         <v>37.25</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>48.17</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="55">
@@ -5045,40 +5045,40 @@
         <v>0.61</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.24</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>-0.68</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.71</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>-1.69</v>
       </c>
       <c r="R56" s="3" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="S56" s="3" t="n">
         <v>-1.78</v>
       </c>
-      <c r="S56" s="3" t="n">
-        <v>-1.79</v>
-      </c>
       <c r="T56" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.5</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.97</v>
+        <v>-1.9</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.89</v>
+        <v>-1.88</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
         <v>0.75</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="57">
@@ -5297,49 +5297,49 @@
         <v>51.76</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>50.44</v>
+        <v>49.05</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>35.9</v>
+        <v>52.19</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>35.94</v>
+        <v>35.89</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>35.61</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>35.62</v>
+        <v>35.54</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>35.69</v>
+        <v>35.66</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>36.91</v>
+        <v>36.31</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>45.14</v>
+        <v>44.85</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>47.64</v>
+        <v>46.32</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>54.94</v>
+        <v>54.88</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>53.36</v>
+        <v>51.42</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>47.64</v>
+        <v>47.4</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>37.34</v>
+        <v>37.37</v>
       </c>
       <c r="Y59" s="3" t="n">
         <v>37.21</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>48.27</v>
+        <v>48.17</v>
       </c>
     </row>
     <row r="60">
@@ -5465,10 +5465,10 @@
         <v>1.6</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.9</v>
+        <v>1.41</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>0.9</v>
@@ -5483,31 +5483,31 @@
         <v>0.93</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="S61" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="U61" s="3" t="n">
         <v>0.93</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.71</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="62">
@@ -5717,49 +5717,49 @@
         <v>52.57</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>51.34</v>
+        <v>49.87</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>36.54</v>
+        <v>53.12</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>36.58</v>
+        <v>36.53</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>36.24</v>
       </c>
       <c r="P64" s="3" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="Q64" s="3" t="n">
         <v>36.25</v>
       </c>
-      <c r="Q64" s="3" t="n">
-        <v>36.29</v>
-      </c>
       <c r="R64" s="3" t="n">
-        <v>37.57</v>
+        <v>36.95</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>45.93</v>
+        <v>45.64</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>48.53</v>
+        <v>47.18</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>55.96</v>
+        <v>55.91</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>54.36</v>
+        <v>52.38</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>48.42</v>
+        <v>48.23</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>37.97</v>
+        <v>38</v>
       </c>
       <c r="Y64" s="3" t="n">
         <v>37.79</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>48.97</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="65">
@@ -5885,49 +5885,49 @@
         <v>2.42</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="M66" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N66" s="3" t="n">
         <v>1.53</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>1.54</v>
       </c>
       <c r="O66" s="3" t="n">
         <v>1.41</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q66" s="3" t="n">
         <v>1.52</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="U66" s="3" t="n">
         <v>1.96</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>1.28</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="67">
@@ -6137,49 +6137,49 @@
         <v>53.18</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>51.83</v>
+        <v>50.4</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>36.93</v>
+        <v>53.68</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>36.96</v>
+        <v>36.92</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>36.62</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>36.63</v>
+        <v>36.55</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>36.71</v>
+        <v>36.68</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>37.93</v>
+        <v>37.34</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>46.03</v>
+        <v>45.73</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>48.58</v>
+        <v>47.23</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>56.02</v>
+        <v>55.97</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>54.41</v>
+        <v>52.44</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>48.57</v>
+        <v>48.33</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>38.37</v>
+        <v>38.36</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>38.03</v>
+        <v>38.07</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>49.33</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="70">
@@ -6305,10 +6305,10 @@
         <v>3.03</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>1.92</v>
@@ -6317,37 +6317,37 @@
         <v>1.79</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>2.03</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="72">
@@ -6557,49 +6557,49 @@
         <v>51.49</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>50.23</v>
+        <v>48.8</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>35.76</v>
+        <v>51.98</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>35.79</v>
+        <v>35.75</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>35.46</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>35.62</v>
+        <v>35.54</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>35.59</v>
+        <v>35.55</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>36.76</v>
+        <v>36.16</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>44.95</v>
+        <v>44.66</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>47.49</v>
+        <v>46.18</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>54.83</v>
+        <v>54.77</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>53.2</v>
+        <v>51.27</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>47.44</v>
+        <v>47.25</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>37.15</v>
+        <v>37.18</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>37.06</v>
+        <v>37.1</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>48.22</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="75">
@@ -6725,10 +6725,10 @@
         <v>1.34</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>0.75</v>
@@ -6743,31 +6743,31 @@
         <v>0.82</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="S76" s="3" t="n">
         <v>0.63</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>0.82</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="77">
@@ -6977,49 +6977,49 @@
         <v>50.15</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>48.98</v>
+        <v>47.63</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>35.01</v>
+        <v>50.78</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>35.04</v>
+        <v>35</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>34.83</v>
+        <v>34.82</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>34.77</v>
+        <v>34.69</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>34.77</v>
+        <v>34.73</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>35.99</v>
+        <v>35.4</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>44.33</v>
+        <v>44.04</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>46.78</v>
+        <v>45.48</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>54</v>
+        <v>53.95</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>52.45</v>
+        <v>50.55</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>46.83</v>
+        <v>46.64</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>36.33</v>
+        <v>36.32</v>
       </c>
       <c r="Y79" s="3" t="n">
         <v>36.51</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>47.01</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="80">
@@ -7397,49 +7397,49 @@
         <v>50.81</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>48.83</v>
+        <v>47.77</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34.63</v>
+        <v>50.23</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>34.42</v>
+        <v>34.34</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>33.81</v>
+        <v>33.84</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>31.95</v>
+        <v>31.88</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>33.14</v>
+        <v>32.57</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>41.39</v>
+        <v>41.12</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>44.34</v>
+        <v>43.11</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>51.09</v>
+        <v>51.04</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>49.02</v>
+        <v>47.2</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>43.64</v>
+        <v>43.47</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>36.19</v>
+        <v>36.18</v>
       </c>
       <c r="Y84" s="3" t="n">
         <v>37.14</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>48.02</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="85">
@@ -7565,16 +7565,16 @@
         <v>0.66</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.14</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.55</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.98</v>
       </c>
       <c r="P86" s="3" t="n">
         <v>-2.81</v>
@@ -7583,22 +7583,22 @@
         <v>-2.75</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-2.85</v>
+        <v>-2.83</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.92</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.44</v>
+        <v>-2.37</v>
       </c>
       <c r="U86" s="3" t="n">
         <v>-2.91</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-3.43</v>
+        <v>-3.35</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.19</v>
+        <v>-3.17</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-0.14</v>
@@ -7817,49 +7817,49 @@
         <v>50.05</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>48.78</v>
+        <v>47.48</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>34.56</v>
+        <v>50.53</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>34.56</v>
+        <v>34.51</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>34.48</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>34.49</v>
+        <v>34.45</v>
       </c>
       <c r="Q89" s="3" t="n">
         <v>34.49</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>35.67</v>
+        <v>35.02</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>43.71</v>
+        <v>43.39</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>45.42</v>
+        <v>44.25</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>51.88</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>50.58</v>
+        <v>48.75</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>45.15</v>
+        <v>44.85</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>35.1</v>
+        <v>35.06</v>
       </c>
       <c r="Y89" s="3" t="n">
         <v>35.14</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>45.46</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="90">
@@ -7985,10 +7985,10 @@
         <v>-0.1</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>-0.48</v>
@@ -7997,37 +7997,37 @@
         <v>-0.34</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.39</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.65</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.24</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.08</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.87</v>
+        <v>-1.8</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.79</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.26</v>
       </c>
       <c r="Y91" s="3" t="n">
         <v>-1.37</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-15T11:09:43</t>
+          <t>CreatedAt: 2026-03-15T12:09:33</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -689,37 +689,37 @@
         <v>51.08</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>35</v>
+        <v>34.35</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>29.69</v>
+        <v>34.08</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>14.36</v>
+        <v>14.31</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>27.48</v>
+        <v>27.24</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>30.02</v>
+        <v>33.75</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>33.63</v>
+        <v>35.09</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>36.28</v>
+        <v>49.71</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>33.53</v>
+        <v>33.56</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>27.39</v>
+        <v>27.42</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>33.92</v>
+        <v>33.93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>34.85</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="5">
@@ -857,37 +857,37 @@
         <v>-1.33</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.93</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.78</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.51</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.76</v>
+        <v>-1.09</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.54</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>-0.33</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="7">
@@ -1109,37 +1109,37 @@
         <v>53.59</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>36.56</v>
+        <v>35.93</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>31.02</v>
+        <v>35.68</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>14.99</v>
+        <v>14.94</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>28.4</v>
+        <v>28.21</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>30.94</v>
+        <v>34.78</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>34.71</v>
+        <v>36.15</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>37.57</v>
+        <v>51.47</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>34.65</v>
+        <v>34.69</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>28.46</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>35.75</v>
+        <v>35.76</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>36.55</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="10">
@@ -1277,37 +1277,37 @@
         <v>1.18</v>
       </c>
       <c r="P11" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>0.59</v>
       </c>
-      <c r="Q11" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>0.62</v>
-      </c>
       <c r="X11" s="3" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -1529,37 +1529,37 @@
         <v>53.64</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>88.53</v>
+        <v>91</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>31.02</v>
+        <v>102.2</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>15</v>
+        <v>14.94</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>149.08</v>
+        <v>149.04</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>30.94</v>
+        <v>34.81</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>34.71</v>
+        <v>36.19</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>37.61</v>
+        <v>160.44</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>34.65</v>
+        <v>34.69</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.46</v>
+        <v>28.49</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>35.75</v>
+        <v>35.76</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>36.55</v>
+        <v>147.44</v>
       </c>
     </row>
     <row r="15">
@@ -1613,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>51.93</v>
+        <v>55.04</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0</v>
+        <v>66.48</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>120.68</v>
+        <v>120.83</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>108.92</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -1697,37 +1697,37 @@
         <v>1.23</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>0.74</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -1949,37 +1949,37 @@
         <v>50.93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>34.86</v>
+        <v>34.22</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>29.63</v>
+        <v>34.05</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>14.36</v>
+        <v>14.3</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>27.48</v>
+        <v>27.24</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>30.08</v>
+        <v>33.82</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>33.69</v>
+        <v>35.13</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>36.39</v>
+        <v>49.85</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>33.63</v>
+        <v>33.66</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>27.47</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>33.95</v>
+        <v>33.96</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>34.98</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="20">
@@ -2117,37 +2117,37 @@
         <v>-1.48</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.06</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.82</v>
       </c>
       <c r="R21" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>-0.27</v>
       </c>
-      <c r="S21" s="3" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>-0.25</v>
-      </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="22">
@@ -2369,37 +2369,37 @@
         <v>50.93</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>34.86</v>
+        <v>34.22</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>29.63</v>
+        <v>34.05</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.36</v>
+        <v>14.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>27.48</v>
+        <v>27.24</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>30.08</v>
+        <v>33.82</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>33.69</v>
+        <v>35.13</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>36.39</v>
+        <v>49.85</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>33.63</v>
+        <v>33.66</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>27.47</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>33.95</v>
+        <v>33.96</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>34.98</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="25">
@@ -2537,37 +2537,37 @@
         <v>-1.48</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.06</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.82</v>
       </c>
       <c r="R26" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>-0.27</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>-0.25</v>
-      </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="27">
@@ -2789,37 +2789,37 @@
         <v>50.63</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>34.63</v>
+        <v>33.99</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>29.49</v>
+        <v>33.95</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>14.3</v>
+        <v>14.24</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>27.45</v>
+        <v>27.21</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>30.11</v>
+        <v>33.82</v>
       </c>
       <c r="U29" s="3" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>33.76</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>33.73</v>
-      </c>
       <c r="X29" s="3" t="n">
-        <v>27.53</v>
+        <v>27.55</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>33.92</v>
+        <v>33.96</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>35.16</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="30">
@@ -2957,28 +2957,28 @@
         <v>-1.77</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.29</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.92</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.3</v>
       </c>
       <c r="S31" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="T31" s="3" t="n">
         <v>-0.44</v>
       </c>
-      <c r="T31" s="3" t="n">
-        <v>-0.36</v>
-      </c>
       <c r="U31" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.77</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.85</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>-0.19</v>
@@ -2987,7 +2987,7 @@
         <v>-0.44</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="32">
@@ -3209,37 +3209,37 @@
         <v>53.64</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>88.42</v>
+        <v>91</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>31.24</v>
+        <v>87</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>15.13</v>
+        <v>15.05</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>149.05</v>
+        <v>149.04</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>30.81</v>
+        <v>34.6</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>34.54</v>
+        <v>36.12</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>37.72</v>
+        <v>160.59</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>34.48</v>
+        <v>34.51</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>28.4</v>
+        <v>28.43</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>36.17</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>36.82</v>
+        <v>147.57</v>
       </c>
     </row>
     <row r="35">
@@ -3293,16 +3293,16 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>51.93</v>
+        <v>55.04</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>51.53</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>120.68</v>
+        <v>120.83</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>108.92</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
@@ -3377,37 +3377,37 @@
         <v>1.23</v>
       </c>
       <c r="P36" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="S36" s="3" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="37">
@@ -3629,37 +3629,37 @@
         <v>51.08</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>35</v>
+        <v>34.35</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.69</v>
+        <v>34.08</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>14.36</v>
+        <v>14.31</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>27.48</v>
+        <v>27.24</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>30.02</v>
+        <v>33.75</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>33.63</v>
+        <v>35.09</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>36.28</v>
+        <v>49.71</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>33.53</v>
+        <v>33.56</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.39</v>
+        <v>27.42</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>33.92</v>
+        <v>33.93</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>34.85</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="40">
@@ -3797,37 +3797,37 @@
         <v>-1.33</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.93</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.78</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.51</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.76</v>
+        <v>-1.09</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.54</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>-0.33</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="42">
@@ -4049,37 +4049,37 @@
         <v>52.41</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>35.87</v>
+        <v>35.21</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.31</v>
+        <v>34.66</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>14.6</v>
+        <v>14.53</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>28</v>
+        <v>27.79</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>30.66</v>
+        <v>34.46</v>
       </c>
       <c r="U44" s="3" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="Y44" s="3" t="n">
         <v>34.61</v>
       </c>
-      <c r="V44" s="3" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>34.57</v>
-      </c>
       <c r="Z44" s="3" t="n">
-        <v>35.37</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="45">
@@ -4217,25 +4217,25 @@
         <v>0</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>-0.21</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>0.11</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0.1</v>
@@ -4247,7 +4247,7 @@
         <v>0.21</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="47">
@@ -4469,37 +4469,37 @@
         <v>54.59</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>37.09</v>
+        <v>36.41</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>31.47</v>
+        <v>35.87</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>27.78</v>
+        <v>27.54</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>28.94</v>
+        <v>32.53</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>34.4</v>
+        <v>35.9</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>37.3</v>
+        <v>51.11</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>34.1</v>
+        <v>34.13</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>27.47</v>
+        <v>27.5</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>35.49</v>
+        <v>35.54</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>36.36</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="50">
@@ -4637,28 +4637,28 @@
         <v>2.18</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.72</v>
       </c>
       <c r="U51" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="X51" s="3" t="n">
         <v>-0.25</v>
@@ -4667,7 +4667,7 @@
         <v>1.14</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.31</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="52">
@@ -4889,37 +4889,37 @@
         <v>52.46</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>35.76</v>
+        <v>35.24</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>30.58</v>
+        <v>33.82</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>14.57</v>
+        <v>14.04</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>26.87</v>
+        <v>26.66</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>29.27</v>
+        <v>32.91</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>33.27</v>
+        <v>35.83</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>35.72</v>
+        <v>50.5</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>34</v>
+        <v>34.06</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>27.8</v>
+        <v>27.83</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>34.99</v>
+        <v>35.03</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>35.81</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="55">
@@ -5057,25 +5057,25 @@
         <v>0.05</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.06</v>
+        <v>-1.05</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.51</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.01</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.35</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.2</v>
+        <v>-0.14</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.32</v>
+        <v>-0.3</v>
       </c>
       <c r="W56" s="3" t="n">
         <v>-0.03</v>
@@ -5087,7 +5087,7 @@
         <v>0.63</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="57">
@@ -5309,37 +5309,37 @@
         <v>54.2</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>37.09</v>
+        <v>36.41</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>31.4</v>
+        <v>35.87</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>15.1</v>
+        <v>15.01</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>28.84</v>
+        <v>28.65</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>31.58</v>
+        <v>35.5</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>35.65</v>
+        <v>37.2</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>38.31</v>
+        <v>52.53</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>35.16</v>
+        <v>35.19</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>28.69</v>
+        <v>28.72</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>35.57</v>
+        <v>35.61</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>36.36</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="60">
@@ -5477,28 +5477,28 @@
         <v>1.79</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0.47</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>0.98</v>
@@ -5507,7 +5507,7 @@
         <v>1.21</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.31</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="62">
@@ -5729,37 +5729,37 @@
         <v>55.11</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>37.75</v>
+        <v>37.02</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>31.96</v>
+        <v>36.51</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>15.35</v>
+        <v>15.26</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>29.36</v>
+        <v>29.16</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>32.15</v>
+        <v>36.14</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>36.32</v>
+        <v>37.9</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>38.99</v>
+        <v>53.47</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>35.75</v>
+        <v>35.78</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>29.12</v>
+        <v>29.14</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.09</v>
+        <v>36.14</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>36.9</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="65">
@@ -5897,28 +5897,28 @@
         <v>2.7</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0.72</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>1.4</v>
@@ -5927,7 +5927,7 @@
         <v>1.73</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.84</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="67">
@@ -6149,37 +6149,37 @@
         <v>55.75</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>38.15</v>
+        <v>37.41</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>32.3</v>
+        <v>36.89</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>15.53</v>
+        <v>15.44</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>29.64</v>
+        <v>29.41</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>32.42</v>
+        <v>36.44</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>36.63</v>
+        <v>38.23</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>39.37</v>
+        <v>53.99</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>36.13</v>
+        <v>36.16</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>29.46</v>
+        <v>29.49</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>36.55</v>
+        <v>36.6</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>37.37</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="70">
@@ -6317,37 +6317,37 @@
         <v>3.35</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>1.74</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.32</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="72">
@@ -6569,37 +6569,37 @@
         <v>54.2</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>37.09</v>
+        <v>36.37</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>31.31</v>
+        <v>35.76</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>15.02</v>
+        <v>14.93</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>28.73</v>
+        <v>28.5</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>31.38</v>
+        <v>35.28</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>35.54</v>
+        <v>37.05</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>38.15</v>
+        <v>52.32</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>34.97</v>
+        <v>35.04</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>28.52</v>
+        <v>28.54</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>35.38</v>
+        <v>35.43</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>36.29</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="75">
@@ -6737,10 +6737,10 @@
         <v>1.79</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>0.39</v>
@@ -6749,16 +6749,16 @@
         <v>0.83</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.91</v>
+        <v>1.02</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>1.07</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>0.8</v>
@@ -6767,7 +6767,7 @@
         <v>1.03</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.23</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="77">
@@ -6989,37 +6989,37 @@
         <v>52.41</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>35.98</v>
+        <v>35.28</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>30.52</v>
+        <v>34.86</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>14.63</v>
+        <v>14.54</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>27.89</v>
+        <v>27.67</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>30.47</v>
+        <v>34.26</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>34.47</v>
+        <v>35.97</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>37.04</v>
+        <v>50.8</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>34.03</v>
+        <v>34.1</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>27.72</v>
+        <v>27.75</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>34.36</v>
+        <v>34.4</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>35.05</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="80">
@@ -7409,37 +7409,37 @@
         <v>52.83</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>36.05</v>
+        <v>35.49</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>30.74</v>
+        <v>33.11</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>14.66</v>
+        <v>13.74</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>26.29</v>
+        <v>26.06</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>28.53</v>
+        <v>32.08</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>32.52</v>
+        <v>35.97</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>34.91</v>
+        <v>50.7</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>34.17</v>
+        <v>34.24</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>27.77</v>
+        <v>27.8</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>34.88</v>
+        <v>34.93</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>35.73</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="85">
@@ -7577,25 +7577,25 @@
         <v>0.42</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.22</v>
+        <v>-1.75</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.8</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.62</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-1.94</v>
+        <v>-2.18</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-1.95</v>
+        <v>0</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.13</v>
+        <v>-0.1</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>0.14</v>
@@ -7607,7 +7607,7 @@
         <v>0.52</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="87">
@@ -7829,37 +7829,37 @@
         <v>50.63</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>34.63</v>
+        <v>33.96</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>29.49</v>
+        <v>33.95</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>14.3</v>
+        <v>14.24</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>27.45</v>
+        <v>27.21</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>30.11</v>
+        <v>33.82</v>
       </c>
       <c r="U89" s="3" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="W89" s="3" t="n">
         <v>33.76</v>
       </c>
-      <c r="V89" s="3" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="W89" s="3" t="n">
-        <v>33.73</v>
-      </c>
       <c r="X89" s="3" t="n">
-        <v>27.53</v>
+        <v>27.55</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.92</v>
+        <v>33.93</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>35.16</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="90">
@@ -7997,37 +7997,37 @@
         <v>-1.77</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.32</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.92</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.3</v>
       </c>
       <c r="S91" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="T91" s="3" t="n">
         <v>-0.44</v>
       </c>
-      <c r="T91" s="3" t="n">
-        <v>-0.36</v>
-      </c>
       <c r="U91" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.77</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.85</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>-0.19</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-15T12:09:33</t>
+          <t>CreatedAt: 2026-03-15T13:09:12</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -692,19 +692,19 @@
         <v>34.35</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>34.08</v>
+        <v>27.05</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>14.31</v>
+        <v>15.3</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>27.24</v>
+        <v>25</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>33.75</v>
+        <v>33.68</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>35.09</v>
+        <v>38.05</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>49.71</v>
@@ -713,13 +713,13 @@
         <v>33.56</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>27.42</v>
+        <v>26.67</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>33.93</v>
+        <v>34.98</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>14.72</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="5">
@@ -860,31 +860,31 @@
         <v>-0.93</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.65</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-1.09</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.12</v>
@@ -1112,34 +1112,34 @@
         <v>35.93</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>35.68</v>
+        <v>28.33</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>14.94</v>
+        <v>16.04</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>28.21</v>
+        <v>25.89</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>34.78</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>36.15</v>
+        <v>39.24</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>51.47</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>34.69</v>
+        <v>34.62</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.46</v>
+        <v>27.68</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>35.76</v>
+        <v>36.83</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>15.44</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="10">
@@ -1280,28 +1280,28 @@
         <v>0.65</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>0.67</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>1.36</v>
@@ -1535,31 +1535,31 @@
         <v>102.2</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.94</v>
+        <v>143.16</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>149.04</v>
+        <v>25.89</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>34.81</v>
+        <v>34.78</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>36.19</v>
+        <v>39.24</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>160.44</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>34.69</v>
+        <v>34.62</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.49</v>
+        <v>27.68</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>35.76</v>
+        <v>36.87</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>147.44</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="15">
@@ -1616,13 +1616,13 @@
         <v>55.04</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>66.48</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>127.12</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>108.92</v>
+        <v>108.97</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1700,31 +1700,31 @@
         <v>0.68</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>0.6</v>
@@ -1952,34 +1952,34 @@
         <v>34.22</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>34.05</v>
+        <v>27.03</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>27.24</v>
+        <v>25</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>33.82</v>
+        <v>33.75</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>35.13</v>
+        <v>38.12</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>49.85</v>
+        <v>49.8</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>33.66</v>
+        <v>33.63</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>27.47</v>
+        <v>26.72</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>33.96</v>
+        <v>35.01</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.78</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="20">
@@ -2120,22 +2120,22 @@
         <v>-1.06</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.68</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.31</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>-0.84</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>-0.44</v>
@@ -2144,7 +2144,7 @@
         <v>-0.27</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>-0.06</v>
@@ -2372,34 +2372,34 @@
         <v>34.22</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>34.05</v>
+        <v>27.03</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>27.24</v>
+        <v>25</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>33.82</v>
+        <v>33.75</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>35.13</v>
+        <v>38.12</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>49.85</v>
+        <v>49.8</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>33.66</v>
+        <v>33.63</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>27.47</v>
+        <v>26.72</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>33.96</v>
+        <v>35.01</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>14.78</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="25">
@@ -2540,22 +2540,22 @@
         <v>-1.06</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.68</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.31</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>-0.84</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>-0.44</v>
@@ -2564,7 +2564,7 @@
         <v>-0.27</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>-0.06</v>
@@ -2792,34 +2792,34 @@
         <v>33.99</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.95</v>
+        <v>26.9</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>14.24</v>
+        <v>15.27</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>27.21</v>
+        <v>25</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>33.82</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>35.2</v>
+        <v>38.16</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>49.95</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>33.76</v>
+        <v>33.73</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>27.55</v>
+        <v>26.78</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>33.96</v>
+        <v>34.98</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>14.82</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="30">
@@ -2960,19 +2960,19 @@
         <v>-1.29</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.42</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>-0.85</v>
@@ -2981,10 +2981,10 @@
         <v>-0.34</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.49</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>-0.01</v>
@@ -3215,31 +3215,31 @@
         <v>87</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>15.05</v>
+        <v>87</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>149.04</v>
+        <v>25.89</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>34.6</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>36.12</v>
+        <v>39.08</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>160.59</v>
+        <v>160.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>34.51</v>
+        <v>34.41</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>28.43</v>
+        <v>27.63</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>36.17</v>
+        <v>37.25</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>147.57</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="35">
@@ -3296,13 +3296,13 @@
         <v>55.04</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>51.53</v>
+        <v>58.73</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>108.92</v>
+        <v>108.97</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3380,34 +3380,34 @@
         <v>0.68</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="37">
@@ -3632,19 +3632,19 @@
         <v>34.35</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>34.08</v>
+        <v>27.05</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>14.31</v>
+        <v>15.3</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>27.24</v>
+        <v>25</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>33.75</v>
+        <v>33.68</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>35.09</v>
+        <v>38.05</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>49.71</v>
@@ -3653,13 +3653,13 @@
         <v>33.56</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.42</v>
+        <v>26.67</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>33.93</v>
+        <v>34.98</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>14.72</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="40">
@@ -3800,31 +3800,31 @@
         <v>-0.93</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.65</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.91</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-1.09</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.5</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.12</v>
@@ -4052,34 +4052,34 @@
         <v>35.21</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>34.66</v>
+        <v>27.62</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>14.53</v>
+        <v>15.58</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>27.79</v>
+        <v>25.5</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>34.46</v>
+        <v>34.43</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>36.08</v>
+        <v>39.08</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>51</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>34.2</v>
+        <v>34.17</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>27.91</v>
+        <v>27.15</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>34.61</v>
+        <v>35.68</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>14.97</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -4220,19 +4220,19 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.08</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.2</v>
@@ -4241,13 +4241,13 @@
         <v>0.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="47">
@@ -4472,34 +4472,34 @@
         <v>36.41</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>35.87</v>
+        <v>28.53</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>14.4</v>
+        <v>15.47</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>27.54</v>
+        <v>25.3</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>32.53</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>35.9</v>
+        <v>38.85</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>51.11</v>
+        <v>51.16</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>34.13</v>
+        <v>34.1</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>27.5</v>
+        <v>26.75</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>35.54</v>
+        <v>36.71</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>15.39</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="50">
@@ -4640,34 +4640,34 @@
         <v>1.13</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>-0.14</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.69</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4892,34 +4892,34 @@
         <v>35.24</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.82</v>
+        <v>26.84</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>14.04</v>
+        <v>15.04</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>26.66</v>
+        <v>24.49</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>32.91</v>
+        <v>32.87</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>35.83</v>
+        <v>38.77</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>50.5</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>34.06</v>
+        <v>34.03</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>27.83</v>
+        <v>27.07</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>35.03</v>
+        <v>36.12</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>15.17</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="55">
@@ -5060,19 +5060,19 @@
         <v>-0.04</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.86</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.57</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.93</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>-1.35</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.19</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>-0.3</v>
@@ -5084,7 +5084,7 @@
         <v>0.08</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="Z56" s="3" t="n">
         <v>0.33</v>
@@ -5312,34 +5312,34 @@
         <v>36.41</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>35.87</v>
+        <v>28.56</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>15.01</v>
+        <v>16.11</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>28.65</v>
+        <v>26.32</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>35.5</v>
+        <v>35.46</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>37.2</v>
+        <v>40.29</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>52.53</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>35.19</v>
+        <v>35.15</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>28.72</v>
+        <v>27.94</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>35.61</v>
+        <v>36.75</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>15.39</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="60">
@@ -5480,19 +5480,19 @@
         <v>1.13</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1.24</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1.73</v>
@@ -5501,13 +5501,13 @@
         <v>1.09</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -5732,34 +5732,34 @@
         <v>37.02</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>36.51</v>
+        <v>29.04</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>15.26</v>
+        <v>16.38</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>29.16</v>
+        <v>26.79</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>36.14</v>
+        <v>36.06</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>37.9</v>
+        <v>41.01</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>53.47</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>35.78</v>
+        <v>35.74</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>29.14</v>
+        <v>28.35</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.14</v>
+        <v>37.29</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>15.62</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="65">
@@ -5900,19 +5900,19 @@
         <v>1.74</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>2.67</v>
@@ -5921,10 +5921,10 @@
         <v>1.68</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>0.78</v>
@@ -6152,34 +6152,34 @@
         <v>37.41</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>36.89</v>
+        <v>29.38</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>15.44</v>
+        <v>16.55</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>29.41</v>
+        <v>27.05</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>36.44</v>
+        <v>36.41</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>38.23</v>
+        <v>41.41</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>53.99</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>36.16</v>
+        <v>36.12</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>29.49</v>
+        <v>28.68</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>36.6</v>
+        <v>37.77</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>15.82</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="70">
@@ -6320,19 +6320,19 @@
         <v>2.13</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>3.19</v>
@@ -6341,10 +6341,10 @@
         <v>2.06</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>0.98</v>
@@ -6572,34 +6572,34 @@
         <v>36.37</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>35.76</v>
+        <v>28.47</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>14.93</v>
+        <v>16.03</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>28.5</v>
+        <v>26.18</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>37.05</v>
+        <v>40.13</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>52.32</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>35.04</v>
+        <v>35.01</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>28.54</v>
+        <v>27.77</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>35.43</v>
+        <v>36.68</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>15.36</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="75">
@@ -6740,19 +6740,19 @@
         <v>1.09</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>1.02</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>1.52</v>
@@ -6761,10 +6761,10 @@
         <v>0.95</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>0.52</v>
@@ -6992,34 +6992,34 @@
         <v>35.28</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>34.86</v>
+        <v>27.7</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>14.54</v>
+        <v>15.61</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>27.67</v>
+        <v>25.42</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>34.26</v>
+        <v>34.22</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>35.97</v>
+        <v>38.96</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>50.8</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>34.1</v>
+        <v>34.06</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>27.75</v>
+        <v>26.99</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>34.4</v>
+        <v>35.47</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>14.84</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="80">
@@ -7412,34 +7412,34 @@
         <v>35.49</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>33.11</v>
+        <v>26.26</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>13.74</v>
+        <v>14.73</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>26.06</v>
+        <v>23.94</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>32.08</v>
+        <v>32.04</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>35.97</v>
+        <v>38.92</v>
       </c>
       <c r="V84" s="3" t="n">
         <v>50.7</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>34.24</v>
+        <v>34.2</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>27.8</v>
+        <v>27.05</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>34.93</v>
+        <v>36.01</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>15.14</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="85">
@@ -7580,19 +7580,19 @@
         <v>0.21</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.44</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.88</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.48</v>
       </c>
       <c r="T86" s="3" t="n">
         <v>-2.18</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="V86" s="3" t="n">
         <v>-0.1</v>
@@ -7601,10 +7601,10 @@
         <v>0.14</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>0.3</v>
@@ -7832,34 +7832,34 @@
         <v>33.96</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>33.95</v>
+        <v>26.9</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>14.24</v>
+        <v>15.27</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>27.21</v>
+        <v>25</v>
       </c>
       <c r="T89" s="3" t="n">
         <v>33.82</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>35.2</v>
+        <v>38.16</v>
       </c>
       <c r="V89" s="3" t="n">
         <v>49.95</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>33.76</v>
+        <v>33.73</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>27.55</v>
+        <v>26.78</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.93</v>
+        <v>34.98</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>14.82</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="90">
@@ -8000,19 +8000,19 @@
         <v>-1.32</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.42</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="V91" s="3" t="n">
         <v>-0.85</v>
@@ -8021,10 +8021,10 @@
         <v>-0.34</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="Z91" s="3" t="n">
         <v>-0.01</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-16T14:08:43</t>
+          <t>CreatedAt: 2026-03-16T15:08:22</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -698,28 +698,28 @@
         <v>38.37</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>39.64</v>
+        <v>45.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>33.68</v>
+        <v>45.24</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>35.29</v>
+        <v>35.25</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>35.19</v>
+        <v>35.22</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>35.12</v>
+        <v>35.05</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.65</v>
+        <v>33.69</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>28.25</v>
+        <v>25.84</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>24.75</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="5">
@@ -866,25 +866,25 @@
         <v>-0.5</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.32</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.17</v>
@@ -1118,28 +1118,28 @@
         <v>39.82</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>40.84</v>
+        <v>46.99</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>34.32</v>
+        <v>46.11</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>36.07</v>
+        <v>36.03</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>36.03</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>36.04</v>
+        <v>35.97</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>34.55</v>
+        <v>34.54</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>29.5</v>
+        <v>26.96</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>26.12</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="10">
@@ -1286,28 +1286,28 @@
         <v>0.96</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12">
@@ -1538,28 +1538,28 @@
         <v>39.82</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>40.84</v>
+        <v>46.99</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>34.32</v>
+        <v>46.15</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>36.07</v>
+        <v>36.03</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>36.03</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>36.04</v>
+        <v>35.97</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>34.55</v>
+        <v>34.58</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>29.53</v>
+        <v>26.96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>26.15</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="15">
@@ -1706,28 +1706,28 @@
         <v>0.96</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
@@ -1958,28 +1958,28 @@
         <v>38.52</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>39.75</v>
+        <v>45.64</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>33.71</v>
+        <v>45.37</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>35.29</v>
+        <v>35.25</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>35.22</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>35.15</v>
+        <v>35.08</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>33.75</v>
+        <v>33.79</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>28.36</v>
+        <v>25.95</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>24.87</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="20">
@@ -2126,28 +2126,28 @@
         <v>-0.35</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.18</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V21" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W21" s="3" t="n">
         <v>-0.6</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
       <c r="X21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="22">
@@ -2378,28 +2378,28 @@
         <v>38.52</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>39.75</v>
+        <v>45.64</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>33.71</v>
+        <v>45.37</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>35.29</v>
+        <v>35.25</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>35.22</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>35.15</v>
+        <v>35.08</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>33.75</v>
+        <v>33.79</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>28.36</v>
+        <v>25.95</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>24.87</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="25">
@@ -2546,28 +2546,28 @@
         <v>-0.35</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.18</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V26" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>-0.6</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
       <c r="X26" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="27">
@@ -2798,28 +2798,28 @@
         <v>38.67</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>39.83</v>
+        <v>45.77</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>33.74</v>
+        <v>45.51</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>35.29</v>
+        <v>35.25</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>35.22</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>35.22</v>
+        <v>35.15</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>33.85</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>28.47</v>
+        <v>26.05</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>25</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="30">
@@ -2966,28 +2966,28 @@
         <v>-0.19</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="U31" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>-0.53</v>
       </c>
-      <c r="V31" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>-0.49</v>
-      </c>
       <c r="X31" s="3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="32">
@@ -3218,28 +3218,28 @@
         <v>39.66</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>40.52</v>
+        <v>46.61</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>33.71</v>
+        <v>45.28</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>35.64</v>
+        <v>35.57</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>36</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>35.78</v>
+        <v>35.71</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>34.09</v>
+        <v>34.13</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>29.38</v>
+        <v>26.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>26.57</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="35">
@@ -3386,28 +3386,28 @@
         <v>0.79</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.27</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.25</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="37">
@@ -3638,28 +3638,28 @@
         <v>38.37</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>39.64</v>
+        <v>45.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>33.68</v>
+        <v>45.24</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>35.29</v>
+        <v>35.25</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>35.19</v>
+        <v>35.22</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>35.12</v>
+        <v>35.05</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>33.65</v>
+        <v>33.69</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>28.25</v>
+        <v>25.84</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>24.75</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="40">
@@ -3806,25 +3806,25 @@
         <v>-0.5</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.32</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.17</v>
@@ -4058,28 +4058,28 @@
         <v>38.75</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>40.27</v>
+        <v>46.09</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>34.39</v>
+        <v>45.92</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>36.11</v>
+        <v>36.07</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>36.03</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>35.93</v>
+        <v>35.82</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>34.13</v>
+        <v>34.16</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>28.73</v>
+        <v>26.29</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>25.28</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="45">
@@ -4226,28 +4226,28 @@
         <v>-0.12</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="T46" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.27</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="47">
@@ -4478,28 +4478,28 @@
         <v>37.77</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>39.36</v>
+        <v>44.97</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>33.58</v>
+        <v>44.7</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>35.32</v>
+        <v>35.25</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>35.22</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>34.98</v>
+        <v>34.91</v>
       </c>
       <c r="X49" s="3" t="n">
         <v>32.87</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>28.88</v>
+        <v>26.39</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>25.53</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="50">
@@ -4646,28 +4646,28 @@
         <v>-1.1</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.79</v>
+        <v>-1.03</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.85</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.77</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.05</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="52">
@@ -4898,28 +4898,28 @@
         <v>38.18</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>38.06</v>
+        <v>43.85</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>32.52</v>
+        <v>43.34</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>34.31</v>
+        <v>34.28</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>34.31</v>
+        <v>34.28</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>35.25</v>
+        <v>35.15</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.26</v>
+        <v>33.29</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>28.28</v>
+        <v>25.84</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>24.9</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="55">
@@ -5066,28 +5066,28 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.15</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.21</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.54</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.58</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.53</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="57">
@@ -5318,28 +5318,28 @@
         <v>39.9</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>41.39</v>
+        <v>47.38</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>35.31</v>
+        <v>47.06</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>37.04</v>
+        <v>37</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>37</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>36.86</v>
+        <v>36.78</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>34.9</v>
+        <v>34.97</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>29.47</v>
+        <v>26.94</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>25.91</v>
+        <v>25.03</v>
       </c>
     </row>
     <row r="60">
@@ -5486,28 +5486,28 @@
         <v>1.04</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="62">
@@ -5738,28 +5738,28 @@
         <v>40.53</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>42.09</v>
+        <v>48.12</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>35.91</v>
+        <v>47.8</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>37.66</v>
+        <v>37.62</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>37.58</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>37.43</v>
+        <v>37.36</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>35.41</v>
+        <v>35.45</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>29.87</v>
+        <v>27.33</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>26.29</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="65">
@@ -5906,28 +5906,28 @@
         <v>1.66</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="67">
@@ -6158,28 +6158,28 @@
         <v>40.95</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>42.49</v>
+        <v>48.63</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>36.25</v>
+        <v>90</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>38.02</v>
+        <v>37.98</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>37.98</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>37.83</v>
+        <v>37.75</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>35.82</v>
+        <v>35.9</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>30.25</v>
+        <v>27.65</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>26.6</v>
+        <v>25.69</v>
       </c>
     </row>
     <row r="70">
@@ -6326,28 +6326,28 @@
         <v>2.09</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>1.97</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="72">
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>0</v>
+        <v>41.74</v>
       </c>
       <c r="U72" s="3" t="n">
         <v>0</v>
@@ -6578,28 +6578,28 @@
         <v>39.74</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>41.22</v>
+        <v>47.18</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>35.17</v>
+        <v>46.82</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>36.93</v>
+        <v>36.85</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>36.85</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>36.67</v>
+        <v>36.59</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.72</v>
+        <v>34.76</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>29.32</v>
+        <v>26.8</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>25.85</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="75">
@@ -6746,28 +6746,28 @@
         <v>0.87</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="77">
@@ -6998,28 +6998,28 @@
         <v>38.87</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>40.15</v>
+        <v>46</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>34.15</v>
+        <v>45.55</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>35.82</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>35.82</v>
+        <v>35.85</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>35.71</v>
+        <v>35.68</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>33.85</v>
+        <v>33.92</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>28.53</v>
+        <v>26.1</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>24.92</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="80">
@@ -7418,28 +7418,28 @@
         <v>38.4</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>37.25</v>
+        <v>42.87</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>31.86</v>
+        <v>42.49</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>33.66</v>
+        <v>33.63</v>
       </c>
       <c r="V84" s="3" t="n">
         <v>33.54</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>35.39</v>
+        <v>35.29</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>33.32</v>
+        <v>33.35</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>28.39</v>
+        <v>25.92</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>25.07</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="85">
@@ -7586,28 +7586,28 @@
         <v>-0.46</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.91</v>
+        <v>-3.13</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.29</v>
+        <v>-3.06</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.15</v>
+        <v>-2.19</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.28</v>
+        <v>-2.31</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.39</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.57</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="87">
@@ -7838,28 +7838,28 @@
         <v>38.67</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>39.83</v>
+        <v>45.77</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>33.74</v>
+        <v>45.51</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>35.29</v>
+        <v>35.25</v>
       </c>
       <c r="V89" s="3" t="n">
         <v>35.22</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>35.22</v>
+        <v>35.15</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>33.85</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>28.47</v>
+        <v>26.05</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>25</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="90">
@@ -8006,28 +8006,28 @@
         <v>-0.19</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="U91" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W91" s="3" t="n">
         <v>-0.53</v>
       </c>
-      <c r="V91" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>-0.49</v>
-      </c>
       <c r="X91" s="3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-18T08:13:04</t>
+          <t>CreatedAt: 2026-03-18T09:10:33</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -680,46 +680,46 @@
         <v>48.86</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>38.35</v>
+        <v>35.34</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>35.23</v>
+        <v>35.14</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>34.99</v>
+        <v>33.44</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>34.49</v>
+        <v>31.03</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>34.85</v>
+        <v>33.47</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>35.05</v>
+        <v>34.18</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>35.23</v>
+        <v>35.13</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>49.15</v>
+        <v>44.04</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>63.76</v>
+        <v>63.83</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>64.14</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>49.77</v>
+        <v>45.16</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>36.91</v>
+        <v>34.99</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.95</v>
+        <v>34.9</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>34.68</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="5">
@@ -848,46 +848,46 @@
         <v>-0.29</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.19</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.17</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.18</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.77</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-0.64</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.45</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.52</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="7">
@@ -1100,46 +1100,46 @@
         <v>49.95</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>39.58</v>
+        <v>36.46</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>36.61</v>
+        <v>36.64</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>36.39</v>
+        <v>34.86</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>35.77</v>
+        <v>32.28</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>36.22</v>
+        <v>34.89</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>36.31</v>
+        <v>35.53</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>36.24</v>
+        <v>36.1</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>50.61</v>
+        <v>45.39</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>66.17</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>50.92</v>
+        <v>46.26</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>38.19</v>
+        <v>36.28</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>36.53</v>
+        <v>36.63</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>36.21</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="10">
@@ -1268,46 +1268,46 @@
         <v>0.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N11" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R11" s="3" t="n">
         <v>1.17</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>1.13</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.26</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>1.39</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.99</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.98</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="12">
@@ -1520,46 +1520,46 @@
         <v>49.95</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>141.53</v>
+        <v>36.46</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>36.65</v>
+        <v>138</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>36.43</v>
+        <v>34.9</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>35.77</v>
+        <v>32.28</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>36.22</v>
+        <v>34.89</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>36.35</v>
+        <v>35.53</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>36.24</v>
+        <v>36.14</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>50.66</v>
+        <v>45.39</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>66.23999999999999</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>50.92</v>
+        <v>46.26</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>38.23</v>
+        <v>36.28</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>36.53</v>
+        <v>36.67</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>36.21</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="15">
@@ -1604,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>101.96</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0</v>
+        <v>101.32</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>0</v>
@@ -1688,46 +1688,46 @@
         <v>0.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R16" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="P16" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S16" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.26</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>1.46</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.99</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="17">
@@ -1940,46 +1940,46 @@
         <v>48.86</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>38.43</v>
+        <v>35.44</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>35.27</v>
+        <v>35.28</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>34.99</v>
+        <v>33.51</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>34.42</v>
+        <v>31.03</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>34.81</v>
+        <v>33.5</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>34.98</v>
+        <v>34.18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>35.2</v>
+        <v>35.09</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>49.15</v>
+        <v>44.08</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>63.58</v>
+        <v>63.64</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>64.02</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>49.57</v>
+        <v>45.03</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>36.81</v>
+        <v>34.92</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.88</v>
+        <v>34.97</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>34.68</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="20">
@@ -2108,46 +2108,46 @@
         <v>-0.29</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.18</v>
+        <v>0.11</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.19</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.13</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.95</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>-0.77</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.59</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.52</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.45</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="22">
@@ -2360,46 +2360,46 @@
         <v>48.86</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>38.43</v>
+        <v>35.44</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>35.27</v>
+        <v>35.28</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.99</v>
+        <v>33.51</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>34.42</v>
+        <v>31.03</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>34.81</v>
+        <v>33.5</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>34.98</v>
+        <v>34.18</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>35.2</v>
+        <v>35.09</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>49.15</v>
+        <v>44.08</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>63.58</v>
+        <v>63.64</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>64.02</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>49.57</v>
+        <v>45.03</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>36.81</v>
+        <v>34.92</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.88</v>
+        <v>34.97</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>34.68</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="25">
@@ -2528,46 +2528,46 @@
         <v>-0.29</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.18</v>
+        <v>0.11</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.19</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.13</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.95</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>-0.77</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.59</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.52</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.45</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="27">
@@ -2780,46 +2780,46 @@
         <v>48.81</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>38.43</v>
+        <v>35.44</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>35.2</v>
+        <v>35.31</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>34.88</v>
+        <v>33.44</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>34.25</v>
+        <v>30.94</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>34.68</v>
+        <v>33.47</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>34.84</v>
+        <v>34.08</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>35.13</v>
+        <v>35.02</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>49.05</v>
+        <v>43.99</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>63.26</v>
+        <v>63.27</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>63.64</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>49.23</v>
+        <v>44.76</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>36.55</v>
+        <v>34.75</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.75</v>
+        <v>34.93</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>34.58</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="30">
@@ -2948,28 +2948,28 @@
         <v>-0.34</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.25</v>
+        <v>0.14</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.28</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.17</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.27</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.21</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.22</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>-1.33</v>
@@ -2978,16 +2978,16 @@
         <v>-1.15</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.49</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="32">
@@ -3200,46 +3200,46 @@
         <v>49.1</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>137.49</v>
+        <v>35.87</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>36.54</v>
+        <v>101</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>36.47</v>
+        <v>34.9</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>35.84</v>
+        <v>32.35</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>36.29</v>
+        <v>34.93</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>36.27</v>
+        <v>35.45</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>35.98</v>
+        <v>35.88</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>50.55</v>
+        <v>45.3</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>64.08</v>
+        <v>64.53</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>66.38</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>50.67</v>
+        <v>46.03</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>38.43</v>
+        <v>36.46</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>37.03</v>
+        <v>37.13</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>36.93</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="35">
@@ -3284,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>98.51000000000001</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>64.55</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>0</v>
@@ -3368,46 +3368,46 @@
         <v>-0.05</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="N36" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="O36" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="S36" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="T36" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U36" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.06</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>1.59</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="37">
@@ -3620,46 +3620,46 @@
         <v>48.86</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>38.35</v>
+        <v>35.34</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>35.23</v>
+        <v>35.14</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>34.99</v>
+        <v>33.44</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>34.49</v>
+        <v>31.03</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>34.85</v>
+        <v>33.47</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>35.05</v>
+        <v>34.18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>35.23</v>
+        <v>35.13</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>49.15</v>
+        <v>44.04</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>63.76</v>
+        <v>63.83</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>64.14</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>49.77</v>
+        <v>45.16</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>36.91</v>
+        <v>34.99</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.95</v>
+        <v>34.9</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>34.68</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="40">
@@ -3788,46 +3788,46 @@
         <v>-0.29</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.19</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.17</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.18</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.77</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-0.64</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.45</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.52</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="42">
@@ -4040,46 +4040,46 @@
         <v>49.7</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>38.9</v>
+        <v>35.3</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>35.8</v>
+        <v>35.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>35.62</v>
+        <v>33.61</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>35.37</v>
+        <v>31.37</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>35.66</v>
+        <v>33.84</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>35.87</v>
+        <v>34.6</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>35.88</v>
+        <v>35.55</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>50.14</v>
+        <v>44.62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>65.44</v>
+        <v>65.05</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>65.37</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>51.08</v>
+        <v>45.98</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>37.73</v>
+        <v>35.48</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>35.69</v>
+        <v>35.35</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>35.45</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="45">
@@ -4208,46 +4208,46 @@
         <v>0.55</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0.43</v>
+        <v>-0.11</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.57</v>
+        <v>0.16</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.85</v>
+        <v>0.46</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.72</v>
+        <v>0.37</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.14</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="47">
@@ -4460,46 +4460,46 @@
         <v>49.55</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>38.39</v>
+        <v>35.3</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>35.48</v>
+        <v>33.34</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>35.3</v>
+        <v>31.89</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>33.27</v>
+        <v>29.64</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>33.52</v>
+        <v>31.97</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>33.93</v>
+        <v>33</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>34.08</v>
+        <v>33.88</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>47.18</v>
+        <v>42.11</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>61.69</v>
+        <v>61.52</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>62.23</v>
+        <v>62.05</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>48.1</v>
+        <v>43.44</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>35.75</v>
+        <v>33.69</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>33.73</v>
+        <v>33.51</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>33.21</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="50">
@@ -4628,46 +4628,46 @@
         <v>0.4</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.04</v>
+        <v>-1.83</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0.04</v>
+        <v>-1.79</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.57</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.66</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.35</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.29</v>
+        <v>-1.36</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.26</v>
+        <v>-2.11</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.9</v>
+        <v>-3.08</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-2.55</v>
+        <v>-2.73</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.26</v>
+        <v>-2.17</v>
       </c>
       <c r="X51" s="3" t="n">
         <v>-1.75</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-1.82</v>
+        <v>-1.91</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.03</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="52">
@@ -4880,46 +4880,46 @@
         <v>47.54</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>37.06</v>
+        <v>34.28</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>35.48</v>
+        <v>35.24</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>35.59</v>
+        <v>33.95</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>35.15</v>
+        <v>31.53</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>35.48</v>
+        <v>34.08</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>35.36</v>
+        <v>34.56</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>34.51</v>
+        <v>34.41</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>48.14</v>
+        <v>43.09</v>
       </c>
       <c r="U54" s="3" t="n">
         <v>62.96</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>63.02</v>
+        <v>63.08</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>48.76</v>
+        <v>44.2</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>36.84</v>
+        <v>34.85</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>35.8</v>
+        <v>35.67</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>35.92</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="55">
@@ -5048,46 +5048,46 @@
         <v>-1.62</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.13</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O56" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P56" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="P56" s="3" t="n">
-        <v>0.35</v>
-      </c>
       <c r="Q56" s="3" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.83</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.12</v>
       </c>
       <c r="U56" s="3" t="n">
         <v>-1.64</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.7</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.41</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.59</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="57">
@@ -5300,46 +5300,46 @@
         <v>51.04</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>39.95</v>
+        <v>36.09</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>36.8</v>
+        <v>35.89</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>36.62</v>
+        <v>34.37</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>36.21</v>
+        <v>31.95</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>36.52</v>
+        <v>34.46</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>36.69</v>
+        <v>35.23</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>36.62</v>
+        <v>36.17</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>51.18</v>
+        <v>45.39</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>66.8</v>
+        <v>66.25</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>52.08</v>
+        <v>46.73</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>38.51</v>
+        <v>36.09</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>36.29</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="60">
@@ -5468,46 +5468,46 @@
         <v>1.89</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.36</v>
+        <v>0.72</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.42</v>
+        <v>0.83</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.95</v>
+        <v>0.58</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.05</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="62">
@@ -5720,46 +5720,46 @@
         <v>51.9</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>40.62</v>
+        <v>36.69</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>37.47</v>
+        <v>36.52</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>37.2</v>
+        <v>34.9</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>36.79</v>
+        <v>32.41</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>37.14</v>
+        <v>35</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>37.31</v>
+        <v>35.82</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>37.23</v>
+        <v>36.74</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>52.04</v>
+        <v>46.1</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>68.06</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>68.19</v>
+        <v>67.63</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>52.9</v>
+        <v>47.46</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>39.11</v>
+        <v>36.65</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.99</v>
+        <v>36.48</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>36.82</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="65">
@@ -5888,46 +5888,46 @@
         <v>2.75</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.93</v>
+        <v>1.22</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.99</v>
+        <v>1.2</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.13</v>
+        <v>1.47</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.47</v>
+        <v>2.83</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.41</v>
+        <v>2.84</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.58</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="67">
@@ -6140,46 +6140,46 @@
         <v>52.4</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>41.01</v>
+        <v>36.58</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>37.79</v>
+        <v>2000</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>37.6</v>
+        <v>34.83</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>37.18</v>
+        <v>32.38</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>37.49</v>
+        <v>34.93</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>37.63</v>
+        <v>2000</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>37.31</v>
+        <v>36.62</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>52.21</v>
+        <v>46.01</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>68.14</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>68.34</v>
+        <v>1999.99</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>53.18</v>
+        <v>1999.99</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>39.27</v>
+        <v>2000</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>37.26</v>
+        <v>2000</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>37.21</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="70">
@@ -6308,46 +6308,46 @@
         <v>3.25</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.54</v>
+        <v>1.17</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.34</v>
+        <v>1.2</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>2.33</v>
+        <v>1.15</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.38</v>
+        <v>1.17</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.4</v>
+        <v>1.29</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.77</v>
+        <v>1.79</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.54</v>
+        <v>2.55</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.71</v>
+        <v>1.06</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.97</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="72">
@@ -6395,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>0</v>
+        <v>1963.63</v>
       </c>
       <c r="O72" s="3" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>0</v>
+        <v>1964.29</v>
       </c>
       <c r="S72" s="3" t="n">
         <v>0</v>
@@ -6419,19 +6419,19 @@
         <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>0</v>
+        <v>1932.65</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>0</v>
+        <v>1952.63</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>0</v>
+        <v>1963.42</v>
       </c>
       <c r="Y72" s="3" t="n">
-        <v>0</v>
+        <v>1963.52</v>
       </c>
       <c r="Z72" s="3" t="n">
-        <v>0</v>
+        <v>1964.75</v>
       </c>
     </row>
     <row r="73">
@@ -6560,46 +6560,46 @@
         <v>50.99</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>39.86</v>
+        <v>36.06</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>36.84</v>
+        <v>35.89</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>36.62</v>
+        <v>34.26</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>36.18</v>
+        <v>31.82</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>36.48</v>
+        <v>34.36</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>36.58</v>
+        <v>35.16</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>36.5</v>
+        <v>36.06</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>51.02</v>
+        <v>45.26</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>66.59</v>
+        <v>66.11</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>66.31</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>51.92</v>
+        <v>46.59</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>38.35</v>
+        <v>35.98</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>36.31</v>
+        <v>35.85</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>36.06</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="75">
@@ -6728,46 +6728,46 @@
         <v>1.84</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1.4</v>
+        <v>0.65</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1.35</v>
+        <v>0.58</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.37</v>
+        <v>0.6</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.39</v>
+        <v>0.72</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.39</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.56</v>
+        <v>0.98</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="77">
@@ -6980,28 +6980,28 @@
         <v>49.15</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>38.47</v>
+        <v>35.41</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>35.44</v>
+        <v>35.17</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>35.27</v>
+        <v>33.68</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>34.8</v>
+        <v>31.21</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>35.09</v>
+        <v>33.63</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>35.19</v>
+        <v>34.35</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>35.37</v>
+        <v>35.23</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>49.44</v>
+        <v>44.21</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>64.59</v>
@@ -7010,16 +7010,16 @@
         <v>64.79000000000001</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>50.36</v>
+        <v>45.61</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>37.5</v>
+        <v>35.44</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>35.55</v>
+        <v>35.42</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>35.23</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="80">
@@ -7400,46 +7400,46 @@
         <v>46.2</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>36.02</v>
+        <v>33.21</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>35.41</v>
+        <v>35.24</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>35.48</v>
+        <v>33.92</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>35.12</v>
+        <v>31.53</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>35.45</v>
+        <v>34.04</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>35.36</v>
+        <v>34.6</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>33.59</v>
+        <v>33.52</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>47.09</v>
+        <v>42.19</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>61.63</v>
+        <v>61.64</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>61.64</v>
+        <v>61.76</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>47.78</v>
+        <v>43.32</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>35.96</v>
+        <v>34.01</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>35.83</v>
+        <v>35.71</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>36.03</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="85">
@@ -7568,46 +7568,46 @@
         <v>-2.96</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-2.45</v>
+        <v>-2.19</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="P86" s="3" t="n">
         <v>0.32</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.71</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.03</v>
       </c>
       <c r="U86" s="3" t="n">
         <v>-2.96</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-3.14</v>
+        <v>-3.03</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.58</v>
+        <v>-2.3</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.43</v>
       </c>
       <c r="Y86" s="3" t="n">
         <v>0.29</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="87">
@@ -7820,46 +7820,46 @@
         <v>48.81</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>38.43</v>
+        <v>35.44</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>35.2</v>
+        <v>35.31</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>34.88</v>
+        <v>33.44</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>34.25</v>
+        <v>30.94</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>34.68</v>
+        <v>33.43</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>34.84</v>
+        <v>34.08</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>35.13</v>
+        <v>35.02</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>49.05</v>
+        <v>43.99</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>63.26</v>
+        <v>63.27</v>
       </c>
       <c r="V89" s="3" t="n">
         <v>63.64</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>49.23</v>
+        <v>44.76</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>36.55</v>
+        <v>34.75</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>34.75</v>
+        <v>34.93</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>34.58</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="90">
@@ -7988,28 +7988,28 @@
         <v>-0.34</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.25</v>
+        <v>0.14</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.28</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.2</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.27</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.21</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.22</v>
       </c>
       <c r="U91" s="3" t="n">
         <v>-1.33</v>
@@ -8018,16 +8018,16 @@
         <v>-1.15</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.49</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-23T11:09:13</t>
+          <t>CreatedAt: 2026-03-23T12:09:03</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -689,37 +689,37 @@
         <v>49.06</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>36.63</v>
+        <v>50.14</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.66</v>
+        <v>75.13</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>33.87</v>
+        <v>34</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>34.32</v>
+        <v>34.33</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>65.04000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>63.83</v>
+        <v>61.26</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>61.62</v>
+        <v>61.68</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>49.56</v>
+        <v>50.14</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.1</v>
+        <v>34.04</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>34.07</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="5">
@@ -857,37 +857,37 @@
         <v>-0.64</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.41</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.71</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>-0.79</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.89</v>
+        <v>-2.31</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.04</v>
+        <v>-2.02</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.78</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-134.14</v>
       </c>
     </row>
     <row r="9">
@@ -1109,37 +1109,37 @@
         <v>49.16</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>36.7</v>
+        <v>50.34</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>33.72</v>
+        <v>75.03</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>34.14</v>
+        <v>34.27</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>34.39</v>
+        <v>34.4</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>50.25</v>
+        <v>50.55</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>65.29000000000001</v>
+        <v>82.88</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>64.45999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>61.74</v>
+        <v>61.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>49.8</v>
+        <v>50.38</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>34.44</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>34.55</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="10">
@@ -1277,37 +1277,37 @@
         <v>-0.54</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.3</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.52</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>-0.72</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.96</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.07</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.48</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>-1.54</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>-134.65</v>
       </c>
     </row>
     <row r="14">
@@ -1529,37 +1529,37 @@
         <v>49.16</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>36.7</v>
+        <v>50.34</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>33.72</v>
+        <v>75.03</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>34.14</v>
+        <v>34.27</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>34.39</v>
+        <v>34.4</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>50.25</v>
+        <v>50.55</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>65.29000000000001</v>
+        <v>82.88</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>64.45999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>61.74</v>
+        <v>61.8</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>49.8</v>
+        <v>50.38</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>34.44</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>34.55</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="15">
@@ -1697,37 +1697,37 @@
         <v>-0.54</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.3</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.52</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>-0.72</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.96</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.07</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.48</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>-1.54</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-134.65</v>
       </c>
     </row>
     <row r="19">
@@ -1949,37 +1949,37 @@
         <v>48.92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>36.52</v>
+        <v>50.09</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>33.49</v>
+        <v>75</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>33.77</v>
+        <v>33.9</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>34.18</v>
+        <v>34.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>64.91</v>
+        <v>82.48</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>63.77</v>
+        <v>61.2</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>61.38</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>49.46</v>
+        <v>49.99</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.03</v>
+        <v>34.04</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>34.17</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="20">
@@ -2117,37 +2117,37 @@
         <v>-0.78</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.55</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.55</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-2.01</v>
+        <v>-2.47</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.08</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.96</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.1</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="22">
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>-134.27</v>
       </c>
     </row>
     <row r="24">
@@ -2369,37 +2369,37 @@
         <v>48.92</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>36.52</v>
+        <v>50.09</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>33.49</v>
+        <v>75</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>33.77</v>
+        <v>33.9</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>34.18</v>
+        <v>34.2</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>64.91</v>
+        <v>82.48</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>63.77</v>
+        <v>61.2</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>61.38</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>49.46</v>
+        <v>49.99</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.03</v>
+        <v>34.04</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>34.17</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="25">
@@ -2537,37 +2537,37 @@
         <v>-0.78</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.55</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.55</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-2.01</v>
+        <v>-2.47</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.08</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.96</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="27">
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0</v>
+        <v>-134.27</v>
       </c>
     </row>
     <row r="29">
@@ -2789,37 +2789,37 @@
         <v>48.68</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>36.27</v>
+        <v>49.89</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.26</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>33.54</v>
+        <v>33.71</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.99</v>
+        <v>34</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>64.79000000000001</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>63.71</v>
+        <v>61.08</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>61.02</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>49.22</v>
+        <v>49.79</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>33.97</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>34.27</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="30">
@@ -2957,37 +2957,37 @@
         <v>-1.02</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.75</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.78</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.01</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>-1.12</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.63</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.17</v>
+        <v>-2.2</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-2.26</v>
+        <v>-2.32</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.85</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="32">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-134.38</v>
       </c>
     </row>
     <row r="34">
@@ -3209,34 +3209,34 @@
         <v>103</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>51.73</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>34.96</v>
+        <v>75.55</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>35.91</v>
+        <v>36.05</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>35.5</v>
+        <v>35.51</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>50.75</v>
+        <v>51.05</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>66.72</v>
+        <v>84.7</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>67.02</v>
+        <v>64.31</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>63.92</v>
+        <v>63.98</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>51.53</v>
+        <v>52.13</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>36.08</v>
+        <v>36.05</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>2000</v>
@@ -3293,7 +3293,7 @@
         <v>52.44</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>39.7</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1964.28</v>
+        <v>1964.21</v>
       </c>
     </row>
     <row r="36">
@@ -3377,37 +3377,37 @@
         <v>0.86</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.76</v>
+        <v>1.09</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.46</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.25</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0.64</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>1.23</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="37">
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
@@ -3629,37 +3629,37 @@
         <v>49.06</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>36.63</v>
+        <v>50.14</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>33.66</v>
+        <v>75.13</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>33.87</v>
+        <v>34</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>34.32</v>
+        <v>34.33</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>65.04000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>63.83</v>
+        <v>61.26</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>61.62</v>
+        <v>61.68</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>49.56</v>
+        <v>50.14</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.1</v>
+        <v>34.04</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>34.07</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="40">
@@ -3797,37 +3797,37 @@
         <v>-0.64</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.41</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.71</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>-0.79</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.89</v>
+        <v>-2.31</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.04</v>
+        <v>-2.02</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.78</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="42">
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
@@ -3995,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>-134.14</v>
       </c>
     </row>
     <row r="44">
@@ -4049,37 +4049,37 @@
         <v>49.65</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>37.25</v>
+        <v>50.69</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>34.47</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>34.82</v>
+        <v>34.93</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>35.32</v>
+        <v>35.33</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>51.41</v>
+        <v>51.77</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>67.06</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>65.94</v>
+        <v>63.28</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>63.47</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>50.65</v>
+        <v>51.19</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>34.81</v>
+        <v>34.79</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>34.79</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="45">
@@ -4217,10 +4217,10 @@
         <v>-0.05</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>0.21</v>
@@ -4232,22 +4232,22 @@
         <v>0.26</v>
       </c>
       <c r="U46" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="V46" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.19</v>
-      </c>
       <c r="X46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>-0.03</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -4415,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>0</v>
+        <v>-134.86</v>
       </c>
     </row>
     <row r="49">
@@ -4469,37 +4469,37 @@
         <v>49.46</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>36.77</v>
+        <v>50.24</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>34.23</v>
+        <v>75.48</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>33.16</v>
+        <v>33.26</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>33.5</v>
+        <v>33.51</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>48.22</v>
+        <v>48.55</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>60.18</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>59.24</v>
+        <v>56.91</v>
       </c>
       <c r="W49" s="3" t="n">
         <v>56.5</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>47.6</v>
+        <v>48.15</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>33.09</v>
+        <v>33.07</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>35.03</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="50">
@@ -4637,10 +4637,10 @@
         <v>-0.25</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>-1.46</v>
@@ -4649,19 +4649,19 @@
         <v>-1.61</v>
       </c>
       <c r="T51" s="3" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="X51" s="3" t="n">
         <v>-2.94</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>-6.74</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="W51" s="3" t="n">
-        <v>-6.78</v>
-      </c>
-      <c r="X51" s="3" t="n">
-        <v>-2.9</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>-1.75</v>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>0</v>
+        <v>-135.07</v>
       </c>
     </row>
     <row r="54">
@@ -4889,37 +4889,37 @@
         <v>49.46</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>36.66</v>
+        <v>49.89</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.99</v>
+        <v>75.27</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>34.2</v>
+        <v>34.58</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>35.04</v>
+        <v>35.3</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>49.43</v>
+        <v>50.11</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>65.48</v>
+        <v>83.53</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>64.45999999999999</v>
+        <v>62.34</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>61.98</v>
+        <v>62.47</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>49.08</v>
+        <v>50.04</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>35.2</v>
+        <v>35.43</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>34.96</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="55">
@@ -5057,37 +5057,37 @@
         <v>-0.25</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.75</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.14</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.4</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.42</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.42</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.3</v>
+        <v>-0.87</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.05</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="57">
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3" t="n">
-        <v>0</v>
+        <v>-135.21</v>
       </c>
     </row>
     <row r="59">
@@ -5309,37 +5309,37 @@
         <v>51.13</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>38.29</v>
+        <v>52.16</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>35.46</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>36.31</v>
+        <v>36.32</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>52.85</v>
+        <v>53.22</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>67.84</v>
+        <v>65.17</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>65.23999999999999</v>
+        <v>65.23</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>52.01</v>
+        <v>52.61</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>35.78</v>
+        <v>35.75</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>35.76</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="60">
@@ -5477,10 +5477,10 @@
         <v>1.43</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>1.18</v>
@@ -5489,19 +5489,19 @@
         <v>1.2</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.93</v>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>0</v>
+        <v>-135.79</v>
       </c>
     </row>
     <row r="64">
@@ -5729,37 +5729,37 @@
         <v>51.88</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>38.85</v>
+        <v>52.86</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>36.02</v>
+        <v>77.31</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>36.36</v>
+        <v>36.47</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>36.88</v>
+        <v>36.93</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>53.68</v>
+        <v>54.11</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>70.15000000000001</v>
+        <v>89.05</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>68.91</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>66.26000000000001</v>
+        <v>66.33</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>52.77</v>
+        <v>53.38</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.3</v>
+        <v>36.27</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>36.28</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="65">
@@ -5897,31 +5897,31 @@
         <v>2.18</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.71</v>
+        <v>2.22</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>1.75</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>2.98</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>1.45</v>
@@ -6068,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
         <v>0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>0</v>
+        <v>-136.32</v>
       </c>
     </row>
     <row r="69">
@@ -6149,37 +6149,37 @@
         <v>52.54</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>39.3</v>
+        <v>53.53</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>36.4</v>
+        <v>77.7</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>36.75</v>
+        <v>36.86</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>37.27</v>
+        <v>37.28</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>54.25</v>
+        <v>54.63</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>89.89</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>69.64</v>
+        <v>66.89</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>66.95999999999999</v>
+        <v>67.03</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>53.38</v>
+        <v>54</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>36.76</v>
+        <v>36.73</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>36.7</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="70">
@@ -6317,31 +6317,31 @@
         <v>2.84</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.16</v>
+        <v>2.89</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S71" s="3" t="n">
         <v>2.16</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>1.91</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>0</v>
+        <v>-136.74</v>
       </c>
     </row>
     <row r="74">
@@ -6569,37 +6569,37 @@
         <v>51.13</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>38.25</v>
+        <v>52.1</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>35.43</v>
+        <v>76.7</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>35.72</v>
+        <v>35.83</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>36.23</v>
+        <v>36.24</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>52.74</v>
+        <v>53.11</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>68.78</v>
+        <v>87.31</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>67.64</v>
+        <v>64.97</v>
       </c>
       <c r="W74" s="3" t="n">
         <v>64.97</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>51.79</v>
+        <v>52.4</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>35.67</v>
+        <v>35.64</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>35.68</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="75">
@@ -6737,10 +6737,10 @@
         <v>1.43</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>1.11</v>
@@ -6749,19 +6749,19 @@
         <v>1.12</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>0.82</v>
@@ -6908,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0</v>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>0</v>
+        <v>-135.72</v>
       </c>
     </row>
     <row r="79">
@@ -6989,37 +6989,37 @@
         <v>49.7</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>37.14</v>
+        <v>50.64</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>34.33</v>
+        <v>75.55</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>34.61</v>
+        <v>34.72</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>35.11</v>
+        <v>35.12</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>51.16</v>
+        <v>51.51</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>66.92</v>
+        <v>84.95</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>65.88</v>
+        <v>63.28</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>63.28</v>
+        <v>63.34</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>50.5</v>
+        <v>51.09</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>34.85</v>
+        <v>34.82</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>34.72</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="80">
@@ -7328,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
@@ -7355,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>0</v>
+        <v>-134.75</v>
       </c>
     </row>
     <row r="84">
@@ -7409,37 +7409,37 @@
         <v>49.06</v>
       </c>
       <c r="P84" s="3" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>82.72</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="Y84" s="3" t="n">
         <v>36.09</v>
       </c>
-      <c r="Q84" s="3" t="n">
-        <v>33.49</v>
-      </c>
-      <c r="R84" s="3" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>34.79</v>
-      </c>
-      <c r="T84" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="U84" s="3" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="V84" s="3" t="n">
-        <v>63.04</v>
-      </c>
-      <c r="W84" s="3" t="n">
-        <v>60.73</v>
-      </c>
-      <c r="X84" s="3" t="n">
-        <v>47.82</v>
-      </c>
-      <c r="Y84" s="3" t="n">
-        <v>35.34</v>
-      </c>
       <c r="Z84" s="3" t="n">
-        <v>35.07</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="85">
@@ -7577,37 +7577,37 @@
         <v>-0.64</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.24</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.68</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.31</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.31</v>
+        <v>0.43</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.26</v>
+        <v>-2.22</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.88</v>
+        <v>-2.23</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.84</v>
+        <v>-1.48</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.55</v>
+        <v>-1.24</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-2.68</v>
+        <v>-1.68</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.49</v>
+        <v>1.26</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.35</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="87">
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>0</v>
@@ -7775,7 +7775,7 @@
         <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>0</v>
+        <v>-135.79</v>
       </c>
     </row>
     <row r="89">
@@ -7829,37 +7829,37 @@
         <v>48.68</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>36.27</v>
+        <v>49.89</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>33.26</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>33.54</v>
+        <v>33.71</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>33.99</v>
+        <v>34</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>64.79000000000001</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>63.71</v>
+        <v>61.08</v>
       </c>
       <c r="W89" s="3" t="n">
         <v>61.02</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>49.22</v>
+        <v>49.79</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.93</v>
+        <v>33.97</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>34.27</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="90">
@@ -7997,37 +7997,37 @@
         <v>-1.02</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.75</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.78</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.01</v>
       </c>
       <c r="S91" s="3" t="n">
         <v>-1.12</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.63</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.17</v>
+        <v>-2.2</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-2.26</v>
+        <v>-2.32</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.85</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="92">
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>0</v>
+        <v>40.67</v>
       </c>
       <c r="R93" s="3" t="n">
         <v>0</v>
@@ -8195,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>0</v>
+        <v>-134.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-24T06:11:04</t>
+          <t>CreatedAt: 2026-03-24T07:10:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -674,52 +674,52 @@
         <v>203.25</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>76.88</v>
+        <v>86.2</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>37.99</v>
+        <v>37.27</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>33.81</v>
+        <v>34.16</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>34.13</v>
+        <v>34.09</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>34.13</v>
+        <v>34.39</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>34.29</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>34.18</v>
+        <v>34.37</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>38.32</v>
+        <v>37.75</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>45.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>104.18</v>
+        <v>104.28</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>283.22</v>
+        <v>288.17</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>156.63</v>
+        <v>173.93</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>104.19</v>
+        <v>104.08</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>89.14</v>
+        <v>100.16</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>48.85</v>
+        <v>48.99</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>45.5</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="5">
@@ -842,52 +842,52 @@
         <v>-3.86</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.29</v>
       </c>
       <c r="L6" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.38</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>-0.38</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>-0.57</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.86</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.56</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-5.95</v>
+        <v>-6.05</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.29</v>
+        <v>-3.65</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>-2.29</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.49</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="7">
@@ -1094,52 +1094,52 @@
         <v>203.45</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>76.72</v>
+        <v>86.03</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>38.22</v>
+        <v>37.24</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>34.05</v>
+        <v>34.43</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>34.47</v>
+        <v>34.5</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>34.4</v>
+        <v>34.69</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>34.63</v>
+        <v>34.66</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>34.56</v>
+        <v>34.78</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>38.89</v>
+        <v>38.32</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>45.91</v>
+        <v>45.95</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>105.22</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>284.61</v>
+        <v>289.31</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>158.81</v>
+        <v>176.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>105.53</v>
+        <v>105.11</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>89.67</v>
+        <v>100.56</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>49.54</v>
+        <v>49.63</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>46.41</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="10">
@@ -1262,25 +1262,25 @@
         <v>-3.66</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.48</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>0</v>
@@ -1292,22 +1292,22 @@
         <v>-0.63</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-4.55</v>
+        <v>-4.92</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.11</v>
+        <v>-0.88</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.26</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.31</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12">
@@ -1514,52 +1514,52 @@
         <v>203.45</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>76.72</v>
+        <v>86.03</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>38.22</v>
+        <v>37.24</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>34.05</v>
+        <v>34.43</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>34.47</v>
+        <v>34.5</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>34.4</v>
+        <v>34.69</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>34.63</v>
+        <v>34.66</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>34.56</v>
+        <v>34.78</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>38.89</v>
+        <v>38.32</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>45.91</v>
+        <v>45.95</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>105.22</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>284.61</v>
+        <v>289.31</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>158.81</v>
+        <v>176.7</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>105.53</v>
+        <v>105.11</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>89.67</v>
+        <v>100.56</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>49.54</v>
+        <v>49.63</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>46.41</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="15">
@@ -1682,25 +1682,25 @@
         <v>-3.66</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.48</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>0</v>
@@ -1712,22 +1712,22 @@
         <v>-0.63</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-4.55</v>
+        <v>-4.92</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.11</v>
+        <v>-0.88</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.26</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.31</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="17">
@@ -1934,52 +1934,52 @@
         <v>203.85</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>76.95</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>38.11</v>
+        <v>37.31</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>33.95</v>
+        <v>34.3</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>34.23</v>
+        <v>34.2</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>34.23</v>
+        <v>34.49</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>34.42</v>
+        <v>34.46</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>34.35</v>
+        <v>34.54</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>38.51</v>
+        <v>37.9</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>45.64</v>
+        <v>45.59</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>104.49</v>
+        <v>104.59</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>283.77</v>
+        <v>288.46</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>157.09</v>
+        <v>174.44</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>104.19</v>
+        <v>104.08</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>88.95999999999999</v>
+        <v>99.87</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>48.85</v>
+        <v>48.95</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>45.68</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="20">
@@ -2102,52 +2102,52 @@
         <v>-3.26</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.21</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.41</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.24</v>
       </c>
       <c r="N21" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="O21" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="P21" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.26</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-5.39</v>
+        <v>-5.77</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.83</v>
+        <v>-3.14</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>-2.29</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.87</v>
+        <v>-2</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>-0.54</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="22">
@@ -2354,52 +2354,52 @@
         <v>203.85</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>76.95</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>38.11</v>
+        <v>37.31</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>33.95</v>
+        <v>34.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>34.23</v>
+        <v>34.2</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.23</v>
+        <v>34.49</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>34.42</v>
+        <v>34.46</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>34.35</v>
+        <v>34.54</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>38.51</v>
+        <v>37.9</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>45.64</v>
+        <v>45.59</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>104.49</v>
+        <v>104.59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>283.77</v>
+        <v>288.46</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>157.09</v>
+        <v>174.44</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>104.19</v>
+        <v>104.08</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>88.95999999999999</v>
+        <v>99.87</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>48.85</v>
+        <v>48.95</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>45.68</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="25">
@@ -2522,52 +2522,52 @@
         <v>-3.26</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.21</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.41</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.24</v>
       </c>
       <c r="N26" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="O26" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="P26" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="R26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.26</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-5.39</v>
+        <v>-5.77</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.83</v>
+        <v>-3.14</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>-2.29</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.87</v>
+        <v>-2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>-0.54</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="27">
@@ -2774,52 +2774,52 @@
         <v>204.45</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>38.22</v>
+        <v>37.35</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.12</v>
+        <v>34.43</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>34.33</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>34.33</v>
+        <v>34.63</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>34.56</v>
+        <v>34.59</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>34.53</v>
+        <v>34.71</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>38.7</v>
+        <v>38.05</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>45.77</v>
+        <v>45.73</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>104.9</v>
+        <v>105.01</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>284.61</v>
+        <v>289.02</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>157.55</v>
+        <v>174.96</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>104.09</v>
+        <v>103.88</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>88.62</v>
+        <v>99.48</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>48.71</v>
+        <v>48.75</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>45.91</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="30">
@@ -2942,52 +2942,52 @@
         <v>-2.66</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1</v>
+        <v>-1.04</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.37</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.64</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.84</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.55</v>
+        <v>-5.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.62</v>
       </c>
       <c r="W31" s="3" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="X31" s="3" t="n">
         <v>-2.39</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>-2.22</v>
-      </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.73</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="32">
@@ -3194,52 +3194,52 @@
         <v>179</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>75.39</v>
+        <v>84.78</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>38.34</v>
+        <v>36.77</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>34.05</v>
+        <v>34.61</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>35.17</v>
+        <v>35.28</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>34.78</v>
+        <v>35.22</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>35.05</v>
+        <v>35.23</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>35.05</v>
+        <v>35.38</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>40.01</v>
+        <v>39.59</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>46.69</v>
+        <v>46.93</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>106.81</v>
+        <v>335.34</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>286.3</v>
+        <v>290.74</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>424.69</v>
+        <v>183.64</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>110.69</v>
+        <v>430.99</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>92.88</v>
+        <v>103.94</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>52.37</v>
+        <v>52.7</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>48.71</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="35">
@@ -3305,16 +3305,16 @@
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>228.75</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>260.16</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>321.77</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
@@ -3365,49 +3365,49 @@
         <v>-2.71</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.39</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-2.86</v>
+        <v>-3.49</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>4.61</v>
+        <v>6.06</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>4.21</v>
+        <v>2.84</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="37">
@@ -3614,52 +3614,52 @@
         <v>203.25</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>76.88</v>
+        <v>86.2</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>37.99</v>
+        <v>37.27</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>33.81</v>
+        <v>34.16</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>34.13</v>
+        <v>34.09</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>34.13</v>
+        <v>34.39</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>34.29</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>34.18</v>
+        <v>34.37</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>38.32</v>
+        <v>37.75</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>45.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>104.18</v>
+        <v>104.28</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>283.22</v>
+        <v>288.17</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>156.63</v>
+        <v>173.93</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>104.19</v>
+        <v>104.08</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>89.14</v>
+        <v>100.16</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>48.85</v>
+        <v>48.99</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="40">
@@ -3782,52 +3782,52 @@
         <v>-3.86</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.29</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="O41" s="3" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>-0.38</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>-0.38</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>-0.57</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.86</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.56</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-5.95</v>
+        <v>-6.05</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.29</v>
+        <v>-3.65</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>-2.29</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.7</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.49</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="42">
@@ -4034,52 +4034,52 @@
         <v>206.08</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>78.03</v>
+        <v>87.5</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>38.34</v>
+        <v>37.68</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>34.22</v>
+        <v>34.54</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>34.5</v>
+        <v>34.44</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>34.51</v>
+        <v>34.69</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>34.63</v>
+        <v>34.59</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>34.56</v>
+        <v>34.71</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>38.89</v>
+        <v>38.32</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>46.27</v>
+        <v>46.32</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>105.95</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>289.16</v>
+        <v>294.52</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>158.81</v>
+        <v>176.52</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>106.37</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>90.73999999999999</v>
+        <v>101.76</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>49.54</v>
+        <v>49.68</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>46.37</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="45">
@@ -4202,22 +4202,22 @@
         <v>-1.03</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -4232,22 +4232,22 @@
         <v>0.11</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.06</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="47">
@@ -4454,52 +4454,52 @@
         <v>186.92</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>72.93000000000001</v>
+        <v>82.78</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>36.2</v>
+        <v>35.62</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>33.75</v>
+        <v>34.54</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>34.47</v>
+        <v>34.4</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>34.58</v>
+        <v>34.73</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>34.7</v>
+        <v>34.66</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>34.7</v>
+        <v>34.89</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>39.24</v>
+        <v>38.74</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>44.07</v>
+        <v>44.16</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.19</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>260.04</v>
+        <v>264.83</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>143.55</v>
+        <v>159.55</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>95.33</v>
+        <v>100.26</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>85.05</v>
+        <v>96.92</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>49.04</v>
+        <v>46.95</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>46.23</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="50">
@@ -4622,52 +4622,52 @@
         <v>-20.19</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-5.18</v>
+        <v>-4.72</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.1</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-2.25</v>
+        <v>-2.21</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-10.75</v>
+        <v>-10.66</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-29.12</v>
+        <v>-29.4</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-16.36</v>
+        <v>-18.03</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-11.15</v>
+        <v>-6.12</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.78</v>
+        <v>-4.94</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-0.34</v>
+        <v>-2.54</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.05</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="52">
@@ -4874,52 +4874,52 @@
         <v>203.65</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>76.5</v>
+        <v>85.53</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>37.55</v>
+        <v>36.95</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>34.42</v>
+        <v>34.75</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>34.5</v>
+        <v>34.44</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>34.23</v>
+        <v>34.45</v>
       </c>
       <c r="P54" s="3" t="n">
         <v>34.39</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>34.29</v>
+        <v>34.44</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>38.89</v>
+        <v>38.32</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>46.37</v>
+        <v>46.41</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>102.56</v>
+        <v>102.47</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>281.29</v>
+        <v>285.93</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>155.56</v>
+        <v>170.91</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>104.39</v>
+        <v>104.08</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>91.66</v>
+        <v>102.58</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>49.89</v>
+        <v>50.03</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>46.55</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="55">
@@ -5042,19 +5042,19 @@
         <v>-3.46</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.97</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="P56" s="3" t="n">
         <v>-0.28</v>
@@ -5069,22 +5069,22 @@
         <v>0.05</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-3.28</v>
+        <v>-3.38</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-7.88</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-4.36</v>
+        <v>-6.67</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.29</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="Z56" s="3" t="n">
         <v>0.37</v>
@@ -5294,52 +5294,52 @@
         <v>211.55</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>80.36</v>
+        <v>90.2</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>39.48</v>
+        <v>38.81</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>35.31</v>
+        <v>35.61</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>35.61</v>
+        <v>35.5</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>35.61</v>
+        <v>35.8</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>35.77</v>
+        <v>35.74</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>35.7</v>
+        <v>35.86</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>40.13</v>
+        <v>39.54</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>47.75</v>
+        <v>47.85</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>109.23</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>298.11</v>
+        <v>303.64</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>163.35</v>
+        <v>181.39</v>
       </c>
       <c r="W59" s="3" t="n">
         <v>109.66</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>93.45</v>
+        <v>104.91</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>50.92</v>
+        <v>51.01</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>47.61</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="60">
@@ -5462,52 +5462,52 @@
         <v>4.44</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>3.39</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>8.94</v>
+        <v>9.41</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.43</v>
+        <v>3.81</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>3.18</v>
+        <v>3.29</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>1.53</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="62">
@@ -5714,52 +5714,52 @@
         <v>214.84</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>81.53</v>
+        <v>91.52</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>40.06</v>
+        <v>39.42</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>35.83</v>
+        <v>36.13</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>36.13</v>
+        <v>36.06</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>36.17</v>
+        <v>36.37</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>36.33</v>
+        <v>36.3</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>36.3</v>
+        <v>36.46</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>40.81</v>
+        <v>40.25</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>48.6</v>
+        <v>48.65</v>
       </c>
       <c r="T64" s="3" t="n">
         <v>111.07</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>303.42</v>
+        <v>309.06</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>166.06</v>
+        <v>184.4</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>111.5</v>
+        <v>111.39</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>94.91</v>
+        <v>106.55</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>51.61</v>
+        <v>51.76</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>48.31</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="65">
@@ -5882,49 +5882,49 @@
         <v>7.73</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>3.42</v>
+        <v>4.03</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>1.66</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>5.22</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>14.26</v>
+        <v>14.83</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>6.14</v>
+        <v>6.82</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>4.08</v>
+        <v>4.69</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>2.13</v>
@@ -6134,52 +6134,52 @@
         <v>215.74</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>82.56</v>
+        <v>92.59</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>40.52</v>
+        <v>39.87</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>36.25</v>
+        <v>36.59</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>36.55</v>
+        <v>36.48</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>36.59</v>
+        <v>36.79</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>36.76</v>
+        <v>36.68</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>36.68</v>
+        <v>36.85</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>41.24</v>
+        <v>40.63</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>49.07</v>
+        <v>49.12</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>112.13</v>
+        <v>112.24</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>305.99</v>
+        <v>311.35</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>166.58</v>
+        <v>185.17</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>112.44</v>
+        <v>112.45</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>96.02</v>
+        <v>107.68</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>52.26</v>
+        <v>52.42</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>48.87</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="70">
@@ -6302,52 +6302,52 @@
         <v>8.630000000000001</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>4.46</v>
+        <v>5.09</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>2.08</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S71" s="3" t="n">
         <v>2.75</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>6.28</v>
+        <v>6.4</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>16.83</v>
+        <v>17.12</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>6.66</v>
+        <v>7.59</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>5.96</v>
+        <v>6.07</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>5.18</v>
+        <v>5.81</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="72">
@@ -6554,52 +6554,52 @@
         <v>210.9</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>80.11</v>
+        <v>90.02</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>39.32</v>
+        <v>38.69</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>35.24</v>
+        <v>35.57</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>35.57</v>
+        <v>35.46</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>35.68</v>
+        <v>35.77</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>35.85</v>
+        <v>35.7</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>35.66</v>
+        <v>35.82</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>40.13</v>
+        <v>39.67</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>47.65</v>
+        <v>47.75</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>108.78</v>
+        <v>108.9</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>297.19</v>
+        <v>302.39</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>162.85</v>
+        <v>180.84</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>109.21</v>
+        <v>109.33</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>93.26000000000001</v>
+        <v>104.69</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>50.81</v>
+        <v>51.01</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>47.71</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="75">
@@ -6722,52 +6722,52 @@
         <v>3.8</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>8.02</v>
+        <v>8.16</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.93</v>
+        <v>3.26</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="77">
@@ -6974,52 +6974,52 @@
         <v>207.11</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>78.11</v>
+        <v>87.5</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>38.34</v>
+        <v>37.72</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>34.25</v>
+        <v>34.54</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>34.47</v>
+        <v>34.4</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>34.51</v>
+        <v>34.73</v>
       </c>
       <c r="P79" s="3" t="n">
         <v>34.66</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>34.63</v>
+        <v>34.78</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>38.89</v>
+        <v>38.32</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>46.32</v>
+        <v>46.37</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>105.85</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>289.16</v>
+        <v>294.23</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>159.92</v>
+        <v>177.58</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>106.48</v>
+        <v>106.37</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>90.83</v>
+        <v>101.86</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>49.39</v>
+        <v>49.48</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>46.18</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="80">
@@ -7394,52 +7394,52 @@
         <v>199.91</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>75.03</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>36.9</v>
+        <v>36.34</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34.53</v>
+        <v>34.89</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>34.54</v>
+        <v>34.47</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>34.33</v>
+        <v>34.56</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>34.42</v>
+        <v>34.46</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>34.22</v>
+        <v>34.37</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>38.85</v>
+        <v>38.28</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>46.27</v>
+        <v>46.37</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>99.86</v>
+        <v>99.67</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>273.83</v>
+        <v>278.62</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>151.72</v>
+        <v>167.21</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>102.68</v>
+        <v>102.18</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>92.12</v>
+        <v>103</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>50.09</v>
+        <v>50.19</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>46.55</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="85">
@@ -7562,13 +7562,13 @@
         <v>-7.2</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-3.08</v>
+        <v>-3.85</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.38</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="N86" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -7577,7 +7577,7 @@
         <v>-0.17</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.21</v>
       </c>
       <c r="Q86" s="3" t="n">
         <v>-0.41</v>
@@ -7586,22 +7586,22 @@
         <v>-0.04</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-5.99</v>
+        <v>-6.18</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-15.33</v>
+        <v>-15.6</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-8.19</v>
+        <v>-10.37</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.8</v>
+        <v>-4.19</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Y86" s="3" t="n">
         <v>0.7</v>
@@ -7814,52 +7814,52 @@
         <v>204.45</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>38.22</v>
+        <v>37.38</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>34.12</v>
+        <v>34.43</v>
       </c>
       <c r="N89" s="3" t="n">
         <v>34.33</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>34.33</v>
+        <v>34.63</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>34.56</v>
+        <v>34.59</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>34.53</v>
+        <v>34.71</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>38.7</v>
+        <v>38.05</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>45.77</v>
+        <v>45.73</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>104.9</v>
+        <v>105.01</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>284.61</v>
+        <v>289.02</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>157.55</v>
+        <v>174.96</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>104.09</v>
+        <v>103.88</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>88.62</v>
+        <v>99.48</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>48.71</v>
+        <v>48.75</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>45.91</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="90">
@@ -7982,52 +7982,52 @@
         <v>-2.66</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1</v>
+        <v>-1.04</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.34</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.64</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.84</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.55</v>
+        <v>-5.2</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.62</v>
       </c>
       <c r="W91" s="3" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="X91" s="3" t="n">
         <v>-2.39</v>
       </c>
-      <c r="X91" s="3" t="n">
-        <v>-2.22</v>
-      </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.73</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-27T05:11:47</t>
+          <t>CreatedAt: 2026-03-27T06:11:37</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -671,52 +671,52 @@
         <v>32.91</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>33.29</v>
+        <v>48.73</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>32.14</v>
+        <v>46.26</v>
       </c>
       <c r="L4" s="3" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>34.57</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>36.12</v>
-      </c>
       <c r="N4" s="3" t="n">
-        <v>34.63</v>
+        <v>32.98</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>32.58</v>
+        <v>32.65</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>32.16</v>
+        <v>32.36</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.01</v>
+        <v>32.84</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>46.89</v>
+        <v>46.98</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>48.1</v>
+        <v>47.03</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>49.17</v>
+        <v>55.12</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>49.08</v>
+        <v>54.69</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>47.72</v>
+        <v>48.51</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>40.13</v>
+        <v>45.94</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>46.35</v>
+        <v>46.4</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>55.5</v>
+        <v>55.55</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>38.76</v>
@@ -839,22 +839,22 @@
         <v>-0.53</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.67</v>
+        <v>-1.07</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.02</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>-0.66</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.49</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>-0.55</v>
@@ -863,28 +863,28 @@
         <v>-0.66</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.13</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.13</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.49</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.53</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.24</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.66</v>
@@ -1091,55 +1091,55 @@
         <v>33.17</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>33.65</v>
+        <v>49.31</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>32.33</v>
+        <v>46.62</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.71</v>
+        <v>33.18</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>36.3</v>
+        <v>34.74</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>34.94</v>
+        <v>33.28</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>32.74</v>
+        <v>32.94</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>32.36</v>
+        <v>32.55</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>33.01</v>
+        <v>32.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>46.89</v>
+        <v>47.08</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>47.77</v>
+        <v>46.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.89</v>
+        <v>55.12</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>49.08</v>
+        <v>54.9</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>47.95</v>
+        <v>48.93</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>40.29</v>
+        <v>46.21</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>46.35</v>
+        <v>46.4</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>55.99</v>
+        <v>56.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="10">
@@ -1259,55 +1259,55 @@
         <v>-0.27</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.49</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-0.36</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.04</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.36</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.49</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.32</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.03</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.97</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1511,55 +1511,55 @@
         <v>33.17</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>33.65</v>
+        <v>49.31</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>32.33</v>
+        <v>46.62</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>34.71</v>
+        <v>33.18</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36.3</v>
+        <v>34.74</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>34.94</v>
+        <v>33.28</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>32.74</v>
+        <v>32.94</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>32.36</v>
+        <v>32.55</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>33.01</v>
+        <v>32.8</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>46.89</v>
+        <v>47.08</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>47.77</v>
+        <v>46.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>48.89</v>
+        <v>55.12</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>49.08</v>
+        <v>54.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>47.95</v>
+        <v>48.93</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>40.29</v>
+        <v>46.21</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>46.35</v>
+        <v>46.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>55.99</v>
+        <v>56.1</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="15">
@@ -1679,55 +1679,55 @@
         <v>-0.27</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.49</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.36</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.04</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.36</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.49</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.32</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.03</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.97</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1931,52 +1931,52 @@
         <v>33.04</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>33.39</v>
+        <v>48.83</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>32.17</v>
+        <v>46.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>34.54</v>
+        <v>33.05</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>36.15</v>
+        <v>34.61</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>34.67</v>
+        <v>33.01</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.65</v>
+        <v>32.71</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>32.23</v>
+        <v>32.43</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>46.8</v>
+        <v>46.89</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>47.96</v>
+        <v>46.89</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>49.12</v>
+        <v>55.12</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>49.17</v>
+        <v>54.79</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>47.85</v>
+        <v>48.69</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>40.29</v>
+        <v>46.12</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>46.4</v>
+        <v>46.49</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>55.61</v>
+        <v>55.66</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>39.07</v>
@@ -2099,49 +2099,49 @@
         <v>-0.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.98</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.43</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.72</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.22</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.29</v>
+        <v>-1.27</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.33</v>
+        <v>-1.42</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.27</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.06</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.84</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>-0.95</v>
@@ -2351,52 +2351,52 @@
         <v>33.04</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>33.39</v>
+        <v>48.83</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>32.17</v>
+        <v>46.4</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>34.54</v>
+        <v>33.05</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>36.15</v>
+        <v>34.61</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>34.67</v>
+        <v>33.01</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>32.65</v>
+        <v>32.71</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>32.23</v>
+        <v>32.43</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>46.8</v>
+        <v>46.89</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>47.96</v>
+        <v>46.89</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>49.12</v>
+        <v>55.12</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>49.17</v>
+        <v>54.79</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>47.85</v>
+        <v>48.69</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>40.29</v>
+        <v>46.12</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>46.4</v>
+        <v>46.49</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>55.61</v>
+        <v>55.66</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>39.07</v>
@@ -2519,49 +2519,49 @@
         <v>-0.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.98</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.43</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.72</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.22</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.29</v>
+        <v>-1.27</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.33</v>
+        <v>-1.42</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.27</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.06</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.84</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>-0.95</v>
@@ -2771,55 +2771,55 @@
         <v>33.17</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>33.52</v>
+        <v>48.92</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>32.23</v>
+        <v>46.53</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>34.51</v>
+        <v>33.01</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>36.15</v>
+        <v>34.61</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>34.67</v>
+        <v>33.01</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>32.68</v>
+        <v>32.78</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>32.32</v>
+        <v>32.49</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>32.95</v>
+        <v>32.74</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>46.71</v>
+        <v>46.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>47.82</v>
+        <v>46.76</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>49.12</v>
+        <v>55.12</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>49.32</v>
+        <v>55.06</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>48.14</v>
+        <v>48.93</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>40.52</v>
+        <v>46.35</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>46.49</v>
+        <v>46.58</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>55.72</v>
+        <v>55.83</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="30">
@@ -2939,55 +2939,55 @@
         <v>-0.27</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="O31" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>-0.42</v>
       </c>
-      <c r="P31" s="3" t="n">
-        <v>-0.39</v>
-      </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.75</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.31</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.03</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.83</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.75</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.78</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3191,52 +3191,52 @@
         <v>33.34</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>34.4</v>
+        <v>139.11</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>32.81</v>
+        <v>103.91</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>35.48</v>
+        <v>33.67</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>36.95</v>
+        <v>35.34</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>35.9</v>
+        <v>103.42</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>33.07</v>
+        <v>33.71</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>141.22</v>
+        <v>32.88</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>33.14</v>
+        <v>103.74</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>47.36</v>
+        <v>48.02</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>47.31</v>
+        <v>46.57</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>47.96</v>
+        <v>55.23</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>48.33</v>
+        <v>54.63</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>47.76</v>
+        <v>49.47</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>39.82</v>
+        <v>46.17</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>45.86</v>
+        <v>45.95</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>2000</v>
+        <v>57.29</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>40.06</v>
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>56.78</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>69.22</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>108.64</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>70.77</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1942.82</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3359,52 +3359,52 @@
         <v>-0.1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.25</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="O36" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>-0.13</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>-0.53</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.1</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-1.94</v>
+        <v>-1.58</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-2.78</v>
+        <v>-1.38</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-2.17</v>
+        <v>-1.58</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-1.34</v>
+        <v>-0.49</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.02</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-1.33</v>
+        <v>-1.38</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>0.64</v>
@@ -3611,52 +3611,52 @@
         <v>32.91</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>33.29</v>
+        <v>48.73</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>32.14</v>
+        <v>46.26</v>
       </c>
       <c r="L39" s="3" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>34.57</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>36.12</v>
-      </c>
       <c r="N39" s="3" t="n">
-        <v>34.63</v>
+        <v>32.98</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>32.58</v>
+        <v>32.65</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>32.16</v>
+        <v>32.36</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>33.01</v>
+        <v>32.84</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>46.89</v>
+        <v>46.98</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>48.1</v>
+        <v>47.03</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>49.17</v>
+        <v>55.12</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>49.08</v>
+        <v>54.69</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>47.72</v>
+        <v>48.51</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>40.13</v>
+        <v>45.94</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>46.35</v>
+        <v>46.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>55.5</v>
+        <v>55.55</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>38.76</v>
@@ -3779,22 +3779,22 @@
         <v>-0.53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.67</v>
+        <v>-1.07</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.02</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>-0.66</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.49</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>-0.55</v>
@@ -3803,28 +3803,28 @@
         <v>-0.66</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.13</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.13</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.49</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.53</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.24</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.66</v>
@@ -4031,52 +4031,52 @@
         <v>33.57</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>33.86</v>
+        <v>49.95</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>32.97</v>
+        <v>47.28</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>35.27</v>
+        <v>33.81</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>36.77</v>
+        <v>35.23</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>35.26</v>
+        <v>33.61</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>33.17</v>
+        <v>33.2</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>32.78</v>
+        <v>32.98</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>33.81</v>
+        <v>33.63</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>48.16</v>
+        <v>48.26</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>49.3</v>
+        <v>48.21</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>50.69</v>
+        <v>56.61</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>50.2</v>
+        <v>55.94</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>48.61</v>
+        <v>49.47</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>40.81</v>
+        <v>46.76</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>47.04</v>
+        <v>47.18</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>56.44</v>
+        <v>56.49</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>39.22</v>
@@ -4199,13 +4199,13 @@
         <v>0.13</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>0</v>
@@ -4220,25 +4220,25 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Q46" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>0.14</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>-0.49</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.14</v>
@@ -4451,49 +4451,49 @@
         <v>30.13</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>30.4</v>
+        <v>45.03</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>30.93</v>
+        <v>44.35</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>33.02</v>
+        <v>31.65</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>34.79</v>
+        <v>33.36</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>35.4</v>
+        <v>33.78</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>33.2</v>
+        <v>33.24</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>32.88</v>
+        <v>33.04</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>33.51</v>
+        <v>33.33</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>46.04</v>
+        <v>46.08</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>46.51</v>
+        <v>45.52</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>45.8</v>
+        <v>51.14</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>45.54</v>
+        <v>50.65</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44.07</v>
+        <v>44.85</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>38.55</v>
+        <v>44.18</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>44.81</v>
+        <v>44.94</v>
       </c>
       <c r="Y49" s="3" t="n">
         <v>54.22</v>
@@ -4619,25 +4619,25 @@
         <v>-3.31</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-3.56</v>
+        <v>-4.77</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.93</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.09</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-1.98</v>
+        <v>-1.87</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="Q51" s="3" t="n">
         <v>-0.17</v>
@@ -4646,25 +4646,25 @@
         <v>-2.03</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-2.74</v>
+        <v>-2.64</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-4.95</v>
+        <v>-5.47</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-4.96</v>
+        <v>-5.57</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.02</v>
+        <v>-5.11</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.62</v>
+        <v>-3</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.38</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-2.33</v>
+        <v>-2.39</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>0.32</v>
@@ -4871,55 +4871,55 @@
         <v>32.75</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>33.42</v>
+        <v>49.02</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>32.39</v>
+        <v>46.35</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>35.41</v>
+        <v>33.91</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>37.14</v>
+        <v>35.59</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>35.43</v>
+        <v>33.74</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>33.37</v>
+        <v>33.14</v>
       </c>
       <c r="P54" s="3" t="n">
         <v>32.81</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.64</v>
+        <v>33.46</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>48.11</v>
+        <v>48.16</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>47.5</v>
+        <v>46.4</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>48.93</v>
+        <v>54.59</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>48.7</v>
+        <v>54.26</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>47.48</v>
+        <v>48.36</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>39.67</v>
+        <v>45.54</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>45.77</v>
+        <v>45.99</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>57.47</v>
+        <v>57.59</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>39.86</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="55">
@@ -5039,25 +5039,25 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.78</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.93</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>-0.03</v>
@@ -5069,25 +5069,25 @@
         <v>-1.76</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.81</v>
+        <v>-2.02</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.95</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.6</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.64</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.33</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="57">
@@ -5291,52 +5291,52 @@
         <v>34.51</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>34.79</v>
+        <v>51.4</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>33.96</v>
+        <v>48.64</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>36.28</v>
+        <v>34.78</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>37.83</v>
+        <v>36.25</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>36.27</v>
+        <v>34.62</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>34.16</v>
+        <v>34.2</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>33.76</v>
+        <v>33.93</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>34.79</v>
+        <v>34.6</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>49.6</v>
+        <v>49.65</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>50.83</v>
+        <v>49.7</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>52.26</v>
+        <v>58.36</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>51.64</v>
+        <v>57.54</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>50</v>
+        <v>50.88</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>41.97</v>
+        <v>48.1</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>48.35</v>
+        <v>48.49</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>58.06</v>
+        <v>58.12</v>
       </c>
       <c r="Z59" s="3" t="n">
         <v>40.43</v>
@@ -5459,25 +5459,25 @@
         <v>1.07</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.83</v>
+        <v>1.59</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>1.06</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Q61" s="3" t="n">
         <v>1.11</v>
@@ -5486,19 +5486,19 @@
         <v>1.54</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>1.16</v>
@@ -5711,52 +5711,52 @@
         <v>35.05</v>
       </c>
       <c r="J64" s="3" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="L64" s="3" t="n">
         <v>35.33</v>
       </c>
-      <c r="K64" s="3" t="n">
-        <v>34.53</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>36.85</v>
-      </c>
       <c r="M64" s="3" t="n">
-        <v>38.42</v>
+        <v>36.81</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>36.81</v>
+        <v>35.12</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>34.66</v>
+        <v>34.7</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>34.25</v>
+        <v>34.46</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>35.37</v>
+        <v>35.18</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>50.44</v>
+        <v>50.48</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>51.68</v>
+        <v>50.53</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>53.19</v>
+        <v>59.4</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>52.61</v>
+        <v>58.56</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>50.88</v>
+        <v>51.77</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>42.67</v>
+        <v>48.9</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>49.15</v>
+        <v>49.3</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>59.03</v>
+        <v>59.09</v>
       </c>
       <c r="Z64" s="3" t="n">
         <v>41.02</v>
@@ -5879,46 +5879,46 @@
         <v>1.61</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.38</v>
+        <v>2.46</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O66" s="3" t="n">
         <v>1.56</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>2.37</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>1.97</v>
@@ -6131,52 +6131,52 @@
         <v>35.42</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>35.59</v>
+        <v>52.76</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>34.89</v>
+        <v>49.98</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>37.28</v>
+        <v>35.7</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>38.83</v>
+        <v>37.24</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>37.27</v>
+        <v>35.53</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>35.07</v>
+        <v>35.1</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>34.65</v>
+        <v>34.86</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>35.75</v>
+        <v>35.55</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>50.92</v>
+        <v>51.02</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>52.23</v>
+        <v>51.07</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>53.64</v>
+        <v>59.9</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>52.83</v>
+        <v>58.8</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>50.99</v>
+        <v>51.88</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>42.8</v>
+        <v>49.05</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>49.51</v>
+        <v>49.66</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>59.65</v>
+        <v>59.71</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>41.54</v>
@@ -6299,52 +6299,52 @@
         <v>1.98</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="M71" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q71" s="3" t="n">
         <v>2.06</v>
       </c>
-      <c r="N71" s="3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>2.07</v>
-      </c>
       <c r="R71" s="3" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.9</v>
+        <v>3.29</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>2.33</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>2.12</v>
@@ -6551,52 +6551,52 @@
         <v>34.37</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>34.65</v>
+        <v>51.24</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>33.89</v>
+        <v>48.54</v>
       </c>
       <c r="L74" s="3" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="M74" s="3" t="n">
         <v>36.17</v>
       </c>
-      <c r="M74" s="3" t="n">
-        <v>37.75</v>
-      </c>
       <c r="N74" s="3" t="n">
-        <v>36.24</v>
+        <v>34.58</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>34.23</v>
+        <v>34.27</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>33.69</v>
+        <v>33.9</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>34.75</v>
+        <v>34.56</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>50.72</v>
+        <v>49.6</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>51.99</v>
+        <v>58.06</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>51.43</v>
+        <v>57.31</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>49.8</v>
+        <v>50.67</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>41.93</v>
+        <v>48.05</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>48.15</v>
+        <v>48.29</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>57.82</v>
+        <v>57.88</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>40.39</v>
@@ -6719,19 +6719,19 @@
         <v>0.93</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="L76" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>1.13</v>
@@ -6740,28 +6740,28 @@
         <v>0.98</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R76" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S76" s="3" t="n">
         <v>1.44</v>
       </c>
-      <c r="S76" s="3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="T76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>1.27</v>
@@ -6971,52 +6971,52 @@
         <v>33.44</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>33.96</v>
+        <v>49.8</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>33.01</v>
+        <v>47.28</v>
       </c>
       <c r="L79" s="3" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="M79" s="3" t="n">
         <v>35.23</v>
       </c>
-      <c r="M79" s="3" t="n">
-        <v>36.77</v>
-      </c>
       <c r="N79" s="3" t="n">
-        <v>35.19</v>
+        <v>33.54</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>33.1</v>
+        <v>33.14</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>32.71</v>
+        <v>32.91</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>33.67</v>
+        <v>33.49</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>48.07</v>
+        <v>48.11</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>49.25</v>
+        <v>48.16</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>50.74</v>
+        <v>56.61</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>50.5</v>
+        <v>56.22</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>49.1</v>
+        <v>49.96</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>41.17</v>
+        <v>47.18</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>47.19</v>
+        <v>47.32</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>56.55</v>
+        <v>56.61</v>
       </c>
       <c r="Z79" s="3" t="n">
         <v>39.42</v>
@@ -7391,55 +7391,55 @@
         <v>32.18</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>32.84</v>
+        <v>48.07</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>31.74</v>
+        <v>45.33</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>35.48</v>
+        <v>34.01</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>37.03</v>
+        <v>35.51</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>35.29</v>
+        <v>33.61</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>33.24</v>
+        <v>33.17</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>32.65</v>
+        <v>32.78</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>33.61</v>
+        <v>33.49</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>47.97</v>
+        <v>48.11</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>46.25</v>
+        <v>45.22</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>47.69</v>
+        <v>53.25</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>47.42</v>
+        <v>52.83</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>46.41</v>
+        <v>47.36</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>38.81</v>
+        <v>44.56</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>44.56</v>
+        <v>44.81</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>57.47</v>
+        <v>57.7</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>39.78</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="85">
@@ -7559,55 +7559,55 @@
         <v>-1.26</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.73</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.95</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-3.01</v>
+        <v>-2.94</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.05</v>
+        <v>-3.35</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-3.08</v>
+        <v>-3.38</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.69</v>
+        <v>-2.6</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.63</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-2.63</v>
+        <v>-2.51</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="87">
@@ -7811,55 +7811,55 @@
         <v>33.17</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>33.52</v>
+        <v>48.92</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>32.23</v>
+        <v>46.53</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>34.51</v>
+        <v>33.01</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>36.15</v>
+        <v>34.61</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>34.67</v>
+        <v>33.01</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>32.68</v>
+        <v>32.78</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>32.32</v>
+        <v>32.49</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>32.95</v>
+        <v>32.74</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>46.71</v>
+        <v>46.8</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>47.82</v>
+        <v>46.76</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>49.12</v>
+        <v>55.12</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>49.32</v>
+        <v>55.06</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>48.14</v>
+        <v>48.93</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>40.52</v>
+        <v>46.35</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>46.49</v>
+        <v>46.58</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>55.72</v>
+        <v>55.83</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="90">
@@ -7979,55 +7979,55 @@
         <v>-0.27</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="O91" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="P91" s="3" t="n">
         <v>-0.42</v>
       </c>
-      <c r="P91" s="3" t="n">
-        <v>-0.39</v>
-      </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.75</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.31</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.4</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.03</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.83</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.75</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.78</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-28T12:10:28</t>
+          <t>CreatedAt: 2026-03-28T13:09:27</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -692,34 +692,34 @@
         <v>32.45</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>32.31</v>
+        <v>32.1</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>32.97</v>
+        <v>33.01</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>34.44</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>49.44</v>
+        <v>52.95</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>49.44</v>
+        <v>49.39</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>35.18</v>
+        <v>48.14</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.95</v>
+        <v>37.64</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>47.88</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="5">
@@ -860,22 +860,22 @@
         <v>-0.78</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.8</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.43</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>-0.3</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="7">
@@ -1112,34 +1112,34 @@
         <v>32.55</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>32.5</v>
+        <v>32.16</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>31.93</v>
+        <v>32.66</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>32.85</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>34.71</v>
+        <v>34.74</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48.64</v>
+        <v>48.54</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>49.78</v>
+        <v>53.32</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>49.78</v>
+        <v>49.73</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>35.46</v>
+        <v>48.53</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>35.34</v>
+        <v>38.14</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>48.8</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="10">
@@ -1280,19 +1280,19 @@
         <v>-0.68</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>-0.85</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.38</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>0</v>
@@ -1301,13 +1301,13 @@
         <v>0.05</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1532,34 +1532,34 @@
         <v>32.55</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>32.5</v>
+        <v>32.16</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>31.93</v>
+        <v>32.66</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>32.85</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>34.71</v>
+        <v>34.74</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>48.64</v>
+        <v>48.54</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>49.78</v>
+        <v>53.32</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>49.78</v>
+        <v>49.73</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>35.46</v>
+        <v>48.53</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>35.34</v>
+        <v>38.14</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>48.8</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="15">
@@ -1700,19 +1700,19 @@
         <v>-0.68</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>-0.85</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.38</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>0</v>
@@ -1721,13 +1721,13 @@
         <v>0.05</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="17">
@@ -1952,34 +1952,34 @@
         <v>32.64</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>32.56</v>
+        <v>32.26</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>31.96</v>
+        <v>32.73</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>33.07</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>34.47</v>
+        <v>34.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>48.49</v>
+        <v>48.39</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>49.53</v>
+        <v>53.06</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>49.49</v>
+        <v>49.44</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>35.25</v>
+        <v>48.24</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.99</v>
+        <v>37.75</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>48.07</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="20">
@@ -2120,34 +2120,34 @@
         <v>-0.59</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.65</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="22">
@@ -2372,34 +2372,34 @@
         <v>32.64</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>32.56</v>
+        <v>32.26</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>31.96</v>
+        <v>32.73</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>33.07</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>34.47</v>
+        <v>34.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>48.49</v>
+        <v>48.39</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>49.53</v>
+        <v>53.06</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>49.49</v>
+        <v>49.44</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>35.25</v>
+        <v>48.24</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.99</v>
+        <v>37.75</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>48.07</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="25">
@@ -2540,34 +2540,34 @@
         <v>-0.59</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.65</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="27">
@@ -2792,34 +2792,34 @@
         <v>32.93</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>32.89</v>
+        <v>32.48</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>32.22</v>
+        <v>32.99</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.23</v>
+        <v>33.27</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>34.57</v>
+        <v>34.61</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>48.64</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>49.58</v>
+        <v>53.16</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>49.49</v>
+        <v>49.44</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>35.28</v>
+        <v>48.29</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.99</v>
+        <v>37.79</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>48.31</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="30">
@@ -2960,34 +2960,34 @@
         <v>-0.3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.42</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="32">
@@ -3212,34 +3212,34 @@
         <v>31.65</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>31.57</v>
+        <v>31.27</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>31.23</v>
+        <v>31.91</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>31.64</v>
+        <v>31.58</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>35.37</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>48.83</v>
+        <v>48.64</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>50.59</v>
+        <v>54.08</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>154.26</v>
+        <v>50.7</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>36.12</v>
+        <v>49.53</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>36.59</v>
+        <v>39.49</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>51.01</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="35">
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>103.51</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
@@ -3380,34 +3380,34 @@
         <v>-1.58</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.63</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.37</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.12</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>1.01</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.55</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="37">
@@ -3632,34 +3632,34 @@
         <v>32.45</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>32.31</v>
+        <v>32.1</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>32.97</v>
+        <v>33.01</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>34.44</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>49.44</v>
+        <v>52.95</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>49.44</v>
+        <v>49.39</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>35.18</v>
+        <v>48.14</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.95</v>
+        <v>37.64</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>47.88</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="40">
@@ -3800,22 +3800,22 @@
         <v>-0.78</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.8</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>-0.6899999999999999</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.43</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>-0.3</v>
@@ -3824,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="42">
@@ -4052,10 +4052,10 @@
         <v>32.93</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>32.69</v>
+        <v>32.61</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>32.38</v>
+        <v>33.09</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>33.67</v>
@@ -4064,22 +4064,22 @@
         <v>35.2</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>48.73</v>
+        <v>48.59</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>49.78</v>
+        <v>53.32</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>50.03</v>
+        <v>49.98</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>35.46</v>
+        <v>48.53</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>35.34</v>
+        <v>37.98</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>48.6</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="45">
@@ -4223,7 +4223,7 @@
         <v>-0.29</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>-0.03</v>
@@ -4241,13 +4241,13 @@
         <v>0.3</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -4472,34 +4472,34 @@
         <v>33.5</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>33.15</v>
+        <v>33.1</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>32.77</v>
+        <v>33.42</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>32</v>
+        <v>31.97</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>33.08</v>
+        <v>33.01</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>43.4</v>
+        <v>43.19</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44.29</v>
+        <v>47.44</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>44.44</v>
+        <v>44.4</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>33.06</v>
+        <v>45.29</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>34.95</v>
+        <v>37.6</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>48.21</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="50">
@@ -4640,34 +4640,34 @@
         <v>0.27</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.73</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.05</v>
+        <v>-2.11</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.38</v>
+        <v>-5.44</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.49</v>
+        <v>-5.88</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.29</v>
+        <v>-5.28</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.12</v>
+        <v>-2.85</v>
       </c>
       <c r="Y51" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="Z51" s="3" t="n">
         <v>-0.17</v>
-      </c>
-      <c r="Z51" s="3" t="n">
-        <v>-0.24</v>
       </c>
     </row>
     <row r="52">
@@ -4892,34 +4892,34 @@
         <v>33.36</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.22</v>
+        <v>33.07</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>32.73</v>
+        <v>33.65</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>33.87</v>
+        <v>33.9</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>35.13</v>
+        <v>35.09</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>47.55</v>
+        <v>47.4</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>48.66</v>
+        <v>52.07</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>48.81</v>
+        <v>48.71</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>34.55</v>
+        <v>47.25</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>34.85</v>
+        <v>38.02</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>49.19</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="55">
@@ -5060,34 +5060,34 @@
         <v>0.13</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.23</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.25</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.97</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.9</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.28</v>
+        <v>0.3</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.74</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="57">
@@ -5312,10 +5312,10 @@
         <v>34.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>33.83</v>
+        <v>33.74</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>33.44</v>
+        <v>34.17</v>
       </c>
       <c r="S59" s="3" t="n">
         <v>34.71</v>
@@ -5324,22 +5324,22 @@
         <v>36.21</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>49.83</v>
+        <v>49.68</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>50.9</v>
+        <v>54.52</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>51.32</v>
+        <v>51.27</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>36.38</v>
+        <v>49.79</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>36.25</v>
+        <v>38.96</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>49.95</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="60">
@@ -5480,10 +5480,10 @@
         <v>0.85</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="S61" s="3" t="n">
         <v>1.01</v>
@@ -5492,22 +5492,22 @@
         <v>1.09</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>1.59</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="62">
@@ -5732,10 +5732,10 @@
         <v>34.65</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>34.33</v>
+        <v>34.31</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>34</v>
+        <v>34.71</v>
       </c>
       <c r="S64" s="3" t="n">
         <v>35.29</v>
@@ -5744,22 +5744,22 @@
         <v>36.82</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>50.66</v>
+        <v>50.5</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>51.69</v>
+        <v>55.43</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>52.19</v>
+        <v>52.14</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>36.91</v>
+        <v>50.57</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.78</v>
+        <v>39.53</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>50.69</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="65">
@@ -5900,10 +5900,10 @@
         <v>1.42</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S66" s="3" t="n">
         <v>1.59</v>
@@ -5915,19 +5915,19 @@
         <v>1.87</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>2.45</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="67">
@@ -6152,10 +6152,10 @@
         <v>35.09</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>34.8</v>
+        <v>34.71</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>34.39</v>
+        <v>35.15</v>
       </c>
       <c r="S69" s="3" t="n">
         <v>35.66</v>
@@ -6164,22 +6164,22 @@
         <v>37.21</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>50.81</v>
+        <v>50.61</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>51.86</v>
+        <v>55.54</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>52.74</v>
+        <v>52.69</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>37.34</v>
+        <v>51.11</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>37.25</v>
+        <v>40</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>51.33</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="70">
@@ -6320,10 +6320,10 @@
         <v>1.86</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="S71" s="3" t="n">
         <v>1.96</v>
@@ -6332,22 +6332,22 @@
         <v>2.08</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.17</v>
+        <v>2.96</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.87</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="72">
@@ -6572,34 +6572,34 @@
         <v>34.26</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>33.97</v>
+        <v>33.88</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>33.47</v>
+        <v>34.21</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>34.64</v>
+        <v>34.67</v>
       </c>
       <c r="T74" s="3" t="n">
         <v>36.17</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>49.68</v>
+        <v>49.53</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>50.69</v>
+        <v>54.3</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>51.11</v>
+        <v>51.06</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>36.34</v>
+        <v>49.73</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>36.18</v>
+        <v>39</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>50.01</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="75">
@@ -6740,13 +6740,13 @@
         <v>1.03</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>1.05</v>
@@ -6755,19 +6755,19 @@
         <v>0.89</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>1.38</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="77">
@@ -6992,10 +6992,10 @@
         <v>33.23</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>32.99</v>
+        <v>32.9</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>32.57</v>
+        <v>33.28</v>
       </c>
       <c r="S79" s="3" t="n">
         <v>33.7</v>
@@ -7004,22 +7004,22 @@
         <v>35.13</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>49.78</v>
+        <v>53.32</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>49.73</v>
+        <v>49.69</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>35.18</v>
+        <v>48.14</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>35.13</v>
+        <v>37.72</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>48.46</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="80">
@@ -7412,34 +7412,34 @@
         <v>32.96</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>32.86</v>
+        <v>32.77</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>32.47</v>
+        <v>33.32</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>33.57</v>
+        <v>33.67</v>
       </c>
       <c r="T84" s="3" t="n">
         <v>34.95</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>46.37</v>
+        <v>46.23</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>47.59</v>
+        <v>50.93</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>47.28</v>
+        <v>47.18</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>33.44</v>
+        <v>45.68</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>33.78</v>
+        <v>37.68</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>48.94</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="85">
@@ -7583,31 +7583,31 @@
         <v>-0.13</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.03</v>
       </c>
       <c r="T86" s="3" t="n">
         <v>-0.17</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.41</v>
+        <v>-2.4</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.19</v>
+        <v>-2.39</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2.5</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.47</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-1.35</v>
+        <v>-0.04</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="87">
@@ -7832,34 +7832,34 @@
         <v>32.93</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>32.89</v>
+        <v>32.48</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>32.22</v>
+        <v>32.99</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>33.23</v>
+        <v>33.27</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>34.57</v>
+        <v>34.61</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>48.64</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>49.58</v>
+        <v>53.16</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>49.49</v>
+        <v>49.44</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>35.28</v>
+        <v>48.29</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>34.99</v>
+        <v>37.79</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>48.31</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="90">
@@ -8000,34 +8000,34 @@
         <v>-0.3</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.42</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="W91" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-29T14:08:47</t>
+          <t>CreatedAt: 2026-03-29T15:08:37</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -698,28 +698,28 @@
         <v>32.27</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>39.11</v>
+        <v>39.03</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>44.18</v>
+        <v>55</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>153.6</v>
+        <v>176.85</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>49.1</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>40.17</v>
+        <v>36.55</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.07</v>
+        <v>33.36</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>37.09</v>
+        <v>40.21</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>34.43</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="5">
@@ -866,28 +866,28 @@
         <v>-0.68</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.55</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-2.12</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.89</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1118,28 +1118,28 @@
         <v>33.04</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>44.57</v>
+        <v>55.38</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>155.3</v>
+        <v>175.98</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>49.74</v>
+        <v>74.52</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>40.82</v>
+        <v>36.99</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>33.64</v>
+        <v>33.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>37.61</v>
+        <v>40.86</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>35.02</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="10">
@@ -1286,28 +1286,28 @@
         <v>0.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.32</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.93</v>
+        <v>-2.99</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="12">
@@ -1538,28 +1538,28 @@
         <v>33.04</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>44.57</v>
+        <v>55.38</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>155.3</v>
+        <v>175.98</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>49.74</v>
+        <v>74.52</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>40.82</v>
+        <v>36.99</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>33.64</v>
+        <v>33.9</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>37.61</v>
+        <v>40.86</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>35.02</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="15">
@@ -1706,28 +1706,28 @@
         <v>0.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.32</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.93</v>
+        <v>-2.99</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="17">
@@ -1958,28 +1958,28 @@
         <v>32.46</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>39.22</v>
+        <v>39.15</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>44.26</v>
+        <v>55.22</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>153.91</v>
+        <v>177.02</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>49.29</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="W19" s="3" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="Y19" s="3" t="n">
         <v>40.37</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>37.2</v>
-      </c>
       <c r="Z19" s="3" t="n">
-        <v>34.57</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="20">
@@ -2126,28 +2126,28 @@
         <v>-0.49</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.55</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-1.95</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.74</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.17</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="22">
@@ -2378,28 +2378,28 @@
         <v>32.46</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>39.22</v>
+        <v>39.15</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>44.26</v>
+        <v>55.22</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>153.91</v>
+        <v>177.02</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>49.29</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="W24" s="3" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="Y24" s="3" t="n">
         <v>40.37</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>37.2</v>
-      </c>
       <c r="Z24" s="3" t="n">
-        <v>34.57</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="25">
@@ -2546,28 +2546,28 @@
         <v>-0.49</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.55</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-1.95</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.74</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.17</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="27">
@@ -2798,28 +2798,28 @@
         <v>32.65</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>39.34</v>
+        <v>39.3</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>44.4</v>
+        <v>55.44</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>154.37</v>
+        <v>177.55</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>49.49</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>40.53</v>
+        <v>36.88</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>33.34</v>
+        <v>33.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>37.35</v>
+        <v>40.49</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>34.71</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="30">
@@ -2966,28 +2966,28 @@
         <v>-0.29</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0</v>
+        <v>-1.42</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="32">
@@ -3218,28 +3218,28 @@
         <v>112.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>40.71</v>
+        <v>39.77</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>45.48</v>
+        <v>55.66</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>158.98</v>
+        <v>170.77</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>51.02</v>
+        <v>75.72</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>42.09</v>
+        <v>37.59</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>34.98</v>
+        <v>35.25</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>38.9</v>
+        <v>42.3</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>36.33</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="35">
@@ -3386,28 +3386,28 @@
         <v>1.88</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.02</v>
+        <v>0.08</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.82</v>
+        <v>0.11</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>4.61</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.53</v>
+        <v>0.91</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.52</v>
+        <v>0.68</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.42</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="37">
@@ -3638,28 +3638,28 @@
         <v>32.27</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>39.11</v>
+        <v>39.03</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>44.18</v>
+        <v>55</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>153.6</v>
+        <v>176.85</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>49.1</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>40.17</v>
+        <v>36.55</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>33.07</v>
+        <v>33.36</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>37.09</v>
+        <v>40.21</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>34.43</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="40">
@@ -3806,28 +3806,28 @@
         <v>-0.68</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.55</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-2.12</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.89</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4058,28 +4058,28 @@
         <v>32.94</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>39.98</v>
+        <v>39.73</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>45.02</v>
+        <v>56</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>155.93</v>
+        <v>180.23</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>49.89</v>
+        <v>75.34</v>
       </c>
       <c r="W44" s="3" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Y44" s="3" t="n">
         <v>40.86</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>37.72</v>
-      </c>
       <c r="Z44" s="3" t="n">
-        <v>35.09</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="45">
@@ -4226,28 +4226,28 @@
         <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.17</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="47">
@@ -4478,28 +4478,28 @@
         <v>32.88</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>37.84</v>
+        <v>37.73</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>42.74</v>
+        <v>53.16</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>138.82</v>
+        <v>160.8</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>44.42</v>
+        <v>67.16</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>38.13</v>
+        <v>34.7</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>31.48</v>
+        <v>31.79</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>35.51</v>
+        <v>38.42</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>34.74</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="50">
@@ -4646,28 +4646,28 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.96</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.39</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-15.55</v>
+        <v>-18.17</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.06</v>
+        <v>-7.66</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.44</v>
+        <v>-2.22</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.84</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.23</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="52">
@@ -4898,28 +4898,28 @@
         <v>32.78</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>39.89</v>
+        <v>39.73</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>44.4</v>
+        <v>55.27</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>151.04</v>
+        <v>174.77</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>48.42</v>
+        <v>73.13</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>39.93</v>
+        <v>36.02</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>32.88</v>
+        <v>33.17</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>37.69</v>
+        <v>40.86</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>35.23</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="55">
@@ -5066,28 +5066,28 @@
         <v>-0.16</v>
       </c>
       <c r="S56" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="Y56" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="T56" s="3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="U56" s="3" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="V56" s="3" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="W56" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="X56" s="3" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="Y56" s="3" t="n">
-        <v>0.19</v>
-      </c>
       <c r="Z56" s="3" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="57">
@@ -5318,28 +5318,28 @@
         <v>34.07</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>41.13</v>
+        <v>41.01</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>46.28</v>
+        <v>57.56</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>159.97</v>
+        <v>185.27</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>51.23</v>
+        <v>77.37</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>41.96</v>
+        <v>38.18</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>34.37</v>
+        <v>34.71</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>38.82</v>
+        <v>42.04</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>36.14</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="60">
@@ -5486,28 +5486,28 @@
         <v>1.12</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="62">
@@ -5738,28 +5738,28 @@
         <v>34.6</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>41.87</v>
+        <v>41.7</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>47.06</v>
+        <v>58.53</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>162.66</v>
+        <v>188.59</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>52.09</v>
+        <v>78.75</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>42.62</v>
+        <v>38.82</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>34.87</v>
+        <v>35.25</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>39.35</v>
+        <v>42.7</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>36.64</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="65">
@@ -5906,28 +5906,28 @@
         <v>1.66</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="W66" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y66" s="3" t="n">
         <v>2.05</v>
       </c>
-      <c r="X66" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y66" s="3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z66" s="3" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="67">
@@ -6158,28 +6158,28 @@
         <v>35.05</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>42.27</v>
+        <v>42.14</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>47.51</v>
+        <v>59.16</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>164.4</v>
+        <v>190.39</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>52.65</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>43.12</v>
+        <v>39.19</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>35.32</v>
+        <v>35.66</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>39.85</v>
+        <v>43.2</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>37.14</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="70">
@@ -6326,28 +6326,28 @@
         <v>2.1</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.85</v>
+        <v>3.61</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>10.03</v>
+        <v>11.42</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.16</v>
+        <v>4.69</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="72">
@@ -6578,28 +6578,28 @@
         <v>34.17</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>41.09</v>
+        <v>40.96</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>46.19</v>
+        <v>57.44</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>159.31</v>
+        <v>184.5</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>51.02</v>
+        <v>77.05</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>41.83</v>
+        <v>38.02</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.26</v>
+        <v>34.6</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>38.66</v>
+        <v>41.91</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>36.22</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="75">
@@ -6746,28 +6746,28 @@
         <v>1.23</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>4.94</v>
+        <v>5.54</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="77">
@@ -6998,28 +6998,28 @@
         <v>32.94</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>39.7</v>
+        <v>39.69</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>44.66</v>
+        <v>55.55</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>154.37</v>
+        <v>178.97</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>49.49</v>
+        <v>74.81</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>40.57</v>
+        <v>36.92</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>33.3</v>
+        <v>33.63</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>37.5</v>
+        <v>40.65</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>34.92</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="80">
@@ -7418,28 +7418,28 @@
         <v>32.58</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>39.89</v>
+        <v>39.73</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>44.49</v>
+        <v>55.33</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>147.72</v>
+        <v>170.93</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>47.4</v>
+        <v>71.52</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>39.09</v>
+        <v>35.26</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>32.21</v>
+        <v>32.49</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>37.88</v>
+        <v>41.02</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>35.3</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="85">
@@ -7586,28 +7586,28 @@
         <v>-0.36</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.22</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.65</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.09</v>
+        <v>-3.29</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.66</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.14</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -7838,28 +7838,28 @@
         <v>32.65</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>39.34</v>
+        <v>39.3</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>44.4</v>
+        <v>55.44</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>154.37</v>
+        <v>177.55</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>49.49</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>40.53</v>
+        <v>36.88</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>33.34</v>
+        <v>33.6</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>37.35</v>
+        <v>40.49</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>34.71</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="90">
@@ -8006,28 +8006,28 @@
         <v>-0.29</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>0</v>
+        <v>-1.42</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="W91" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-03-30T04:11:47</t>
+          <t>CreatedAt: 2026-03-30T05:11:27</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -668,58 +668,58 @@
         <v>46.94</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>33.62</v>
+        <v>33.34</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>33.21</v>
+        <v>83</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>32.59</v>
+        <v>-100</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>25.64</v>
+        <v>32.27</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>32.46</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>15.41</v>
+        <v>15.58</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>25.51</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>32.93</v>
+        <v>33.15</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>32.85</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>32.66</v>
+        <v>32.78</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>33.52</v>
+        <v>33.92</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>35.92</v>
+        <v>35.88</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>39.43</v>
+        <v>37.1</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>49.72</v>
+        <v>45.38</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>38.5</v>
+        <v>33.51</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>32.66</v>
+        <v>25.64</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>33.54</v>
+        <v>33.23</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>33.53</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="5">
@@ -836,28 +836,28 @@
         <v>-0.23</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.98</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.13</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>-1.14</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>-0.99</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-1.05</v>
@@ -866,25 +866,25 @@
         <v>-1.18</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.26</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.18</v>
       </c>
       <c r="U6" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>-1.1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-1.11</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.8</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>-132.51</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1088,58 +1088,58 @@
         <v>47.41</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.03</v>
+        <v>33.74</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>33.7</v>
+        <v>83.53</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>32.91</v>
+        <v>-100</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>25.97</v>
+        <v>32.74</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.84</v>
+        <v>32.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.67</v>
+        <v>15.84</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>25.93</v>
+        <v>25.91</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>33.41</v>
+        <v>33.61</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>33.23</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>33.14</v>
+        <v>33.19</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>33.65</v>
+        <v>33.99</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>36.23</v>
+        <v>36.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>39.82</v>
+        <v>37.43</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>50.25</v>
+        <v>45.92</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>38.65</v>
+        <v>33.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>32.94</v>
+        <v>25.86</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>33.97</v>
+        <v>33.68</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>33.96</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="10">
@@ -1256,55 +1256,55 @@
         <v>0.24</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.17</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.65</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.79</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.66</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.19</v>
       </c>
       <c r="T11" s="3" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>-0.83</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-1.11</v>
-      </c>
       <c r="W11" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.01</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.54</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.64</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>-0.37</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>-132.83</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1508,58 +1508,58 @@
         <v>47.41</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>34.03</v>
+        <v>33.74</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>33.7</v>
+        <v>83.53</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>32.91</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>25.97</v>
+        <v>32.74</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>32.84</v>
+        <v>32.8</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.67</v>
+        <v>15.84</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>25.93</v>
+        <v>25.91</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>33.41</v>
+        <v>33.61</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>33.23</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>33.14</v>
+        <v>33.19</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>33.65</v>
+        <v>33.99</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>36.23</v>
+        <v>36.2</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>39.82</v>
+        <v>37.43</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>50.25</v>
+        <v>45.92</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>38.65</v>
+        <v>33.6</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>32.94</v>
+        <v>25.86</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>33.97</v>
+        <v>33.68</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>33.96</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="15">
@@ -1676,55 +1676,55 @@
         <v>0.24</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.17</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.65</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.79</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-0.66</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.19</v>
       </c>
       <c r="T16" s="3" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="V16" s="3" t="n">
         <v>-0.83</v>
       </c>
-      <c r="U16" s="3" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>-1.11</v>
-      </c>
       <c r="W16" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.01</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.54</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.64</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>-0.37</v>
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>-132.83</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1928,58 +1928,58 @@
         <v>47.17</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>33.86</v>
+        <v>33.54</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>33.41</v>
+        <v>83.23</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>32.75</v>
+        <v>-100</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>25.76</v>
+        <v>32.46</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>32.58</v>
+        <v>32.55</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.46</v>
+        <v>15.61</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>25.63</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>33.09</v>
+        <v>33.28</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32.98</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>32.75</v>
+        <v>32.84</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>33.52</v>
+        <v>33.89</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>36.06</v>
+        <v>35.98</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>39.58</v>
+        <v>37.25</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>49.81</v>
+        <v>45.51</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>38.61</v>
+        <v>33.54</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>32.75</v>
+        <v>25.71</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>33.61</v>
+        <v>33.32</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>33.63</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="20">
@@ -2096,58 +2096,58 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.47</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.82</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-1.01</v>
+        <v>-1.04</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>-0.87</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="R21" s="3" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T21" s="3" t="n">
         <v>-1.08</v>
       </c>
-      <c r="S21" s="3" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-1.01</v>
-      </c>
       <c r="U21" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.89</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.23</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.07</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="22">
@@ -2267,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
+        <v>-132.67</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2348,58 +2348,58 @@
         <v>47.17</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>33.86</v>
+        <v>33.54</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>33.41</v>
+        <v>83.23</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>32.75</v>
+        <v>-100</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>25.76</v>
+        <v>32.46</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>32.58</v>
+        <v>32.55</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>15.46</v>
+        <v>15.61</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>25.63</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>33.09</v>
+        <v>33.28</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>32.98</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>32.75</v>
+        <v>32.84</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>33.52</v>
+        <v>33.89</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>36.06</v>
+        <v>35.98</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>39.58</v>
+        <v>37.25</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>49.81</v>
+        <v>45.51</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>38.61</v>
+        <v>33.54</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>32.75</v>
+        <v>25.71</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>33.61</v>
+        <v>33.32</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>33.63</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="25">
@@ -2516,58 +2516,58 @@
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.47</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.82</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-1.01</v>
+        <v>-1.04</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>-0.87</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="R26" s="3" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T26" s="3" t="n">
         <v>-1.08</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>-1.01</v>
-      </c>
       <c r="U26" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.89</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.23</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.07</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="27">
@@ -2687,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>-132.67</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2768,58 +2768,58 @@
         <v>47.46</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>34.13</v>
+        <v>33.81</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>33.67</v>
+        <v>83.53</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>32.95</v>
+        <v>-100</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>25.97</v>
+        <v>32.68</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>32.74</v>
+        <v>32.71</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>15.5</v>
+        <v>15.66</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>25.78</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>33.28</v>
+        <v>33.44</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>33.14</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>32.85</v>
+        <v>32.94</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.58</v>
+        <v>33.86</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>36.23</v>
+        <v>36.16</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>39.82</v>
+        <v>37.43</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>50.01</v>
+        <v>45.74</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>38.76</v>
+        <v>33.7</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>32.91</v>
+        <v>25.84</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>33.7</v>
+        <v>33.42</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>33.69</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="30">
@@ -2936,55 +2936,55 @@
         <v>0.28</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.72</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.88</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0.72</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.77</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0.76</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.02</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.32</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.9</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.01</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.57</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>-0.64</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>-132.83</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3191,55 +3191,55 @@
         <v>129</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>34.28</v>
+        <v>99</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>33.11</v>
+        <v>-100</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>26.28</v>
+        <v>33.3</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>33.49</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>16.39</v>
+        <v>129.53</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>26.69</v>
+        <v>26.66</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>34.29</v>
+        <v>129.18</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>33.9</v>
+        <v>33.93</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>34.35</v>
+        <v>34.33</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>33.94</v>
+        <v>34.32</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>36.55</v>
+        <v>36.52</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>40.13</v>
+        <v>37.77</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>51.51</v>
+        <v>46.98</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>38.57</v>
+        <v>33.54</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>33.3</v>
+        <v>26.15</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>35.1</v>
+        <v>34.78</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>35.07</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="35">
@@ -3272,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>94.84</v>
+        <v>95.12</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>14.89</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>112.96</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>94.69</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0.52</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>-0.43</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>-0.1</v>
@@ -3374,40 +3374,40 @@
         <v>0.38</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.86</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.55</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.26</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="37">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>-133.06</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3608,58 +3608,58 @@
         <v>46.94</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>33.62</v>
+        <v>33.34</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>33.21</v>
+        <v>83</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>32.59</v>
+        <v>-100</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>25.64</v>
+        <v>32.27</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>32.46</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>15.41</v>
+        <v>15.58</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>25.51</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>32.93</v>
+        <v>33.15</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>32.85</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>32.66</v>
+        <v>32.78</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>33.52</v>
+        <v>33.92</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>35.92</v>
+        <v>35.88</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>39.43</v>
+        <v>37.1</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>49.72</v>
+        <v>45.38</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>38.5</v>
+        <v>33.51</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>32.66</v>
+        <v>25.64</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>33.54</v>
+        <v>33.23</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>33.53</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="40">
@@ -3776,28 +3776,28 @@
         <v>-0.23</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.7</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.98</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.13</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>-1.14</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>-0.99</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>-1.05</v>
@@ -3806,25 +3806,25 @@
         <v>-1.18</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.26</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.18</v>
       </c>
       <c r="U41" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Y41" s="3" t="n">
         <v>-1.1</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>-1.11</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.8</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>-132.51</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -4028,58 +4028,58 @@
         <v>47.46</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>33.89</v>
+        <v>33.67</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>33.8</v>
+        <v>83.56</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>33.18</v>
+        <v>-100</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>26.12</v>
+        <v>32.94</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>33.23</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>15.84</v>
+        <v>16.01</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>26.11</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>33.55</v>
+        <v>33.74</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>33.46</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>33.46</v>
+        <v>33.59</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>34.55</v>
+        <v>35</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>36.88</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>40.29</v>
+        <v>37.92</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>51.25</v>
+        <v>46.7</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>39.73</v>
+        <v>34.58</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>33.53</v>
+        <v>26.35</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>34.47</v>
+        <v>34.19</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>34.3</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="45">
@@ -4199,25 +4199,25 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>-0.36</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.46</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>-0.39</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>-0.44</v>
@@ -4226,25 +4226,25 @@
         <v>-0.37</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>-0.18</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>-0.03</v>
@@ -4367,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0</v>
+        <v>-133.12</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4448,58 +4448,58 @@
         <v>44.97</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>32.53</v>
+        <v>32.23</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>32.42</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>31.94</v>
+        <v>-100</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>25.15</v>
+        <v>31.72</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>33.46</v>
+        <v>33.9</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>15.87</v>
+        <v>16.27</v>
       </c>
       <c r="O49" s="3" t="n">
         <v>26.53</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>33.95</v>
+        <v>34.18</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>34</v>
+        <v>33.97</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>32.47</v>
+        <v>32.59</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>33.01</v>
+        <v>33.41</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>34.67</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>36.06</v>
+        <v>33.9</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>45.94</v>
+        <v>41.77</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>37.2</v>
+        <v>32.35</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>31.35</v>
+        <v>24.96</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>34.2</v>
+        <v>33.88</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>34.33</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="50">
@@ -4616,22 +4616,22 @@
         <v>-2.2</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.51</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.55</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.59</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-1.33</v>
+        <v>-1.68</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.31</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>0.03</v>
@@ -4640,34 +4640,34 @@
         <v>-0.03</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.37</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.77</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>-2.39</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-4.47</v>
+        <v>-4.24</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.42</v>
+        <v>-4.97</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.26</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.29</v>
+        <v>-1.45</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>-0.44</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="52">
@@ -4787,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>-131.89</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4868,58 +4868,58 @@
         <v>47.31</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>33.27</v>
+        <v>83.13</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>32.88</v>
+        <v>-100</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>26.02</v>
+        <v>32.94</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>33.59</v>
+        <v>33.73</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>16.01</v>
+        <v>16.24</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>26.42</v>
+        <v>26.53</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>33.88</v>
+        <v>34.25</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.8</v>
+        <v>33.93</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>33.8</v>
+        <v>34.06</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>33.84</v>
+        <v>34.38</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>35.88</v>
+        <v>36.02</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>39.24</v>
+        <v>37.07</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>50.06</v>
+        <v>45.56</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>38.76</v>
+        <v>33.74</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.11</v>
+        <v>25.99</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>34.86</v>
+        <v>34.53</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>34.75</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="55">
@@ -5036,58 +5036,58 @@
         <v>0.14</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.57</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.53</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.46</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.79</v>
       </c>
       <c r="T56" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="V56" s="3" t="n">
         <v>-1.18</v>
       </c>
-      <c r="U56" s="3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="V56" s="3" t="n">
-        <v>-1.3</v>
-      </c>
       <c r="W56" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.88</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="57">
@@ -5207,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>-132.96</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5288,58 +5288,58 @@
         <v>48.68</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>34.72</v>
+        <v>34.5</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>34.88</v>
+        <v>84.63</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>34.33</v>
+        <v>-100</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>27.11</v>
+        <v>34.18</v>
       </c>
       <c r="M59" s="3" t="n">
         <v>34.45</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>16.44</v>
+        <v>16.62</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>27.07</v>
+        <v>27.1</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>34.75</v>
+        <v>34.98</v>
       </c>
       <c r="Q59" s="3" t="n">
         <v>34.7</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>34.63</v>
+        <v>34.76</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>35.72</v>
+        <v>36.15</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>37.98</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>41.36</v>
+        <v>38.92</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>52.84</v>
+        <v>48.09</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>40.96</v>
+        <v>35.65</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>34.53</v>
+        <v>27.11</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>35.54</v>
+        <v>35.2</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>35.32</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="60">
@@ -5459,13 +5459,13 @@
         <v>0.76</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0.79</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="M61" s="3" t="n">
         <v>0.86</v>
@@ -5474,10 +5474,10 @@
         <v>0.43</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="Q61" s="3" t="n">
         <v>0.8</v>
@@ -5486,28 +5486,28 @@
         <v>0.8</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>0.91</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="62">
@@ -5627,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0</v>
+        <v>-134.28</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5708,58 +5708,58 @@
         <v>49.45</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>35.26</v>
+        <v>35.04</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>35.46</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>34.86</v>
+        <v>-100</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>27.53</v>
+        <v>34.72</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>34.99</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>16.68</v>
+        <v>16.87</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>27.46</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>35.25</v>
+        <v>35.49</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>35.17</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>35.17</v>
+        <v>35.3</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>36.28</v>
+        <v>36.72</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>38.53</v>
+        <v>38.57</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>42</v>
+        <v>39.53</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>53.72</v>
+        <v>48.89</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>41.56</v>
+        <v>36.21</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>35.04</v>
+        <v>27.51</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.02</v>
+        <v>35.72</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>35.84</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="65">
@@ -5879,13 +5879,13 @@
         <v>1.3</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>1.32</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="M66" s="3" t="n">
         <v>1.4</v>
@@ -5897,7 +5897,7 @@
         <v>0.96</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q66" s="3" t="n">
         <v>1.27</v>
@@ -5906,28 +5906,28 @@
         <v>1.34</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="67">
@@ -6047,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>-134.81</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6128,58 +6128,58 @@
         <v>100</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>35.41</v>
+        <v>35.18</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>35.87</v>
+        <v>85.59</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>35.31</v>
+        <v>-100</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>27.91</v>
+        <v>35.19</v>
       </c>
       <c r="M69" s="3" t="n">
         <v>35.43</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>16.91</v>
+        <v>17.1</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>27.87</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>35.73</v>
+        <v>35.97</v>
       </c>
       <c r="Q69" s="3" t="n">
         <v>35.68</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>35.61</v>
+        <v>35.74</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>36.7</v>
+        <v>37.18</v>
       </c>
       <c r="T69" s="3" t="n">
         <v>38.89</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>42.22</v>
+        <v>39.73</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>54.29</v>
+        <v>49.41</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>42.04</v>
+        <v>36.63</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>35.48</v>
+        <v>27.86</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>36.51</v>
+        <v>36.21</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>36.29</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="70">
@@ -6296,58 +6296,58 @@
         <v>2.85</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>1.84</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>1.37</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q71" s="3" t="n">
         <v>1.78</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>1.83</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="72">
@@ -6467,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0</v>
+        <v>-135.25</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6548,58 +6548,58 @@
         <v>48.58</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>34.69</v>
+        <v>34.43</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>34.88</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>34.33</v>
+        <v>-100</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>27.22</v>
+        <v>34.32</v>
       </c>
       <c r="M74" s="3" t="n">
         <v>34.63</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>16.51</v>
+        <v>16.71</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>27.21</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>34.78</v>
+        <v>35.02</v>
       </c>
       <c r="Q74" s="3" t="n">
         <v>34.73</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>34.59</v>
+        <v>34.76</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>35.68</v>
+        <v>36.11</v>
       </c>
       <c r="T74" s="3" t="n">
         <v>37.9</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>41.19</v>
+        <v>38.8</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>52.67</v>
+        <v>47.94</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>40.83</v>
+        <v>35.54</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.43</v>
+        <v>27.06</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>35.5</v>
+        <v>35.17</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>35.4</v>
+        <v>35.13</v>
       </c>
     </row>
     <row r="75">
@@ -6716,37 +6716,37 @@
         <v>1.41</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K76" s="3" t="n">
         <v>0.79</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="M76" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>0.71</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q76" s="3" t="n">
         <v>0.83</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>0.83</v>
@@ -6755,19 +6755,19 @@
         <v>0.66</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="77">
@@ -6887,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>-134.28</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6968,58 +6968,58 @@
         <v>47.17</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>33.96</v>
+        <v>33.74</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>33.97</v>
+        <v>83.7</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>33.54</v>
+        <v>-100</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>26.49</v>
+        <v>33.4</v>
       </c>
       <c r="M79" s="3" t="n">
         <v>33.59</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>16.01</v>
+        <v>16.19</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>33.98</v>
+        <v>34.21</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>33.9</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>33.83</v>
+        <v>33.96</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>34.76</v>
+        <v>35.18</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>37.06</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>40.53</v>
+        <v>38.14</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>51.36</v>
+        <v>46.74</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>39.77</v>
+        <v>34.61</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>33.63</v>
+        <v>26.41</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>34.65</v>
+        <v>34.32</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>34.33</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="80">
@@ -7307,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0</v>
+        <v>-133.49</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7388,58 +7388,58 @@
         <v>47.17</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>33.79</v>
+        <v>33.98</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>32.54</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>32.13</v>
+        <v>-100</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>25.42</v>
+        <v>32.55</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33.73</v>
+        <v>34.24</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>16.08</v>
+        <v>16.47</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>26.32</v>
+        <v>26.77</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>33.71</v>
+        <v>34.52</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>33.63</v>
+        <v>34.21</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>33.6</v>
+        <v>34.26</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>32.88</v>
+        <v>33.86</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>34.97</v>
+        <v>35.54</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>38.31</v>
+        <v>36.64</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>49.57</v>
+        <v>45.12</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>38.5</v>
+        <v>33.47</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>32.85</v>
+        <v>25.79</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>35.39</v>
+        <v>35.06</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>35.51</v>
+        <v>35.21</v>
       </c>
     </row>
     <row r="85">
@@ -7556,58 +7556,58 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.17</v>
+        <v>0.24</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-1.43</v>
+        <v>-0.95</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-1.41</v>
+        <v>-0.91</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.07</v>
+        <v>-0.85</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.06</v>
+        <v>0.28</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.18</v>
+        <v>0.27</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.31</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.31</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.24</v>
+        <v>0.31</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.87</v>
+        <v>-1.32</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.1</v>
+        <v>-1.53</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.22</v>
+        <v>-1.5</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.62</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.14</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.62</v>
       </c>
       <c r="Y86" s="3" t="n">
         <v>0.74</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="87">
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>-132.58</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7808,58 +7808,58 @@
         <v>47.46</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>34.13</v>
+        <v>33.81</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>33.67</v>
+        <v>83.53</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>32.95</v>
+        <v>-100</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>25.97</v>
+        <v>32.68</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>32.74</v>
+        <v>32.71</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>15.5</v>
+        <v>15.66</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>25.78</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>33.28</v>
+        <v>33.44</v>
       </c>
       <c r="Q89" s="3" t="n">
         <v>33.14</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>32.85</v>
+        <v>32.94</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>33.58</v>
+        <v>33.86</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>36.23</v>
+        <v>36.16</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>39.82</v>
+        <v>37.43</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>50.01</v>
+        <v>45.74</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>38.76</v>
+        <v>33.7</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>32.91</v>
+        <v>25.84</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.7</v>
+        <v>33.45</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>33.69</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="90">
@@ -7976,55 +7976,55 @@
         <v>0.28</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.72</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.88</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="O91" s="3" t="n">
         <v>-0.72</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.77</v>
       </c>
       <c r="Q91" s="3" t="n">
         <v>-0.76</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.02</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.32</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.9</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.01</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.57</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.87</v>
       </c>
       <c r="Z91" s="3" t="n">
         <v>-0.64</v>
@@ -8147,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0</v>
+        <v>-132.83</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-01T03:13:27</t>
+          <t>CreatedAt: 2026-04-01T04:11:47</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -665,61 +665,61 @@
         <v>75.08</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>75.14</v>
+        <v>79.86</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>47.24</v>
+        <v>61.05</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>35.19</v>
+        <v>48.37</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>32.67</v>
+        <v>32.23</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>32.8</v>
+        <v>32.28</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>46.77</v>
+        <v>35.01</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>46.76</v>
+        <v>46.84</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>46.85</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>47.02</v>
+        <v>40.13</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>47.14</v>
+        <v>48.33</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>46.95</v>
+        <v>40.09</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>48.56</v>
+        <v>48.95</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>57.54</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>59.93</v>
+        <v>60.23</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>43.68</v>
+        <v>47.52</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>39.85</v>
+        <v>39.97</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>37.42</v>
+        <v>39.73</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>34.39</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="5">
@@ -833,61 +833,61 @@
         <v>0.23</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>-0.26</v>
       </c>
       <c r="L6" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>-0.33</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="N6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.39</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-0.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.54</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="7">
@@ -1085,61 +1085,61 @@
         <v>76.61</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>76.29000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>48.3</v>
+        <v>62.24</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>35.94</v>
+        <v>49.35</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>33.2</v>
+        <v>32.78</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.2</v>
+        <v>32.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>33.23</v>
+        <v>33.29</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>47.33</v>
+        <v>35.43</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>47.27</v>
+        <v>47.32</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>47.68</v>
+        <v>40.66</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>47.81</v>
+        <v>48.92</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>47.47</v>
+        <v>40.53</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>49</v>
+        <v>49.39</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>58.53</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>61.08</v>
+        <v>61.45</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>44.65</v>
+        <v>48.53</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>40.74</v>
+        <v>40.86</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>38.45</v>
+        <v>40.83</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>35.47</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="10">
@@ -1253,58 +1253,58 @@
         <v>1.76</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="L11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M11" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>0.13</v>
-      </c>
       <c r="N11" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>0.59</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>0.63</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.32</v>
@@ -1505,61 +1505,61 @@
         <v>76.61</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>76.29000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>48.3</v>
+        <v>62.24</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>35.94</v>
+        <v>49.35</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>33.2</v>
+        <v>32.78</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>33.2</v>
+        <v>32.7</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>33.23</v>
+        <v>33.29</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>47.33</v>
+        <v>35.43</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>47.27</v>
+        <v>47.32</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>47.68</v>
+        <v>40.66</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>47.81</v>
+        <v>48.92</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>47.47</v>
+        <v>40.53</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>49</v>
+        <v>49.39</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>58.53</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>61.08</v>
+        <v>61.45</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>44.65</v>
+        <v>48.53</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>40.74</v>
+        <v>40.86</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>38.45</v>
+        <v>40.83</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>35.47</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="15">
@@ -1673,58 +1673,58 @@
         <v>1.76</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="L16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M16" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M16" s="3" t="n">
-        <v>0.13</v>
-      </c>
       <c r="N16" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>0.59</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0.63</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>0.32</v>
@@ -1925,61 +1925,61 @@
         <v>75.23</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>75.37</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>47.52</v>
+        <v>61.29</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>35.4</v>
+        <v>48.61</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>32.8</v>
+        <v>32.39</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>32.87</v>
+        <v>32.37</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>32.9</v>
+        <v>32.93</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.81</v>
+        <v>35.08</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>46.8</v>
+        <v>46.93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>46.94</v>
+        <v>46.99</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>47.25</v>
+        <v>40.29</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>47.33</v>
+        <v>48.48</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>47.09</v>
+        <v>40.21</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>48.66</v>
+        <v>49.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>57.83</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>43.98</v>
+        <v>47.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>40.05</v>
+        <v>40.17</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>37.61</v>
+        <v>39.93</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>34.53</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="20">
@@ -2093,61 +2093,61 @@
         <v>0.38</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.32</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.18</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="22">
@@ -2345,61 +2345,61 @@
         <v>75.23</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>75.37</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>47.52</v>
+        <v>61.29</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>35.4</v>
+        <v>48.61</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>32.8</v>
+        <v>32.39</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>32.87</v>
+        <v>32.37</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>32.9</v>
+        <v>32.93</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46.81</v>
+        <v>35.08</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>46.8</v>
+        <v>46.93</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>46.94</v>
+        <v>46.99</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>47.25</v>
+        <v>40.29</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>47.33</v>
+        <v>48.48</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>47.09</v>
+        <v>40.21</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>48.66</v>
+        <v>49.1</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>57.83</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>43.98</v>
+        <v>47.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>40.05</v>
+        <v>40.17</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>37.61</v>
+        <v>39.93</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>34.53</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="25">
@@ -2513,61 +2513,61 @@
         <v>0.38</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.32</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.18</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="27">
@@ -2765,61 +2765,61 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>75.52</v>
+        <v>80.34</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>47.67</v>
+        <v>61.42</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>35.51</v>
+        <v>48.76</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>32.9</v>
+        <v>32.49</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>32.9</v>
+        <v>32.37</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46.81</v>
+        <v>35.01</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>46.76</v>
+        <v>46.93</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>46.94</v>
+        <v>46.99</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>47.35</v>
+        <v>40.37</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>47.38</v>
+        <v>48.48</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>47.14</v>
+        <v>40.25</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>48.75</v>
+        <v>49.15</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>58.06</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>60.53</v>
+        <v>60.89</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.25</v>
+        <v>48.09</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>40.21</v>
+        <v>40.33</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>37.72</v>
+        <v>40.05</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>34.67</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="30">
@@ -2933,61 +2933,61 @@
         <v>0.3</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.68</v>
+        <v>1.04</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0.23</v>
       </c>
       <c r="M31" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3" t="n">
         <v>-0.2</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>-0.1</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="X31" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="Y31" s="3" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="32">
@@ -3185,61 +3185,61 @@
         <v>81.72</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>79.37</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>50.8</v>
+        <v>65.45</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>37.71</v>
+        <v>51.78</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>34.45</v>
+        <v>34.02</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>34.3</v>
+        <v>33.78</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>34.51</v>
+        <v>34.61</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>49.25</v>
+        <v>36.87</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>48.73</v>
+        <v>48.87</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>48.43</v>
+        <v>48.48</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>48.97</v>
+        <v>41.75</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>49.36</v>
+        <v>50.5</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>48.65</v>
+        <v>41.54</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>49.95</v>
+        <v>50.4</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>60.61</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>63.72</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>46.49</v>
+        <v>50.58</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>42.82</v>
+        <v>43</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>41.36</v>
+        <v>43.87</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>38.63</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="35">
@@ -3353,61 +3353,61 @@
         <v>6.86</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>4.52</v>
+        <v>7.27</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.66</v>
+        <v>4.65</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.45</v>
+        <v>3.31</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>2.67</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="37">
@@ -3605,61 +3605,61 @@
         <v>75.08</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>75.14</v>
+        <v>79.86</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>47.24</v>
+        <v>61.05</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>35.19</v>
+        <v>48.37</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>32.67</v>
+        <v>32.23</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>32.8</v>
+        <v>32.28</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46.77</v>
+        <v>35.01</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>46.76</v>
+        <v>46.84</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>46.85</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>47.02</v>
+        <v>40.13</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>47.14</v>
+        <v>48.33</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>46.95</v>
+        <v>40.09</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>48.56</v>
+        <v>48.95</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>57.54</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>59.93</v>
+        <v>60.23</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>43.68</v>
+        <v>47.52</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>39.85</v>
+        <v>39.97</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>37.42</v>
+        <v>39.73</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>34.39</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="40">
@@ -3773,61 +3773,61 @@
         <v>0.23</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>-0.26</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>-0.33</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="N41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.39</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>-0.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.54</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="42">
@@ -4025,61 +4025,61 @@
         <v>75.84</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>47.33</v>
+        <v>61.29</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>35.19</v>
+        <v>48.37</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>32.71</v>
+        <v>32.26</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>32.83</v>
+        <v>32.31</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>32.77</v>
+        <v>32.93</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>46.68</v>
+        <v>34.98</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>46.71</v>
+        <v>46.84</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>46.88</v>
+        <v>39.97</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>47.19</v>
+        <v>48.38</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>47.19</v>
+        <v>40.29</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>48.85</v>
+        <v>49.39</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>58.06</v>
+        <v>58</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>60.53</v>
+        <v>60.83</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>43.98</v>
+        <v>47.85</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>40.01</v>
+        <v>40.09</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>37.57</v>
+        <v>39.89</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>35.12</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="45">
@@ -4193,25 +4193,25 @@
         <v>0.99</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>-0.23</v>
       </c>
       <c r="L46" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M46" s="3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M46" s="3" t="n">
-        <v>-0.33</v>
-      </c>
       <c r="N46" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.42</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>-0.5600000000000001</v>
@@ -4220,34 +4220,34 @@
         <v>-0.51</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T46" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="T46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="47">
@@ -4445,61 +4445,61 @@
         <v>75.45</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>71.89</v>
+        <v>75.31</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>45.15</v>
+        <v>58.35</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>33.58</v>
+        <v>46.16</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>31.19</v>
+        <v>30.77</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>31.28</v>
+        <v>30.78</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>31.08</v>
+        <v>33.23</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>47.14</v>
+        <v>35.29</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>47.18</v>
+        <v>47.31</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>47.08</v>
+        <v>44.85</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>47.35</v>
+        <v>38.48</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>44.56</v>
+        <v>45.73</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>43.93</v>
+        <v>37.51</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>43.66</v>
+        <v>46.42</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>51.97</v>
+        <v>51.87</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>54.19</v>
+        <v>54.46</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>41.26</v>
+        <v>45.53</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.65</v>
+        <v>37.69</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>35.26</v>
+        <v>39.22</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>35.29</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="50">
@@ -4613,61 +4613,61 @@
         <v>0.6</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-2.95</v>
+        <v>-3.99</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.45</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-1.68</v>
+        <v>-2.31</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.82</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-2.02</v>
+        <v>0</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-0.24</v>
+        <v>-2.47</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0.19</v>
+        <v>-1.73</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.63</v>
+        <v>-2.65</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.21</v>
+        <v>-2.74</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-5.2</v>
+        <v>-2.92</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.98</v>
+        <v>-6.07</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-6.34</v>
+        <v>-6.32</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.76</v>
+        <v>-2.37</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.52</v>
+        <v>-2.56</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-2.5</v>
+        <v>-0.78</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.14</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="52">
@@ -4865,61 +4865,61 @@
         <v>76.15000000000001</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>74.77</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>47.09</v>
+        <v>60.74</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>34.67</v>
+        <v>47.66</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>32.51</v>
+        <v>32.07</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>33.03</v>
+        <v>32.5</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>33.06</v>
+        <v>33.16</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>47.33</v>
+        <v>35.43</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>47.32</v>
+        <v>47.45</v>
       </c>
       <c r="P54" s="3" t="n">
         <v>47.46</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>46.88</v>
+        <v>39.97</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>46.72</v>
+        <v>47.9</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>46.72</v>
+        <v>39.89</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>48.22</v>
+        <v>48.71</v>
       </c>
       <c r="U54" s="3" t="n">
         <v>56.31</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>59.23</v>
+        <v>59.46</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>42.95</v>
+        <v>46.73</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>40.09</v>
+        <v>40.17</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>37.95</v>
+        <v>40.25</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>35.33</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="55">
@@ -5033,13 +5033,13 @@
         <v>1.29</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.55</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>-0.42</v>
@@ -5048,10 +5048,10 @@
         <v>-0.1</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0.05</v>
@@ -5060,13 +5060,13 @@
         <v>0.14</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>-0.63</v>
@@ -5075,19 +5075,19 @@
         <v>-1.63</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.31</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.17</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>-0.08</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="57">
@@ -5285,61 +5285,61 @@
         <v>77.65000000000001</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>77.72</v>
+        <v>82.34</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>48.35</v>
+        <v>62.68</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>36.05</v>
+        <v>49.56</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>33.61</v>
+        <v>33.15</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>33.77</v>
+        <v>33.23</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>33.7</v>
+        <v>33.87</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>48.1</v>
+        <v>36.01</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>48.09</v>
+        <v>48.22</v>
       </c>
       <c r="P59" s="3" t="n">
         <v>48.14</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>48.17</v>
+        <v>41.03</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>48.25</v>
+        <v>49.52</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>48.25</v>
+        <v>41.24</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>49.95</v>
+        <v>50.56</v>
       </c>
       <c r="U59" s="3" t="n">
         <v>59.37</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>61.96</v>
+        <v>62.27</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>45.02</v>
+        <v>48.98</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>40.95</v>
+        <v>40.99</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>38.45</v>
+        <v>40.83</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>36.16</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="60">
@@ -5453,25 +5453,25 @@
         <v>2.8</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.21</v>
+        <v>1.88</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.79</v>
+        <v>1.09</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="L61" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M61" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="M61" s="3" t="n">
+      <c r="N61" s="3" t="n">
         <v>0.61</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>0.82</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>0.82</v>
@@ -5480,34 +5480,34 @@
         <v>0.82</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="U61" s="3" t="n">
         <v>1.42</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="62">
@@ -5705,61 +5705,61 @@
         <v>78.70999999999999</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>78.86</v>
+        <v>83.56</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>49</v>
+        <v>63.54</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>36.54</v>
+        <v>50.22</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>34.06</v>
+        <v>33.6</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>34.26</v>
+        <v>33.71</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>34.19</v>
+        <v>34.36</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>48.74</v>
+        <v>36.49</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>48.73</v>
+        <v>48.87</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>48.78</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>48.77</v>
+        <v>41.58</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>48.9</v>
+        <v>50.19</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>48.95</v>
+        <v>41.84</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>50.73</v>
+        <v>51.29</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>60.3</v>
+        <v>60.23</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>62.99</v>
+        <v>63.24</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>45.72</v>
+        <v>49.74</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>41.5</v>
+        <v>41.58</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>38.97</v>
+        <v>41.37</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>36.69</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="65">
@@ -5873,61 +5873,61 @@
         <v>3.86</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>4.02</v>
+        <v>4.26</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.86</v>
+        <v>2.73</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="L66" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M66" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="M66" s="3" t="n">
+      <c r="N66" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="N66" s="3" t="n">
-        <v>1.46</v>
-      </c>
       <c r="O66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P66" s="3" t="n">
         <v>1.46</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>1.33</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="67">
@@ -6125,61 +6125,61 @@
         <v>79.70999999999999</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>79.7</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>49.21</v>
+        <v>64</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>36.73</v>
+        <v>50.49</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>34.24</v>
+        <v>33.77</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>34.44</v>
+        <v>33.89</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>34.37</v>
+        <v>34.54</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>49.05</v>
+        <v>36.72</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>49.04</v>
+        <v>49.17</v>
       </c>
       <c r="P69" s="3" t="n">
         <v>49.09</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>49.07</v>
+        <v>41.84</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>49.1</v>
+        <v>50.4</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>49.16</v>
+        <v>41.97</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>50.89</v>
+        <v>51.45</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>60.49</v>
+        <v>60.42</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>63.12</v>
+        <v>63.37</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>45.86</v>
+        <v>49.9</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>41.67</v>
+        <v>41.75</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>39.17</v>
+        <v>41.59</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>37.16</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="70">
@@ -6293,25 +6293,25 @@
         <v>4.86</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>4.86</v>
+        <v>5.24</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.07</v>
+        <v>3.2</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="L71" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M71" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="M71" s="3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="N71" s="3" t="n">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>1.77</v>
@@ -6320,34 +6320,34 @@
         <v>1.77</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="72">
@@ -6545,61 +6545,61 @@
         <v>77.56999999999999</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>77.56</v>
+        <v>82.17</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>48.15</v>
+        <v>62.43</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>35.9</v>
+        <v>49.35</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>33.5</v>
+        <v>33.05</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>33.67</v>
+        <v>33.13</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>48</v>
+        <v>35.94</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>48.19</v>
+        <v>48.32</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>48.19</v>
+        <v>48.09</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>48.22</v>
+        <v>41.03</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>48</v>
+        <v>49.27</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>48.01</v>
+        <v>41.03</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>49.5</v>
+        <v>50.3</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>59.07</v>
+        <v>58.83</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>61.64</v>
+        <v>61.89</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>44.83</v>
+        <v>48.78</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>40.74</v>
+        <v>40.78</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>38.22</v>
+        <v>40.66</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>36.2</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="75">
@@ -6713,61 +6713,61 @@
         <v>2.71</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="K76" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M76" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="L76" s="3" t="n">
+      <c r="N76" s="3" t="n">
         <v>0.54</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>0.72</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>0.92</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.06</v>
+        <v>0.82</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.12</v>
+        <v>0.88</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>1.11</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="77">
@@ -6965,61 +6965,61 @@
         <v>74.84999999999999</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>74.84</v>
+        <v>79.3</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>47.14</v>
+        <v>60.8</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>35.26</v>
+        <v>48.47</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>32.93</v>
+        <v>32.49</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>33.13</v>
+        <v>32.6</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>33.1</v>
+        <v>33.23</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>47.28</v>
+        <v>35.4</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>47.27</v>
+        <v>47.4</v>
       </c>
       <c r="P79" s="3" t="n">
         <v>47.32</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>47.16</v>
+        <v>40.21</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>47.19</v>
+        <v>48.38</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>47.14</v>
+        <v>40.25</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>48.85</v>
+        <v>49.34</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>57.94</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>60.53</v>
+        <v>60.77</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>44.03</v>
+        <v>47.9</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>40.17</v>
+        <v>40.25</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>37.76</v>
+        <v>40.01</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>35.15</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="80">
@@ -7385,61 +7385,61 @@
         <v>77.48999999999999</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>76.06</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>48.1</v>
+        <v>62.04</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>34.23</v>
+        <v>47.1</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>32.01</v>
+        <v>31.63</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>33.23</v>
+        <v>32.7</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33.26</v>
+        <v>33.36</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>47.47</v>
+        <v>35.5</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>47.32</v>
+        <v>47.4</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>47.56</v>
+        <v>47.51</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>47.06</v>
+        <v>40.13</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>47</v>
+        <v>48.19</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>47.28</v>
+        <v>40.37</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>49</v>
+        <v>49.49</v>
       </c>
       <c r="U84" s="3" t="n">
         <v>55.88</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>58.77</v>
+        <v>59</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>42.66</v>
+        <v>46.42</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>40.82</v>
+        <v>40.95</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>38.65</v>
+        <v>40.95</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>36.13</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="85">
@@ -7553,40 +7553,40 @@
         <v>2.63</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>1.22</v>
+        <v>-2.31</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.96</v>
+        <v>1.24</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.37</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.85</v>
       </c>
       <c r="L86" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="N86" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="O86" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>0.24</v>
-      </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>-0.19</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="T86" s="3" t="n">
         <v>0.15</v>
@@ -7595,19 +7595,19 @@
         <v>-2.07</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.77</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.49</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="87">
@@ -7805,61 +7805,61 @@
         <v>75.15000000000001</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>75.52</v>
+        <v>80.34</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>47.67</v>
+        <v>61.42</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>35.51</v>
+        <v>48.76</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>32.9</v>
+        <v>32.49</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>32.9</v>
+        <v>32.37</v>
       </c>
       <c r="M89" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>46.77</v>
+        <v>35.01</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>46.76</v>
+        <v>46.93</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>46.94</v>
+        <v>46.99</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>47.35</v>
+        <v>40.37</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>47.38</v>
+        <v>48.48</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>47.14</v>
+        <v>40.25</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>48.71</v>
+        <v>49.15</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>58.06</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>60.53</v>
+        <v>60.89</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.25</v>
+        <v>48.09</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>40.21</v>
+        <v>40.33</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>37.72</v>
+        <v>40.05</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>34.67</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="90">
@@ -7973,61 +7973,61 @@
         <v>0.3</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.68</v>
+        <v>1.04</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>-0.23</v>
       </c>
       <c r="M91" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="n">
         <v>-0.2</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>-0.15</v>
       </c>
       <c r="U91" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="X91" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y91" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="Y91" s="3" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-01T06:11:08</t>
+          <t>CreatedAt: 2026-04-01T08:12:07</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -674,52 +674,52 @@
         <v>61.18</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>49.02</v>
+        <v>49.85</v>
       </c>
       <c r="L4" s="3" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="N4" s="3" t="n">
         <v>33.22</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>48.61</v>
-      </c>
       <c r="O4" s="3" t="n">
-        <v>48.51</v>
+        <v>33.12</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>48.18</v>
+        <v>39.69</v>
       </c>
       <c r="Q4" s="3" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>40.01</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>40.05</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>49.22</v>
-      </c>
       <c r="U4" s="3" t="n">
-        <v>60.11</v>
+        <v>60.17</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>60.41</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>47.57</v>
+        <v>47.82</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>40.09</v>
+        <v>47.66</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>39.69</v>
+        <v>40.01</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>39.34</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="5">
@@ -842,52 +842,52 @@
         <v>0.06</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.59</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.78</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.63</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="Q6" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="7">
@@ -1094,52 +1094,52 @@
         <v>62.23</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>49.51</v>
+        <v>50.4</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.58</v>
+        <v>49.72</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>35.22</v>
+        <v>49.04</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>49.04</v>
+        <v>33.59</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>48.85</v>
+        <v>33.41</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.52</v>
+        <v>40.05</v>
       </c>
       <c r="Q9" s="3" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="R9" s="3" t="n">
         <v>40.45</v>
       </c>
-      <c r="R9" s="3" t="n">
-        <v>49.2</v>
-      </c>
       <c r="S9" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="T9" s="3" t="n">
         <v>40.33</v>
       </c>
-      <c r="T9" s="3" t="n">
-        <v>49.51</v>
-      </c>
       <c r="U9" s="3" t="n">
-        <v>60.96</v>
+        <v>61.02</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>61.51</v>
+        <v>61.39</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>48.53</v>
+        <v>48.83</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>40.9</v>
+        <v>48.68</v>
       </c>
       <c r="Y9" s="3" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>40.74</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>40.49</v>
       </c>
     </row>
     <row r="10">
@@ -1262,52 +1262,52 @@
         <v>1.12</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.34</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="Q11" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R11" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>0.3</v>
-      </c>
       <c r="S11" s="3" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="W11" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Z11" s="3" t="n">
         <v>0.53</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0.24</v>
       </c>
     </row>
     <row r="12">
@@ -1514,52 +1514,52 @@
         <v>62.23</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>49.51</v>
+        <v>50.4</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>33.58</v>
+        <v>49.72</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>35.22</v>
+        <v>49.04</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>49.04</v>
+        <v>33.59</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>48.85</v>
+        <v>33.41</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>48.52</v>
+        <v>40.05</v>
       </c>
       <c r="Q14" s="3" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>40.45</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>49.2</v>
-      </c>
       <c r="S14" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
         <v>40.33</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>49.51</v>
-      </c>
       <c r="U14" s="3" t="n">
-        <v>60.96</v>
+        <v>61.02</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>61.51</v>
+        <v>61.39</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>48.53</v>
+        <v>48.83</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>40.9</v>
+        <v>48.68</v>
       </c>
       <c r="Y14" s="3" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="Z14" s="3" t="n">
         <v>40.74</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>40.49</v>
       </c>
     </row>
     <row r="15">
@@ -1682,52 +1682,52 @@
         <v>1.12</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.34</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="Q16" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R16" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="R16" s="3" t="n">
-        <v>0.3</v>
-      </c>
       <c r="S16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="W16" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Z16" s="3" t="n">
         <v>0.53</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v>0.24</v>
       </c>
     </row>
     <row r="17">
@@ -1934,52 +1934,52 @@
         <v>61.36</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>49.07</v>
+        <v>49.85</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>33.25</v>
+        <v>49.18</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>34.91</v>
+        <v>48.56</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>48.61</v>
+        <v>33.26</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>48.56</v>
+        <v>33.18</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>48.28</v>
+        <v>39.77</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>40.17</v>
+        <v>35.15</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>48.85</v>
+        <v>40.09</v>
       </c>
       <c r="S19" s="3" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="T19" s="3" t="n">
         <v>40.13</v>
       </c>
-      <c r="T19" s="3" t="n">
-        <v>49.32</v>
-      </c>
       <c r="U19" s="3" t="n">
-        <v>60.35</v>
+        <v>60.41</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>60.77</v>
+        <v>60.65</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>47.85</v>
+        <v>48.1</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>40.29</v>
+        <v>47.95</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>39.89</v>
+        <v>40.21</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>39.5</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="20">
@@ -2102,52 +2102,52 @@
         <v>0.25</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.45</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.64</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.83</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.53</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="S21" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>-0.12</v>
       </c>
-      <c r="T21" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="U21" s="3" t="n">
+      <c r="V21" s="3" t="n">
         <v>-0.18</v>
       </c>
-      <c r="V21" s="3" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="W21" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="22">
@@ -2354,52 +2354,52 @@
         <v>61.36</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>49.07</v>
+        <v>49.85</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>33.25</v>
+        <v>49.18</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>34.91</v>
+        <v>48.56</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>48.61</v>
+        <v>33.26</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>48.56</v>
+        <v>33.18</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>48.28</v>
+        <v>39.77</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>40.17</v>
+        <v>35.15</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>48.85</v>
+        <v>40.09</v>
       </c>
       <c r="S24" s="3" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="T24" s="3" t="n">
         <v>40.13</v>
       </c>
-      <c r="T24" s="3" t="n">
-        <v>49.32</v>
-      </c>
       <c r="U24" s="3" t="n">
-        <v>60.35</v>
+        <v>60.41</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>60.77</v>
+        <v>60.65</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>47.85</v>
+        <v>48.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>40.29</v>
+        <v>47.95</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>39.89</v>
+        <v>40.21</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>39.5</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="25">
@@ -2522,52 +2522,52 @@
         <v>0.25</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.45</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.64</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.83</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.6</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.53</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="S26" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>-0.12</v>
       </c>
-      <c r="T26" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="U26" s="3" t="n">
+      <c r="V26" s="3" t="n">
         <v>-0.18</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="W26" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="27">
@@ -2774,52 +2774,52 @@
         <v>61.42</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>48.97</v>
+        <v>49.75</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>33.22</v>
+        <v>49.03</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.84</v>
+        <v>48.42</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>48.47</v>
+        <v>33.19</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>48.42</v>
+        <v>33.15</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>48.28</v>
+        <v>39.81</v>
       </c>
       <c r="Q29" s="3" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="T29" s="3" t="n">
         <v>40.25</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>49.36</v>
-      </c>
       <c r="U29" s="3" t="n">
-        <v>60.53</v>
+        <v>60.59</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>61.01</v>
+        <v>60.95</v>
       </c>
       <c r="W29" s="3" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>48.09</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>40.45</v>
-      </c>
       <c r="Y29" s="3" t="n">
-        <v>40.01</v>
+        <v>40.29</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>39.62</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="30">
@@ -2942,52 +2942,52 @@
         <v>0.31</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.55</v>
       </c>
       <c r="L31" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>-0.43</v>
-      </c>
       <c r="Q31" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="S31" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="T31" s="3" t="n">
         <v>-0.08</v>
       </c>
-      <c r="T31" s="3" t="n">
-        <v>-0.25</v>
-      </c>
       <c r="U31" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="X31" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="Y31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="32">
@@ -3194,52 +3194,52 @@
         <v>65.22</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>51.36</v>
+        <v>52.61</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>34.91</v>
+        <v>52</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>36.53</v>
+        <v>51.07</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>50.92</v>
+        <v>34.94</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>50.1</v>
+        <v>34.37</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>49.36</v>
+        <v>40.86</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>41.28</v>
+        <v>36.38</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>50.36</v>
+        <v>41.5</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>41.03</v>
+        <v>39.27</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>50.11</v>
+        <v>40.86</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>62.73</v>
+        <v>62.92</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>63.7</v>
+        <v>63.57</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>50.58</v>
+        <v>50.9</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>42.81</v>
+        <v>51.03</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>43.68</v>
+        <v>44.19</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>43.99</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="35">
@@ -3362,52 +3362,52 @@
         <v>4.11</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.48</v>
+        <v>3.32</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.67</v>
+        <v>4.02</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>3.74</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="37">
@@ -3614,52 +3614,52 @@
         <v>61.18</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>49.02</v>
+        <v>49.85</v>
       </c>
       <c r="L39" s="3" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="N39" s="3" t="n">
         <v>33.22</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>48.61</v>
-      </c>
       <c r="O39" s="3" t="n">
-        <v>48.51</v>
+        <v>33.12</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>48.18</v>
+        <v>39.69</v>
       </c>
       <c r="Q39" s="3" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="T39" s="3" t="n">
         <v>40.01</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>40.05</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>49.22</v>
-      </c>
       <c r="U39" s="3" t="n">
-        <v>60.11</v>
+        <v>60.17</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>60.41</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>47.57</v>
+        <v>47.82</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>40.09</v>
+        <v>47.66</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>39.69</v>
+        <v>40.01</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>39.34</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="40">
@@ -3782,52 +3782,52 @@
         <v>0.06</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.59</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.78</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.63</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="Q41" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y41" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="42">
@@ -4034,34 +4034,34 @@
         <v>61.79</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>49.51</v>
+        <v>50.6</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>33.35</v>
+        <v>49.97</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>34.98</v>
+        <v>49.29</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>48.7</v>
+        <v>33.45</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>48.56</v>
+        <v>33.28</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>48.14</v>
+        <v>39.69</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>39.89</v>
+        <v>35.01</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>48.9</v>
+        <v>40.17</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>40.33</v>
+        <v>38.56</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>49.66</v>
+        <v>40.37</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>60.65</v>
@@ -4070,16 +4070,16 @@
         <v>60.95</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>47.95</v>
+        <v>48.15</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>40.21</v>
+        <v>47.66</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>39.89</v>
+        <v>40.09</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>40.17</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="45">
@@ -4202,22 +4202,22 @@
         <v>0.68</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.15</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.43</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.52</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>-0.28</v>
@@ -4226,28 +4226,28 @@
         <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47">
@@ -4454,52 +4454,52 @@
         <v>58.2</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>47.06</v>
+        <v>47.9</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>31.83</v>
+        <v>47.36</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>35.4</v>
+        <v>49.68</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>49.29</v>
+        <v>33.92</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>49.14</v>
+        <v>33.71</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>46.22</v>
+        <v>38.15</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>38.44</v>
+        <v>33.77</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>46.31</v>
+        <v>38.04</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>37.55</v>
+        <v>36.07</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>46.67</v>
+        <v>38.05</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>54.24</v>
+        <v>54.34</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>54.56</v>
+        <v>54.61</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>45.62</v>
+        <v>45.9</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.8</v>
+        <v>44.71</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>39.22</v>
+        <v>39.38</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>39.89</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="50">
@@ -4625,46 +4625,46 @@
         <v>-2.4</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-1.78</v>
+        <v>-2.46</v>
       </c>
       <c r="M51" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N51" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="N51" s="3" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="O51" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.06</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.52</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.59</v>
+        <v>-2.13</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-2.7</v>
+        <v>-2.49</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.28</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-6.29</v>
+        <v>-6.19</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-6.33</v>
+        <v>-6.23</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.3</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.53</v>
+        <v>-3</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>-0.36</v>
@@ -4874,49 +4874,49 @@
         <v>60.09</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>48.78</v>
+        <v>49.8</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>33.51</v>
+        <v>49.92</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>35.33</v>
+        <v>49.34</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>49.44</v>
+        <v>33.92</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>49.24</v>
+        <v>33.78</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>48.86</v>
+        <v>40.33</v>
       </c>
       <c r="Q54" s="3" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="T54" s="3" t="n">
         <v>39.85</v>
       </c>
-      <c r="R54" s="3" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="S54" s="3" t="n">
-        <v>39.81</v>
-      </c>
-      <c r="T54" s="3" t="n">
-        <v>48.93</v>
-      </c>
       <c r="U54" s="3" t="n">
-        <v>58.77</v>
+        <v>58.88</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>59.47</v>
+        <v>59.52</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>46.83</v>
+        <v>47.12</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>40.29</v>
+        <v>47.71</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>40.25</v>
+        <v>40.45</v>
       </c>
       <c r="Z54" s="3" t="n">
         <v>40.49</v>
@@ -5042,52 +5042,52 @@
         <v>-1.02</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.5</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.44</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.34</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.65</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.08</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="57">
@@ -5294,49 +5294,49 @@
         <v>63.4</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>51.05</v>
+        <v>52.07</v>
       </c>
       <c r="L59" s="3" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="O59" s="3" t="n">
         <v>34.33</v>
       </c>
-      <c r="M59" s="3" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="N59" s="3" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="O59" s="3" t="n">
-        <v>50.04</v>
-      </c>
       <c r="P59" s="3" t="n">
-        <v>49.51</v>
+        <v>40.86</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>40.95</v>
+        <v>35.97</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>50.05</v>
+        <v>41.12</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>41.24</v>
+        <v>39.47</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>50.83</v>
+        <v>41.32</v>
       </c>
       <c r="U59" s="3" t="n">
         <v>62.02</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>62.39</v>
+        <v>62.33</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>49.08</v>
+        <v>49.28</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>41.11</v>
+        <v>48.68</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>40.83</v>
+        <v>40.99</v>
       </c>
       <c r="Z59" s="3" t="n">
         <v>41.41</v>
@@ -5462,34 +5462,34 @@
         <v>2.28</v>
       </c>
       <c r="K61" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M61" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="L61" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="M61" s="3" t="n">
+      <c r="N61" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q61" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="N61" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>0.78</v>
-      </c>
       <c r="R61" s="3" t="n">
-        <v>1.15</v>
+        <v>0.95</v>
       </c>
       <c r="S61" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="T61" s="3" t="n">
         <v>0.99</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>1.22</v>
       </c>
       <c r="U61" s="3" t="n">
         <v>1.49</v>
@@ -5501,13 +5501,13 @@
         <v>1.08</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.82</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="62">
@@ -5714,49 +5714,49 @@
         <v>64.26000000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>51.8</v>
+        <v>52.83</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>34.83</v>
+        <v>52.33</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>36.53</v>
+        <v>51.71</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>50.92</v>
+        <v>35.05</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>50.72</v>
+        <v>34.79</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>50.17</v>
+        <v>41.41</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>41.5</v>
+        <v>36.46</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>50.78</v>
+        <v>41.71</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>41.84</v>
+        <v>40.04</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>51.57</v>
+        <v>41.92</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>63.05</v>
+        <v>62.99</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>63.36</v>
+        <v>63.37</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>49.84</v>
+        <v>50.05</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>41.66</v>
+        <v>49.34</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>41.37</v>
+        <v>41.54</v>
       </c>
       <c r="Z64" s="3" t="n">
         <v>41.97</v>
@@ -5882,52 +5882,52 @@
         <v>3.15</v>
       </c>
       <c r="K66" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M66" s="3" t="n">
         <v>2.33</v>
       </c>
-      <c r="L66" s="3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>1.21</v>
-      </c>
       <c r="N66" s="3" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="S66" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T66" s="3" t="n">
         <v>1.59</v>
       </c>
-      <c r="T66" s="3" t="n">
-        <v>1.96</v>
-      </c>
       <c r="U66" s="3" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>1.37</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="67">
@@ -6134,52 +6134,52 @@
         <v>65.02</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>52.45</v>
+        <v>53.45</v>
       </c>
       <c r="L69" s="3" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>52.37</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="O69" s="3" t="n">
         <v>35.01</v>
       </c>
-      <c r="M69" s="3" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>51.18</v>
-      </c>
-      <c r="O69" s="3" t="n">
-        <v>51.03</v>
-      </c>
       <c r="P69" s="3" t="n">
-        <v>50.48</v>
+        <v>41.67</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>41.76</v>
+        <v>36.65</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>50.99</v>
+        <v>41.89</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>41.97</v>
+        <v>40.17</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>51.73</v>
+        <v>42.05</v>
       </c>
       <c r="U69" s="3" t="n">
         <v>63.12</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>63.56</v>
+        <v>63.43</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>50</v>
+        <v>50.21</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>41.84</v>
+        <v>49.59</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>41.59</v>
+        <v>41.76</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>42.5</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="70">
@@ -6302,52 +6302,52 @@
         <v>3.9</v>
       </c>
       <c r="K71" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M71" s="3" t="n">
         <v>2.99</v>
       </c>
-      <c r="L71" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="N71" s="3" t="n">
-        <v>1.84</v>
+        <v>1.37</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="S71" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T71" s="3" t="n">
         <v>1.72</v>
-      </c>
-      <c r="T71" s="3" t="n">
-        <v>2.12</v>
       </c>
       <c r="U71" s="3" t="n">
         <v>2.59</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="72">
@@ -6554,49 +6554,49 @@
         <v>63.07</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>50.89</v>
+        <v>51.91</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>34.23</v>
+        <v>51.36</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>35.97</v>
+        <v>50.91</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>50.14</v>
+        <v>34.65</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>50.1</v>
+        <v>34.4</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>49.51</v>
+        <v>40.86</v>
       </c>
       <c r="Q74" s="3" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="R74" s="3" t="n">
         <v>40.95</v>
       </c>
-      <c r="R74" s="3" t="n">
-        <v>49.85</v>
-      </c>
       <c r="S74" s="3" t="n">
-        <v>41.03</v>
+        <v>39.31</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>50.57</v>
+        <v>41.15</v>
       </c>
       <c r="U74" s="3" t="n">
         <v>61.45</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>62.07</v>
+        <v>62.01</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>48.88</v>
+        <v>49.08</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>40.9</v>
+        <v>48.44</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>40.66</v>
+        <v>40.82</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>41.41</v>
@@ -6722,34 +6722,34 @@
         <v>1.96</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.62</v>
+        <v>1.54</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.65</v>
+        <v>1.53</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="Q76" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R76" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="R76" s="3" t="n">
-        <v>0.95</v>
-      </c>
       <c r="S76" s="3" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>0.92</v>
@@ -6761,13 +6761,13 @@
         <v>0.88</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="77">
@@ -6974,52 +6974,52 @@
         <v>61.11</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>49.46</v>
+        <v>50.3</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>33.61</v>
+        <v>49.82</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>35.33</v>
+        <v>49.38</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>49.34</v>
+        <v>33.85</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>49.19</v>
+        <v>33.71</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>48.71</v>
+        <v>40.21</v>
       </c>
       <c r="Q79" s="3" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="R79" s="3" t="n">
         <v>40.17</v>
       </c>
-      <c r="R79" s="3" t="n">
-        <v>48.9</v>
-      </c>
       <c r="S79" s="3" t="n">
-        <v>40.25</v>
+        <v>38.56</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>49.61</v>
+        <v>40.33</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>60.53</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>60.89</v>
+        <v>60.83</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>40.33</v>
+        <v>47.71</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>40.01</v>
+        <v>40.17</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>40.25</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="80">
@@ -7394,52 +7394,52 @@
         <v>59.45</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>48.02</v>
+        <v>49.12</v>
       </c>
       <c r="L84" s="3" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="O84" s="3" t="n">
         <v>33.75</v>
       </c>
-      <c r="M84" s="3" t="n">
-        <v>35.54</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="O84" s="3" t="n">
-        <v>49.19</v>
-      </c>
       <c r="P84" s="3" t="n">
-        <v>48.96</v>
+        <v>40.41</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>40.01</v>
+        <v>35.15</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>48.61</v>
+        <v>39.93</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>40.25</v>
+        <v>38.64</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>49.66</v>
+        <v>40.49</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>58.2</v>
+        <v>58.43</v>
       </c>
       <c r="V84" s="3" t="n">
         <v>59</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>46.46</v>
+        <v>46.84</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>41.03</v>
+        <v>48.58</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>40.99</v>
+        <v>41.24</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>41.32</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="85">
@@ -7562,52 +7562,52 @@
         <v>-1.66</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.18</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.33</v>
+        <v>-2.1</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.89</v>
+        <v>-1.83</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.36</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="87">
@@ -7814,52 +7814,52 @@
         <v>61.42</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>48.97</v>
+        <v>49.75</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>33.22</v>
+        <v>48.99</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>34.84</v>
+        <v>48.42</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>48.47</v>
+        <v>33.19</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>48.42</v>
+        <v>33.15</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>48.28</v>
+        <v>39.81</v>
       </c>
       <c r="Q89" s="3" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="T89" s="3" t="n">
         <v>40.25</v>
       </c>
-      <c r="R89" s="3" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="S89" s="3" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="T89" s="3" t="n">
-        <v>49.36</v>
-      </c>
       <c r="U89" s="3" t="n">
-        <v>60.53</v>
+        <v>60.59</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>61.01</v>
+        <v>60.95</v>
       </c>
       <c r="W89" s="3" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="X89" s="3" t="n">
         <v>48.09</v>
       </c>
-      <c r="X89" s="3" t="n">
-        <v>40.45</v>
-      </c>
       <c r="Y89" s="3" t="n">
-        <v>40.01</v>
+        <v>40.29</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>39.62</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="90">
@@ -7982,52 +7982,52 @@
         <v>0.31</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.55</v>
       </c>
       <c r="L91" s="3" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="P91" s="3" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M91" s="3" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>-0.43</v>
-      </c>
       <c r="Q91" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="S91" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="T91" s="3" t="n">
         <v>-0.08</v>
       </c>
-      <c r="T91" s="3" t="n">
-        <v>-0.25</v>
-      </c>
       <c r="U91" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="V91" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="X91" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Y91" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="Y91" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-02T16:08:07</t>
+          <t>CreatedAt: 2026-04-02T17:09:17</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -704,22 +704,22 @@
         <v>45.63</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>45</v>
+        <v>79.84</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>39.85</v>
+        <v>48.79</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>32.8</v>
+        <v>32.54</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.06</v>
+        <v>40.6</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>31.23</v>
+        <v>34.46</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>25.84</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="5">
@@ -872,22 +872,22 @@
         <v>-0.73</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.52</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.17</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.45</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1124,22 +1124,22 @@
         <v>46.13</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>45.72</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>40.4</v>
+        <v>49.81</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>33.35</v>
+        <v>33.12</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>34.07</v>
+        <v>41.88</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>32.22</v>
+        <v>35.55</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>26.58</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="10">
@@ -1292,22 +1292,22 @@
         <v>-0.23</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="12">
@@ -1544,22 +1544,22 @@
         <v>46.13</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>45.72</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>40.4</v>
+        <v>49.81</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>33.35</v>
+        <v>33.12</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>34.07</v>
+        <v>41.88</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>32.22</v>
+        <v>35.55</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>26.58</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="15">
@@ -1712,22 +1712,22 @@
         <v>-0.23</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
@@ -1964,22 +1964,22 @@
         <v>45.72</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>45.09</v>
+        <v>80</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>39.89</v>
+        <v>48.94</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>32.92</v>
+        <v>32.67</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>33.29</v>
+        <v>40.88</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>31.45</v>
+        <v>34.7</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>26.02</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="20">
@@ -2132,22 +2132,22 @@
         <v>-0.64</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.36</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.03</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.59</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="22">
@@ -2384,22 +2384,22 @@
         <v>45.72</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>45.09</v>
+        <v>80</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>39.89</v>
+        <v>48.94</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>32.92</v>
+        <v>32.67</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>33.29</v>
+        <v>40.88</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>31.45</v>
+        <v>34.7</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>26.02</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="25">
@@ -2552,22 +2552,22 @@
         <v>-0.64</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.36</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.03</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.59</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="27">
@@ -2804,22 +2804,22 @@
         <v>45.85</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>45.13</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>39.92</v>
+        <v>49.03</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>33.06</v>
+        <v>32.83</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>33.55</v>
+        <v>41.21</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>31.67</v>
+        <v>34.91</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>26.2</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="30">
@@ -2972,22 +2972,22 @@
         <v>-0.5</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.68</v>
+        <v>-1.12</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.93</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.34</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32">
@@ -3224,22 +3224,22 @@
         <v>47.25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>47.82</v>
+        <v>84.05</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>42.24</v>
+        <v>52.87</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>34.67</v>
+        <v>34.46</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>36.48</v>
+        <v>44.81</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>34.74</v>
+        <v>38.33</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>28.33</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="35">
@@ -3392,22 +3392,22 @@
         <v>0.9</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.44</v>
+        <v>2.91</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>3.06</v>
+        <v>3.76</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.16</v>
+        <v>3.49</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.46</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="37">
@@ -3644,22 +3644,22 @@
         <v>45.63</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>45</v>
+        <v>79.84</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>39.85</v>
+        <v>48.79</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>32.8</v>
+        <v>32.54</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>33.06</v>
+        <v>40.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>31.23</v>
+        <v>34.46</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>25.84</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="40">
@@ -3812,22 +3812,22 @@
         <v>-0.73</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.52</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.17</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.45</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4064,22 +4064,22 @@
         <v>46.45</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>46.09</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>40.93</v>
+        <v>50.11</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>33.49</v>
+        <v>33.29</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>33.42</v>
+        <v>41.05</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>31.58</v>
+        <v>34.84</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>26.02</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="45">
@@ -4232,13 +4232,13 @@
         <v>0.09</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0</v>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="47">
@@ -4484,22 +4484,22 @@
         <v>41.65</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>44.26</v>
+        <v>78.16</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>39.31</v>
+        <v>48.13</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>32.13</v>
+        <v>32.01</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>31.86</v>
+        <v>39.13</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>29.96</v>
+        <v>34.7</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>25.91</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="50">
@@ -4652,22 +4652,22 @@
         <v>-4.71</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-1.55</v>
+        <v>-3.2</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.83</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>-1.25</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.92</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-1.62</v>
+        <v>-0.14</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="52">
@@ -4904,22 +4904,22 @@
         <v>45.45</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>40.84</v>
+        <v>50.01</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>33.22</v>
+        <v>33.09</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.83</v>
+        <v>41.55</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>32.12</v>
+        <v>35.44</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>26.36</v>
+        <v>35.21</v>
       </c>
     </row>
     <row r="55">
@@ -5072,22 +5072,22 @@
         <v>-0.91</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.36</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W56" s="3" t="n">
         <v>-0.17</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="57">
@@ -5324,22 +5324,22 @@
         <v>47.89</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>47.47</v>
+        <v>84.14</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>42.2</v>
+        <v>51.67</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>34.53</v>
+        <v>34.35</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>34.42</v>
+        <v>42.27</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>32.52</v>
+        <v>35.88</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>26.75</v>
+        <v>35.83</v>
       </c>
     </row>
     <row r="60">
@@ -5492,22 +5492,22 @@
         <v>1.53</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.66</v>
+        <v>2.78</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.88</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="62">
@@ -5744,22 +5744,22 @@
         <v>48.69</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>48.27</v>
+        <v>85.64</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>42.95</v>
+        <v>52.59</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>35.07</v>
+        <v>34.93</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>35.03</v>
+        <v>42.89</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>32.96</v>
+        <v>36.41</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>27.22</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="65">
@@ -5912,22 +5912,22 @@
         <v>2.34</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.46</v>
+        <v>4.28</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>1.68</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="67">
@@ -6164,22 +6164,22 @@
         <v>49.21</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>48.73</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>43.36</v>
+        <v>53.1</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>35.48</v>
+        <v>35.3</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>35.36</v>
+        <v>43.44</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>33.38</v>
+        <v>36.87</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>27.46</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="70">
@@ -6332,22 +6332,22 @@
         <v>2.85</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.92</v>
+        <v>5.1</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.56</v>
+        <v>3.13</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="72">
@@ -6584,22 +6584,22 @@
         <v>47.69</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>47.37</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>42.15</v>
+        <v>51.61</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>34.45</v>
+        <v>34.28</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.31</v>
+        <v>42.1</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>32.35</v>
+        <v>35.81</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>26.64</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="75">
@@ -6752,22 +6752,22 @@
         <v>1.34</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.77</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="77">
@@ -7004,22 +7004,22 @@
         <v>46.36</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>45.81</v>
+        <v>81.36</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>40.8</v>
+        <v>49.96</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>33.39</v>
+        <v>33.25</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>33.42</v>
+        <v>41.05</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>31.58</v>
+        <v>34.84</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>25.86</v>
+        <v>34.54</v>
       </c>
     </row>
     <row r="80">
@@ -7424,22 +7424,22 @@
         <v>44.57</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>44.13</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>41.17</v>
+        <v>50.47</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>33.52</v>
+        <v>33.39</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>34</v>
+        <v>41.76</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>32.29</v>
+        <v>35.62</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>26.55</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="85">
@@ -7592,22 +7592,22 @@
         <v>-1.78</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-1.68</v>
+        <v>-2.68</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="87">
@@ -7844,22 +7844,22 @@
         <v>45.85</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>45.13</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>39.92</v>
+        <v>49.03</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>33.06</v>
+        <v>32.83</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>33.55</v>
+        <v>41.21</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>31.67</v>
+        <v>34.91</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>26.2</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="90">
@@ -8012,22 +8012,22 @@
         <v>-0.5</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.68</v>
+        <v>-1.12</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.93</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.34</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-04T01:11:08</t>
+          <t>CreatedAt: 2026-04-04T02:11:48</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -659,67 +659,67 @@
         <v>50.65</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46.07</v>
+        <v>47.74</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>34.66</v>
+        <v>47.63</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>39.81</v>
+        <v>33.92</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>43.02</v>
+        <v>44.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>34.55</v>
+        <v>31.26</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>30.99</v>
+        <v>31.07</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>30.96</v>
+        <v>31.02</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>31.01</v>
+        <v>33.32</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>30.63</v>
+        <v>30.66</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>18.76</v>
+        <v>18.7</v>
       </c>
       <c r="P4" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>18.72</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>23.16</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>30.81</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>18.74</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>30.72</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>18.65</v>
+        <v>18.7</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>18.7</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="5">
@@ -827,13 +827,13 @@
         <v>0.71</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.13</v>
@@ -842,43 +842,43 @@
         <v>-0.03</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>-0.28</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>-0.49</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-0.43</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.47</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>-0.58</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.33</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>-0.37</v>
@@ -1079,67 +1079,67 @@
         <v>52.96</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>48.48</v>
+        <v>50.34</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>36.69</v>
+        <v>49.85</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>41.7</v>
+        <v>35.54</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.87</v>
+        <v>46.92</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>35.58</v>
+        <v>32.29</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>31.65</v>
+        <v>31.93</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>31.49</v>
+        <v>31.68</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>31.26</v>
+        <v>33.59</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>19.19</v>
+        <v>19.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>19.16</v>
+        <v>19.25</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>31.59</v>
+        <v>31.72</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>31.18</v>
+        <v>34.12</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>30.99</v>
+        <v>31.15</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>23.13</v>
+        <v>23.44</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>18.67</v>
+        <v>18.76</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>30.96</v>
+        <v>31.21</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>19.04</v>
+        <v>19.07</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>32.45</v>
+        <v>32.55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>19.72</v>
+        <v>19.86</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.73</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="10">
@@ -1247,67 +1247,67 @@
         <v>3.02</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.27</v>
+        <v>2.74</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
       <c r="L11" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N11" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="O11" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-0.37</v>
-      </c>
       <c r="T11" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.15</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.22</v>
+        <v>0.03</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="12">
@@ -1499,67 +1499,67 @@
         <v>52.96</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>48.48</v>
+        <v>50.39</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>36.73</v>
+        <v>49.85</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>41.7</v>
+        <v>35.54</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>44.91</v>
+        <v>46.92</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>35.58</v>
+        <v>96.31</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>31.65</v>
+        <v>31.93</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>31.49</v>
+        <v>31.68</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>31.26</v>
+        <v>33.59</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>19.19</v>
+        <v>19.22</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>19.16</v>
+        <v>19.25</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>31.59</v>
+        <v>31.72</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>31.18</v>
+        <v>34.12</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>30.99</v>
+        <v>31.15</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>23.11</v>
+        <v>23.44</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>18.67</v>
+        <v>18.76</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>30.96</v>
+        <v>31.21</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>19.04</v>
+        <v>19.07</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>32.45</v>
+        <v>32.55</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>19.72</v>
+        <v>19.86</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>19.73</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="15">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>64.02</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1667,67 +1667,67 @@
         <v>3.02</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.01</v>
+        <v>3.28</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.31</v>
+        <v>2.74</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
       <c r="L16" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N16" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="O16" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S16" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="N16" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-0.37</v>
-      </c>
       <c r="T16" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.19</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.15</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.22</v>
+        <v>0.03</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="17">
@@ -1919,67 +1919,67 @@
         <v>51.12</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46.5</v>
+        <v>48.23</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>34.98</v>
+        <v>48.02</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>40.13</v>
+        <v>34.16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>43.37</v>
+        <v>45.16</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>34.87</v>
+        <v>31.54</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>31.21</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>31.15</v>
-      </c>
       <c r="M19" s="3" t="n">
-        <v>31.13</v>
+        <v>33.49</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>30.72</v>
+        <v>30.75</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>30.96</v>
+        <v>30.84</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>30.93</v>
+        <v>33.51</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>30.84</v>
+        <v>30.72</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>23.22</v>
+        <v>23.37</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.8</v>
+        <v>18.76</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>30.99</v>
+        <v>31.02</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>18.85</v>
+        <v>18.83</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>30.99</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>18.82</v>
+        <v>18.89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>18.89</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="20">
@@ -2087,67 +2087,67 @@
         <v>1.18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>-0.4</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="Q21" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="R21" s="3" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.46</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>-0.52</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="22">
@@ -2339,67 +2339,67 @@
         <v>51.12</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46.5</v>
+        <v>48.23</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>34.98</v>
+        <v>48.02</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>40.13</v>
+        <v>34.16</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>43.37</v>
+        <v>45.16</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>34.87</v>
+        <v>31.54</v>
       </c>
       <c r="K24" s="3" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>31.21</v>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>31.15</v>
-      </c>
       <c r="M24" s="3" t="n">
-        <v>31.13</v>
+        <v>33.49</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>30.72</v>
+        <v>30.75</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.96</v>
+        <v>30.84</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>30.93</v>
+        <v>33.51</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>30.84</v>
+        <v>30.72</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>23.22</v>
+        <v>23.37</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.8</v>
+        <v>18.76</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>30.99</v>
+        <v>31.02</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>18.85</v>
+        <v>18.83</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>30.99</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>18.82</v>
+        <v>18.89</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>18.89</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="25">
@@ -2507,67 +2507,67 @@
         <v>1.18</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>-0.4</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="Q26" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>-0.34</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.46</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>-0.52</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="27">
@@ -2759,67 +2759,67 @@
         <v>51.59</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46.88</v>
+        <v>48.63</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>35.3</v>
+        <v>48.32</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>40.46</v>
+        <v>34.41</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>43.72</v>
+        <v>45.49</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>35.22</v>
+        <v>31.86</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>31.53</v>
+        <v>31.61</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>31.37</v>
+        <v>31.43</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>31.32</v>
+        <v>33.69</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>30.84</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>18.89</v>
+        <v>18.87</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>18.85</v>
+        <v>18.87</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>31.08</v>
+        <v>30.99</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>31.02</v>
+        <v>33.64</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>30.93</v>
+        <v>30.81</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>23.34</v>
+        <v>23.51</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>18.95</v>
+        <v>18.91</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>18.99</v>
+        <v>18.96</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>31.3</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>19.02</v>
+        <v>19.08</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>19.08</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2927,19 +2927,19 @@
         <v>1.65</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.88</v>
+        <v>1.21</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.38</v>
@@ -2951,19 +2951,19 @@
         <v>-0.03</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.11</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.2</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>-0.43</v>
@@ -2972,13 +2972,13 @@
         <v>-0.12</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>0.22</v>
@@ -2987,7 +2987,7 @@
         <v>0.19</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="32">
@@ -3179,64 +3179,64 @@
         <v>54.22</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>49.97</v>
+        <v>51.95</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>37.82</v>
+        <v>51.26</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>42.69</v>
+        <v>36.42</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>45.73</v>
+        <v>47.98</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>36.07</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>31.91</v>
+        <v>32.29</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>31.75</v>
+        <v>32.01</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>31.13</v>
+        <v>33.52</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>31.53</v>
+        <v>31.65</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>19.35</v>
+        <v>19.39</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>19.33</v>
+        <v>19.49</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>31.88</v>
+        <v>32.18</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>31.18</v>
+        <v>34.36</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>31.11</v>
+        <v>31.46</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>23.06</v>
+        <v>23.51</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>18.61</v>
+        <v>18.78</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>31.02</v>
+        <v>31.4</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>19.2</v>
+        <v>19.27</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>33.35</v>
+        <v>33.5</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>20.27</v>
+        <v>20.49</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>20.28</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>64.02</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3347,67 +3347,67 @@
         <v>4.28</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>4.5</v>
+        <v>4.83</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3.16</v>
+        <v>2.77</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.84</v>
+        <v>3.31</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="L36" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>0.41</v>
-      </c>
       <c r="O36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="P36" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>0.23</v>
-      </c>
       <c r="X36" s="3" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="37">
@@ -3599,67 +3599,67 @@
         <v>50.65</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46.07</v>
+        <v>47.74</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>34.66</v>
+        <v>47.63</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39.81</v>
+        <v>33.92</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>43.02</v>
+        <v>44.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>34.55</v>
+        <v>31.26</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>30.99</v>
+        <v>31.07</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>30.96</v>
+        <v>31.02</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>31.01</v>
+        <v>33.32</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>30.63</v>
+        <v>30.66</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>18.76</v>
+        <v>18.7</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="W39" s="3" t="n">
         <v>18.72</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>23.16</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>30.81</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>18.74</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>30.72</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>18.65</v>
+        <v>18.7</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>18.7</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="40">
@@ -3767,13 +3767,13 @@
         <v>0.71</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.13</v>
@@ -3782,43 +3782,43 @@
         <v>-0.03</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>-0.28</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>-0.49</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>-0.43</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.47</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>-0.58</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.33</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>-0.37</v>
@@ -4019,49 +4019,49 @@
         <v>50.55</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46.07</v>
+        <v>47.69</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>34.87</v>
+        <v>47.83</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>40.09</v>
+        <v>34.13</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>43.37</v>
+        <v>45.16</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>34.76</v>
+        <v>31.48</v>
       </c>
       <c r="K44" s="3" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="S44" s="3" t="n">
         <v>31.24</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>31.55</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>31.55</v>
-      </c>
       <c r="T44" s="3" t="n">
-        <v>23.69</v>
+        <v>23.77</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>18.93</v>
@@ -4070,16 +4070,16 @@
         <v>31.27</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>19.02</v>
+        <v>19</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>31.37</v>
+        <v>31.4</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>18.99</v>
+        <v>19.06</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>18.93</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="45">
@@ -4187,19 +4187,19 @@
         <v>0.61</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.45</v>
+        <v>0.72</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0.09</v>
@@ -4214,22 +4214,22 @@
         <v>0</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.02</v>
@@ -4238,16 +4238,16 @@
         <v>0.09</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="47">
@@ -4439,67 +4439,67 @@
         <v>49.01</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>44.8</v>
+        <v>46.24</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>34.07</v>
+        <v>46.6</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>36.88</v>
+        <v>31.33</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>37.76</v>
+        <v>39.36</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>30.5</v>
+        <v>27.62</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>27.44</v>
+        <v>27.54</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>29.09</v>
+        <v>29.14</v>
       </c>
       <c r="M49" s="3" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="Q49" s="3" t="n">
         <v>29.52</v>
       </c>
-      <c r="N49" s="3" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="Q49" s="3" t="n">
-        <v>29.75</v>
-      </c>
       <c r="R49" s="3" t="n">
-        <v>29.67</v>
+        <v>31.9</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>29.62</v>
+        <v>29.42</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>20.87</v>
+        <v>20.98</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>16.68</v>
+        <v>16.69</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>27.57</v>
+        <v>27.54</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>17.84</v>
+        <v>17.82</v>
       </c>
       <c r="X49" s="3" t="n">
         <v>29.49</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>17.82</v>
+        <v>17.87</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>17.6</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="50">
@@ -4607,58 +4607,58 @@
         <v>-0.93</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.88</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-2.65</v>
+        <v>-2.32</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-5.14</v>
+        <v>-5.31</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-4.09</v>
+        <v>-3.67</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-3.7</v>
+        <v>-3.69</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.15</v>
+        <v>-2.16</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.94</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>-1.37</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.62</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.95</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.82</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.59</v>
+        <v>-2.64</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.23</v>
+        <v>-2.22</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.61</v>
+        <v>-3.64</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.14</v>
       </c>
       <c r="X51" s="3" t="n">
         <v>-1.59</v>
@@ -4667,7 +4667,7 @@
         <v>-1.02</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="52">
@@ -4859,67 +4859,67 @@
         <v>49.01</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>45.56</v>
+        <v>47.21</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>34.45</v>
+        <v>47.11</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>39.45</v>
+        <v>33.55</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>42.72</v>
+        <v>44.53</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>34.28</v>
+        <v>120.59</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>30.39</v>
+        <v>30.62</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>30.45</v>
+        <v>30.63</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>30.38</v>
+        <v>32.8</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>30.45</v>
+        <v>30.57</v>
       </c>
       <c r="O54" s="3" t="n">
         <v>18.58</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>18.56</v>
+        <v>18.61</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>30.63</v>
+        <v>30.66</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>30.75</v>
+        <v>33.38</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>30.81</v>
+        <v>30.78</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>22.58</v>
+        <v>22.8</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>18.25</v>
+        <v>18.29</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>30.21</v>
+        <v>30.27</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>18.47</v>
+        <v>18.5</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>30.93</v>
+        <v>30.96</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>18.85</v>
+        <v>18.95</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="55">
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>0</v>
@@ -5030,64 +5030,64 @@
         <v>0.09</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.61</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.67</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.92</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.58</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.37</v>
       </c>
       <c r="P56" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="S56" s="3" t="n">
         <v>-0.46</v>
       </c>
-      <c r="Q56" s="3" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="R56" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="S56" s="3" t="n">
-        <v>-0.55</v>
-      </c>
       <c r="T56" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.82</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.91</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.46</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="Y56" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Z56" s="3" t="n">
         <v>0.02</v>
-      </c>
-      <c r="Z56" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5279,52 +5279,52 @@
         <v>51.97</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>47.32</v>
+        <v>48.98</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>35.85</v>
+        <v>49.17</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>41.22</v>
+        <v>35.09</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>44.68</v>
+        <v>46.53</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>35.92</v>
+        <v>32.53</v>
       </c>
       <c r="K59" s="3" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="N59" s="3" t="n">
         <v>32.34</v>
       </c>
-      <c r="L59" s="3" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="N59" s="3" t="n">
+      <c r="O59" s="3" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="Q59" s="3" t="n">
         <v>32.31</v>
       </c>
-      <c r="O59" s="3" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="Q59" s="3" t="n">
-        <v>32.71</v>
-      </c>
       <c r="R59" s="3" t="n">
-        <v>32.84</v>
+        <v>35.15</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>32.74</v>
+        <v>32.41</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>24.54</v>
+        <v>24.58</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>19.49</v>
+        <v>19.52</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>32.18</v>
@@ -5336,10 +5336,10 @@
         <v>32.45</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>19.64</v>
+        <v>19.7</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>19.52</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="60">
@@ -5447,52 +5447,52 @@
         <v>2.03</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1</v>
@@ -5699,49 +5699,49 @@
         <v>52.57</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>47.92</v>
+        <v>49.6</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>36.34</v>
+        <v>49.8</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>41.74</v>
+        <v>35.57</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>45.29</v>
+        <v>47.17</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>36.48</v>
+        <v>33.01</v>
       </c>
       <c r="K64" s="3" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="N64" s="3" t="n">
         <v>32.89</v>
       </c>
-      <c r="L64" s="3" t="n">
-        <v>33.02</v>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>33.14</v>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>32.86</v>
-      </c>
       <c r="O64" s="3" t="n">
-        <v>20.09</v>
+        <v>20.01</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>20.09</v>
+        <v>20.03</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>32.98</v>
+        <v>32.82</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>33.15</v>
+        <v>35.7</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>33.08</v>
+        <v>32.95</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>24.82</v>
+        <v>25</v>
       </c>
       <c r="U64" s="3" t="n">
         <v>19.82</v>
@@ -5756,10 +5756,10 @@
         <v>32.96</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>19.93</v>
+        <v>19.99</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>19.81</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="65">
@@ -5867,28 +5867,28 @@
         <v>2.63</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.93</v>
+        <v>2.69</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>1.74</v>
@@ -5897,19 +5897,19 @@
         <v>1.06</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="U66" s="3" t="n">
         <v>0.91</v>
@@ -5927,7 +5927,7 @@
         <v>1.1</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="67">
@@ -6119,49 +6119,49 @@
         <v>53.35</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>48.58</v>
+        <v>50.29</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>36.85</v>
+        <v>50.49</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>42.32</v>
+        <v>36.03</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>45.87</v>
+        <v>47.77</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>36.91</v>
+        <v>33.43</v>
       </c>
       <c r="K69" s="3" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="N69" s="3" t="n">
         <v>33.28</v>
       </c>
-      <c r="L69" s="3" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>33.53</v>
-      </c>
-      <c r="N69" s="3" t="n">
+      <c r="O69" s="3" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="Q69" s="3" t="n">
         <v>33.24</v>
       </c>
-      <c r="O69" s="3" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>33.66</v>
-      </c>
       <c r="R69" s="3" t="n">
-        <v>33.76</v>
+        <v>36.16</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>33.69</v>
+        <v>33.34</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>25.22</v>
+        <v>25.27</v>
       </c>
       <c r="U69" s="3" t="n">
         <v>19.88</v>
@@ -6170,16 +6170,16 @@
         <v>32.82</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>19.99</v>
+        <v>19.98</v>
       </c>
       <c r="X69" s="3" t="n">
         <v>33.35</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>20.19</v>
+        <v>20.25</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>20.06</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -6287,49 +6287,49 @@
         <v>3.41</v>
       </c>
       <c r="F71" s="3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I71" s="3" t="n">
         <v>3.11</v>
       </c>
-      <c r="G71" s="3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>2.98</v>
-      </c>
       <c r="J71" s="3" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="L71" s="3" t="n">
         <v>2.14</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>2.13</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="U71" s="3" t="n">
         <v>0.97</v>
@@ -6344,7 +6344,7 @@
         <v>2.27</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>1.32</v>
@@ -6539,49 +6539,49 @@
         <v>51.59</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>35.66</v>
+        <v>48.87</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>40.92</v>
+        <v>34.84</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>44.17</v>
+        <v>46.05</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>35.66</v>
+        <v>32.29</v>
       </c>
       <c r="K74" s="3" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="S74" s="3" t="n">
         <v>32.14</v>
       </c>
-      <c r="L74" s="3" t="n">
-        <v>32.34</v>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>32.21</v>
-      </c>
-      <c r="O74" s="3" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="P74" s="3" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="Q74" s="3" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="R74" s="3" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="S74" s="3" t="n">
-        <v>32.47</v>
-      </c>
       <c r="T74" s="3" t="n">
-        <v>24.33</v>
+        <v>24.36</v>
       </c>
       <c r="U74" s="3" t="n">
         <v>19.3</v>
@@ -6590,16 +6590,16 @@
         <v>31.81</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>19.47</v>
+        <v>19.45</v>
       </c>
       <c r="X74" s="3" t="n">
         <v>32.21</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>19.48</v>
+        <v>19.54</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>19.28</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="75">
@@ -6710,16 +6710,16 @@
         <v>1.41</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="K76" s="3" t="n">
         <v>1</v>
@@ -6728,28 +6728,28 @@
         <v>1.1</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>0.39</v>
@@ -6758,7 +6758,7 @@
         <v>0.64</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>1.13</v>
@@ -6767,7 +6767,7 @@
         <v>0.64</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -6959,49 +6959,49 @@
         <v>49.94</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>45.47</v>
+        <v>47.12</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>34.42</v>
+        <v>47.11</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>39.53</v>
+        <v>33.65</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>42.89</v>
+        <v>44.67</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>34.59</v>
+        <v>31.29</v>
       </c>
       <c r="K79" s="3" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="N79" s="3" t="n">
         <v>31.15</v>
       </c>
-      <c r="L79" s="3" t="n">
+      <c r="O79" s="3" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="S79" s="3" t="n">
         <v>31.24</v>
       </c>
-      <c r="M79" s="3" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>31.36</v>
-      </c>
       <c r="T79" s="3" t="n">
-        <v>23.46</v>
+        <v>23.63</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>18.91</v>
@@ -7010,16 +7010,16 @@
         <v>31.18</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>18.97</v>
+        <v>18.96</v>
       </c>
       <c r="X79" s="3" t="n">
         <v>31.09</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>18.83</v>
+        <v>18.89</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>18.74</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="80">
@@ -7379,67 +7379,67 @@
         <v>48.11</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>45.79</v>
+        <v>47.55</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>34.66</v>
+        <v>47.39</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>39.41</v>
+        <v>33.48</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>42.76</v>
+        <v>44.58</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>34.18</v>
+        <v>115.15</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>30.39</v>
+        <v>30.62</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>30.42</v>
+        <v>30.63</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>30.23</v>
+        <v>32.74</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>30.39</v>
+        <v>30.51</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>18.49</v>
+        <v>18.52</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>18.45</v>
+        <v>18.52</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>30.54</v>
+        <v>30.6</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>30.66</v>
+        <v>33.28</v>
       </c>
       <c r="S84" s="3" t="n">
         <v>31.18</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>22.23</v>
+        <v>22.48</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>18.01</v>
+        <v>18.06</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>29.84</v>
+        <v>29.95</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>18.27</v>
+        <v>18.32</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>31.09</v>
+        <v>31.21</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>19.02</v>
+        <v>19.16</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>18.95</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="85">
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="K85" s="3" t="n">
         <v>0</v>
@@ -7547,67 +7547,67 @@
         <v>-1.83</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-0.41</v>
+        <v>-2.13</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.61</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.67</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.98</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.64</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.43</v>
       </c>
       <c r="P86" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="R86" s="3" t="n">
         <v>-0.57</v>
       </c>
-      <c r="Q86" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>-0.74</v>
-      </c>
       <c r="S86" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.15</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.85</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.23</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="87">
@@ -7799,67 +7799,67 @@
         <v>51.59</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>46.88</v>
+        <v>48.63</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>35.3</v>
+        <v>48.32</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>40.46</v>
+        <v>34.41</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>43.72</v>
+        <v>45.49</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>35.22</v>
+        <v>31.86</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>31.53</v>
+        <v>31.61</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>31.37</v>
+        <v>31.43</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>31.32</v>
+        <v>33.69</v>
       </c>
       <c r="N89" s="3" t="n">
         <v>30.84</v>
       </c>
       <c r="O89" s="3" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="P89" s="3" t="n">
         <v>18.89</v>
       </c>
-      <c r="P89" s="3" t="n">
-        <v>18.85</v>
-      </c>
       <c r="Q89" s="3" t="n">
-        <v>31.08</v>
+        <v>30.99</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>31.02</v>
+        <v>33.64</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>30.93</v>
+        <v>30.81</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>23.34</v>
+        <v>23.51</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>18.95</v>
+        <v>18.91</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>18.99</v>
+        <v>18.96</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>31.3</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>19.02</v>
+        <v>19.08</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>19.08</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90">
@@ -7967,19 +7967,19 @@
         <v>1.65</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.88</v>
+        <v>1.21</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>0.38</v>
@@ -7991,19 +7991,19 @@
         <v>-0.03</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.09</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.2</v>
       </c>
       <c r="S91" s="3" t="n">
         <v>-0.43</v>
@@ -8012,13 +8012,13 @@
         <v>-0.12</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>0.22</v>
@@ -8027,7 +8027,7 @@
         <v>0.19</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-04T04:11:07</t>
+          <t>CreatedAt: 2026-04-04T05:12:27</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -668,22 +668,22 @@
         <v>43.51</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>50.91</v>
+        <v>53.16</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>31.26</v>
+        <v>38.84</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>33.59</v>
+        <v>33.62</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>31.02</v>
+        <v>30.87</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>34.19</v>
+        <v>37.43</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>30.84</v>
+        <v>30.81</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>19.98</v>
@@ -695,31 +695,31 @@
         <v>30.69</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>34.12</v>
+        <v>33.31</v>
       </c>
       <c r="S4" s="3" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>30.84</v>
       </c>
-      <c r="T4" s="3" t="n">
-        <v>31.04</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>18.65</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>30.99</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>30.87</v>
-      </c>
       <c r="Y4" s="3" t="n">
-        <v>44.35</v>
+        <v>44.39</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>18.74</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="5">
@@ -836,19 +836,19 @@
         <v>0.57</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.23</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.45</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>-0.49</v>
@@ -863,16 +863,16 @@
         <v>-0.46</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-0.37</v>
@@ -884,10 +884,10 @@
         <v>-0.37</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.49</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="7">
@@ -1088,58 +1088,58 @@
         <v>45.02</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>52.61</v>
+        <v>54.99</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>32.06</v>
+        <v>39.32</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>34.3</v>
+        <v>34.37</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>31.84</v>
+        <v>31.72</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>34.74</v>
+        <v>38.19</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>31.62</v>
+        <v>31.58</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>20.57</v>
+        <v>20.55</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>20.53</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>34.91</v>
+        <v>34.08</v>
       </c>
       <c r="S9" s="3" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="T9" s="3" t="n">
         <v>31.33</v>
       </c>
-      <c r="T9" s="3" t="n">
-        <v>31.44</v>
-      </c>
       <c r="U9" s="3" t="n">
-        <v>18.74</v>
+        <v>24.03</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>31.46</v>
+        <v>34.34</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>31.65</v>
+        <v>31.68</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>32.71</v>
+        <v>32.68</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.81</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="10">
@@ -1256,49 +1256,49 @@
         <v>2.07</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0.28</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.24</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>1.47</v>
@@ -1508,58 +1508,58 @@
         <v>45.02</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>52.61</v>
+        <v>54.99</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>95.98999999999999</v>
+        <v>39.32</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>34.3</v>
+        <v>34.37</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>31.84</v>
+        <v>31.72</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>34.74</v>
+        <v>38.19</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>31.62</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>20.57</v>
+        <v>20.55</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>20.53</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>31.72</v>
+        <v>31.69</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>34.91</v>
+        <v>34.08</v>
       </c>
       <c r="S14" s="3" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="T14" s="3" t="n">
         <v>31.33</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>31.44</v>
-      </c>
       <c r="U14" s="3" t="n">
-        <v>18.74</v>
+        <v>24.03</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>31.46</v>
+        <v>34.37</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>31.65</v>
+        <v>31.68</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>32.71</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>47.15</v>
+        <v>47.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>19.81</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="15">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>63.93</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1676,55 +1676,55 @@
         <v>2.07</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.24</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1.03</v>
@@ -1928,58 +1928,58 @@
         <v>43.87</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>51.17</v>
+        <v>53.48</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>31.51</v>
+        <v>39.16</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>33.86</v>
+        <v>33.89</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>31.24</v>
+        <v>31.09</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>34.36</v>
+        <v>37.66</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>30.96</v>
+        <v>30.93</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>20.08</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>20.04</v>
+        <v>20.02</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>30.84</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>34.25</v>
+        <v>33.44</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>30.93</v>
+        <v>33.34</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>31.19</v>
+        <v>30.96</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.78</v>
+        <v>23.72</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>31.21</v>
+        <v>33.79</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>31.05</v>
+        <v>30.99</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>31.15</v>
+        <v>31.12</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>44.75</v>
+        <v>44.79</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>18.91</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="20">
@@ -2096,19 +2096,19 @@
         <v>0.92</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.22</v>
+        <v>0.55</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>-0.37</v>
@@ -2117,25 +2117,25 @@
         <v>-0.2</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>-0.31</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>-0.22</v>
@@ -2144,7 +2144,7 @@
         <v>-0.09</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.13</v>
@@ -2348,58 +2348,58 @@
         <v>43.87</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>51.17</v>
+        <v>53.48</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>31.51</v>
+        <v>39.16</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>33.86</v>
+        <v>33.89</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>31.24</v>
+        <v>31.09</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>34.36</v>
+        <v>37.66</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>30.96</v>
+        <v>30.93</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>20.08</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>20.04</v>
+        <v>20.02</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>30.84</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>34.25</v>
+        <v>33.44</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>30.93</v>
+        <v>33.34</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>31.19</v>
+        <v>30.96</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.78</v>
+        <v>23.72</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>31.21</v>
+        <v>33.79</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>31.05</v>
+        <v>30.99</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>31.15</v>
+        <v>31.12</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>44.75</v>
+        <v>44.79</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>18.91</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="25">
@@ -2516,19 +2516,19 @@
         <v>0.92</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.22</v>
+        <v>0.55</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>-0.37</v>
@@ -2537,25 +2537,25 @@
         <v>-0.2</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>-0.31</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>-0.22</v>
@@ -2564,7 +2564,7 @@
         <v>-0.09</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0.13</v>
@@ -2768,58 +2768,58 @@
         <v>44.27</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>51.43</v>
+        <v>53.75</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>31.8</v>
+        <v>39.52</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>34.16</v>
+        <v>34.23</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>31.49</v>
+        <v>31.34</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.6</v>
+        <v>37.92</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>31.08</v>
+        <v>31.05</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>20.18</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>30.99</v>
+        <v>30.96</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>34.43</v>
+        <v>33.61</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>31.02</v>
+        <v>33.44</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>31.38</v>
+        <v>31.15</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>18.93</v>
+        <v>23.94</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>31.49</v>
+        <v>34.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>31.27</v>
+        <v>31.18</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>31.46</v>
+        <v>31.43</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>45.2</v>
+        <v>45.25</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>19.12</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="30">
@@ -2936,19 +2936,19 @@
         <v>1.33</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0.25</v>
@@ -2957,37 +2957,37 @@
         <v>-0.1</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="T31" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="32">
@@ -3188,58 +3188,58 @@
         <v>45.93</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>53.56</v>
+        <v>55.99</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>96.43000000000001</v>
+        <v>39.56</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>34.62</v>
+        <v>34.69</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>32.2</v>
+        <v>32.05</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>34.7</v>
+        <v>38.23</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>31.91</v>
+        <v>31.87</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>20.8</v>
+        <v>20.78</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>20.8</v>
+        <v>20.78</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>32.18</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>35.16</v>
+        <v>34.36</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>31.62</v>
+        <v>34.22</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>31.57</v>
+        <v>31.49</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>18.74</v>
+        <v>24.16</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>31.71</v>
+        <v>34.72</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>32.04</v>
+        <v>32.11</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>33.66</v>
+        <v>33.67</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>48.63</v>
+        <v>48.68</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>20.39</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="35">
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>63.93</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3356,58 +3356,58 @@
         <v>2.99</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.57</v>
       </c>
       <c r="O36" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>0.52</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0.54</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.36</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="37">
@@ -3608,22 +3608,22 @@
         <v>43.51</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>50.91</v>
+        <v>53.16</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>31.26</v>
+        <v>38.84</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>33.59</v>
+        <v>33.62</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>31.02</v>
+        <v>30.87</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>34.19</v>
+        <v>37.43</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>30.84</v>
+        <v>30.81</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>19.98</v>
@@ -3635,31 +3635,31 @@
         <v>30.69</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>34.12</v>
+        <v>33.31</v>
       </c>
       <c r="S39" s="3" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>30.84</v>
       </c>
-      <c r="T39" s="3" t="n">
-        <v>31.04</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>18.65</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>30.99</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>30.87</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>30.87</v>
-      </c>
       <c r="Y39" s="3" t="n">
-        <v>44.35</v>
+        <v>44.39</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>18.74</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="40">
@@ -3776,19 +3776,19 @@
         <v>0.57</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.23</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.45</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>-0.49</v>
@@ -3803,16 +3803,16 @@
         <v>-0.46</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-0.37</v>
@@ -3824,10 +3824,10 @@
         <v>-0.37</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.49</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="42">
@@ -4028,22 +4028,22 @@
         <v>43.6</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>51.12</v>
+        <v>53.37</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>31.45</v>
+        <v>38.84</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>33.86</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>31.39</v>
+        <v>31.15</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>34.56</v>
+        <v>37.88</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>31.3</v>
+        <v>31.27</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>20.28</v>
@@ -4055,31 +4055,31 @@
         <v>31.09</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>34.6</v>
+        <v>33.81</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>31.39</v>
+        <v>33.84</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>31.6</v>
+        <v>31.37</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.83</v>
+        <v>23.72</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>31.3</v>
+        <v>33.86</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>31.33</v>
+        <v>31.24</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>31.52</v>
+        <v>31.49</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>45.15</v>
+        <v>45.2</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>18.95</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="45">
@@ -4196,19 +4196,19 @@
         <v>0.65</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>-0.03</v>
@@ -4226,28 +4226,28 @@
         <v>-0.03</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.28</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="47">
@@ -4448,58 +4448,58 @@
         <v>39.84</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>44.41</v>
+        <v>46.12</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>27.57</v>
+        <v>33.93</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>29.74</v>
+        <v>29.71</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>29.12</v>
+        <v>28.81</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>32.52</v>
+        <v>35.67</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>29.95</v>
+        <v>29.47</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>19.26</v>
+        <v>18.99</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>19.24</v>
+        <v>18.97</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>29.5</v>
+        <v>29.08</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>32.61</v>
+        <v>31.87</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>29.56</v>
+        <v>31.93</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>27.87</v>
+        <v>27.67</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>16.63</v>
+        <v>21</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>27.63</v>
+        <v>29.92</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>28.98</v>
+        <v>28.9</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>29.17</v>
+        <v>29.22</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>42.38</v>
+        <v>42.46</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>17.67</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="50">
@@ -4616,58 +4616,58 @@
         <v>-3.11</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-5.99</v>
+        <v>-6.46</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-3.72</v>
+        <v>-4.68</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-3.98</v>
+        <v>-4.04</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.18</v>
+        <v>-2.3</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-2.08</v>
+        <v>-2.21</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.83</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.29</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.29</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.65</v>
+        <v>-2.06</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.02</v>
+        <v>-1.98</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.88</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>-3.54</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.26</v>
+        <v>-2.79</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.73</v>
+        <v>-4.01</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.31</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.07</v>
+        <v>-1.99</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>-2.42</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="52">
@@ -4868,22 +4868,22 @@
         <v>42.82</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>49.46</v>
+        <v>51.49</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>121.03</v>
+        <v>37.89</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>32.93</v>
+        <v>32.96</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>30.51</v>
+        <v>30.33</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>33.72</v>
+        <v>36.92</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>30.81</v>
+        <v>30.78</v>
       </c>
       <c r="O54" s="3" t="n">
         <v>19.9</v>
@@ -4895,31 +4895,31 @@
         <v>30.69</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>34.22</v>
+        <v>33.44</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>30.96</v>
+        <v>33.34</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>30.38</v>
+        <v>30.18</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>18.29</v>
+        <v>23.03</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>30.78</v>
+        <v>33.29</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>30.6</v>
+        <v>30.51</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>31.15</v>
+        <v>31.18</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>44.79</v>
+        <v>45.11</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>18.72</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="55">
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>90.12</v>
+        <v>0</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         <v>-0.13</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.08</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.72</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>-0.79</v>
@@ -5048,7 +5048,7 @@
         <v>-0.79</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.96</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>-0.52</v>
@@ -5063,31 +5063,31 @@
         <v>-0.46</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.47</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>-1.03</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.63</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="57">
@@ -5288,22 +5288,22 @@
         <v>44.78</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>52.61</v>
+        <v>54.88</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>32.49</v>
+        <v>40.05</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>35.05</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>32.54</v>
+        <v>32.28</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>35.89</v>
+        <v>39.3</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>32.54</v>
+        <v>32.47</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>21.06</v>
@@ -5315,31 +5315,31 @@
         <v>32.28</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>35.92</v>
+        <v>35.07</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>32.57</v>
+        <v>35.07</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>32.65</v>
+        <v>32.41</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>19.4</v>
+        <v>24.43</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>32.17</v>
+        <v>34.8</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>32.31</v>
+        <v>32.21</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>32.57</v>
+        <v>32.58</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>46.71</v>
+        <v>46.75</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>19.56</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="60">
@@ -5456,22 +5456,22 @@
         <v>1.84</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>0.78</v>
@@ -5483,31 +5483,31 @@
         <v>1.13</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -5708,58 +5708,58 @@
         <v>45.35</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>53.28</v>
+        <v>55.63</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>32.97</v>
+        <v>40.64</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>35.61</v>
+        <v>35.64</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>33.09</v>
+        <v>32.79</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>33.09</v>
+        <v>33.02</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>21.41</v>
+        <v>21.42</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>21.37</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>32.79</v>
+        <v>32.82</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>36.49</v>
+        <v>35.66</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>33.12</v>
+        <v>35.7</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>33.21</v>
+        <v>32.96</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>19.7</v>
+        <v>24.81</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>32.67</v>
+        <v>35.34</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>32.81</v>
+        <v>32.68</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>33.06</v>
+        <v>33.1</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>47.4</v>
+        <v>47.45</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>19.83</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="65">
@@ -5876,22 +5876,22 @@
         <v>2.4</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>1.89</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O66" s="3" t="n">
         <v>1.13</v>
@@ -5900,34 +5900,34 @@
         <v>1.11</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="67">
@@ -6128,58 +6128,58 @@
         <v>45.98</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>54.02</v>
+        <v>56.35</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>33.43</v>
+        <v>41.16</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>36.03</v>
+        <v>36.06</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>33.48</v>
+        <v>33.17</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>36.92</v>
+        <v>40.43</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>33.47</v>
+        <v>33.4</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>21.67</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>21.62</v>
+        <v>21.64</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>33.21</v>
+        <v>33.24</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>36.96</v>
+        <v>36.08</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>33.47</v>
+        <v>36.08</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>33.56</v>
+        <v>33.31</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>19.78</v>
+        <v>24.91</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>32.81</v>
+        <v>35.49</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>32.92</v>
+        <v>32.82</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>33.48</v>
+        <v>33.49</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>48.01</v>
+        <v>48.05</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>20.1</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="70">
@@ -6296,58 +6296,58 @@
         <v>3.03</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>2.31</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>1.39</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>0.89</v>
+        <v>1.12</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="72">
@@ -6548,22 +6548,22 @@
         <v>44.41</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>52.12</v>
+        <v>54.37</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>32.26</v>
+        <v>39.64</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>34.84</v>
+        <v>34.83</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>32.4</v>
+        <v>32.01</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>35.67</v>
+        <v>39.17</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>32.43</v>
+        <v>32.37</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>20.93</v>
@@ -6575,31 +6575,31 @@
         <v>32.18</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>35.81</v>
+        <v>34.89</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>32.27</v>
+        <v>34.89</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>32.38</v>
+        <v>32.04</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>19.2</v>
+        <v>24.23</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>31.84</v>
+        <v>34.41</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>32.07</v>
+        <v>31.88</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>32.24</v>
+        <v>32.31</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>46.32</v>
+        <v>46.22</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>19.32</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="75">
@@ -6716,22 +6716,22 @@
         <v>1.47</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="M76" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N76" s="3" t="n">
         <v>1.07</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>1.1</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>0.65</v>
@@ -6743,31 +6743,31 @@
         <v>1.03</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>0.48</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="77">
@@ -6968,22 +6968,22 @@
         <v>42.95</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>50.4</v>
+        <v>52.57</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>31.29</v>
+        <v>38.61</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>33.72</v>
+        <v>33.75</v>
       </c>
       <c r="L79" s="3" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="N79" s="3" t="n">
         <v>31.3</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>31.33</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>20.28</v>
@@ -6995,31 +6995,31 @@
         <v>31.15</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>34.63</v>
+        <v>33.84</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>31.39</v>
+        <v>33.81</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>31.41</v>
+        <v>31.21</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>18.89</v>
+        <v>23.79</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>31.36</v>
+        <v>33.93</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>31.27</v>
+        <v>31.21</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>31.24</v>
+        <v>31.21</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>44.79</v>
+        <v>44.88</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>18.78</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="80">
@@ -7388,58 +7388,58 @@
         <v>42.77</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>48.23</v>
+        <v>50.26</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>116.43</v>
+        <v>37.78</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>32.93</v>
+        <v>32.96</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>30.48</v>
+        <v>30.3</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33.62</v>
+        <v>36.85</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>30.78</v>
+        <v>30.75</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>19.84</v>
+        <v>19.82</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
       <c r="Q84" s="3" t="n">
         <v>30.63</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>34.22</v>
+        <v>33.44</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>31.33</v>
+        <v>33.74</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>29.97</v>
+        <v>29.78</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>18.06</v>
+        <v>22.73</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>30.45</v>
+        <v>32.97</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>30.33</v>
+        <v>30.27</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>31.4</v>
+        <v>31.43</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>45.34</v>
+        <v>45.57</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>18.97</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="85">
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>85.87</v>
+        <v>0</v>
       </c>
       <c r="K85" s="3" t="n">
         <v>0</v>
@@ -7556,10 +7556,10 @@
         <v>-0.17</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-2.17</v>
+        <v>-2.31</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.83</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>-0.79</v>
@@ -7568,46 +7568,46 @@
         <v>-0.82</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-0.98</v>
+        <v>-1.03</v>
       </c>
       <c r="N86" s="3" t="n">
         <v>-0.55</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="Q86" s="3" t="n">
         <v>-0.52</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.43</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.07</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.96</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="87">
@@ -7808,58 +7808,58 @@
         <v>44.27</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>51.43</v>
+        <v>53.75</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>31.8</v>
+        <v>39.52</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>34.16</v>
+        <v>34.23</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>31.49</v>
+        <v>31.34</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>34.6</v>
+        <v>37.92</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>31.08</v>
+        <v>31.05</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>20.18</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>30.99</v>
+        <v>30.96</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>34.43</v>
+        <v>33.61</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>31.05</v>
+        <v>33.44</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>31.38</v>
+        <v>31.15</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>18.93</v>
+        <v>23.94</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>31.49</v>
+        <v>34.1</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>31.27</v>
+        <v>31.18</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>31.46</v>
+        <v>31.43</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>45.2</v>
+        <v>45.25</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>19.12</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="90">
@@ -7976,19 +7976,19 @@
         <v>1.33</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>-0.25</v>
@@ -7997,37 +7997,37 @@
         <v>-0.1</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.37</v>
       </c>
       <c r="T91" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W91" s="3" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-04T07:11:37</t>
+          <t>CreatedAt: 2026-04-04T08:10:57</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -677,49 +677,49 @@
         <v>38.83</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>42.81</v>
+        <v>31.05</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>30.69</v>
+        <v>34.22</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>30.78</v>
+        <v>30.6</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>21.15</v>
+        <v>23.32</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>21.1</v>
+        <v>19.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.63</v>
+        <v>29.14</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>33.19</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>30.81</v>
+        <v>33.12</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>31.02</v>
+        <v>31.1</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>30.9</v>
+        <v>30.96</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>31.02</v>
+        <v>34.52</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>30.84</v>
+        <v>30.75</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>39.16</v>
+        <v>30.87</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>18.78</v>
+        <v>40.2</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>18.7</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="5">
@@ -845,46 +845,46 @@
         <v>0.12</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.38</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="O6" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>-0.34</v>
-      </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.47</v>
       </c>
       <c r="R6" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>-0.55</v>
-      </c>
       <c r="T6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="W6" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-0.19</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.06</v>
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -1097,49 +1097,49 @@
         <v>39.75</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>43.74</v>
+        <v>38.64</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>31.27</v>
+        <v>34.95</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>31.62</v>
+        <v>31.49</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.77</v>
+        <v>24.06</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>21.72</v>
+        <v>20.59</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>31.62</v>
+        <v>30.12</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>33.96</v>
+        <v>33.99</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.39</v>
+        <v>33.79</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>31.55</v>
+        <v>31.67</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>31.74</v>
+        <v>35.36</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>31.72</v>
+        <v>31.65</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>41.5</v>
+        <v>32.71</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>19.94</v>
+        <v>42.74</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.77</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="10">
@@ -1265,49 +1265,49 @@
         <v>1.03</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0.51</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.98</v>
+        <v>2.14</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="12">
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0</v>
@@ -1517,49 +1517,49 @@
         <v>39.75</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>43.74</v>
+        <v>38.64</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>31.27</v>
+        <v>34.95</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>31.62</v>
+        <v>31.49</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>21.77</v>
+        <v>24.08</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>21.72</v>
+        <v>20.59</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>31.62</v>
+        <v>30.15</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>33.99</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>31.39</v>
+        <v>33.82</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>31.58</v>
+        <v>31.67</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>31.59</v>
+        <v>31.65</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>31.74</v>
+        <v>35.36</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>31.72</v>
+        <v>31.65</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>41.5</v>
+        <v>32.71</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>19.96</v>
+        <v>42.74</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>19.79</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="15">
@@ -1685,46 +1685,46 @@
         <v>1.03</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1.03</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>0</v>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
@@ -1937,49 +1937,49 @@
         <v>39.1</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>42.97</v>
+        <v>31.27</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>30.81</v>
+        <v>34.36</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>30.9</v>
+        <v>30.72</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>21.25</v>
+        <v>23.44</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>21.19</v>
+        <v>20.02</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>30.75</v>
+        <v>29.26</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>33.32</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>30.9</v>
+        <v>33.22</v>
       </c>
       <c r="T19" s="3" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>31.21</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>31.18</v>
-      </c>
       <c r="V19" s="3" t="n">
-        <v>31.24</v>
+        <v>34.83</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>31.02</v>
+        <v>30.93</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>39.51</v>
+        <v>31.15</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>18.95</v>
+        <v>40.56</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>18.87</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="20">
@@ -2105,49 +2105,49 @@
         <v>0.39</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.24</v>
       </c>
       <c r="N21" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="R21" s="3" t="n">
         <v>-0.4</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.43</v>
-      </c>
       <c r="S21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="22">
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>0</v>
@@ -2357,49 +2357,49 @@
         <v>39.1</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>42.97</v>
+        <v>31.27</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>30.81</v>
+        <v>34.36</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>30.9</v>
+        <v>30.72</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>21.25</v>
+        <v>23.44</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>21.19</v>
+        <v>20.02</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.75</v>
+        <v>29.26</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>33.32</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>30.9</v>
+        <v>33.22</v>
       </c>
       <c r="T24" s="3" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="U24" s="3" t="n">
         <v>31.21</v>
       </c>
-      <c r="U24" s="3" t="n">
-        <v>31.18</v>
-      </c>
       <c r="V24" s="3" t="n">
-        <v>31.24</v>
+        <v>34.83</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>31.02</v>
+        <v>30.93</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>39.51</v>
+        <v>31.15</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>18.95</v>
+        <v>40.56</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>18.87</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="25">
@@ -2525,49 +2525,49 @@
         <v>0.39</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.24</v>
       </c>
       <c r="N26" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>-0.4</v>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.43</v>
-      </c>
       <c r="S26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="27">
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
@@ -2777,49 +2777,49 @@
         <v>39.42</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>43.16</v>
+        <v>31.49</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>30.93</v>
+        <v>34.53</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>31.02</v>
+        <v>30.84</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>21.36</v>
+        <v>23.58</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.29</v>
+        <v>20.12</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>30.9</v>
+        <v>29.41</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>33.45</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>30.99</v>
+        <v>33.32</v>
       </c>
       <c r="T29" s="3" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>31.43</v>
       </c>
-      <c r="U29" s="3" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>39.91</v>
-      </c>
       <c r="Y29" s="3" t="n">
-        <v>19.14</v>
+        <v>40.97</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>19.06</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="30">
@@ -2945,49 +2945,49 @@
         <v>0.71</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="32">
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>0</v>
@@ -3197,49 +3197,49 @@
         <v>40.2</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>44.24</v>
+        <v>32.65</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>31.4</v>
+        <v>35.12</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>31.91</v>
+        <v>31.85</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>22.04</v>
+        <v>24.38</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>22.01</v>
+        <v>20.89</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>32.11</v>
+        <v>30.62</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>34.23</v>
+        <v>34.3</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>31.74</v>
+        <v>34.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>31.74</v>
+        <v>31.83</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>31.72</v>
+        <v>31.81</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>32.07</v>
+        <v>35.69</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>32.14</v>
+        <v>32.08</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>42.75</v>
+        <v>33.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>20.57</v>
+        <v>44.08</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>20.37</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="35">
@@ -3365,49 +3365,49 @@
         <v>1.49</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.22</v>
+        <v>0.53</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>3.12</v>
+        <v>2.46</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.6</v>
+        <v>3.48</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="37">
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>0</v>
@@ -3617,49 +3617,49 @@
         <v>38.83</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>42.81</v>
+        <v>31.05</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>30.69</v>
+        <v>34.22</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>30.78</v>
+        <v>30.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>21.15</v>
+        <v>23.32</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>21.1</v>
+        <v>19.94</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.63</v>
+        <v>29.14</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>33.19</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>30.81</v>
+        <v>33.12</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>31.02</v>
+        <v>31.1</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>30.9</v>
+        <v>30.96</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>31.02</v>
+        <v>34.52</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>30.84</v>
+        <v>30.75</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>39.16</v>
+        <v>30.87</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>18.78</v>
+        <v>40.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>18.7</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="40">
@@ -3785,46 +3785,46 @@
         <v>0.12</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.38</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="O41" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P41" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="P41" s="3" t="n">
-        <v>-0.34</v>
-      </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.47</v>
       </c>
       <c r="R41" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>-0.55</v>
-      </c>
       <c r="T41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="W41" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="Y41" s="3" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>-0.19</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.06</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>0</v>
@@ -4037,49 +4037,49 @@
         <v>38.99</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>43.03</v>
+        <v>31.21</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>31.15</v>
+        <v>34.6</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>31.24</v>
+        <v>31.05</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>21.46</v>
+        <v>23.65</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>21.4</v>
+        <v>20.22</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>31.02</v>
+        <v>29.52</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>33.72</v>
+        <v>33.69</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>31.39</v>
+        <v>33.75</v>
       </c>
       <c r="T44" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="X44" s="3" t="n">
         <v>31.52</v>
       </c>
-      <c r="U44" s="3" t="n">
-        <v>31.09</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>39.99</v>
-      </c>
       <c r="Y44" s="3" t="n">
-        <v>19.1</v>
+        <v>40.93</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>18.91</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="45">
@@ -4205,16 +4205,16 @@
         <v>0.27</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>-0.04</v>
@@ -4226,28 +4226,28 @@
         <v>-0.03</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>-0.06</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="47">
@@ -4373,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -4457,49 +4457,49 @@
         <v>34.14</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>40.68</v>
+        <v>28.89</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>29.36</v>
+        <v>32.58</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>29.47</v>
+        <v>29.33</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>20.12</v>
+        <v>22.17</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>20.1</v>
+        <v>18.99</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>29.08</v>
+        <v>27.67</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>31.78</v>
+        <v>31.75</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>29.62</v>
+        <v>31.81</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>27.83</v>
+        <v>27.87</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>27.49</v>
+        <v>27.54</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>27.66</v>
+        <v>30.65</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>28.95</v>
+        <v>28.9</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.11</v>
+        <v>29.25</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>17.94</v>
+        <v>38.41</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>17.66</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="50">
@@ -4625,46 +4625,46 @@
         <v>-4.57</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.22</v>
       </c>
       <c r="M51" s="3" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="N51" s="3" t="n">
         <v>-1.82</v>
       </c>
-      <c r="N51" s="3" t="n">
-        <v>-1.83</v>
-      </c>
       <c r="O51" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.51</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.27</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.04</v>
+        <v>-1.94</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>-1.97</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.88</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.53</v>
+        <v>-3.54</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.66</v>
+        <v>-3.64</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.71</v>
+        <v>-4.11</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.28</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.52</v>
+        <v>-1.99</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.19</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>-1.1</v>
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M53" s="3" t="n">
         <v>0</v>
@@ -4877,49 +4877,49 @@
         <v>37.92</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>42.21</v>
+        <v>30.48</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>30.42</v>
+        <v>33.82</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>30.81</v>
+        <v>30.66</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>21.08</v>
+        <v>23.28</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>21.04</v>
+        <v>19.9</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>30.66</v>
+        <v>29.17</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>33.35</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>30.93</v>
+        <v>33.22</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>30.33</v>
+        <v>30.38</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>30.15</v>
+        <v>30.18</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>30.78</v>
+        <v>34.11</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>30.57</v>
+        <v>30.48</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>39.59</v>
+        <v>31.21</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>19.06</v>
+        <v>40.81</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>18.78</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="55">
@@ -5045,28 +5045,28 @@
         <v>-0.8</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.64</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.78</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>-0.49</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.44</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.47</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>-1.03</v>
@@ -5075,19 +5075,19 @@
         <v>-1</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.65</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="57">
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>0</v>
@@ -5297,49 +5297,49 @@
         <v>40.24</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>44.17</v>
+        <v>32.28</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>32.38</v>
+        <v>35.89</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>32.47</v>
+        <v>32.28</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>22.29</v>
+        <v>24.56</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>22.24</v>
+        <v>21.02</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>32.24</v>
+        <v>30.68</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>35.02</v>
+        <v>34.98</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>32.57</v>
+        <v>34.98</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>32.6</v>
+        <v>32.65</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>31.98</v>
+        <v>32.04</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>32.17</v>
+        <v>35.65</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>32.24</v>
+        <v>32.14</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>41.37</v>
+        <v>32.61</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>19.76</v>
+        <v>42.29</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>19.52</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="60">
@@ -5465,49 +5465,49 @@
         <v>1.53</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>1.26</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1.24</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.79</v>
+        <v>1.69</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="62">
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M63" s="3" t="n">
         <v>0</v>
@@ -5717,49 +5717,49 @@
         <v>40.84</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>44.69</v>
+        <v>32.79</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>32.92</v>
+        <v>36.53</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>33.02</v>
+        <v>32.82</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>22.66</v>
+        <v>24.97</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>22.62</v>
+        <v>21.37</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>32.75</v>
+        <v>31.17</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>35.61</v>
+        <v>35.57</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>33.12</v>
+        <v>35.57</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>33.12</v>
+        <v>33.17</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>32.48</v>
+        <v>32.51</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>32.67</v>
+        <v>36.17</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>32.75</v>
+        <v>32.65</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>41.98</v>
+        <v>33.09</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>20.05</v>
+        <v>42.92</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>19.79</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="65">
@@ -5885,28 +5885,28 @@
         <v>2.12</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>1.85</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>1.76</v>
@@ -5915,16 +5915,16 @@
         <v>1.33</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.08</v>
+        <v>2.32</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>1.03</v>
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0</v>
@@ -6137,49 +6137,49 @@
         <v>41.36</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>45.07</v>
+        <v>33.21</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>33.31</v>
+        <v>36.92</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>33.4</v>
+        <v>33.21</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>22.93</v>
+        <v>25.26</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>22.91</v>
+        <v>21.65</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>33.17</v>
+        <v>31.57</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>36.02</v>
+        <v>35.99</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>33.51</v>
+        <v>35.99</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>33.51</v>
+        <v>33.56</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>32.61</v>
+        <v>32.65</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>32.81</v>
+        <v>36.32</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>32.88</v>
+        <v>32.78</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>42.52</v>
+        <v>33.52</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>20.31</v>
+        <v>43.47</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>20.06</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="70">
@@ -6305,49 +6305,49 @@
         <v>2.65</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>2.27</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U71" s="3" t="n">
         <v>1.47</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.89</v>
+        <v>2.28</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.34</v>
+        <v>2.87</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="72">
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M73" s="3" t="n">
         <v>0</v>
@@ -6557,49 +6557,49 @@
         <v>39.91</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>43.9</v>
+        <v>32.05</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>32.28</v>
+        <v>35.78</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>32.37</v>
+        <v>32.18</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>22.15</v>
+        <v>24.4</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>22.17</v>
+        <v>20.95</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>32.14</v>
+        <v>30.59</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>34.8</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>32.37</v>
+        <v>34.76</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>32.23</v>
+        <v>32.28</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>31.72</v>
+        <v>31.78</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>31.84</v>
+        <v>35.25</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>31.91</v>
+        <v>31.85</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>41.02</v>
+        <v>32.34</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>19.53</v>
+        <v>41.81</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>19.34</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="75">
@@ -6728,43 +6728,43 @@
         <v>0.93</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="O76" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P76" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="P76" s="3" t="n">
-        <v>0.73</v>
-      </c>
       <c r="Q76" s="3" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0.67</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>0.58</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
         <v>0</v>
@@ -6977,49 +6977,49 @@
         <v>38.71</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>42.97</v>
+        <v>31.12</v>
       </c>
       <c r="M79" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="U79" s="3" t="n">
         <v>31.18</v>
       </c>
-      <c r="N79" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>21.46</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>21.44</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="T79" s="3" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>31.15</v>
-      </c>
       <c r="V79" s="3" t="n">
-        <v>31.36</v>
+        <v>34.76</v>
       </c>
       <c r="W79" s="3" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="X79" s="3" t="n">
         <v>31.24</v>
       </c>
-      <c r="X79" s="3" t="n">
-        <v>39.63</v>
-      </c>
       <c r="Y79" s="3" t="n">
-        <v>18.97</v>
+        <v>40.6</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>18.76</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="80">
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="n">
         <v>0</v>
@@ -7397,49 +7397,49 @@
         <v>37.99</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>42.18</v>
+        <v>30.51</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>30.39</v>
+        <v>33.79</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>30.81</v>
+        <v>30.66</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>21.02</v>
+        <v>23.23</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>20.96</v>
+        <v>19.82</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>30.57</v>
+        <v>29.12</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>33.35</v>
+        <v>33.32</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>31.3</v>
+        <v>33.65</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>29.93</v>
+        <v>29.95</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>29.75</v>
+        <v>29.78</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>30.45</v>
+        <v>33.75</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>30.3</v>
+        <v>30.24</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>39.91</v>
+        <v>31.46</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>19.26</v>
+        <v>41.22</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>18.99</v>
+        <v>19.03</v>
       </c>
     </row>
     <row r="85">
@@ -7565,10 +7565,10 @@
         <v>-0.72</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.61</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N86" s="3" t="n">
         <v>-0.49</v>
@@ -7577,37 +7577,37 @@
         <v>-0.44</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>-0.4</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.47</v>
       </c>
       <c r="U86" s="3" t="n">
         <v>-1.4</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.01</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="87">
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M88" s="3" t="n">
         <v>0</v>
@@ -7817,49 +7817,49 @@
         <v>39.42</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>43.16</v>
+        <v>31.49</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>30.93</v>
+        <v>34.53</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>31.02</v>
+        <v>30.84</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>21.36</v>
+        <v>23.58</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>21.29</v>
+        <v>20.12</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>30.9</v>
+        <v>29.41</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>33.45</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>30.99</v>
+        <v>33.32</v>
       </c>
       <c r="T89" s="3" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="X89" s="3" t="n">
         <v>31.43</v>
       </c>
-      <c r="U89" s="3" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="V89" s="3" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="W89" s="3" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="X89" s="3" t="n">
-        <v>39.91</v>
-      </c>
       <c r="Y89" s="3" t="n">
-        <v>19.14</v>
+        <v>40.97</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>19.06</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="90">
@@ -7985,49 +7985,49 @@
         <v>0.71</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="S91" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="92">
@@ -8153,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="M93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-05T17:07:37</t>
+          <t>CreatedAt: 2026-04-05T18:07:37</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -707,19 +707,19 @@
         <v>44.49</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>58.74</v>
+        <v>54.7</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>34.83</v>
+        <v>54.48</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>44.58</v>
+        <v>44.67</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>41.3</v>
+        <v>44.4</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>36.22</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="5">
@@ -875,16 +875,16 @@
         <v>-0.85</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.88</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.87</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.67</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.51</v>
@@ -1127,19 +1127,19 @@
         <v>45.43</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>60.53</v>
+        <v>56.36</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>36.25</v>
+        <v>56.54</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>47.13</v>
+        <v>47.17</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>43.53</v>
+        <v>46.84</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>37.98</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="10">
@@ -1295,16 +1295,16 @@
         <v>0.09</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.8</v>
+        <v>1.19</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1.25</v>
@@ -1547,16 +1547,16 @@
         <v>45.43</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>60.53</v>
+        <v>56.36</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>36.29</v>
+        <v>56.54</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>47.13</v>
+        <v>47.22</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>43.58</v>
+        <v>46.84</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>37.98</v>
@@ -1715,19 +1715,19 @@
         <v>0.09</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.83</v>
+        <v>1.19</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="17">
@@ -1967,19 +1967,19 @@
         <v>44.76</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>59.15</v>
+        <v>55.13</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>35.07</v>
+        <v>54.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>44.93</v>
+        <v>45.02</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>41.63</v>
+        <v>44.8</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>36.54</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="20">
@@ -2135,16 +2135,16 @@
         <v>-0.58</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.44</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.55</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.45</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>-0.18</v>
@@ -2387,19 +2387,19 @@
         <v>44.76</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>59.15</v>
+        <v>55.13</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>35.07</v>
+        <v>54.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>44.93</v>
+        <v>45.02</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>41.63</v>
+        <v>44.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>36.54</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="25">
@@ -2555,16 +2555,16 @@
         <v>-0.58</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.44</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.55</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.45</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>-0.18</v>
@@ -2807,19 +2807,19 @@
         <v>45.16</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>59.74</v>
+        <v>55.68</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>35.38</v>
+        <v>55.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>45.34</v>
+        <v>45.38</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>42.05</v>
+        <v>45.25</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>36.98</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="30">
@@ -2975,16 +2975,16 @@
         <v>-0.18</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>0.26</v>
@@ -3227,16 +3227,16 @@
         <v>46.08</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>61.65</v>
+        <v>57.35</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>37.16</v>
+        <v>57.78</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>48.65</v>
+        <v>48.74</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>44.84</v>
+        <v>48.2</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>38.86</v>
@@ -3395,19 +3395,19 @@
         <v>0.74</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="37">
@@ -3647,19 +3647,19 @@
         <v>44.49</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>58.74</v>
+        <v>54.7</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>34.83</v>
+        <v>54.48</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>44.58</v>
+        <v>44.67</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>41.3</v>
+        <v>44.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>36.22</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="40">
@@ -3815,16 +3815,16 @@
         <v>-0.85</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.88</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.87</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.67</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.51</v>
@@ -4067,16 +4067,16 @@
         <v>45.61</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>60.28</v>
+        <v>56.08</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>35.53</v>
+        <v>55.85</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>45.57</v>
+        <v>45.75</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>42.13</v>
+        <v>45.29</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>36.87</v>
@@ -4235,19 +4235,19 @@
         <v>0.27</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="X46" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>0.21</v>
-      </c>
       <c r="Z46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="47">
@@ -4487,19 +4487,19 @@
         <v>40.19</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>52.72</v>
+        <v>49</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>32.65</v>
+        <v>51.2</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>41.59</v>
+        <v>43.98</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>38.25</v>
+        <v>41.15</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>33.48</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="50">
@@ -4655,19 +4655,19 @@
         <v>-5.14</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-6.96</v>
+        <v>-6.57</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.81</v>
+        <v>-4.15</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-3.74</v>
+        <v>-1.5</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-3.67</v>
+        <v>-3.91</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-3.25</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="52">
@@ -4907,19 +4907,19 @@
         <v>44.8</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>58.85</v>
+        <v>54.8</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>34.62</v>
+        <v>54.53</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>44.36</v>
+        <v>44.5</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>41.1</v>
+        <v>44.18</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>35.9</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="55">
@@ -5075,19 +5075,19 @@
         <v>-0.54</v>
       </c>
       <c r="V56" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="W56" s="3" t="n">
         <v>-0.82</v>
-      </c>
-      <c r="W56" s="3" t="n">
-        <v>-0.83</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>-0.98</v>
       </c>
       <c r="Y56" s="3" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="Z56" s="3" t="n">
         <v>-0.82</v>
-      </c>
-      <c r="Z56" s="3" t="n">
-        <v>-0.83</v>
       </c>
     </row>
     <row r="57">
@@ -5327,19 +5327,19 @@
         <v>47.33</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>62.36</v>
+        <v>58.01</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>36.7</v>
+        <v>57.84</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>47.18</v>
+        <v>47.37</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>43.62</v>
+        <v>46.89</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>38.13</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="60">
@@ -5495,16 +5495,16 @@
         <v>1.99</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.25</v>
+        <v>2.49</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>1.41</v>
@@ -5747,19 +5747,19 @@
         <v>48.13</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>63.42</v>
+        <v>58.99</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>37.28</v>
+        <v>58.82</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>47.93</v>
+        <v>48.12</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>44.27</v>
+        <v>47.59</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>38.7</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="65">
@@ -5915,16 +5915,16 @@
         <v>2.79</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.83</v>
+        <v>3.47</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>1.97</v>
@@ -6167,16 +6167,16 @@
         <v>48.65</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>59.62</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>37.56</v>
+        <v>59.45</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>48.44</v>
+        <v>48.64</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>44.84</v>
+        <v>48.2</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>39.19</v>
@@ -6335,19 +6335,19 @@
         <v>3.31</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>4.42</v>
+        <v>4.05</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="72">
@@ -6587,19 +6587,19 @@
         <v>46.79</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>61.65</v>
+        <v>57.35</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>36.33</v>
+        <v>57.24</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>46.79</v>
+        <v>47.08</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>43.22</v>
+        <v>46.46</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>37.7</v>
+        <v>37.66</v>
       </c>
     </row>
     <row r="75">
@@ -6755,16 +6755,16 @@
         <v>1.45</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.87</v>
+        <v>1.89</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>0.98</v>
@@ -7007,19 +7007,19 @@
         <v>45.34</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>59.68</v>
+        <v>55.57</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>35.46</v>
+        <v>55.35</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>45.34</v>
+        <v>45.48</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>41.92</v>
+        <v>45.06</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>36.72</v>
+        <v>36.69</v>
       </c>
     </row>
     <row r="80">
@@ -7427,19 +7427,19 @@
         <v>45.75</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>60.04</v>
+        <v>55.85</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>35.78</v>
+        <v>55.8</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>45.75</v>
+        <v>45.84</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>42.39</v>
+        <v>45.57</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>36.94</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="85">
@@ -7595,16 +7595,16 @@
         <v>0.41</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>0.22</v>
@@ -7847,19 +7847,19 @@
         <v>45.16</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>59.74</v>
+        <v>55.68</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>35.38</v>
+        <v>55.3</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>45.34</v>
+        <v>45.38</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>42.05</v>
+        <v>45.25</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>36.98</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="90">
@@ -8015,16 +8015,16 @@
         <v>-0.18</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="Z91" s="3" t="n">
         <v>0.26</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-05T23:14:37</t>
+          <t>CreatedAt: 2026-04-06T01:12:58</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -653,73 +653,73 @@
         <v>44.96</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44.78</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>58.51</v>
+        <v>54.96</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>42.66</v>
+        <v>38.67</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45.36</v>
+        <v>58.35</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>88.68000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>65.09</v>
+        <v>77.84</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>63.39</v>
+        <v>76.38</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>63.27</v>
+        <v>73.38</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>84.41</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>79.31</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>67.33</v>
+        <v>72.77</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>44.58</v>
+        <v>44.72</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>36.15</v>
+        <v>47.97</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>50.2</v>
+        <v>55.73</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.22</v>
+        <v>55.67</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>43.23</v>
+        <v>42.84</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>43.62</v>
+        <v>44.69</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>43.45</v>
+        <v>42.16</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>31.12</v>
+        <v>33.61</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.95</v>
+        <v>33.75</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>34.2</v>
+        <v>34.15</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.32</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="5">
@@ -821,73 +821,73 @@
         <v>-0.45</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>-0.31</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="7">
@@ -1073,73 +1073,73 @@
         <v>45.82</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46.01</v>
+        <v>46.34</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>62.31</v>
+        <v>56.53</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45.5</v>
+        <v>40.33</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.87</v>
+        <v>61.44</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>93.37</v>
+        <v>97.33</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>67.39</v>
+        <v>80.08</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>65.47</v>
+        <v>78.55</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>65.73999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>81.58</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>71.11</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>74.54000000000001</v>
+        <v>81.78</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>69.88</v>
+        <v>75.42</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>46.17</v>
+        <v>46.36</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>37.4</v>
+        <v>49.68</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>51.61</v>
+        <v>57.42</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>44.44</v>
+        <v>57.41</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>44.19</v>
+        <v>43.73</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>44.77</v>
+        <v>45.91</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>45.23</v>
+        <v>43.75</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>32.74</v>
+        <v>35.25</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>36</v>
+        <v>35.68</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>36.4</v>
+        <v>36.39</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>34.53</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="10">
@@ -1241,73 +1241,73 @@
         <v>0.41</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.14</v>
+        <v>1.82</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.87</v>
+        <v>3.44</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>5.04</v>
+        <v>2.14</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.34</v>
+        <v>0.33</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1.47</v>
+        <v>0.91</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>1.93</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="12">
@@ -1493,73 +1493,73 @@
         <v>45.82</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46.01</v>
+        <v>46.34</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>62.31</v>
+        <v>56.53</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45.55</v>
+        <v>40.38</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>47.87</v>
+        <v>61.44</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>93.37</v>
+        <v>97.33</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>67.39</v>
+        <v>80.08</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>65.47</v>
+        <v>78.55</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>65.73999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>81.58</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>71.11</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>74.54000000000001</v>
+        <v>81.86</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>69.88</v>
+        <v>75.5</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>46.17</v>
+        <v>46.36</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>37.44</v>
+        <v>49.68</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>51.61</v>
+        <v>57.42</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>44.48</v>
+        <v>57.41</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>44.19</v>
+        <v>43.73</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>44.77</v>
+        <v>45.96</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>45.27</v>
+        <v>43.75</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>32.74</v>
+        <v>35.25</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>36</v>
+        <v>35.68</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>36.44</v>
+        <v>36.39</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>34.57</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="15">
@@ -1661,73 +1661,73 @@
         <v>0.41</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.19</v>
+        <v>1.86</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.87</v>
+        <v>3.44</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5.04</v>
+        <v>2.14</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.34</v>
+        <v>0.41</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.47</v>
+        <v>0.98</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="17">
@@ -1913,73 +1913,73 @@
         <v>45.41</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>45.32</v>
+        <v>45.5</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>59.34</v>
+        <v>55.62</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>43.36</v>
+        <v>39.31</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>46.06</v>
+        <v>59.25</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>89.76000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>65.95</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>64.16</v>
+        <v>74.41</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>79.37</v>
+        <v>78.08</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>69.7</v>
+        <v>85.16</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>72.69</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>68.06999999999999</v>
+        <v>73.42</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>44.98</v>
+        <v>45.11</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>36.4</v>
+        <v>48.31</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>50.55</v>
+        <v>56.12</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>43.39</v>
+        <v>55.94</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>43.53</v>
+        <v>43.17</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>43.88</v>
+        <v>44.96</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>43.79</v>
+        <v>42.45</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>31.34</v>
+        <v>33.84</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>34.19</v>
+        <v>33.92</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.44</v>
+        <v>34.36</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.51</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="20">
@@ -2084,70 +2084,70 @@
         <v>0.23</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="G21" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="I21" s="3" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.3</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M21" s="3" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>-0.49</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="U21" s="3" t="n">
+      <c r="V21" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>-0.44</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>-0.26</v>
       </c>
     </row>
     <row r="22">
@@ -2333,73 +2333,73 @@
         <v>45.41</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>45.32</v>
+        <v>45.5</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>59.34</v>
+        <v>55.62</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>43.36</v>
+        <v>39.31</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>46.06</v>
+        <v>59.25</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>89.76000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>65.95</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>64.16</v>
+        <v>74.41</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>79.37</v>
+        <v>78.08</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>69.7</v>
+        <v>85.16</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>72.69</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>68.06999999999999</v>
+        <v>73.42</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>44.98</v>
+        <v>45.11</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>36.4</v>
+        <v>48.31</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>50.55</v>
+        <v>56.12</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>43.39</v>
+        <v>55.94</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>43.53</v>
+        <v>43.17</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>43.88</v>
+        <v>44.96</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>43.79</v>
+        <v>42.45</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>31.34</v>
+        <v>33.84</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>34.19</v>
+        <v>33.92</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>34.44</v>
+        <v>34.36</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.51</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="25">
@@ -2504,70 +2504,70 @@
         <v>0.23</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="G26" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="I26" s="3" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M26" s="3" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>-0.49</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="U26" s="3" t="n">
+      <c r="V26" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>-0.44</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>-0.26</v>
       </c>
     </row>
     <row r="27">
@@ -2753,73 +2753,73 @@
         <v>45.96</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>45.96</v>
+        <v>46.15</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>60.32</v>
+        <v>56.48</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>44.13</v>
+        <v>40</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>46.83</v>
+        <v>60.29</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>91.06</v>
+        <v>97.53</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>66.97</v>
+        <v>80</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>78.87</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>65.14</v>
+        <v>75.61</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>80.5</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>86.09</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>73.56</v>
+        <v>80.88</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>68.89</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>45.43</v>
+        <v>45.52</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>36.73</v>
+        <v>48.74</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>50.9</v>
+        <v>56.68</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>43.65</v>
+        <v>56.33</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>43.97</v>
+        <v>43.6</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>44.23</v>
+        <v>45.32</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>44.14</v>
+        <v>42.83</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>31.53</v>
+        <v>34.05</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>34.36</v>
+        <v>34.06</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.61</v>
+        <v>34.53</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.71</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="30">
@@ -2921,73 +2921,73 @@
         <v>0.55</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.81</v>
+        <v>1.19</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>1.13</v>
+        <v>0.71</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.28</v>
+        <v>-0.6</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.57</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.48</v>
+        <v>-0.37</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.68</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.13</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="32">
@@ -3173,73 +3173,73 @@
         <v>46.57</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>46.92</v>
+        <v>47.35</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>64.08</v>
+        <v>57.65</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46.91</v>
+        <v>41.2</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>48.86</v>
+        <v>62.64</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>95.8</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>68.02</v>
+        <v>80.75</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>65.88</v>
+        <v>78.95</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>66.63</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>82.77</v>
+        <v>80.98</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>71.91</v>
+        <v>87.39</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>75.54000000000001</v>
+        <v>83.03</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>70.95999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>46.89</v>
+        <v>47.12</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>38.03</v>
+        <v>50.51</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>52.3</v>
+        <v>58.18</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>45.21</v>
+        <v>58.41</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>44.46</v>
+        <v>44.04</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>45.32</v>
+        <v>46.57</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>46.17</v>
+        <v>44.56</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>33.87</v>
+        <v>36.42</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>37.39</v>
+        <v>37.05</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>37.92</v>
+        <v>37.95</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>36.05</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="35">
@@ -3341,73 +3341,73 @@
         <v>1.16</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5.58</v>
+        <v>2.36</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>4.55</v>
+        <v>2.68</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.86</v>
+        <v>4.64</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.47</v>
+        <v>3.35</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>3.39</v>
+        <v>2.43</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.73</v>
+        <v>0.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>3.28</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="37">
@@ -3593,73 +3593,73 @@
         <v>44.96</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>44.78</v>
+        <v>45</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>58.51</v>
+        <v>54.96</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>42.66</v>
+        <v>38.67</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45.36</v>
+        <v>58.35</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>88.68000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>65.09</v>
+        <v>77.84</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>63.39</v>
+        <v>76.38</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>63.27</v>
+        <v>73.38</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>84.41</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>79.31</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>67.33</v>
+        <v>72.77</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>44.58</v>
+        <v>44.72</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>36.15</v>
+        <v>47.97</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>50.2</v>
+        <v>55.73</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>43.22</v>
+        <v>55.67</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>43.23</v>
+        <v>42.84</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>43.62</v>
+        <v>44.69</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>43.45</v>
+        <v>42.16</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>31.12</v>
+        <v>33.61</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>33.95</v>
+        <v>33.75</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>34.2</v>
+        <v>34.15</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.32</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="40">
@@ -3761,73 +3761,73 @@
         <v>-0.45</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3" t="n">
         <v>-0.31</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="42">
@@ -4013,73 +4013,73 @@
         <v>45.73</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>45.36</v>
+        <v>45.54</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>59.04</v>
+        <v>55.62</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>42.45</v>
+        <v>38.56</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45.27</v>
+        <v>58.35</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>89.04000000000001</v>
+        <v>95.86</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>65.09</v>
+        <v>77.77</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>63.52</v>
+        <v>76.23</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>63.52</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>79.06</v>
+        <v>77.31</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>70.04000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>72.83</v>
+        <v>80.48</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>68.06999999999999</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>45.07</v>
+        <v>45.34</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>36.62</v>
+        <v>48.64</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>51.3</v>
+        <v>56.85</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>44.26</v>
+        <v>57.12</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>43.92</v>
+        <v>43.6</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>44.32</v>
+        <v>45.5</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>44.32</v>
+        <v>43.09</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>31.72</v>
+        <v>34.36</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>34.33</v>
+        <v>34.27</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>34.64</v>
+        <v>34.67</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>33.24</v>
+        <v>40.89</v>
       </c>
     </row>
     <row r="45">
@@ -4184,70 +4184,70 @@
         <v>0.27</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.23</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.38</v>
+        <v>-1.22</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-1.46</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.32</v>
+        <v>-1.24</v>
       </c>
       <c r="M46" s="3" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="P46" s="3" t="n">
         <v>-0.14</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="Q46" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="47">
@@ -4433,73 +4433,73 @@
         <v>43.7</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>43.35</v>
+        <v>43.53</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>56.26</v>
+        <v>53.21</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>38.79</v>
+        <v>35.21</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>41.55</v>
+        <v>53.56</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>57.9</v>
+        <v>69.03</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>56.85</v>
+        <v>68.3</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>56.81</v>
+        <v>65.53</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>70.55</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>68.20999999999999</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>63.87</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>42.12</v>
+        <v>41.49</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>34.13</v>
+        <v>44.55</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>48.04</v>
+        <v>52.4</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>39.3</v>
+        <v>50.13</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>38.99</v>
+        <v>38.43</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>39.36</v>
+        <v>40.08</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>39.25</v>
+        <v>37.95</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>27.87</v>
+        <v>29.81</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>31.34</v>
+        <v>31.2</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>31.71</v>
+        <v>31.5</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>30.2</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="50">
@@ -4601,73 +4601,73 @@
         <v>-1.7</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.74</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-2.25</v>
+        <v>-2.08</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-3.57</v>
+        <v>-3.31</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-3.45</v>
+        <v>-4.45</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-10.23</v>
+        <v>-11.98</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-7.06</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-7.05</v>
+        <v>-9.15</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-7.22</v>
+        <v>-9.17</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-8.82</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-4.84</v>
+        <v>-7.23</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-4.98</v>
+        <v>-6.66</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-4.54</v>
+        <v>-6.28</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-3.03</v>
+        <v>-3.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.49</v>
+        <v>-4.19</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.22</v>
+        <v>-4.51</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-4.87</v>
+        <v>-6.87</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-5.07</v>
+        <v>-5.3</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-4.96</v>
+        <v>-5.37</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.02</v>
+        <v>-5.05</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-3.57</v>
+        <v>-4.2</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.56</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-2.76</v>
+        <v>-2.96</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.57</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="52">
@@ -4853,73 +4853,73 @@
         <v>45.09</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>44.73</v>
+        <v>45</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>57.64</v>
+        <v>54.69</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>41.94</v>
+        <v>38.18</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>44.64</v>
+        <v>57.54</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>87.11</v>
+        <v>93.69</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>62.58</v>
+        <v>75.44</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>61.8</v>
+        <v>75.19</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>62.28</v>
+        <v>72.67</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>77.20999999999999</v>
+        <v>76.48</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>69.34999999999999</v>
+        <v>85.83</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>72.47</v>
+        <v>80.48</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>67.53</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>44.75</v>
+        <v>44.76</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>36.29</v>
+        <v>47.93</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>50.9</v>
+        <v>56.06</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>44</v>
+        <v>56.44</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>43.32</v>
+        <v>44.13</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>43.36</v>
+        <v>41.99</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>30.61</v>
+        <v>33.05</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.61</v>
+        <v>33.45</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>34.23</v>
+        <v>34.02</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>32.51</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="55">
@@ -5021,73 +5021,73 @@
         <v>-0.32</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.27</v>
       </c>
       <c r="E56" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="M56" s="3" t="n">
         <v>-0.86</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>-0.83</v>
-      </c>
       <c r="N56" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="P56" s="3" t="n">
         <v>-0.72</v>
       </c>
-      <c r="O56" s="3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="P56" s="3" t="n">
+      <c r="Q56" s="3" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Y56" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="Z56" s="3" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="Q56" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R56" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="S56" s="3" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="T56" s="3" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="U56" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V56" s="3" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="W56" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="X56" s="3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="Y56" s="3" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="Z56" s="3" t="n">
-        <v>-0.26</v>
       </c>
     </row>
     <row r="57">
@@ -5273,73 +5273,73 @@
         <v>47.3</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>46.92</v>
+        <v>47.11</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>61.01</v>
+        <v>57.53</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>43.67</v>
+        <v>39.67</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>46.58</v>
+        <v>59.98</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>91.63</v>
+        <v>98.75</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>66.76000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>65.47</v>
+        <v>75.84</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>81.73999999999999</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>72.34999999999999</v>
+        <v>88.55</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>75.38</v>
+        <v>83.45</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>70.52</v>
+        <v>76.59</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>46.65</v>
+        <v>46.83</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>37.91</v>
+        <v>50.25</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>53.11</v>
+        <v>58.79</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>45.73</v>
+        <v>58.95</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>45.23</v>
+        <v>44.86</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>45.6</v>
+        <v>46.76</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>45.6</v>
+        <v>44.24</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>32.64</v>
+        <v>35.32</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>35.25</v>
+        <v>35.16</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>35.65</v>
+        <v>35.64</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>34.32</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="60">
@@ -5441,73 +5441,73 @@
         <v>1.89</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U61" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="V61" s="3" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>1.18</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="62">
@@ -5693,73 +5693,73 @@
         <v>47.95</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>47.56</v>
+        <v>47.75</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>61.91</v>
+        <v>58.32</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>44.27</v>
+        <v>40.21</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>47.22</v>
+        <v>60.8</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>92.98</v>
+        <v>100.2</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>67.81</v>
+        <v>81.08</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>66.42</v>
+        <v>79.84</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>66.56</v>
+        <v>76.86</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>83.11</v>
+        <v>81.31</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>73.56999999999999</v>
+        <v>89.83</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>76.56</v>
+        <v>84.67</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>71.63</v>
+        <v>77.7</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>47.38</v>
+        <v>47.52</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>38.51</v>
+        <v>50.98</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>54.01</v>
+        <v>59.65</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>46.55</v>
+        <v>59.88</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>45.99</v>
+        <v>45.56</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>46.36</v>
+        <v>47.49</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>46.31</v>
+        <v>44.98</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>33.16</v>
+        <v>35.84</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>35.77</v>
+        <v>35.68</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.13</v>
+        <v>36.09</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>34.86</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="65">
@@ -5861,73 +5861,73 @@
         <v>2.54</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>4.65</v>
+        <v>5.01</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>3.74</v>
+        <v>2.76</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="U66" s="3" t="n">
         <v>2.04</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="67">
@@ -6113,73 +6113,73 @@
         <v>48.61</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>48.22</v>
+        <v>48.42</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>62.71</v>
+        <v>59.13</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>44.83</v>
+        <v>40.76</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>47.82</v>
+        <v>61.64</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>94.06999999999999</v>
+        <v>101.37</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>68.23</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>66.91</v>
+        <v>80.59</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>66.97</v>
+        <v>77.66</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>84.08</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>74.34999999999999</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>77.54000000000001</v>
+        <v>85.83</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>72.54000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>47.99</v>
+        <v>48.12</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>38.96</v>
+        <v>51.63</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>54.58</v>
+        <v>60.41</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>46.99</v>
+        <v>60.58</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>46.28</v>
+        <v>45.84</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>46.6</v>
+        <v>47.79</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>46.61</v>
+        <v>45.22</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>33.51</v>
+        <v>36.22</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>36.59</v>
+        <v>36.58</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>35.28</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="70">
@@ -6281,73 +6281,73 @@
         <v>3.21</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.82</v>
+        <v>3.64</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>5.74</v>
+        <v>6.18</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>2.95</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4.71</v>
+        <v>3.96</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4.16</v>
+        <v>4.47</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="Q71" s="3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U71" s="3" t="n">
         <v>2.34</v>
       </c>
-      <c r="R71" s="3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="S71" s="3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T71" s="3" t="n">
+      <c r="V71" s="3" t="n">
         <v>2.22</v>
       </c>
-      <c r="U71" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V71" s="3" t="n">
-        <v>2.33</v>
-      </c>
       <c r="W71" s="3" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>2.12</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="72">
@@ -6533,73 +6533,73 @@
         <v>46.91</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>46.53</v>
+        <v>46.72</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>60.5</v>
+        <v>57.12</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>43.23</v>
+        <v>39.31</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>46.15</v>
+        <v>59.49</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>90.68000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>66.08</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>64.81</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>81.23999999999999</v>
+        <v>79.42</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>71.76000000000001</v>
+        <v>87.92</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>70.16</v>
+        <v>76.19</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>46.41</v>
+        <v>46.5</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>37.67</v>
+        <v>49.94</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>52.78</v>
+        <v>58.42</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>45.31</v>
+        <v>58.41</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>44.82</v>
+        <v>44.45</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>45.18</v>
+        <v>46.28</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>45.13</v>
+        <v>43.84</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>32.27</v>
+        <v>34.99</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.96</v>
+        <v>34.87</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>35.32</v>
+        <v>35.31</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>34</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="75">
@@ -6701,73 +6701,73 @@
         <v>1.5</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="I76" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="X76" s="3" t="n">
         <v>1.12</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>1.08</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>0.85</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="77">
@@ -6953,73 +6953,73 @@
         <v>45.41</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>45.09</v>
+        <v>45.27</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>58.51</v>
+        <v>55.29</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.36</v>
+        <v>38.52</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>88.33</v>
+        <v>95.19</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>64.95999999999999</v>
+        <v>78</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>63.9</v>
+        <v>77.45</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>64.03</v>
+        <v>74.7</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>79.37</v>
+        <v>78.55</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>70.18000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>73.19</v>
+        <v>81.45</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>68.41</v>
+        <v>74.52</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>45.16</v>
+        <v>45.48</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>36.62</v>
+        <v>48.74</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>51.25</v>
+        <v>56.9</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>44.17</v>
+        <v>57</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>44.06</v>
+        <v>43.73</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>44.32</v>
+        <v>45.45</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>44.28</v>
+        <v>43</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>31.43</v>
+        <v>34.01</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>33.88</v>
+        <v>33.75</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>32.77</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="80">
@@ -7373,73 +7373,73 @@
         <v>45.82</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>45.54</v>
+        <v>45.87</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>58.51</v>
+        <v>55.57</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>42.66</v>
+        <v>38.91</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>45.45</v>
+        <v>58.77</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>88.15000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>61</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>60.23</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>60.69</v>
+        <v>71.56</v>
       </c>
       <c r="L84" s="3" t="n">
         <v>75.23999999999999</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>69.20999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>81.12</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>67.27</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>44.89</v>
+        <v>45.07</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>36.4</v>
+        <v>48.21</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>51.15</v>
+        <v>56.34</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>44.75</v>
+        <v>57.46</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>42.44</v>
+        <v>42.17</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>42.95</v>
+        <v>43.7</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>42.99</v>
+        <v>41.75</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>30.31</v>
+        <v>32.89</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>34.05</v>
+        <v>34.13</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>34.93</v>
+        <v>34.7</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>33.34</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="85">
@@ -7541,73 +7541,73 @@
         <v>0.41</v>
       </c>
       <c r="D86" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="S86" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>0.58</v>
-      </c>
       <c r="T86" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.56</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.75</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.29</v>
+        <v>-1.25</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>-1.12</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="87">
@@ -7793,73 +7793,73 @@
         <v>46</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>45.96</v>
+        <v>46.15</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>60.32</v>
+        <v>56.48</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>44.13</v>
+        <v>40</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>46.83</v>
+        <v>60.29</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>91.06</v>
+        <v>97.63</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>66.97</v>
+        <v>80</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>78.87</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>65.2</v>
+        <v>75.61</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>80.5</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>86.09</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>73.56</v>
+        <v>80.88</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>68.89</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>45.43</v>
+        <v>45.52</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>36.73</v>
+        <v>48.74</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>50.9</v>
+        <v>56.68</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>43.65</v>
+        <v>56.33</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>43.97</v>
+        <v>43.6</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>44.23</v>
+        <v>45.32</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>44.14</v>
+        <v>42.83</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>31.53</v>
+        <v>34.05</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>34.36</v>
+        <v>34.06</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>34.61</v>
+        <v>34.53</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.71</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="90">
@@ -7961,73 +7961,73 @@
         <v>0.6</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1.81</v>
+        <v>1.19</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>1.13</v>
+        <v>0.71</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0.28</v>
+        <v>-0.6</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.57</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0.48</v>
+        <v>-0.37</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.68</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.13</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-07T07:11:47</t>
+          <t>CreatedAt: 2026-04-07T08:10:17</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -677,49 +677,49 @@
         <v>41.86</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>39.83</v>
+        <v>41.65</v>
       </c>
       <c r="M4" s="3" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="N4" s="3" t="n">
         <v>24.09</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>23.4</v>
-      </c>
       <c r="O4" s="3" t="n">
-        <v>25.21</v>
+        <v>30.67</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.83</v>
+        <v>30.82</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.6</v>
+        <v>30.85</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>44.8</v>
+        <v>54.86</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>51.37</v>
+        <v>58.99</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>72.77</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>97.56999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>292.64</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>72.76000000000001</v>
+        <v>69.14</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>76.8</v>
+        <v>67.5</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>35.64</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
     </row>
     <row r="5">
@@ -845,49 +845,49 @@
         <v>-0.46</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.46</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-0.31</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.04</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.89</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.37</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-9.359999999999999</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.45</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.77</v>
+        <v>-1.55</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>-0.39</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="7">
@@ -1097,49 +1097,49 @@
         <v>43.49</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>41.55</v>
+        <v>43.45</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>24.9</v>
+        <v>26.14</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>24.33</v>
+        <v>25.07</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>25.98</v>
+        <v>31.67</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>25.74</v>
+        <v>31.89</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>29.54</v>
+        <v>31.89</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>46.07</v>
+        <v>56.46</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>52.76</v>
+        <v>60.65</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>74.20999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>99.41</v>
+        <v>92.89</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>299.01</v>
+        <v>299.31</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>80.17</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>37.15</v>
+        <v>37.19</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>49.07</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="10">
@@ -1265,49 +1265,49 @@
         <v>1.17</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2.99</v>
+        <v>-2.69</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="12">
@@ -1517,49 +1517,49 @@
         <v>43.49</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>41.55</v>
+        <v>43.45</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>24.9</v>
+        <v>26.14</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>24.33</v>
+        <v>25.07</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>26.01</v>
+        <v>31.67</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>25.74</v>
+        <v>31.89</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>29.54</v>
+        <v>31.92</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>46.07</v>
+        <v>56.46</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>52.76</v>
+        <v>60.65</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>74.20999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>99.41</v>
+        <v>92.89</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>299.01</v>
+        <v>299.31</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>75.04000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>80.17</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>37.15</v>
+        <v>37.19</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>49.12</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="15">
@@ -1685,49 +1685,49 @@
         <v>1.17</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-2.99</v>
+        <v>-2.69</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="17">
@@ -1937,49 +1937,49 @@
         <v>42.11</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>40.03</v>
+        <v>41.82</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>24.21</v>
+        <v>25.39</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>23.54</v>
+        <v>24.23</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>25.36</v>
+        <v>30.88</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>25.02</v>
+        <v>31.03</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>28.83</v>
+        <v>31.13</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>45.16</v>
+        <v>55.29</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>51.78</v>
+        <v>59.46</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>73.34</v>
+        <v>79.3</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>98.34</v>
+        <v>91.88</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>295.79</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>73.63</v>
+        <v>70.03</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>77.56</v>
+        <v>68.16</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>35.96</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>47.35</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="20">
@@ -2105,49 +2105,49 @@
         <v>-0.21</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="M21" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N21" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="O21" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.61</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.83</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.35</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.77</v>
+        <v>-1.56</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>-6.21</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.89</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22">
@@ -2357,49 +2357,49 @@
         <v>42.11</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>40.03</v>
+        <v>41.82</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>24.21</v>
+        <v>25.39</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>23.54</v>
+        <v>24.23</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>25.36</v>
+        <v>30.88</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>25.02</v>
+        <v>31.03</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>28.83</v>
+        <v>31.13</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>45.16</v>
+        <v>55.29</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>51.78</v>
+        <v>59.46</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>73.34</v>
+        <v>79.3</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>98.34</v>
+        <v>91.88</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>295.79</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>73.63</v>
+        <v>70.03</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>77.56</v>
+        <v>68.16</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>35.96</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>47.35</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="25">
@@ -2525,49 +2525,49 @@
         <v>-0.21</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="M26" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="O26" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.61</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.83</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.35</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.77</v>
+        <v>-1.56</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>-6.21</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.89</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -2777,49 +2777,49 @@
         <v>42.36</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>40.19</v>
+        <v>42.03</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>24.35</v>
+        <v>25.52</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>25.54</v>
+        <v>31.1</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>25.23</v>
+        <v>31.28</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>29.09</v>
+        <v>31.41</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>45.57</v>
+        <v>55.79</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>52.24</v>
+        <v>59.99</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>73.98999999999999</v>
+        <v>80.09</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>99.41</v>
+        <v>92.89</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>300.2</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>74.81</v>
+        <v>71.09</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>78.41</v>
+        <v>68.91</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>36.25</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>47.92</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="30">
@@ -2945,49 +2945,49 @@
         <v>0.04</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="32">
@@ -3197,49 +3197,49 @@
         <v>44.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>42.69</v>
+        <v>44.69</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>25.36</v>
+        <v>26.63</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>24.87</v>
+        <v>25.65</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>26.41</v>
+        <v>32.19</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>26.28</v>
+        <v>32.53</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30</v>
+        <v>32.39</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>46.64</v>
+        <v>57.15</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>53.41</v>
+        <v>61.33</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>74.89</v>
+        <v>81.06</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>100.31</v>
+        <v>93.73</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>301.4</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>75.81</v>
+        <v>72.03</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>81.84</v>
+        <v>72</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>37.93</v>
+        <v>37.97</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>50.22</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="35">
@@ -3365,49 +3365,49 @@
         <v>2.18</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>3.27</v>
+        <v>2.95</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="37">
@@ -3617,49 +3617,49 @@
         <v>41.86</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>39.83</v>
+        <v>41.65</v>
       </c>
       <c r="M39" s="3" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="N39" s="3" t="n">
         <v>24.09</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>23.4</v>
-      </c>
       <c r="O39" s="3" t="n">
-        <v>25.21</v>
+        <v>30.67</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>24.83</v>
+        <v>30.82</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>28.6</v>
+        <v>30.85</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>44.8</v>
+        <v>54.86</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>51.37</v>
+        <v>58.99</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>72.77</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>97.56999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>292.64</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>72.76000000000001</v>
+        <v>69.14</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>76.8</v>
+        <v>67.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>35.64</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
     </row>
     <row r="40">
@@ -3785,49 +3785,49 @@
         <v>-0.46</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.46</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>-0.31</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.04</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.89</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.37</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-9.359999999999999</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.45</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.77</v>
+        <v>-1.55</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>-0.39</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="42">
@@ -4037,49 +4037,49 @@
         <v>42.96</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>40.96</v>
+        <v>42.88</v>
       </c>
       <c r="M44" s="3" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="N44" s="3" t="n">
         <v>24.64</v>
       </c>
-      <c r="N44" s="3" t="n">
-        <v>23.92</v>
-      </c>
       <c r="O44" s="3" t="n">
-        <v>25.77</v>
+        <v>31.35</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>25.35</v>
+        <v>31.44</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>29.15</v>
+        <v>31.41</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>45.8</v>
+        <v>56.12</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>52.4</v>
+        <v>60.11</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>74.20999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>99.31</v>
+        <v>92.7</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>298.42</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>73.19</v>
+        <v>69.55</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>78.25</v>
+        <v>68.7</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>36</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>47.21</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="45">
@@ -4205,43 +4205,43 @@
         <v>0.64</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>0.17</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.23</v>
-      </c>
       <c r="R46" s="3" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.74</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>-3.58</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.04</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>-0.04</v>
@@ -4457,49 +4457,49 @@
         <v>40</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>37.93</v>
+        <v>39.77</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>22.83</v>
+        <v>23.9</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>22.09</v>
+        <v>22.76</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>23.85</v>
+        <v>29.01</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>23.33</v>
+        <v>28.93</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>26.88</v>
+        <v>28.96</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>42.7</v>
+        <v>52.44</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>49.16</v>
+        <v>56.45</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>66.47</v>
+        <v>71.95</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>89.38</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>269.16</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>65.86</v>
+        <v>62.58</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>73.09</v>
+        <v>64.23</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>33.33</v>
+        <v>33.34</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>43.63</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="50">
@@ -4625,49 +4625,49 @@
         <v>-2.32</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.51</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.7</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.71</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.12</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.77</v>
+        <v>-2.2</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.04</v>
+        <v>-2.2</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.82</v>
+        <v>-3.46</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.34</v>
+        <v>-3.84</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-10.73</v>
+        <v>-10.01</v>
       </c>
       <c r="V51" s="3" t="n">
         <v>-32.84</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-8.43</v>
+        <v>-8.01</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.48</v>
+        <v>-4.82</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>-2.7</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-3.58</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="52">
@@ -4877,49 +4877,49 @@
         <v>41.05</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>39.91</v>
+        <v>41.73</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>24.18</v>
+        <v>25.34</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>23.49</v>
+        <v>24.21</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>25.21</v>
+        <v>30.7</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>24.7</v>
+        <v>30.64</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>28.44</v>
+        <v>30.67</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>44.94</v>
+        <v>55.18</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>50.82</v>
+        <v>58.42</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>71.78</v>
+        <v>77.7</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>96.72</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>294.06</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>71.98999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>77.48</v>
+        <v>68.23</v>
       </c>
       <c r="Y54" s="3" t="n">
         <v>35.71</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>46.88</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="55">
@@ -5045,49 +5045,49 @@
         <v>-1.27</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="M56" s="3" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="N56" s="3" t="n">
         <v>-0.27</v>
       </c>
-      <c r="N56" s="3" t="n">
-        <v>-0.26</v>
-      </c>
       <c r="O56" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.43</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.72</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.87</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.73</v>
+        <v>-2.95</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-3.39</v>
+        <v>-3.16</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>-7.94</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.19</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.82</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>-0.32</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="57">
@@ -5297,49 +5297,49 @@
         <v>44.27</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>42.29</v>
+        <v>44.27</v>
       </c>
       <c r="M59" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="N59" s="3" t="n">
         <v>25.41</v>
       </c>
-      <c r="N59" s="3" t="n">
-        <v>24.66</v>
-      </c>
       <c r="O59" s="3" t="n">
-        <v>26.6</v>
+        <v>32.32</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>26.12</v>
+        <v>32.39</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>30.03</v>
+        <v>32.36</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>47.27</v>
+        <v>57.98</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>53.96</v>
+        <v>61.96</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>76.5</v>
+        <v>82.8</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>102.15</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>307.54</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>75.12</v>
+        <v>71.38</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>80.58</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="Y59" s="3" t="n">
         <v>37</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>48.62</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="60">
@@ -5465,49 +5465,49 @@
         <v>1.95</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>5.54</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.96</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="62">
@@ -5717,49 +5717,49 @@
         <v>44.97</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>42.96</v>
+        <v>44.98</v>
       </c>
       <c r="M64" s="3" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="N64" s="3" t="n">
         <v>25.79</v>
       </c>
-      <c r="N64" s="3" t="n">
-        <v>25.03</v>
-      </c>
       <c r="O64" s="3" t="n">
-        <v>27</v>
+        <v>32.8</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>26.5</v>
+        <v>32.87</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>30.47</v>
+        <v>32.87</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>48.02</v>
+        <v>58.9</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>54.86</v>
+        <v>63</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>77.78</v>
+        <v>84.19</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>103.85</v>
+        <v>96.94</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>312.95</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>76.27</v>
+        <v>72.48</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>81.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="Y64" s="3" t="n">
         <v>37.54</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>49.28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65">
@@ -5885,49 +5885,49 @@
         <v>2.65</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.27</v>
+        <v>3.54</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.74</v>
+        <v>3.49</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>10.95</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>3.36</v>
+        <v>2.95</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="67">
@@ -6137,49 +6137,49 @@
         <v>45.45</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>43.42</v>
+        <v>45.46</v>
       </c>
       <c r="M69" s="3" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="N69" s="3" t="n">
         <v>26.09</v>
       </c>
-      <c r="N69" s="3" t="n">
-        <v>25.35</v>
-      </c>
       <c r="O69" s="3" t="n">
-        <v>27.31</v>
+        <v>33.22</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>26.84</v>
+        <v>33.26</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.83</v>
+        <v>33.22</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>48.53</v>
+        <v>59.53</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>55.15</v>
+        <v>63.33</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>78.19</v>
+        <v>84.63</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>104.06</v>
+        <v>97.14</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>313.28</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>75.95999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>82.44</v>
+        <v>72.45</v>
       </c>
       <c r="Y69" s="3" t="n">
         <v>37.81</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>49.95</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="70">
@@ -6305,49 +6305,49 @@
         <v>3.14</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>3.01</v>
+        <v>3.63</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.67</v>
+        <v>3.98</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>11.28</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>3.87</v>
+        <v>3.41</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>1.78</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="72">
@@ -6557,49 +6557,49 @@
         <v>44.17</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>42.15</v>
+        <v>44.13</v>
       </c>
       <c r="M74" s="3" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="N74" s="3" t="n">
         <v>25.28</v>
       </c>
-      <c r="N74" s="3" t="n">
-        <v>24.53</v>
-      </c>
       <c r="O74" s="3" t="n">
-        <v>26.52</v>
+        <v>32.26</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>26.04</v>
+        <v>32.29</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>29.88</v>
+        <v>32.16</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>47.07</v>
+        <v>57.75</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>53.96</v>
+        <v>61.96</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>76.19</v>
+        <v>82.47</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>101.84</v>
+        <v>95.06</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>307.85</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>75.12</v>
+        <v>71.38</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>80.33</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Y74" s="3" t="n">
         <v>36.81</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>48.47</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="75">
@@ -6725,49 +6725,49 @@
         <v>1.86</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>5.85</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>0.77</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="77">
@@ -6977,49 +6977,49 @@
         <v>42.32</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>40.47</v>
+        <v>42.28</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>24.45</v>
+        <v>25.59</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>23.75</v>
+        <v>24.47</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>25.59</v>
+        <v>31.13</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>25.1</v>
+        <v>31.13</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>28.92</v>
+        <v>31.16</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>45.52</v>
+        <v>55.9</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>52.5</v>
+        <v>60.29</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>74.51000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>100.11</v>
+        <v>93.45</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>302</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>74.29000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>78.56999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>36.03</v>
+        <v>36.04</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>47.21</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="80">
@@ -7397,49 +7397,49 @@
         <v>40.57</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>40.75</v>
+        <v>42.49</v>
       </c>
       <c r="M84" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="N84" s="3" t="n">
         <v>24.72</v>
       </c>
-      <c r="N84" s="3" t="n">
-        <v>23.96</v>
-      </c>
       <c r="O84" s="3" t="n">
-        <v>25.7</v>
+        <v>31.25</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>25.1</v>
+        <v>31.13</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>28.86</v>
+        <v>31.13</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>45.61</v>
+        <v>56.01</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>50.19</v>
+        <v>57.64</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>76.81</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>95.89</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="V84" s="3" t="n">
         <v>289.83</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>71.36</v>
+        <v>67.81</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>78.25</v>
+        <v>69.19</v>
       </c>
       <c r="Y84" s="3" t="n">
         <v>36.29</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>47.49</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="85">
@@ -7565,49 +7565,49 @@
         <v>-1.74</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="P86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.31</v>
+        <v>-2.65</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.62</v>
+        <v>-3.84</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-4.22</v>
+        <v>-3.94</v>
       </c>
       <c r="V86" s="3" t="n">
         <v>-12.17</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.93</v>
+        <v>-2.78</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.31</v>
+        <v>0.14</v>
       </c>
       <c r="Y86" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="87">
@@ -7817,49 +7817,49 @@
         <v>42.36</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>40.19</v>
+        <v>42.03</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>24.35</v>
+        <v>25.52</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>25.54</v>
+        <v>31.1</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>25.23</v>
+        <v>31.28</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>29.09</v>
+        <v>31.41</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>45.57</v>
+        <v>55.79</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>52.24</v>
+        <v>59.99</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>73.98999999999999</v>
+        <v>80.09</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>99.41</v>
+        <v>92.89</v>
       </c>
       <c r="V89" s="3" t="n">
         <v>300.2</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>74.81</v>
+        <v>71.09</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>78.41</v>
+        <v>68.91</v>
       </c>
       <c r="Y89" s="3" t="n">
         <v>36.25</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>47.92</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="90">
@@ -7985,49 +7985,49 @@
         <v>0.04</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V91" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="Y91" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-09T00:11:42</t>
+          <t>CreatedAt: 2026-04-09T01:11:33</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -662,64 +662,64 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>133.4</v>
+        <v>7.38</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>25.17</v>
+        <v>14.56</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.51</v>
+        <v>7.31</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.57</v>
+        <v>14.6</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>6.21</v>
+        <v>5.99</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>6.36</v>
+        <v>6.03</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>14.57</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>14.61</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>14.64</v>
-      </c>
       <c r="T4" s="3" t="n">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>31.77</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>35.75</v>
+        <v>34.58</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>31.96</v>
+        <v>32.03</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>25.55</v>
+        <v>29.63</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>25.67</v>
+        <v>31.5</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>31.97</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="5">
@@ -833,61 +833,61 @@
         <v>0.03</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="O6" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>-0.19</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="S6" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-0.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.76</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.58</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="7">
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>118.76</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -1082,64 +1082,64 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>15.31</v>
+        <v>7.69</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>26.08</v>
+        <v>15.06</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>7.64</v>
+        <v>7.45</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>14.75</v>
+        <v>14.79</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6.52</v>
+        <v>6.17</v>
       </c>
       <c r="M9" s="3" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="N9" s="3" t="n">
         <v>14.94</v>
       </c>
-      <c r="N9" s="3" t="n">
-        <v>14.96</v>
-      </c>
       <c r="O9" s="3" t="n">
-        <v>11.6</v>
+        <v>15.06</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.43</v>
+        <v>14.98</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>14.66</v>
+        <v>12.18</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>14.64</v>
+        <v>14.58</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>14.53</v>
+        <v>14.56</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>31.74</v>
+        <v>31.81</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>36.04</v>
+        <v>34.96</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>32.64</v>
+        <v>32.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>26.47</v>
+        <v>30.66</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>26.75</v>
+        <v>32.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>33.5</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="10">
@@ -1250,64 +1250,64 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.86</v>
+        <v>0.53</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="S11" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>-0.38</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-0.54</v>
-      </c>
       <c r="W11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -1499,67 +1499,67 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>97.63</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15.31</v>
+        <v>7.7</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>26.08</v>
+        <v>15.06</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>7.64</v>
+        <v>7.45</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>14.75</v>
+        <v>14.79</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>6.52</v>
+        <v>6.17</v>
       </c>
       <c r="M14" s="3" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="N14" s="3" t="n">
         <v>14.94</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>14.96</v>
-      </c>
       <c r="O14" s="3" t="n">
-        <v>11.6</v>
+        <v>15.08</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.66</v>
+        <v>12.18</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>14.64</v>
+        <v>14.58</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>14.51</v>
+        <v>14.56</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>31.74</v>
+        <v>31.77</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>36.04</v>
+        <v>34.96</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>32.67</v>
+        <v>32.7</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>26.47</v>
+        <v>30.66</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>26.75</v>
+        <v>32.83</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>33.54</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="15">
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>97.63</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>90.06999999999999</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
@@ -1670,64 +1670,64 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.86</v>
+        <v>0.53</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="S16" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="V16" s="3" t="n">
         <v>-0.38</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>-0.54</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -1922,43 +1922,43 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14.74</v>
+        <v>7.43</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>25.35</v>
+        <v>14.67</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>7.57</v>
+        <v>7.36</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>14.69</v>
+        <v>14.73</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>6.26</v>
+        <v>6.04</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>6.42</v>
+        <v>6.08</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>14.73</v>
+        <v>14.69</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>11.35</v>
+        <v>14.72</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>7.26</v>
+        <v>14.63</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.61</v>
+        <v>14.66</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>14.6</v>
+        <v>12.13</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>14.75</v>
+        <v>14.72</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>14.78</v>
@@ -1967,19 +1967,19 @@
         <v>32.03</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>36.07</v>
+        <v>34.89</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>25.81</v>
+        <v>29.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>25.98</v>
+        <v>31.88</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.35</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="20">
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.13</v>
@@ -2099,34 +2099,34 @@
         <v>0.04</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.18</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>-0.27</v>
@@ -2135,19 +2135,19 @@
         <v>-0.45</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.29</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="22">
@@ -2342,43 +2342,43 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>133.5</v>
+        <v>7.43</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>25.35</v>
+        <v>14.67</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>7.57</v>
+        <v>7.36</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>14.69</v>
+        <v>14.73</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6.26</v>
+        <v>6.04</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>6.42</v>
+        <v>6.08</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>14.73</v>
+        <v>14.69</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>11.35</v>
+        <v>14.72</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>7.26</v>
+        <v>14.63</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>14.61</v>
+        <v>14.66</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>14.6</v>
+        <v>12.13</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>14.75</v>
+        <v>14.72</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>14.78</v>
@@ -2387,19 +2387,19 @@
         <v>32.03</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>36.07</v>
+        <v>34.89</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>32.22</v>
+        <v>32.31</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>25.81</v>
+        <v>29.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.98</v>
+        <v>31.88</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.35</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="25">
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.13</v>
@@ -2519,34 +2519,34 @@
         <v>0.04</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>-0.27</v>
@@ -2555,19 +2555,19 @@
         <v>-0.45</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.29</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>118.76</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
@@ -2762,64 +2762,64 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.83</v>
+        <v>7.47</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>25.53</v>
+        <v>14.75</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>7.63</v>
+        <v>7.43</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>14.84</v>
+        <v>14.88</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.31</v>
+        <v>6.1</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.47</v>
+        <v>6.13</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.83</v>
+        <v>14.86</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.88</v>
+        <v>14.82</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>11.44</v>
+        <v>14.86</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>7.32</v>
+        <v>14.75</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>14.73</v>
+        <v>14.76</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>14.72</v>
+        <v>12.22</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>14.91</v>
+        <v>14.87</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>14.93</v>
+        <v>14.95</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>32.31</v>
+        <v>32.34</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>36.47</v>
+        <v>35.31</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>32.51</v>
+        <v>32.63</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>26.09</v>
+        <v>30.23</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>26.35</v>
+        <v>32.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.78</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="30">
@@ -2930,64 +2930,64 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>0.22</v>
       </c>
-      <c r="H31" s="3" t="n">
-        <v>0.31</v>
-      </c>
       <c r="I31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="K31" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="M31" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O31" s="3" t="n">
+      <c r="P31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="S31" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>-0.11</v>
-      </c>
       <c r="W31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="32">
@@ -3179,67 +3179,67 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>97.63</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>15.74</v>
+        <v>7.91</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>26.61</v>
+        <v>15.35</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>7.68</v>
+        <v>7.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>14.78</v>
+        <v>14.85</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>6.35</v>
+        <v>6.13</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>6.55</v>
+        <v>6.2</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>15.03</v>
+        <v>15.07</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>11.71</v>
+        <v>15.23</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>97.59</v>
+        <v>97.5</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>15.16</v>
+        <v>15.14</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>14.67</v>
+        <v>12.21</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>14.53</v>
+        <v>14.47</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>14.38</v>
+        <v>14.44</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>31.74</v>
+        <v>31.84</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>36.21</v>
+        <v>35.2</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>33</v>
+        <v>33.07</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>26.9</v>
+        <v>31.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>27.26</v>
+        <v>33.45</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>34.29</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="35">
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>97.63</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>90.06999999999999</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
@@ -3350,64 +3350,64 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.46</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.61</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.64</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="37">
@@ -3602,64 +3602,64 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>133.4</v>
+        <v>7.38</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>25.17</v>
+        <v>14.56</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>7.51</v>
+        <v>7.31</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>14.57</v>
+        <v>14.6</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>6.21</v>
+        <v>5.99</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>6.36</v>
+        <v>6.03</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>14.57</v>
       </c>
       <c r="N39" s="3" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>14.61</v>
       </c>
-      <c r="O39" s="3" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>14.64</v>
-      </c>
       <c r="T39" s="3" t="n">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>31.77</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>35.75</v>
+        <v>34.58</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>31.96</v>
+        <v>32.03</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>25.55</v>
+        <v>29.63</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>25.67</v>
+        <v>31.5</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>31.97</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="40">
@@ -3773,61 +3773,61 @@
         <v>0.03</v>
       </c>
       <c r="H41" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K41" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="L41" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="O41" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>-0.19</v>
       </c>
-      <c r="P41" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="S41" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>-0.7</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.76</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.58</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="42">
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>118.76</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0</v>
@@ -4022,64 +4022,64 @@
         <v>0</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>14.68</v>
+        <v>7.39</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>25.38</v>
+        <v>14.62</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>7.51</v>
+        <v>7.32</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>6.21</v>
+        <v>5.97</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>6.35</v>
+        <v>5.99</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>14.57</v>
+        <v>14.51</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>14.6</v>
+        <v>14.52</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>11.28</v>
+        <v>14.59</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>7.22</v>
+        <v>14.55</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>14.55</v>
+        <v>14.63</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>14.5</v>
+        <v>12.09</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>14.74</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>14.8</v>
+        <v>14.81</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>32.03</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>36.04</v>
+        <v>34.82</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>32.22</v>
+        <v>32.28</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>25.63</v>
+        <v>29.72</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>25.54</v>
+        <v>31.37</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>31.93</v>
+        <v>31.65</v>
       </c>
     </row>
     <row r="45">
@@ -4190,64 +4190,64 @@
         <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.26</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.26</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.15</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>-0.45</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.52</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.38</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="47">
@@ -4442,64 +4442,64 @@
         <v>0</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>13.6</v>
+        <v>6.77</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>23.66</v>
+        <v>13.53</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>6.71</v>
+        <v>6.49</v>
       </c>
       <c r="J49" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>5.47</v>
+        <v>5.33</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>5.61</v>
+        <v>5.34</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>12.83</v>
+        <v>12.9</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>12.85</v>
+        <v>12.89</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>12.88</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>6.71</v>
+        <v>13.51</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>13.58</v>
+        <v>13.56</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>13.58</v>
+        <v>11.23</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>13.86</v>
+        <v>13.72</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>13.9</v>
+        <v>13.82</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>30.12</v>
+        <v>30.07</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>33.96</v>
+        <v>32.82</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>30.05</v>
+        <v>30.13</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>23.8</v>
+        <v>27.62</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>23.61</v>
+        <v>28.99</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>29.61</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="50">
@@ -4610,64 +4610,64 @@
         <v>0</v>
       </c>
       <c r="G51" s="3" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="R51" s="3" t="n">
         <v>-1.01</v>
       </c>
-      <c r="H51" s="3" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="Q51" s="3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="R51" s="3" t="n">
+      <c r="S51" s="3" t="n">
         <v>-1.21</v>
       </c>
-      <c r="S51" s="3" t="n">
-        <v>-1.16</v>
-      </c>
       <c r="T51" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.23</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.41</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-2.62</v>
+        <v>-2.53</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-2.52</v>
+        <v>-2.47</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.17</v>
+        <v>-2.46</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.75</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="52">
@@ -4862,64 +4862,64 @@
         <v>0</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>14.52</v>
+        <v>7.27</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>24.85</v>
+        <v>14.25</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>7.28</v>
+        <v>7.08</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>14.32</v>
+        <v>14.35</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>6.19</v>
+        <v>5.97</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>6.32</v>
+        <v>6.01</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>14.66</v>
+        <v>14.73</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>14.6</v>
+        <v>14.65</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>11.28</v>
+        <v>14.64</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>7.25</v>
+        <v>14.62</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>14.67</v>
+        <v>14.72</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>14.51</v>
+        <v>12.06</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>14.75</v>
+        <v>14.71</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>14.78</v>
+        <v>14.81</v>
       </c>
       <c r="U54" s="3" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="W54" s="3" t="n">
         <v>31.41</v>
       </c>
-      <c r="V54" s="3" t="n">
-        <v>35.41</v>
-      </c>
-      <c r="W54" s="3" t="n">
-        <v>31.26</v>
-      </c>
       <c r="X54" s="3" t="n">
-        <v>24.99</v>
+        <v>29.09</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>25.34</v>
+        <v>31.19</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>31.71</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="55">
@@ -5030,64 +5030,64 @@
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.28</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="P56" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="Q56" s="3" t="n">
         <v>-0.12</v>
       </c>
-      <c r="Q56" s="3" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="R56" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.18</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.01</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.1</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.19</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.99</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5282,64 +5282,64 @@
         <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>15.02</v>
+        <v>7.55</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>25.95</v>
+        <v>14.94</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>15.03</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>6.38</v>
+        <v>6.14</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>6.52</v>
+        <v>6.17</v>
       </c>
       <c r="M59" s="3" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="P59" s="3" t="n">
         <v>14.98</v>
       </c>
-      <c r="N59" s="3" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="O59" s="3" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>7.45</v>
-      </c>
       <c r="Q59" s="3" t="n">
-        <v>15.03</v>
+        <v>15.06</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>14.94</v>
+        <v>12.42</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>15.17</v>
+        <v>15.14</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>15.2</v>
+        <v>15.23</v>
       </c>
       <c r="U59" s="3" t="n">
         <v>32.87</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>36.95</v>
+        <v>35.73</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>33</v>
+        <v>33.07</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>26.2</v>
+        <v>30.41</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>26.11</v>
+        <v>32.1</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>32.65</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="60">
@@ -5450,64 +5450,64 @@
         <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>0.19</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="U61" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="62">
@@ -5702,64 +5702,64 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>15.19</v>
+        <v>7.65</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>26.27</v>
+        <v>15.14</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>7.82</v>
+        <v>7.6</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>15.25</v>
+        <v>15.22</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>6.46</v>
+        <v>6.22</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>6.61</v>
+        <v>6.24</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>15.19</v>
+        <v>15.14</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>15.22</v>
+        <v>15.14</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>11.78</v>
+        <v>15.2</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>7.55</v>
+        <v>15.16</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>15.23</v>
+        <v>15.26</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>15.14</v>
+        <v>12.59</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>15.37</v>
+        <v>15.36</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>15.41</v>
+        <v>15.45</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>33.34</v>
+        <v>33.37</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>37.48</v>
+        <v>36.25</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>33.44</v>
+        <v>33.51</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>26.52</v>
+        <v>30.82</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>26.43</v>
+        <v>32.5</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>32.98</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="65">
@@ -5870,64 +5870,64 @@
         <v>0</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0.35</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="V66" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="W66" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="W66" s="3" t="n">
-        <v>0.87</v>
-      </c>
       <c r="X66" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="67">
@@ -6119,67 +6119,67 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="G69" s="3" t="n">
-        <v>15.22</v>
-      </c>
       <c r="H69" s="3" t="n">
-        <v>26.3</v>
+        <v>2000</v>
       </c>
       <c r="I69" s="3" t="n">
+        <v>1999.99</v>
+      </c>
+      <c r="J69" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="J69" s="3" t="n">
-        <v>15.25</v>
-      </c>
       <c r="K69" s="3" t="n">
-        <v>6.47</v>
+        <v>6.23</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>6.61</v>
+        <v>6.26</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>2000</v>
+        <v>15.18</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>15.25</v>
+        <v>15.19</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>7.57</v>
+        <v>2000</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>15.26</v>
+        <v>15.28</v>
       </c>
       <c r="R69" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="S69" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="S69" s="3" t="n">
-        <v>15.4</v>
-      </c>
       <c r="T69" s="3" t="n">
-        <v>15.42</v>
+        <v>15.45</v>
       </c>
       <c r="U69" s="3" t="n">
         <v>33.34</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>37.48</v>
+        <v>2000</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>33.44</v>
+        <v>33.54</v>
       </c>
       <c r="X69" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>26.45</v>
+        <v>2000</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>33.09</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="70">
@@ -6290,64 +6290,64 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H71" s="3" t="n">
         <v>0.61</v>
       </c>
-      <c r="H71" s="3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="I71" s="3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="U71" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="72">
@@ -6371,19 +6371,19 @@
         <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0</v>
+        <v>1992.35</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0</v>
+        <v>1984.86</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1992.17</v>
+        <v>1992.39</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0</v>
+        <v>1984.75</v>
       </c>
       <c r="K72" s="3" t="n">
         <v>0</v>
@@ -6392,25 +6392,25 @@
         <v>0</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1984.78</v>
+        <v>0</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>1988.19</v>
+        <v>1984.75</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>0</v>
+        <v>1984.81</v>
       </c>
       <c r="Q72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>1984.83</v>
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>0</v>
+        <v>1984.64</v>
       </c>
       <c r="T72" s="3" t="n">
         <v>0</v>
@@ -6419,19 +6419,19 @@
         <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>0</v>
+        <v>1963.75</v>
       </c>
       <c r="W72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>1973.43</v>
+        <v>1969.18</v>
       </c>
       <c r="Y72" s="3" t="n">
-        <v>0</v>
+        <v>1967.47</v>
       </c>
       <c r="Z72" s="3" t="n">
-        <v>0</v>
+        <v>1967.17</v>
       </c>
     </row>
     <row r="73">
@@ -6542,64 +6542,64 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>14.89</v>
+        <v>7.49</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>25.77</v>
+        <v>14.83</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>7.66</v>
+        <v>7.43</v>
       </c>
       <c r="J74" s="3" t="n">
         <v>14.94</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>6.47</v>
+        <v>6.12</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>14.88</v>
+        <v>14.86</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>14.91</v>
+        <v>14.85</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>11.56</v>
+        <v>14.92</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>7.42</v>
+        <v>14.89</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>14.96</v>
+        <v>14.98</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>14.88</v>
+        <v>12.36</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>15.11</v>
+        <v>15.08</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>15.1</v>
+        <v>15.13</v>
       </c>
       <c r="U74" s="3" t="n">
         <v>32.74</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>36.83</v>
+        <v>35.59</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>32.83</v>
+        <v>32.9</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>25.99</v>
+        <v>30.17</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>25.95</v>
+        <v>31.88</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>32.42</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="75">
@@ -6710,64 +6710,64 @@
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="I76" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O76" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="J76" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K76" s="3" t="n">
+      <c r="P76" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T76" s="3" t="n">
         <v>0.08</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>0.05</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>0.26</v>
       </c>
       <c r="V76" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Z76" s="3" t="n">
         <v>0.26</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Z76" s="3" t="n">
-        <v>0.32</v>
       </c>
     </row>
     <row r="77">
@@ -6962,43 +6962,43 @@
         <v>0</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>14.61</v>
+        <v>7.35</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>25.22</v>
+        <v>14.53</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>7.53</v>
+        <v>7.32</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>14.73</v>
+        <v>14.75</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>6.25</v>
+        <v>6.04</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>6.4</v>
+        <v>6.07</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>14.73</v>
+        <v>14.77</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>14.76</v>
+        <v>14.78</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>11.45</v>
+        <v>14.79</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>7.36</v>
+        <v>14.75</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>14.88</v>
+        <v>14.83</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>14.79</v>
+        <v>12.24</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>15.02</v>
+        <v>14.93</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>15.05</v>
@@ -7007,19 +7007,19 @@
         <v>32.47</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>36.58</v>
+        <v>35.34</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>32.57</v>
+        <v>32.6</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>25.96</v>
+        <v>30.08</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>25.87</v>
+        <v>31.75</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>32.09</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="80">
@@ -7382,64 +7382,64 @@
         <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>14.74</v>
+        <v>7.37</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>25.17</v>
+        <v>14.45</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>7.17</v>
+        <v>7.03</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>14.06</v>
+        <v>14.21</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>6.26</v>
+        <v>6.05</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>6.35</v>
+        <v>6.09</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>14.69</v>
+        <v>14.88</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>14.63</v>
+        <v>14.78</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>11.32</v>
+        <v>14.76</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>7.28</v>
+        <v>14.75</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>14.82</v>
+        <v>14.85</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>14.66</v>
+        <v>12.16</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>14.93</v>
+        <v>14.87</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>14.98</v>
+        <v>15.01</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>31.05</v>
+        <v>31.1</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>34.97</v>
+        <v>33.82</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>30.9</v>
+        <v>31.08</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>24.7</v>
+        <v>28.81</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>25.69</v>
+        <v>31.68</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>32.22</v>
+        <v>31.81</v>
       </c>
     </row>
     <row r="85">
@@ -7550,64 +7550,64 @@
         <v>0</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.29</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.54</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="L86" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="T86" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M86" s="3" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="Q86" s="3" t="n">
+      <c r="U86" s="3" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="Y86" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="R86" s="3" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="U86" s="3" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="V86" s="3" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="W86" s="3" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="X86" s="3" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="Y86" s="3" t="n">
-        <v>-0.18</v>
-      </c>
       <c r="Z86" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="87">
@@ -7802,64 +7802,64 @@
         <v>0</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>14.83</v>
+        <v>7.47</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>25.53</v>
+        <v>14.75</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>7.64</v>
+        <v>7.43</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>14.84</v>
+        <v>14.88</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>6.31</v>
+        <v>6.1</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>6.47</v>
+        <v>6.13</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>14.83</v>
+        <v>14.86</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>14.88</v>
+        <v>14.82</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>11.44</v>
+        <v>14.86</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>7.32</v>
+        <v>14.75</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>14.73</v>
+        <v>14.76</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>14.72</v>
+        <v>12.22</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>14.91</v>
+        <v>14.87</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>14.93</v>
+        <v>14.95</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>32.31</v>
+        <v>32.38</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>36.47</v>
+        <v>35.31</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>32.54</v>
+        <v>32.63</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>26.09</v>
+        <v>30.23</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>26.35</v>
+        <v>32.3</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.78</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="90">
@@ -7970,64 +7970,64 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H91" s="3" t="n">
         <v>0.22</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0.31</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0.11</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="K91" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L91" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="L91" s="3" t="n">
+      <c r="M91" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O91" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M91" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O91" s="3" t="n">
+      <c r="P91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="R91" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="P91" s="3" t="n">
+      <c r="S91" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="V91" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="Q91" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>-0.11</v>
-      </c>
       <c r="W91" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-12T22:15:25</t>
+          <t>CreatedAt: 2026-04-13T00:13:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30.45</v>
+        <v>32.35</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>30.37</v>
+        <v>30.31</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>21.55</v>
+        <v>20.27</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>30.58</v>
+        <v>30.41</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>56.32</v>
+        <v>41.49</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>30.21</v>
+        <v>31.76</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>14.46</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>29.74</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>32.78</v>
+        <v>32.94</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>29.48</v>
+        <v>29.42</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>32.62</v>
+        <v>32.55</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>34.85</v>
+        <v>35.03</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>34.92</v>
+        <v>34.78</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>35.03</v>
+        <v>34.99</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>41.37</v>
+        <v>41.41</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>46.37</v>
+        <v>46.23</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>41.85</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>62.81</v>
+        <v>55.7</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>41.81</v>
+        <v>41.77</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>42.22</v>
+        <v>37.71</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>33.04</v>
+        <v>45.85</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.6</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="5">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>0.36</v>
-      </c>
       <c r="E6" s="3" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>-0.09</v>
@@ -851,43 +851,43 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.75</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q6" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>-0.53</v>
-      </c>
       <c r="S6" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.83</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.02</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.34</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1</v>
+        <v>-1.04</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.53</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.73</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="7">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>31.28</v>
+        <v>33.32</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>209.13</v>
+        <v>31.23</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>200.29</v>
+        <v>20.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>210.04</v>
+        <v>210.98</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>212.75</v>
+        <v>223.44</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>184.48</v>
+        <v>211.14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>176.13</v>
+        <v>202.51</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>167.52</v>
+        <v>193.78</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>167.56</v>
+        <v>193.94</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>210.63</v>
+        <v>211.11</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>214.23</v>
+        <v>214.76</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>210.83</v>
+        <v>210.97</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>214.35</v>
+        <v>214.72</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>217.07</v>
+        <v>217.3</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>216.46</v>
+        <v>216.88</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>217.22</v>
+        <v>217.78</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>43.51</v>
+        <v>43.41</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.8</v>
+        <v>48.66</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>44.23</v>
+        <v>44.18</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>66.04000000000001</v>
+        <v>58.56</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>44.04</v>
+        <v>43.95</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>223.38</v>
+        <v>217.59</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>214.09</v>
+        <v>227.09</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>214.22</v>
+        <v>220.15</v>
       </c>
     </row>
     <row r="10">
@@ -1238,28 +1238,28 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0.72</v>
@@ -1268,46 +1268,46 @@
         <v>1.39</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>1.44</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="12">
@@ -1325,49 +1325,49 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>177.97</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>178.11</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>178.26</v>
+        <v>179.36</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>153.51</v>
+        <v>179.84</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>152.65</v>
+        <v>177.64</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>152.36</v>
+        <v>178.74</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>152.4</v>
+        <v>178.69</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>152.53</v>
+        <v>178.92</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>179.12</v>
+        <v>179.6</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>179.48</v>
+        <v>179.87</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>179.58</v>
+        <v>179.78</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>179.67</v>
+        <v>180.11</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>180.11</v>
+        <v>180.15</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>179.54</v>
+        <v>180.07</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>180.07</v>
+        <v>180.67</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -1385,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>179.06</v>
+        <v>178</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>178.97</v>
+        <v>178.56</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>179.54</v>
+        <v>178.95</v>
       </c>
     </row>
     <row r="13">
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>31.31</v>
+        <v>33.32</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>300</v>
+        <v>49.64</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>300</v>
+        <v>20.86</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>300</v>
@@ -1538,19 +1538,19 @@
         <v>300</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>43.51</v>
+        <v>43.41</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>48.8</v>
+        <v>48.71</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>44.23</v>
+        <v>44.18</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>66.04000000000001</v>
+        <v>58.56</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>44.04</v>
+        <v>43.95</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>300</v>
@@ -1577,49 +1577,49 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>90.83</v>
+        <v>18.41</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>99.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>89.93000000000001</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>87.25</v>
+        <v>76.52</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>115.49</v>
+        <v>88.86</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>123.87</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>132.48</v>
+        <v>106.22</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>132.44</v>
+        <v>106.06</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>89.34</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>85.76000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>89.17</v>
+        <v>89</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>85.61</v>
+        <v>85.27</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>82.89</v>
+        <v>82.66</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>83.5</v>
+        <v>83.12</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>76.62</v>
+        <v>82.37</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>85.91</v>
+        <v>72.86</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>85.78</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="16">
@@ -1658,28 +1658,28 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.32</v>
+        <v>2.49</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0.72</v>
@@ -1691,43 +1691,43 @@
         <v>1.43</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1.46</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="17">
@@ -1745,49 +1745,49 @@
         <v>0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>177.97</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>178.11</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>178.26</v>
+        <v>179.36</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>153.51</v>
+        <v>179.84</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>152.65</v>
+        <v>177.64</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>152.36</v>
+        <v>178.74</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>152.4</v>
+        <v>178.69</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>152.53</v>
+        <v>178.92</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>179.12</v>
+        <v>179.6</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>179.48</v>
+        <v>179.87</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>179.58</v>
+        <v>179.78</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>179.67</v>
+        <v>180.11</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>180.11</v>
+        <v>180.15</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>179.54</v>
+        <v>180.07</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>180.07</v>
+        <v>180.67</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>0</v>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>179.06</v>
+        <v>178</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>178.97</v>
+        <v>178.56</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>179.54</v>
+        <v>178.95</v>
       </c>
     </row>
     <row r="18">
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>30.58</v>
+        <v>32.48</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.5</v>
+        <v>30.43</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>21.63</v>
+        <v>20.38</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>30.77</v>
+        <v>30.59</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>56.72</v>
+        <v>41.78</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>30.48</v>
+        <v>32.05</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>22.96</v>
+        <v>22.98</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>14.59</v>
+        <v>14.58</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.34</v>
+        <v>14.32</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>30.01</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>33.1</v>
+        <v>33.23</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>29.71</v>
+        <v>29.65</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.84</v>
+        <v>32.78</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>35.06</v>
+        <v>35.23</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>35.13</v>
+        <v>34.99</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>35.27</v>
+        <v>35.23</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>41.7</v>
+        <v>41.74</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.73</v>
+        <v>46.64</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>42.22</v>
+        <v>42.18</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>63.31</v>
+        <v>56.08</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>42.05</v>
+        <v>42.01</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>42.51</v>
+        <v>38.01</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>33.27</v>
+        <v>46.17</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.83</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="20">
@@ -2078,28 +2078,28 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>0.49</v>
-      </c>
       <c r="E21" s="3" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0.09</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0.03</v>
@@ -2108,46 +2108,46 @@
         <v>-0.12</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="P21" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="R21" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="S21" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.5</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>-0.61</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.95</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.42</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="22">
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>30.58</v>
+        <v>32.48</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>30.5</v>
+        <v>30.43</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>21.63</v>
+        <v>20.38</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>30.77</v>
+        <v>30.59</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>56.72</v>
+        <v>41.78</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>30.48</v>
+        <v>32.05</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>22.96</v>
+        <v>22.98</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>14.59</v>
+        <v>14.58</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>14.34</v>
+        <v>14.32</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>30.01</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>33.1</v>
+        <v>33.23</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>29.71</v>
+        <v>29.65</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>32.84</v>
+        <v>32.78</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>35.06</v>
+        <v>35.23</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>35.13</v>
+        <v>34.99</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>35.27</v>
+        <v>35.23</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>41.7</v>
+        <v>41.74</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>46.73</v>
+        <v>46.64</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>42.22</v>
+        <v>42.18</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>63.31</v>
+        <v>56.08</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>42.05</v>
+        <v>42.01</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>42.51</v>
+        <v>38.01</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>33.27</v>
+        <v>46.17</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.83</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="25">
@@ -2498,28 +2498,28 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0.49</v>
-      </c>
       <c r="E26" s="3" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.09</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.03</v>
@@ -2528,46 +2528,46 @@
         <v>-0.12</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="P26" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="S26" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>-0.61</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.95</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.42</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="27">
@@ -2750,22 +2750,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>30.61</v>
+        <v>32.51</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>30.56</v>
+        <v>30.5</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.7</v>
+        <v>20.42</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.86</v>
+        <v>30.69</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>56.95</v>
+        <v>41.91</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>30.67</v>
+        <v>32.25</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>23.12</v>
@@ -2774,52 +2774,52 @@
         <v>14.68</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>14.45</v>
+        <v>14.42</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>30.22</v>
+        <v>30.19</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>33.37</v>
+        <v>33.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>29.89</v>
+        <v>29.83</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>33</v>
+        <v>32.91</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>35.13</v>
+        <v>35.3</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>35.23</v>
+        <v>35.06</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>35.48</v>
+        <v>35.41</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>41.95</v>
+        <v>41.99</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.06</v>
+        <v>46.97</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>42.51</v>
+        <v>42.47</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>63.68</v>
+        <v>56.42</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>42.26</v>
+        <v>42.22</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>42.73</v>
+        <v>38.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>33.4</v>
+        <v>46.31</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>33.03</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="30">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.18</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.39</v>
       </c>
       <c r="P31" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>-0.17</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>-0.28</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="32">
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>31.67</v>
+        <v>33.78</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>122.36</v>
+        <v>50</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>122.17</v>
+        <v>21.08</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>122.32</v>
+        <v>121.15</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>148.1</v>
+        <v>121.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>148.21</v>
+        <v>123.26</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>148.12</v>
+        <v>121.71</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>147.93</v>
+        <v>121.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>147.91</v>
+        <v>121.52</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>121.8</v>
+        <v>121.35</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>121.57</v>
+        <v>121.14</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>121.39</v>
+        <v>121.15</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>121.49</v>
+        <v>121.08</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>121.13</v>
+        <v>121.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>121.65</v>
+        <v>121.12</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>121.05</v>
+        <v>120.44</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>44.57</v>
+        <v>44.42</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>45.55</v>
+        <v>45.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>67.70999999999999</v>
+        <v>60.04</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>45.35</v>
+        <v>45.26</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>122.07</v>
+        <v>123.01</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>122.29</v>
+        <v>123.06</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>121.7</v>
+        <v>122.52</v>
       </c>
     </row>
     <row r="35">
@@ -3257,49 +3257,49 @@
         <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>90.83</v>
+        <v>18.41</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>99.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>89.93000000000001</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>87.25</v>
+        <v>76.52</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>115.48</v>
+        <v>88.86</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>123.87</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>132.48</v>
+        <v>106.22</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>132.44</v>
+        <v>106.06</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>89.34</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>85.76000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>89.17</v>
+        <v>89</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>85.61</v>
+        <v>85.27</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>82.89</v>
+        <v>82.66</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>83.5</v>
+        <v>83.12</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>0</v>
@@ -3317,13 +3317,13 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>76.62</v>
+        <v>82.37</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>85.91</v>
+        <v>72.86</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>85.78</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="36">
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4.93</v>
+        <v>3.53</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.16</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>2.86</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.91</v>
+        <v>3.61</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="37">
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>30.45</v>
+        <v>32.35</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>30.37</v>
+        <v>30.31</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>21.55</v>
+        <v>20.27</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>30.58</v>
+        <v>30.41</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>56.32</v>
+        <v>41.49</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>30.21</v>
+        <v>31.76</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>14.46</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>29.74</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>32.78</v>
+        <v>32.94</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>29.48</v>
+        <v>29.42</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>32.62</v>
+        <v>32.55</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>34.85</v>
+        <v>35.03</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>34.92</v>
+        <v>34.78</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>35.03</v>
+        <v>34.99</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>41.37</v>
+        <v>41.41</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>46.37</v>
+        <v>46.23</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>41.85</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>62.81</v>
+        <v>55.7</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>41.81</v>
+        <v>41.77</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>42.22</v>
+        <v>37.71</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>33.04</v>
+        <v>45.85</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.6</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="40">
@@ -3758,22 +3758,22 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D41" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>0.36</v>
-      </c>
       <c r="E41" s="3" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>-0.09</v>
@@ -3791,43 +3791,43 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.75</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q41" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>-0.53</v>
-      </c>
       <c r="S41" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.83</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.02</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>-0.92</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.34</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1</v>
+        <v>-1.04</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.53</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.73</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="42">
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>30.03</v>
+        <v>31.9</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>29.89</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>21.16</v>
+        <v>19.93</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>29.97</v>
+        <v>29.83</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>55.54</v>
+        <v>40.91</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>30</v>
+        <v>31.54</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>22.59</v>
+        <v>22.62</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>14.31</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>14.04</v>
+        <v>14.03</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>29.39</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>32.55</v>
+        <v>32.68</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>29.42</v>
+        <v>29.39</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>32.58</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>34.75</v>
+        <v>34.96</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>34.92</v>
+        <v>34.82</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>35.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>41.37</v>
+        <v>41.49</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>46.46</v>
+        <v>46.37</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>42.01</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>63.12</v>
+        <v>55.97</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>42.1</v>
+        <v>42.05</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>42.18</v>
+        <v>37.71</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>32.91</v>
+        <v>45.76</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>32.6</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="45">
@@ -4178,22 +4178,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.19</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.25</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>-0.27</v>
@@ -4208,7 +4208,7 @@
         <v>-0.73</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.82</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>-0.71</v>
@@ -4226,7 +4226,7 @@
         <v>-0.46</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>-0.88</v>
@@ -4235,19 +4235,19 @@
         <v>-0.76</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.06</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.76</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.53</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="47">
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>27.53</v>
+        <v>29.36</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>27.43</v>
+        <v>27.48</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>19.38</v>
+        <v>18.26</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>27.48</v>
+        <v>27.33</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>51.54</v>
+        <v>37.9</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>26.58</v>
+        <v>27.9</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>20.27</v>
+        <v>20.25</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>12.93</v>
+        <v>12.91</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>12.69</v>
+        <v>12.66</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>26.71</v>
+        <v>26.68</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>29.5</v>
+        <v>29.59</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>26.71</v>
+        <v>26.63</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>31.01</v>
+        <v>30.98</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>33.03</v>
+        <v>33.14</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>33.16</v>
+        <v>33</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>31.74</v>
+        <v>31.69</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>37.44</v>
+        <v>37.51</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>42.08</v>
+        <v>41.92</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>38.08</v>
+        <v>38.05</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>57.02</v>
+        <v>50.52</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.55</v>
+        <v>33.52</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>29.18</v>
+        <v>40.62</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>30.23</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>-2.62</v>
+        <v>-2.73</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-2.58</v>
+        <v>-2.53</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-1.88</v>
+        <v>-1.79</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.65</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-4.38</v>
+        <v>-3.26</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.96</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-2.59</v>
+        <v>-2.63</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.6</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.63</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-3.42</v>
+        <v>-3.44</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-3.83</v>
+        <v>-3.91</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-3.42</v>
+        <v>-3.46</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.32</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-2.35</v>
+        <v>-2.45</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.38</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.81</v>
+        <v>-3.87</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-4.68</v>
+        <v>-4.73</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-5.26</v>
+        <v>-5.32</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-4.68</v>
+        <v>-4.72</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-7.3</v>
+        <v>-6.52</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.06</v>
+        <v>-5.09</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.22</v>
+        <v>-4.73</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-4.29</v>
+        <v>-5.97</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.96</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="52">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>29.7</v>
+        <v>31.61</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>29.62</v>
+        <v>29.68</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>20.95</v>
+        <v>19.79</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>29.67</v>
+        <v>29.57</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>55.54</v>
+        <v>40.87</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>30.18</v>
+        <v>31.73</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>22.44</v>
+        <v>22.46</v>
       </c>
       <c r="J54" s="3" t="n">
         <v>14.08</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>13.96</v>
+        <v>13.95</v>
       </c>
       <c r="L54" s="3" t="n">
         <v>29.51</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>33.23</v>
+        <v>33.36</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>30.04</v>
+        <v>30.01</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>33.2</v>
+        <v>33.17</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>35.23</v>
+        <v>35.41</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>35.27</v>
+        <v>35.13</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>35.45</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>41.21</v>
+        <v>41.29</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>46.18</v>
+        <v>46.05</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>40.89</v>
+        <v>40.93</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>61.49</v>
+        <v>54.53</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>41.4</v>
+        <v>41.52</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>42.18</v>
+        <v>37.71</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>33.47</v>
+        <v>46.22</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>32.96</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="55">
@@ -5018,22 +5018,22 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.47</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.33</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.29</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>-0.43</v>
@@ -5048,46 +5048,46 @@
         <v>-0.62</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>-0.11</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.95</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.2</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.88</v>
+        <v>-1.84</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-2.83</v>
+        <v>-2.51</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.29</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.53</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="57">
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>30.7</v>
+        <v>32.64</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>30.59</v>
+        <v>30.56</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>21.63</v>
+        <v>20.38</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>30.61</v>
+        <v>30.5</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>56.83</v>
+        <v>41.82</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>30.73</v>
+        <v>32.31</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>23.21</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>14.7</v>
+        <v>14.71</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>14.45</v>
+        <v>14.44</v>
       </c>
       <c r="L59" s="3" t="n">
         <v>30.28</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>33.47</v>
+        <v>33.6</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>30.28</v>
+        <v>30.25</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>33.54</v>
+        <v>33.5</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>35.66</v>
+        <v>35.87</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>35.88</v>
+        <v>35.73</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>36.02</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>42.37</v>
+        <v>42.5</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>47.63</v>
+        <v>47.53</v>
       </c>
       <c r="U59" s="3" t="n">
         <v>43.07</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>57.32</v>
       </c>
       <c r="W59" s="3" t="n">
         <v>43.2</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>43.24</v>
+        <v>38.67</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>33.7</v>
+        <v>46.87</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>33.43</v>
+        <v>40.03</v>
       </c>
     </row>
     <row r="60">
@@ -5441,25 +5441,25 @@
         <v>0.55</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0.52</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0.14</v>
@@ -5468,19 +5468,19 @@
         <v>0.15</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0.29</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0.47</v>
@@ -5495,19 +5495,19 @@
         <v>0.3</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="62">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>31.11</v>
+        <v>33.01</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>30.94</v>
+        <v>30.91</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>21.86</v>
+        <v>20.61</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>30.99</v>
+        <v>30.84</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>57.6</v>
+        <v>42.38</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>31.17</v>
+        <v>32.78</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>23.55</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>14.89</v>
+        <v>14.91</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>14.66</v>
+        <v>14.65</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>30.74</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>33.98</v>
+        <v>34.11</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>30.74</v>
+        <v>30.71</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>33.98</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>36.21</v>
+        <v>36.39</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>36.43</v>
+        <v>36.32</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>36.61</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>43.02</v>
+        <v>43.15</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>48.35</v>
+        <v>48.26</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>43.73</v>
+        <v>43.78</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>65.7</v>
+        <v>58.26</v>
       </c>
       <c r="W64" s="3" t="n">
         <v>43.82</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>43.86</v>
+        <v>39.18</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>34.18</v>
+        <v>47.49</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>33.87</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="65">
@@ -5858,28 +5858,28 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>0.35</v>
@@ -5888,7 +5888,7 @@
         <v>0.61</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>0.61</v>
@@ -5897,37 +5897,37 @@
         <v>0.68</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>1.06</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>1.01</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y66" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z66" s="3" t="n">
         <v>0.72</v>
-      </c>
-      <c r="Z66" s="3" t="n">
-        <v>0.68</v>
       </c>
     </row>
     <row r="67">
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>31.15</v>
+        <v>33.08</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>31</v>
+        <v>30.97</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>21.92</v>
+        <v>20.67</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>31.02</v>
+        <v>30.91</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>57.66</v>
+        <v>42.43</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>31.17</v>
+        <v>32.78</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>23.55</v>
+        <v>23.57</v>
       </c>
       <c r="J69" s="3" t="n">
         <v>14.92</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>14.68</v>
+        <v>14.66</v>
       </c>
       <c r="L69" s="3" t="n">
         <v>30.74</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>33.98</v>
+        <v>34.11</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>30.74</v>
+        <v>30.71</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>34.01</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>36.17</v>
+        <v>36.39</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>36.39</v>
+        <v>36.28</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>36.54</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>42.76</v>
+        <v>42.88</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>48.06</v>
+        <v>47.97</v>
       </c>
       <c r="U69" s="3" t="n">
         <v>43.51</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>65.3</v>
+        <v>57.9</v>
       </c>
       <c r="W69" s="3" t="n">
         <v>43.73</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>43.86</v>
+        <v>39.18</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>34.15</v>
+        <v>47.54</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>33.9</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="70">
@@ -6278,22 +6278,22 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0.93</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>0.68</v>
@@ -6308,7 +6308,7 @@
         <v>0.61</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>0.61</v>
@@ -6335,19 +6335,19 @@
         <v>0.74</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="W71" s="3" t="n">
         <v>0.92</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.71</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="72">
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>30.33</v>
+        <v>32.25</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>30.19</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>21.29</v>
+        <v>20.07</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>30.12</v>
+        <v>30.04</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>56.21</v>
+        <v>41.36</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>30.27</v>
+        <v>31.83</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>22.86</v>
+        <v>22.89</v>
       </c>
       <c r="J74" s="3" t="n">
         <v>14.51</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>14.27</v>
+        <v>14.25</v>
       </c>
       <c r="L74" s="3" t="n">
         <v>29.92</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>33.07</v>
+        <v>33.2</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>30.01</v>
+        <v>29.98</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>35.34</v>
+        <v>35.52</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>35.62</v>
+        <v>35.52</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>35.73</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>41.86</v>
+        <v>41.99</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>47.01</v>
+        <v>46.92</v>
       </c>
       <c r="U74" s="3" t="n">
         <v>42.64</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>63.87</v>
+        <v>56.64</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>42.64</v>
+        <v>42.6</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>42.73</v>
+        <v>38.2</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>33.17</v>
+        <v>46.13</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>33.03</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="75">
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>0.18</v>
@@ -6707,10 +6707,10 @@
         <v>0.02</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>-0.03</v>
@@ -6728,7 +6728,7 @@
         <v>-0.21</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>-0.12</v>
@@ -6737,7 +6737,7 @@
         <v>-0.1</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q76" s="3" t="n">
         <v>0.14</v>
@@ -6755,19 +6755,19 @@
         <v>-0.13</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.46</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>-0.17</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="77">
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>30.15</v>
+        <v>32.09</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>30.01</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>21.26</v>
+        <v>20.05</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>30.09</v>
+        <v>29.98</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>55.93</v>
+        <v>41.15</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>30.3</v>
+        <v>31.86</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>22.86</v>
+        <v>22.89</v>
       </c>
       <c r="J79" s="3" t="n">
         <v>14.51</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>14.31</v>
+        <v>14.3</v>
       </c>
       <c r="L79" s="3" t="n">
         <v>30.13</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>33.33</v>
+        <v>33.5</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>30.13</v>
+        <v>30.1</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>35.37</v>
+        <v>35.59</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>35.48</v>
+        <v>35.38</v>
       </c>
       <c r="R79" s="3" t="n">
         <v>35.55</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>42.11</v>
+        <v>42.24</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>47.34</v>
+        <v>47.25</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>42.77</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>64.31999999999999</v>
+        <v>57.04</v>
       </c>
       <c r="W79" s="3" t="n">
         <v>42.81</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>42.77</v>
+        <v>38.24</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>33.47</v>
+        <v>46.59</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>33.19</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="80">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>29.91</v>
+        <v>31.8</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>29.92</v>
+        <v>29.95</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>21.16</v>
+        <v>20.01</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>29.97</v>
+        <v>29.86</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>56.32</v>
+        <v>41.44</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>30.61</v>
+        <v>32.15</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>22.16</v>
+        <v>22.2</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>13.85</v>
+        <v>13.84</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>28.91</v>
+        <v>28.94</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33.3</v>
+        <v>33.46</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>30.13</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>33.3</v>
+        <v>33.27</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>35.13</v>
+        <v>35.27</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>34.99</v>
+        <v>34.82</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>35.2</v>
+        <v>35.17</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>39.88</v>
+        <v>39.92</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>44.74</v>
+        <v>44.57</v>
       </c>
       <c r="U84" s="3" t="n">
         <v>38.5</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>58.1</v>
+        <v>51.52</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>40.35</v>
+        <v>40.81</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>42.51</v>
+        <v>37.98</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>33.77</v>
+        <v>46.54</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>33.23</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="85">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.29</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="F86" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>-0.62</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.19</v>
       </c>
       <c r="M86" s="3" t="n">
         <v>-0.03</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.32</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.23</v>
+        <v>-2.32</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.6</v>
+        <v>-2.67</v>
       </c>
       <c r="U86" s="3" t="n">
         <v>-4.27</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-6.22</v>
+        <v>-5.51</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -7790,22 +7790,22 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>30.61</v>
+        <v>32.51</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>30.56</v>
+        <v>30.5</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>21.7</v>
+        <v>20.42</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>30.86</v>
+        <v>30.69</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>56.95</v>
+        <v>41.91</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>30.67</v>
+        <v>32.25</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>23.12</v>
@@ -7814,52 +7814,52 @@
         <v>14.68</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>14.45</v>
+        <v>14.42</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>30.22</v>
+        <v>30.19</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>33.37</v>
+        <v>33.5</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>29.89</v>
+        <v>29.83</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>33</v>
+        <v>32.91</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>35.13</v>
+        <v>35.3</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>35.23</v>
+        <v>35.06</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>35.48</v>
+        <v>35.41</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>41.95</v>
+        <v>41.99</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>47.06</v>
+        <v>46.97</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>42.51</v>
+        <v>42.47</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>63.68</v>
+        <v>56.42</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>42.26</v>
+        <v>42.22</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>42.73</v>
+        <v>38.2</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.4</v>
+        <v>46.31</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>33.03</v>
+        <v>39.24</v>
       </c>
     </row>
     <row r="90">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0.18</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.39</v>
       </c>
       <c r="P91" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="S91" s="3" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>-0.17</v>
       </c>
       <c r="T91" s="3" t="n">
         <v>-0.28</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-13T06:10:23</t>
+          <t>CreatedAt: 2026-04-13T07:10:13</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -674,52 +674,52 @@
         <v>41.63</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>41.2</v>
+        <v>32.95</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>22.68</v>
+        <v>32.8</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>23.27</v>
+        <v>22.08</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>22.04</v>
+        <v>20.91</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>33.31</v>
+        <v>32.65</v>
       </c>
       <c r="P4" s="3" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>34.92</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>41.29</v>
-      </c>
       <c r="R4" s="3" t="n">
-        <v>34.75</v>
+        <v>34.86</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>45.64</v>
+        <v>45.27</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>58.59</v>
+        <v>58.24</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>130.58</v>
+        <v>170.73</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>169.37</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>44.34</v>
+        <v>45.68</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>42.18</v>
+        <v>42.51</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>43.5</v>
+        <v>45.58</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.32</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="5">
@@ -842,52 +842,52 @@
         <v>-0.25</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.4</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.62</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.91</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.73</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.77</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.63</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.13</v>
+        <v>-4.1</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-4.4</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.05</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.51</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.36</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="7">
@@ -1094,10 +1094,10 @@
         <v>43.09</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>42.94</v>
+        <v>34.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>299.97</v>
+        <v>34.07</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>300</v>
@@ -1106,40 +1106,40 @@
         <v>300</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>300</v>
+        <v>299.96</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>300</v>
+        <v>299.96</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>300</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>299.96</v>
+        <v>300</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>46.78</v>
+        <v>46.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>60.78</v>
+        <v>60.42</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>134.92</v>
+        <v>176.24</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>174.47</v>
+        <v>174.3</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>46.62</v>
+        <v>47.97</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>224.27</v>
+        <v>224.64</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>226.57</v>
+        <v>228.85</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>214.17</v>
+        <v>215.56</v>
       </c>
     </row>
     <row r="10">
@@ -1262,52 +1262,52 @@
         <v>1.21</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.31</v>
+        <v>0.65</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.86</v>
+        <v>0.54</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.7</v>
+        <v>0.52</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="12">
@@ -1349,25 +1349,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>276.4</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>275.79</v>
+        <v>277.05</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>277.12</v>
+        <v>278.32</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>265.19</v>
+        <v>265.85</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>263.5</v>
+        <v>263.76</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>257.15</v>
+        <v>263.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>263.83</v>
+        <v>263.72</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -1385,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>179.95</v>
+        <v>179.92</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>180.49</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>179.91</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="13">
@@ -1514,10 +1514,10 @@
         <v>43.09</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>42.98</v>
+        <v>34.3</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>300</v>
+        <v>34.07</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>300</v>
@@ -1538,19 +1538,19 @@
         <v>300</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>46.78</v>
+        <v>46.5</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>60.78</v>
+        <v>60.42</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>134.92</v>
+        <v>176.41</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>174.65</v>
+        <v>174.3</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>46.62</v>
+        <v>47.97</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>300</v>
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>75.73</v>
+        <v>75.36</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>73.38</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>85.79000000000001</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="16">
@@ -1682,52 +1682,52 @@
         <v>1.21</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.12</v>
+        <v>0.96</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.86</v>
+        <v>0.54</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.87</v>
+        <v>0.52</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
@@ -1769,25 +1769,25 @@
         <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>276.4</v>
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>275.79</v>
+        <v>277.05</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>277.12</v>
+        <v>278.32</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>265.19</v>
+        <v>265.85</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>263.5</v>
+        <v>263.76</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>257.15</v>
+        <v>263.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>263.83</v>
+        <v>263.72</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>0</v>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>179.95</v>
+        <v>179.92</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>180.48</v>
+        <v>180.49</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>179.91</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="18">
@@ -1934,52 +1934,52 @@
         <v>41.96</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>41.53</v>
+        <v>33.18</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>22.81</v>
+        <v>32.99</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>23.4</v>
+        <v>22.21</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>22.19</v>
+        <v>21.03</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>33.58</v>
+        <v>32.91</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>35.16</v>
+        <v>34.92</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>41.61</v>
+        <v>35.17</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>35.03</v>
+        <v>35.13</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>45.91</v>
+        <v>45.63</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>59.11</v>
+        <v>58.7</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>131.6</v>
+        <v>172.07</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>170.53</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>44.65</v>
+        <v>45.99</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>42.47</v>
+        <v>42.85</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>43.8</v>
+        <v>45.94</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.54</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="20">
@@ -2102,10 +2102,10 @@
         <v>0.08</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.43</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>-0.5600000000000001</v>
@@ -2114,40 +2114,40 @@
         <v>-0.55</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.49</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.49</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.87</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1</v>
+        <v>-1.17</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-2.11</v>
+        <v>-2.75</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>-3.24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.74</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="22">
@@ -2354,52 +2354,52 @@
         <v>41.96</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>41.53</v>
+        <v>33.18</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>22.81</v>
+        <v>32.99</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>23.4</v>
+        <v>22.21</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>22.19</v>
+        <v>21.03</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>33.58</v>
+        <v>32.91</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>35.16</v>
+        <v>34.92</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>41.61</v>
+        <v>35.17</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>35.03</v>
+        <v>35.13</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>45.91</v>
+        <v>45.63</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>59.11</v>
+        <v>58.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>131.6</v>
+        <v>172.07</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>170.53</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>44.65</v>
+        <v>45.99</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>42.47</v>
+        <v>42.85</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>43.8</v>
+        <v>45.94</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.54</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="25">
@@ -2522,10 +2522,10 @@
         <v>0.08</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.43</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>-0.5600000000000001</v>
@@ -2534,40 +2534,40 @@
         <v>-0.55</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.49</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.49</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.87</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1</v>
+        <v>-1.17</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-2.11</v>
+        <v>-2.75</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>-3.24</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.74</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="27">
@@ -2774,52 +2774,52 @@
         <v>42.26</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>41.74</v>
+        <v>33.38</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>22.9</v>
+        <v>33.12</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>23.52</v>
+        <v>22.32</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>22.29</v>
+        <v>21.17</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>33.78</v>
+        <v>33.13</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>35.37</v>
+        <v>35.09</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>41.82</v>
+        <v>35.34</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>35.3</v>
+        <v>35.41</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>46.23</v>
+        <v>45.99</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>59.64</v>
+        <v>59.22</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>132.65</v>
+        <v>173.44</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>171.54</v>
+        <v>171.71</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.87</v>
+        <v>46.22</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>42.64</v>
+        <v>43.11</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>43.97</v>
+        <v>46.17</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.67</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="30">
@@ -2942,52 +2942,52 @@
         <v>0.38</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.03</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0.45</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.32</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.32</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.21</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.51</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.65</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.39</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.23</v>
+        <v>-2.06</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.23</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="32">
@@ -3197,49 +3197,49 @@
         <v>82.98999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>24.06</v>
+        <v>34.71</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>24.71</v>
+        <v>23.39</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>23.28</v>
+        <v>22.06</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>35.57</v>
+        <v>34.89</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>37.34</v>
+        <v>37.08</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>43.6</v>
+        <v>36.84</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>36.81</v>
+        <v>36.95</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>47.25</v>
+        <v>46.92</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.91</v>
+        <v>61.54</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>137.28</v>
+        <v>179.31</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>177.5</v>
+        <v>176.96</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>47.8</v>
+        <v>49.19</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>121.18</v>
+        <v>121.23</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>121.01</v>
+        <v>121.09</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>121.2</v>
+        <v>121.19</v>
       </c>
     </row>
     <row r="35">
@@ -3317,13 +3317,13 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>75.73</v>
+        <v>75.36</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>73.38</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>85.79000000000001</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="36">
@@ -3362,52 +3362,52 @@
         <v>1.79</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.79</v>
+        <v>1.28</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>3.57</v>
+        <v>4.48</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>3.73</v>
+        <v>3.19</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="37">
@@ -3446,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>39.15</v>
+        <v>48</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
@@ -3614,52 +3614,52 @@
         <v>41.63</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>41.2</v>
+        <v>32.95</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>22.68</v>
+        <v>32.8</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>23.27</v>
+        <v>22.08</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>22.04</v>
+        <v>20.91</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>33.31</v>
+        <v>32.65</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>34.92</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>41.29</v>
-      </c>
       <c r="R39" s="3" t="n">
-        <v>34.75</v>
+        <v>34.86</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>45.64</v>
+        <v>45.27</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>58.59</v>
+        <v>58.24</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>130.58</v>
+        <v>170.73</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>169.37</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>44.34</v>
+        <v>45.68</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>42.18</v>
+        <v>42.51</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>43.5</v>
+        <v>45.58</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.32</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="40">
@@ -3782,52 +3782,52 @@
         <v>-0.25</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.4</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.62</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.91</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.73</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.77</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.63</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.13</v>
+        <v>-4.1</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-4.4</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.05</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.51</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.36</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="42">
@@ -4034,52 +4034,52 @@
         <v>41.14</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>40.8</v>
+        <v>32.66</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>22.57</v>
+        <v>32.45</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>23.29</v>
+        <v>22.1</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>22.12</v>
+        <v>20.97</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>33.28</v>
+        <v>32.68</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>34.79</v>
+        <v>34.61</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>41.29</v>
+        <v>34.99</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>34.85</v>
+        <v>34.99</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>45.82</v>
+        <v>45.5</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>58.93</v>
+        <v>58.64</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>131.35</v>
+        <v>171.73</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>170.53</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>44.69</v>
+        <v>45.99</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>42.22</v>
+        <v>42.51</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>43.41</v>
+        <v>45.35</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>32.47</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="45">
@@ -4202,52 +4202,52 @@
         <v>-0.74</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.97</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.66</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.66</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-1.01</v>
+        <v>-1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.23</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-2.36</v>
+        <v>-3.09</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>-3.24</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.74</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.59</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="47">
@@ -4454,52 +4454,52 @@
         <v>37.19</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>37.31</v>
+        <v>29.74</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>20.79</v>
+        <v>29.87</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>21.26</v>
+        <v>20.22</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>21.04</v>
+        <v>19.96</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>31.68</v>
+        <v>31.14</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>33.04</v>
+        <v>32.91</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>39.1</v>
+        <v>33.17</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>31.48</v>
+        <v>31.61</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>41.51</v>
+        <v>41.22</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>53.34</v>
+        <v>53.13</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>118.64</v>
+        <v>155.13</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>153.51</v>
+        <v>153.65</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>40.19</v>
+        <v>41.35</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.68</v>
+        <v>37.91</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>38.51</v>
+        <v>40.2</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>30.21</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="50">
@@ -4622,52 +4622,52 @@
         <v>-4.69</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-4.55</v>
+        <v>-3.6</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-2.47</v>
+        <v>-3.55</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-2.7</v>
+        <v>-2.55</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.62</v>
       </c>
       <c r="O51" s="3" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="P51" s="3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="P51" s="3" t="n">
-        <v>-2.51</v>
-      </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.89</v>
+        <v>-2.49</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.97</v>
+        <v>-4.01</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-5.31</v>
+        <v>-5.28</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-6.77</v>
+        <v>-6.75</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-15.07</v>
+        <v>-19.7</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-20.26</v>
+        <v>-20.13</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.22</v>
+        <v>-5.38</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.09</v>
+        <v>-5.12</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.75</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.78</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="52">
@@ -4874,52 +4874,52 @@
         <v>40.42</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>40.6</v>
+        <v>32.34</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>22.5</v>
+        <v>32.32</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>23.61</v>
+        <v>22.43</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>22.4</v>
+        <v>21.23</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>33.64</v>
+        <v>33.04</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>34.85</v>
+        <v>34.72</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>41.25</v>
+        <v>34.96</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>34.96</v>
+        <v>35.1</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>45.29</v>
+        <v>44.97</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>58.02</v>
+        <v>57.79</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>126.5</v>
+        <v>165.55</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>164.87</v>
+        <v>164.71</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>43.96</v>
+        <v>45.23</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>42.14</v>
+        <v>42.39</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>43.8</v>
+        <v>45.67</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>32.57</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="55">
@@ -5042,52 +5042,52 @@
         <v>-1.46</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.77</v>
+        <v>-1.1</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>-0.34</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="P56" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="Q56" s="3" t="n">
         <v>-0.7</v>
       </c>
-      <c r="Q56" s="3" t="n">
-        <v>-0.74</v>
-      </c>
       <c r="R56" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.53</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.08</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-7.21</v>
+        <v>-9.27</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-8.9</v>
+        <v>-9.06</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="57">
@@ -5294,52 +5294,52 @@
         <v>42.17</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>42.03</v>
+        <v>33.58</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>23.34</v>
+        <v>33.49</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>24.06</v>
+        <v>22.83</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>22.85</v>
+        <v>21.68</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>34.35</v>
+        <v>33.73</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>35.8</v>
+        <v>35.66</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>42.46</v>
+        <v>36.02</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>35.77</v>
+        <v>35.95</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>46.97</v>
+        <v>46.64</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>60.35</v>
+        <v>60.12</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>134.52</v>
+        <v>175.88</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>174.65</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>45.82</v>
+        <v>47.1</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>43.24</v>
+        <v>43.5</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>44.37</v>
+        <v>46.31</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>33.33</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="60">
@@ -5462,13 +5462,13 @@
         <v>0.3</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>0.11</v>
@@ -5480,7 +5480,7 @@
         <v>0.25</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0.32</v>
@@ -5492,22 +5492,22 @@
         <v>0.24</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>0.48</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="62">
@@ -5714,52 +5714,52 @@
         <v>42.78</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>42.63</v>
+        <v>34.09</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>23.69</v>
+        <v>34</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>24.43</v>
+        <v>23.2</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>23.2</v>
+        <v>22.01</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>34.88</v>
+        <v>34.21</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>36.35</v>
+        <v>36.21</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>43.07</v>
+        <v>36.57</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>36.32</v>
+        <v>36.54</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>47.69</v>
+        <v>47.35</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>61.28</v>
+        <v>61.03</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>136.58</v>
+        <v>178.58</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>177.32</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>46.48</v>
+        <v>47.83</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>43.82</v>
+        <v>44.08</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>44.91</v>
+        <v>46.83</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>33.77</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="65">
@@ -5882,52 +5882,52 @@
         <v>0.9</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="P66" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>1.16</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>3.55</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -6134,52 +6134,52 @@
         <v>42.78</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>42.67</v>
+        <v>34.09</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>23.72</v>
+        <v>34.03</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>24.43</v>
+        <v>23.2</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>23.23</v>
+        <v>22.01</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>34.84</v>
+        <v>34.25</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>36.35</v>
+        <v>36.17</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>43.07</v>
+        <v>36.53</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>36.28</v>
+        <v>36.46</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>47.45</v>
+        <v>47.11</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>60.97</v>
+        <v>60.66</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>135.88</v>
+        <v>177.49</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>176.42</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>46.38</v>
+        <v>47.73</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>43.82</v>
+        <v>44.08</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>44.96</v>
+        <v>46.93</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>33.84</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="70">
@@ -6302,52 +6302,52 @@
         <v>0.9</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>2.65</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="72">
@@ -6554,52 +6554,52 @@
         <v>41.63</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>41.66</v>
+        <v>33.28</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>23.1</v>
+        <v>33.16</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>23.8</v>
+        <v>22.6</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>22.63</v>
+        <v>21.47</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>34.04</v>
+        <v>33.43</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>35.48</v>
+        <v>35.3</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>42.16</v>
+        <v>35.77</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>35.34</v>
+        <v>35.52</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>46.41</v>
+        <v>46.08</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>59.64</v>
+        <v>59.4</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>132.91</v>
+        <v>173.78</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>172.57</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>45.18</v>
+        <v>46.49</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>42.68</v>
+        <v>42.98</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>43.67</v>
+        <v>45.58</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>32.86</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="75">
@@ -6722,37 +6722,37 @@
         <v>-0.25</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L76" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M76" s="3" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>-0.17</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>-0.11</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>-0.11</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>-0.48</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.04</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>-1.21</v>
@@ -6761,13 +6761,13 @@
         <v>-0.23</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.36</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="77">
@@ -6974,52 +6974,52 @@
         <v>41.88</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>41.86</v>
+        <v>33.34</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>23.27</v>
+        <v>33.42</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>23.97</v>
+        <v>22.76</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>22.74</v>
+        <v>21.57</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>34.18</v>
+        <v>33.56</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>35.55</v>
+        <v>35.41</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>41.99</v>
+        <v>35.66</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>35.45</v>
+        <v>35.62</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>46.83</v>
+        <v>46.5</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>60.11</v>
+        <v>59.87</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>133.71</v>
+        <v>174.83</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>173.77</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>45.41</v>
+        <v>46.73</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>42.77</v>
+        <v>43.02</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>44.06</v>
+        <v>45.94</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>32.99</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="80">
@@ -7394,52 +7394,52 @@
         <v>39.51</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>39.83</v>
+        <v>31.7</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>21.97</v>
+        <v>31.56</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>23.56</v>
+        <v>22.36</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>22.36</v>
+        <v>21.17</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>33.48</v>
+        <v>32.87</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>34.42</v>
+        <v>34.28</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>40.61</v>
+        <v>34.45</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>34.41</v>
+        <v>34.58</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>43.52</v>
+        <v>43.21</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>55.92</v>
+        <v>55.7</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>118.64</v>
+        <v>155.68</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>155.02</v>
+        <v>154.88</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>43.21</v>
+        <v>44.46</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>44.11</v>
+        <v>45.99</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>32.67</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="85">
@@ -7562,52 +7562,52 @@
         <v>-2.37</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-2.03</v>
+        <v>-1.65</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.86</v>
       </c>
       <c r="M86" s="3" t="n">
         <v>-0.4</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.21</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.04</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3.28</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-4.19</v>
+        <v>-4.18</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-15.07</v>
+        <v>-19.15</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-18.76</v>
+        <v>-18.9</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.2</v>
+        <v>-2.27</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="87">
@@ -7814,52 +7814,52 @@
         <v>42.26</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>41.74</v>
+        <v>33.38</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>22.9</v>
+        <v>33.12</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>23.52</v>
+        <v>22.32</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>22.29</v>
+        <v>21.17</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>33.78</v>
+        <v>33.13</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>35.37</v>
+        <v>35.09</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>41.82</v>
+        <v>35.34</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>35.3</v>
+        <v>35.41</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>46.23</v>
+        <v>45.99</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>59.64</v>
+        <v>59.22</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>132.65</v>
+        <v>173.61</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>171.54</v>
+        <v>171.71</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.87</v>
+        <v>46.22</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>42.64</v>
+        <v>43.11</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>43.97</v>
+        <v>46.17</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.67</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="90">
@@ -7982,52 +7982,52 @@
         <v>0.38</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.03</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="M91" s="3" t="n">
         <v>-0.45</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.32</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.32</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.21</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.51</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.65</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.22</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.23</v>
+        <v>-2.06</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.23</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-13T09:09:43</t>
+          <t>CreatedAt: 2026-04-13T10:09:32</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -683,25 +683,25 @@
         <v>22.79</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25.77</v>
+        <v>14.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>29.33</v>
+        <v>29.42</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>32.58</v>
+        <v>22.69</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>34.79</v>
+        <v>23.21</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>32.71</v>
+        <v>32.39</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>41.17</v>
+        <v>40.37</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>58.36</v>
+        <v>58.01</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>170.73</v>
@@ -710,10 +710,10 @@
         <v>169.37</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>45.68</v>
+        <v>45.63</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>42.47</v>
+        <v>42.39</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>41.53</v>
@@ -851,25 +851,25 @@
         <v>-0.52</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.33</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.68</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.57</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.05</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.68</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-4.27</v>
@@ -878,7 +878,7 @@
         <v>-4.74</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.1</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>-0.51</v>
@@ -1103,10 +1103,10 @@
         <v>23.62</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>26.7</v>
+        <v>14.86</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>300</v>
+        <v>30.52</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>300</v>
@@ -1118,28 +1118,28 @@
         <v>300</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>42.24</v>
+        <v>41.25</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>60.54</v>
+        <v>59.82</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>176.41</v>
+        <v>175.52</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>174.46</v>
+        <v>174.11</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>47.97</v>
+        <v>47.83</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>224.6</v>
+        <v>223.78</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>224.45</v>
+        <v>224.26</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>214.21</v>
+        <v>214.13</v>
       </c>
     </row>
     <row r="10">
@@ -1271,43 +1271,43 @@
         <v>0.31</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.68</v>
+        <v>0.28</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.54</v>
+        <v>0.17</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.54</v>
+        <v>0.12</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>1.41</v>
+        <v>0.53</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="12">
@@ -1358,16 +1358,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>269.36</v>
+        <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>265.98</v>
+        <v>276.46</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>263.91</v>
+        <v>276.06</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>265.96</v>
+        <v>266.39</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -1385,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>179.92</v>
+        <v>179.28</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>180.4</v>
+        <v>180.29</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>179.9</v>
+        <v>179.86</v>
       </c>
     </row>
     <row r="13">
@@ -1523,10 +1523,10 @@
         <v>23.62</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>26.73</v>
+        <v>14.86</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>300</v>
+        <v>30.55</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>300</v>
@@ -1538,19 +1538,19 @@
         <v>300</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>42.28</v>
+        <v>41.25</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>60.54</v>
+        <v>59.82</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>176.41</v>
+        <v>175.52</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>174.46</v>
+        <v>174.11</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>47.97</v>
+        <v>47.83</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>300</v>
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>76.17</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>75.54000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>85.75</v>
+        <v>85.87</v>
       </c>
     </row>
     <row r="16">
@@ -1691,43 +1691,43 @@
         <v>0.31</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.68</v>
+        <v>0.28</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.54</v>
+        <v>0.17</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.54</v>
+        <v>0.12</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1.41</v>
+        <v>0.53</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="17">
@@ -1778,16 +1778,16 @@
         <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>269.36</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>265.98</v>
+        <v>276.46</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>263.91</v>
+        <v>276.06</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>265.96</v>
+        <v>266.39</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>0</v>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>179.92</v>
+        <v>179.28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>180.4</v>
+        <v>180.29</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>179.9</v>
+        <v>179.86</v>
       </c>
     </row>
     <row r="18">
@@ -1943,37 +1943,37 @@
         <v>35.11</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>25.92</v>
+        <v>14.48</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>29.56</v>
+        <v>29.62</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>32.81</v>
+        <v>22.83</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>35.03</v>
+        <v>23.35</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>32.97</v>
+        <v>32.65</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>41.49</v>
+        <v>40.69</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>58.87</v>
+        <v>58.47</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>172.24</v>
+        <v>172.07</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>170.7</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>45.99</v>
+        <v>45.95</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>42.81</v>
+        <v>42.72</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>41.82</v>
@@ -2111,34 +2111,34 @@
         <v>-0.41</v>
       </c>
       <c r="N21" s="3" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="R21" s="3" t="n">
         <v>-0.62</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
       <c r="S21" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.73</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.23</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-2.76</v>
+        <v>-2.93</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>-3.41</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>-0.17</v>
@@ -2363,37 +2363,37 @@
         <v>22.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>25.92</v>
+        <v>14.48</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>29.56</v>
+        <v>29.62</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>32.81</v>
+        <v>22.83</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>35.03</v>
+        <v>23.35</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>32.97</v>
+        <v>32.65</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>41.49</v>
+        <v>40.69</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>58.87</v>
+        <v>58.47</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>172.24</v>
+        <v>172.07</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>170.7</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>45.99</v>
+        <v>45.95</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>42.81</v>
+        <v>42.72</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>41.82</v>
@@ -2531,34 +2531,34 @@
         <v>-0.41</v>
       </c>
       <c r="N26" s="3" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>-0.62</v>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
       <c r="S26" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.73</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.23</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-2.76</v>
+        <v>-2.93</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>-3.41</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>-0.17</v>
@@ -2783,25 +2783,25 @@
         <v>35.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>26.02</v>
+        <v>14.54</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>29.73</v>
+        <v>29.77</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>32.97</v>
+        <v>22.94</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>35.23</v>
+        <v>23.49</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>33.23</v>
+        <v>32.87</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>41.82</v>
+        <v>41.05</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>59.4</v>
+        <v>58.99</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>173.78</v>
@@ -2813,7 +2813,7 @@
         <v>46.22</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>43.07</v>
+        <v>42.98</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>41.99</v>
@@ -2951,25 +2951,25 @@
         <v>-0.32</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.19</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.33</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.39</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.71</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>-1.22</v>
@@ -3203,43 +3203,43 @@
         <v>83.55</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>27.2</v>
+        <v>15.09</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>31.3</v>
+        <v>31.12</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>34.8</v>
+        <v>24</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>36.76</v>
+        <v>24.28</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>34.68</v>
+        <v>34.16</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>42.62</v>
+        <v>41.42</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.66</v>
+        <v>60.67</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>179.3</v>
+        <v>178.02</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>176.94</v>
+        <v>176.58</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>49.13</v>
+        <v>48.93</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>121.23</v>
+        <v>121.76</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>121.08</v>
+        <v>121.09</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>121.2</v>
+        <v>121.24</v>
       </c>
     </row>
     <row r="35">
@@ -3317,13 +3317,13 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>76.17</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.54000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>85.75</v>
+        <v>85.87</v>
       </c>
     </row>
     <row r="36">
@@ -3371,43 +3371,43 @@
         <v>0.75</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.46</v>
+        <v>0.74</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.21</v>
+        <v>0.51</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.66</v>
+        <v>0.97</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>4.3</v>
+        <v>3.03</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="37">
@@ -3623,25 +3623,25 @@
         <v>22.79</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>25.77</v>
+        <v>14.4</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>29.33</v>
+        <v>29.42</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>32.58</v>
+        <v>22.69</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>34.79</v>
+        <v>23.21</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>32.71</v>
+        <v>32.39</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>41.17</v>
+        <v>40.37</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>58.36</v>
+        <v>58.01</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>170.73</v>
@@ -3650,10 +3650,10 @@
         <v>169.37</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>45.68</v>
+        <v>45.63</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>42.47</v>
+        <v>42.39</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>41.53</v>
@@ -3791,25 +3791,25 @@
         <v>-0.52</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.33</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.68</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.57</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.05</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.68</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>-4.27</v>
@@ -3818,7 +3818,7 @@
         <v>-4.74</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.1</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>-0.51</v>
@@ -4043,37 +4043,37 @@
         <v>22.81</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>25.79</v>
+        <v>14.43</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>29.42</v>
+        <v>29.39</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>32.55</v>
+        <v>22.74</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>34.85</v>
+        <v>23.31</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>32.91</v>
+        <v>32.68</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>41.37</v>
+        <v>40.57</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>58.76</v>
+        <v>58.47</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>171.9</v>
+        <v>172.07</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>170.87</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>45.99</v>
+        <v>45.95</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>42.47</v>
+        <v>42.35</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>41.41</v>
@@ -4211,37 +4211,37 @@
         <v>-0.5</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.71</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.52</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.47</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.85</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>-1.23</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-3.09</v>
+        <v>-2.93</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>-3.25</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.55</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>-0.62</v>
@@ -4463,43 +4463,43 @@
         <v>20.71</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>24.58</v>
+        <v>13.62</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>28.03</v>
+        <v>27.94</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>30.95</v>
+        <v>21.62</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>33.1</v>
+        <v>22.11</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>29.78</v>
+        <v>29.65</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>37.55</v>
+        <v>36.85</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>53.37</v>
+        <v>53.2</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>155.69</v>
+        <v>156.25</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>154.22</v>
+        <v>154.49</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>41.46</v>
+        <v>41.5</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.9</v>
+        <v>37.79</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>36.74</v>
+        <v>36.84</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>30.22</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="50">
@@ -4631,43 +4631,43 @@
         <v>-2.61</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-1.97</v>
+        <v>-1.1</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.15</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-2.38</v>
+        <v>-1.64</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.45</v>
+        <v>-1.66</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.75</v>
+        <v>-3.62</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-4.69</v>
+        <v>-4.57</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-6.62</v>
+        <v>-6.49</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-19.31</v>
+        <v>-18.75</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-19.89</v>
+        <v>-19.62</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.27</v>
+        <v>-5.23</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.08</v>
+        <v>-5.1</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-5.29</v>
+        <v>-5.19</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.78</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="52">
@@ -4883,28 +4883,28 @@
         <v>22.97</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>26.15</v>
+        <v>14.48</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>29.73</v>
+        <v>29.54</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>32.65</v>
+        <v>22.74</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>34.89</v>
+        <v>23.31</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>33.04</v>
+        <v>32.81</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>40.89</v>
+        <v>40.06</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>57.96</v>
+        <v>57.62</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>166.03</v>
+        <v>165.25</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>165.35</v>
@@ -4913,13 +4913,13 @@
         <v>45.28</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>42.35</v>
+        <v>42.26</v>
       </c>
       <c r="Y54" s="3" t="n">
         <v>41.78</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>32.58</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="55">
@@ -5051,28 +5051,28 @@
         <v>-0.34</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.25</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.47</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.46</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.03</v>
+        <v>-2.07</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.75</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>-8.76</v>
@@ -5081,13 +5081,13 @@
         <v>-1.45</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="57">
@@ -5303,28 +5303,28 @@
         <v>23.48</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>26.65</v>
+        <v>14.85</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>30.36</v>
+        <v>30.31</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>33.54</v>
+        <v>23.45</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>35.91</v>
+        <v>24.01</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>33.84</v>
+        <v>33.57</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>42.37</v>
+        <v>41.54</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>60.23</v>
+        <v>59.88</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>176.05</v>
+        <v>176.23</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>174.99</v>
@@ -5333,7 +5333,7 @@
         <v>47.1</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>43.46</v>
+        <v>43.33</v>
       </c>
       <c r="Y59" s="3" t="n">
         <v>42.33</v>
@@ -5471,28 +5471,28 @@
         <v>0.16</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>0.87</v>
@@ -5501,7 +5501,7 @@
         <v>0.38</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.3</v>
@@ -5723,28 +5723,28 @@
         <v>23.84</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>27.06</v>
+        <v>15.07</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>30.89</v>
+        <v>30.81</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>34.05</v>
+        <v>23.78</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>36.46</v>
+        <v>24.41</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>34.36</v>
+        <v>34.12</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>43.06</v>
+        <v>42.22</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>61.16</v>
+        <v>60.85</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>178.75</v>
+        <v>178.93</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>177.67</v>
@@ -5753,7 +5753,7 @@
         <v>47.83</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>44.04</v>
+        <v>43.91</v>
       </c>
       <c r="Y64" s="3" t="n">
         <v>42.85</v>
@@ -5891,28 +5891,28 @@
         <v>0.52</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.51</v>
+        <v>0.35</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>1.16</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>3.55</v>
@@ -5921,7 +5921,7 @@
         <v>1.1</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -6143,43 +6143,43 @@
         <v>23.84</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>27.06</v>
+        <v>15.07</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>30.83</v>
+        <v>30.77</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>34.01</v>
+        <v>23.81</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>36.43</v>
+        <v>24.38</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>34.32</v>
+        <v>34.05</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>42.8</v>
+        <v>41.97</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>60.78</v>
+        <v>60.48</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>177.66</v>
+        <v>177.84</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>176.58</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>47.73</v>
+        <v>47.68</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>44.04</v>
+        <v>43.91</v>
       </c>
       <c r="Y69" s="3" t="n">
         <v>42.89</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>33.85</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="70">
@@ -6311,43 +6311,43 @@
         <v>0.52</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.51</v>
+        <v>0.35</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>0.79</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>2.47</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>0.86</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -6563,28 +6563,28 @@
         <v>23.2</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>26.38</v>
+        <v>14.68</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>30.12</v>
+        <v>30.13</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>33.23</v>
+        <v>23.24</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>35.66</v>
+        <v>23.8</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>33.43</v>
+        <v>33.2</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>41.86</v>
+        <v>41.05</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>59.52</v>
+        <v>59.22</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>173.95</v>
+        <v>174.47</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>172.9</v>
@@ -6593,7 +6593,7 @@
         <v>46.49</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>42.94</v>
+        <v>42.68</v>
       </c>
       <c r="Y74" s="3" t="n">
         <v>41.66</v>
@@ -6731,28 +6731,28 @@
         <v>-0.12</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.52</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>-1.21</v>
@@ -6761,7 +6761,7 @@
         <v>-0.23</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>-0.37</v>
@@ -6983,25 +6983,25 @@
         <v>23.32</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>26.54</v>
+        <v>14.73</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>30.24</v>
+        <v>30.1</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>33.33</v>
+        <v>23.26</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>35.55</v>
+        <v>23.77</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>33.53</v>
+        <v>33.27</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>42.24</v>
+        <v>41.42</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>59.99</v>
+        <v>59.7</v>
       </c>
       <c r="U79" s="3" t="n">
         <v>175</v>
@@ -7013,7 +7013,7 @@
         <v>46.73</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>42.98</v>
+        <v>42.9</v>
       </c>
       <c r="Y79" s="3" t="n">
         <v>42.03</v>
@@ -7403,40 +7403,40 @@
         <v>22.93</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>26.1</v>
+        <v>14.44</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>29.59</v>
+        <v>29.36</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>32.21</v>
+        <v>22.43</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>34.35</v>
+        <v>22.97</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>32.52</v>
+        <v>32.3</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>39.33</v>
+        <v>38.53</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>55.86</v>
+        <v>55.53</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>156.11</v>
+        <v>154.32</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>155.6</v>
+        <v>155.74</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>44.54</v>
+        <v>44.5</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>42.56</v>
+        <v>42.43</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>42.07</v>
+        <v>42.03</v>
       </c>
       <c r="Z84" s="3" t="n">
         <v>32.71</v>
@@ -7571,40 +7571,40 @@
         <v>-0.39</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.29</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.73</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1.13</v>
+        <v>-0.83</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.97</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.91</v>
+        <v>-2.89</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-4.13</v>
+        <v>-4.16</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-18.89</v>
+        <v>-20.68</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-18.52</v>
+        <v>-18.38</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.18</v>
+        <v>-2.23</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.47</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>-0.29</v>
@@ -7823,25 +7823,25 @@
         <v>35.2</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>26.02</v>
+        <v>14.54</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>29.73</v>
+        <v>29.77</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>32.97</v>
+        <v>22.94</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>35.23</v>
+        <v>23.49</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>33.27</v>
+        <v>32.87</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>41.82</v>
+        <v>41.05</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>59.4</v>
+        <v>58.99</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>173.78</v>
@@ -7853,7 +7853,7 @@
         <v>46.22</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>43.07</v>
+        <v>42.98</v>
       </c>
       <c r="Y89" s="3" t="n">
         <v>41.99</v>
@@ -7991,25 +7991,25 @@
         <v>-0.32</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.19</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.33</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.71</v>
       </c>
       <c r="U91" s="3" t="n">
         <v>-1.22</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-13T13:08:42</t>
+          <t>CreatedAt: 2026-04-13T14:08:22</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -695,28 +695,28 @@
         <v>32.74</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>42.13</v>
+        <v>32.87</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>32.68</v>
+        <v>45.4</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>57.73</v>
+        <v>45.27</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>67.55</v>
+        <v>65.61</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>97.53</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>43.96</v>
+        <v>58.34</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>42.39</v>
+        <v>45.86</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>41.49</v>
+        <v>41.57</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>29.48</v>
@@ -863,25 +863,25 @@
         <v>-0.52</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.62</v>
       </c>
       <c r="S6" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="X6" s="3" t="n">
         <v>-0.78</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>-0.51</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>-0.5</v>
@@ -1115,31 +1115,31 @@
         <v>33.64</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>43.54</v>
+        <v>34.08</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>33.37</v>
+        <v>46.31</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>59.52</v>
+        <v>46.64</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>68.92</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>100.98</v>
+        <v>77.63</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>46.07</v>
+        <v>61.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>225.8</v>
+        <v>228.97</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>224.21</v>
+        <v>225.81</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>212.27</v>
+        <v>211.05</v>
       </c>
     </row>
     <row r="10">
@@ -1283,31 +1283,31 @@
         <v>0.37</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12">
@@ -1385,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>181.3</v>
+        <v>180.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>180.29</v>
+        <v>181.75</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>181.05</v>
+        <v>179.8</v>
       </c>
     </row>
     <row r="13">
@@ -1535,22 +1535,22 @@
         <v>33.64</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>43.54</v>
+        <v>34.11</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>33.37</v>
+        <v>46.31</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>59.52</v>
+        <v>46.64</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>68.92</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>100.98</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>46.07</v>
+        <v>61.46</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>300</v>
@@ -1637,13 +1637,13 @@
         <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>74.2</v>
+        <v>71.03</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>75.73999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>87.73</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="16">
@@ -1703,31 +1703,31 @@
         <v>0.37</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.44</v>
+        <v>0.61</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.15</v>
+        <v>1.66</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>181.3</v>
+        <v>180.8</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>180.29</v>
+        <v>181.75</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>181.05</v>
+        <v>179.8</v>
       </c>
     </row>
     <row r="18">
@@ -1955,28 +1955,28 @@
         <v>32.91</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>42.34</v>
+        <v>33.13</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>32.94</v>
+        <v>45.72</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>58.18</v>
+        <v>45.63</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>68.09</v>
+        <v>66.2</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>98.2</v>
+        <v>74.58</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>44.26</v>
+        <v>58.69</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>42.72</v>
+        <v>46.08</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>41.78</v>
+        <v>41.82</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>29.68</v>
@@ -2123,28 +2123,28 @@
         <v>-0.36</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.16</v>
+        <v>-0.68</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.34</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.66</v>
+        <v>-1.12</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.55</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>-0.42</v>
@@ -2375,28 +2375,28 @@
         <v>32.91</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>42.34</v>
+        <v>33.13</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>32.94</v>
+        <v>45.72</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>58.18</v>
+        <v>45.63</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>68.09</v>
+        <v>66.2</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>98.2</v>
+        <v>74.58</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>44.26</v>
+        <v>58.69</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>42.72</v>
+        <v>46.08</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>41.78</v>
+        <v>41.82</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>29.68</v>
@@ -2543,28 +2543,28 @@
         <v>-0.36</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.16</v>
+        <v>-0.68</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.34</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.66</v>
+        <v>-1.12</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.55</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>-0.42</v>
@@ -2795,25 +2795,25 @@
         <v>33.04</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>42.55</v>
+        <v>33.37</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.2</v>
+        <v>46.04</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>58.7</v>
+        <v>45.99</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>68.48999999999999</v>
+        <v>66.66</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>98.79000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.52</v>
+        <v>58.98</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>42.98</v>
+        <v>46.26</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>41.99</v>
@@ -2963,28 +2963,28 @@
         <v>-0.23</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.13</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.18</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.9</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.83</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.37</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>-0.27</v>
@@ -3215,31 +3215,31 @@
         <v>95</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>44.25</v>
+        <v>34.64</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>33.5</v>
+        <v>46.5</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>60.37</v>
+        <v>47.31</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>72.15000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>102.75</v>
+        <v>79.5</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>47.14</v>
+        <v>63.15</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>119.78</v>
+        <v>120.59</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>121.09</v>
+        <v>119.73</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>119.95</v>
+        <v>121.21</v>
       </c>
     </row>
     <row r="35">
@@ -3317,13 +3317,13 @@
         <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>74.2</v>
+        <v>71.03</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.73999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>87.73</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="36">
@@ -3383,31 +3383,31 @@
         <v>0.78</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.22</v>
+        <v>3.35</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.36</v>
+        <v>3.51</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="37">
@@ -3635,28 +3635,28 @@
         <v>32.74</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>42.13</v>
+        <v>32.87</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>32.68</v>
+        <v>45.4</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>57.73</v>
+        <v>45.27</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>67.55</v>
+        <v>65.61</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>97.53</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>43.96</v>
+        <v>58.34</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>42.39</v>
+        <v>45.86</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>41.49</v>
+        <v>41.57</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>29.48</v>
@@ -3803,25 +3803,25 @@
         <v>-0.52</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.62</v>
       </c>
       <c r="S41" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>-0.78</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>-0.51</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>-0.5</v>
@@ -4055,31 +4055,31 @@
         <v>32.68</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>42.38</v>
+        <v>32.87</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>32.78</v>
+        <v>45.58</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>58.12</v>
+        <v>45.4</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>67.89</v>
+        <v>66</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>98.2</v>
+        <v>74.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>44.22</v>
+        <v>58.86</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>42.35</v>
+        <v>45.99</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>41.37</v>
+        <v>41.53</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>29.62</v>
+        <v>29.65</v>
       </c>
     </row>
     <row r="45">
@@ -4223,31 +4223,31 @@
         <v>-0.59</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.62</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.22</v>
+        <v>-0.91</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.12</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.42</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.64</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="47">
@@ -4475,31 +4475,31 @@
         <v>30.89</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>38.38</v>
+        <v>29.57</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>29.75</v>
+        <v>41.01</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>52.84</v>
+        <v>41.09</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>61.75</v>
+        <v>59.93</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>88.93000000000001</v>
+        <v>67.48</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>39.9</v>
+        <v>53.25</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.79</v>
+        <v>41.2</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>36.77</v>
+        <v>36.97</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>27.61</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="50">
@@ -4643,31 +4643,31 @@
         <v>-2.38</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-4.72</v>
+        <v>-3.93</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.72</v>
+        <v>-5.21</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-6.5</v>
+        <v>-5.22</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-7.22</v>
+        <v>-7.19</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-10.94</v>
+        <v>-8.44</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.03</v>
+        <v>-6.55</v>
       </c>
       <c r="X51" s="3" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="Y51" s="3" t="n">
         <v>-5.1</v>
       </c>
-      <c r="Y51" s="3" t="n">
-        <v>-5.22</v>
-      </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="52">
@@ -4895,31 +4895,31 @@
         <v>32.65</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>42.46</v>
+        <v>33.07</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>32.4</v>
+        <v>44.74</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>57.23</v>
+        <v>44.79</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>65.38</v>
+        <v>63.93</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>94.84999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>43.57</v>
+        <v>58.4</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>42.26</v>
+        <v>46.22</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>41.74</v>
+        <v>42.03</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>29.71</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="55">
@@ -5063,31 +5063,31 @@
         <v>-0.62</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.43</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.48</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.12</v>
+        <v>-1.52</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-3.6</v>
+        <v>-3.2</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-5.03</v>
+        <v>-3.2</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.4</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.42</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="57">
@@ -5315,28 +5315,28 @@
         <v>33.6</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>43.54</v>
+        <v>33.77</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>33.6</v>
+        <v>46.73</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>59.58</v>
+        <v>46.45</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>69.53</v>
+        <v>67.53</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>100.48</v>
+        <v>76.3</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>45.29</v>
+        <v>60.35</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>43.33</v>
+        <v>47.11</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>42.28</v>
+        <v>42.45</v>
       </c>
       <c r="Z59" s="3" t="n">
         <v>30.43</v>
@@ -5483,28 +5483,28 @@
         <v>0.34</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.44</v>
+        <v>0.27</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>0.33</v>
@@ -5735,28 +5735,28 @@
         <v>34.09</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>44.25</v>
+        <v>34.25</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>34.11</v>
+        <v>47.45</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>60.49</v>
+        <v>47.16</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>68.63</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>102.02</v>
+        <v>77.47</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>45.98</v>
+        <v>61.27</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>43.91</v>
+        <v>47.78</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>42.8</v>
+        <v>42.98</v>
       </c>
       <c r="Z64" s="3" t="n">
         <v>30.81</v>
@@ -5903,28 +5903,28 @@
         <v>0.82</v>
       </c>
       <c r="R66" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X66" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="S66" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X66" s="3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y66" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>0.71</v>
@@ -6155,28 +6155,28 @@
         <v>34.09</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>44.16</v>
+        <v>34.22</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>33.91</v>
+        <v>47.41</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>60.13</v>
+        <v>46.92</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>70.17</v>
+        <v>68.22</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>101.39</v>
+        <v>77</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>45.89</v>
+        <v>61.09</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>43.91</v>
+        <v>47.78</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>42.85</v>
+        <v>43.02</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>30.87</v>
@@ -6323,28 +6323,28 @@
         <v>0.82</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.44</v>
+        <v>1.19</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>0.96</v>
+        <v>1.28</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>0.77</v>
@@ -6575,28 +6575,28 @@
         <v>33.23</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>43.01</v>
+        <v>33.33</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>33.17</v>
+        <v>46.13</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>58.87</v>
+        <v>45.9</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>68.84</v>
+        <v>66.92</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>99.28</v>
+        <v>75.39</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>44.7</v>
+        <v>59.62</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>42.68</v>
+        <v>46.45</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>41.61</v>
+        <v>41.82</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>30.01</v>
@@ -6743,28 +6743,28 @@
         <v>-0.03</v>
       </c>
       <c r="R76" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="S76" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="S76" s="3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="T76" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.53</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.25</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>-0.09</v>
@@ -6995,28 +6995,28 @@
         <v>33.27</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>43.1</v>
+        <v>33.5</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>33.47</v>
+        <v>46.22</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>59.34</v>
+        <v>46.31</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>68.97</v>
+        <v>67.12</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>99.87</v>
+        <v>75.92</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>44.92</v>
+        <v>59.8</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>42.9</v>
+        <v>46.63</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>41.99</v>
+        <v>42.07</v>
       </c>
       <c r="Z79" s="3" t="n">
         <v>30.1</v>
@@ -7415,31 +7415,31 @@
         <v>32.11</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>41.68</v>
+        <v>32.68</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>31.16</v>
+        <v>43.08</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>55.05</v>
+        <v>43.24</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>61.36</v>
+        <v>60.36</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>89.09</v>
+        <v>68.77</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>42.82</v>
+        <v>57.72</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>42.47</v>
+        <v>46.68</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>42.03</v>
+        <v>42.5</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>29.8</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="85">
@@ -7583,31 +7583,31 @@
         <v>-1.16</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.42</v>
+        <v>-0.82</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.31</v>
+        <v>-3.14</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-4.29</v>
+        <v>-3.07</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-7.61</v>
+        <v>-6.76</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-10.78</v>
+        <v>-7.15</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.08</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.42</v>
+        <v>0.05</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.04</v>
+        <v>0.42</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="87">
@@ -7835,25 +7835,25 @@
         <v>33.04</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>42.55</v>
+        <v>33.37</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>33.2</v>
+        <v>46.04</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>58.7</v>
+        <v>45.99</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>68.48999999999999</v>
+        <v>66.66</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>98.79000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.52</v>
+        <v>58.98</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>42.98</v>
+        <v>46.26</v>
       </c>
       <c r="Y89" s="3" t="n">
         <v>41.99</v>
@@ -8003,28 +8003,28 @@
         <v>-0.23</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.13</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.18</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.9</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.83</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.37</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="Z91" s="3" t="n">
         <v>-0.27</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-14T02:11:52</t>
+          <t>CreatedAt: 2026-04-14T03:11:33</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -662,64 +662,64 @@
         <v>30.24</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>35.21</v>
-      </c>
       <c r="I4" s="3" t="n">
-        <v>23.21</v>
+        <v>23.23</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>26.79</v>
+        <v>22.87</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>30</v>
+        <v>29.94</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>29.82</v>
+        <v>23.92</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>29.72</v>
+        <v>29.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>29.59</v>
+        <v>32.98</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>29.35</v>
+        <v>29.4</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>34.37</v>
+        <v>34.43</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>32.95</v>
+        <v>33.01</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>42.98</v>
+        <v>44.19</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>44.5</v>
+        <v>44.94</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>46.87</v>
+        <v>50.39</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>44.32</v>
+        <v>54.03</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>43.91</v>
+        <v>44.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>44.02</v>
+        <v>47.91</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>40.92</v>
+        <v>41</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>41.08</v>
+        <v>41</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>30.25</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="5">
@@ -830,58 +830,58 @@
         <v>0.24</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>-0.24</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.31</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>-0.76</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-0.89</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.33</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.36</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.53</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.82</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>-0.62</v>
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>25.49</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>7.94</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1082,64 +1082,64 @@
         <v>31.58</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.45</v>
+        <v>36.94</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>36.79</v>
+        <v>61.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>23.92</v>
+        <v>23.93</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>27.53</v>
+        <v>23.43</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>30.98</v>
+        <v>24.86</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>30.94</v>
+        <v>30.89</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>30.86</v>
+        <v>34.36</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>31.02</v>
+        <v>31.07</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>36.2</v>
+        <v>36.27</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>34.25</v>
+        <v>34.32</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>44.9</v>
+        <v>46.17</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>45.7</v>
+        <v>46.15</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.28</v>
+        <v>52.01</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>45.8</v>
+        <v>55.88</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>45.54</v>
+        <v>45.88</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>46.12</v>
+        <v>50.14</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>42.85</v>
+        <v>42.94</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>43.48</v>
+        <v>43.35</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.14</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="10">
@@ -1250,28 +1250,28 @@
         <v>1.58</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>0.9</v>
@@ -1283,31 +1283,31 @@
         <v>0.41</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="12">
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>0</v>
@@ -1502,64 +1502,64 @@
         <v>31.61</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44.45</v>
+        <v>36.94</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>36.83</v>
+        <v>61.6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>23.92</v>
+        <v>23.93</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>27.56</v>
+        <v>23.43</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>31.17</v>
+        <v>31.11</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>30.98</v>
+        <v>24.86</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>30.94</v>
+        <v>30.89</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>30.86</v>
+        <v>34.39</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>31.02</v>
+        <v>31.1</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>36.2</v>
+        <v>36.27</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>34.25</v>
+        <v>34.35</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>44.9</v>
+        <v>46.17</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>45.7</v>
+        <v>46.15</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>48.33</v>
+        <v>52.01</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>45.84</v>
+        <v>55.93</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>45.59</v>
+        <v>45.88</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>46.12</v>
+        <v>50.14</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>42.9</v>
+        <v>42.98</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>43.48</v>
+        <v>43.35</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>32.17</v>
+        <v>35.43</v>
       </c>
     </row>
     <row r="15">
@@ -1670,64 +1670,64 @@
         <v>1.61</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>0.18</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="17">
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0</v>
@@ -1922,64 +1922,64 @@
         <v>30.49</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>42.82</v>
+        <v>41.55</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>35.39</v>
+        <v>60.3</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>23.33</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>26.9</v>
+        <v>22.96</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>30.12</v>
+        <v>30.06</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>29.88</v>
+        <v>23.97</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>29.75</v>
+        <v>29.76</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>29.67</v>
+        <v>33.04</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>29.44</v>
+        <v>29.49</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>34.5</v>
+        <v>34.57</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>33.08</v>
+        <v>33.14</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>43.19</v>
+        <v>44.41</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>44.58</v>
+        <v>45.03</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>47.01</v>
+        <v>50.54</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>44.45</v>
+        <v>54.18</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>44.08</v>
+        <v>44.37</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>44.24</v>
+        <v>48.14</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>41.12</v>
+        <v>41.25</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>41.33</v>
+        <v>41.24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>30.49</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="20">
@@ -2090,28 +2090,28 @@
         <v>0.49</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.26</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.48</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>-0.68</v>
@@ -2123,31 +2123,31 @@
         <v>-0.76</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.11</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.21</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.25</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.58</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="22">
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0</v>
@@ -2342,64 +2342,64 @@
         <v>30.49</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>68.3</v>
+        <v>35.59</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>35.39</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>23.33</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>26.9</v>
+        <v>22.96</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>30.12</v>
+        <v>30.06</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>29.88</v>
+        <v>23.97</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>29.75</v>
+        <v>29.76</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>29.67</v>
+        <v>33.04</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>29.44</v>
+        <v>29.49</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>34.5</v>
+        <v>34.57</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>33.08</v>
+        <v>33.14</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>43.19</v>
+        <v>44.41</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>44.58</v>
+        <v>45.03</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>47.01</v>
+        <v>50.54</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>44.45</v>
+        <v>54.18</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>44.08</v>
+        <v>44.37</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>44.24</v>
+        <v>48.14</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>41.12</v>
+        <v>41.25</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>41.33</v>
+        <v>41.24</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>30.49</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="25">
@@ -2510,28 +2510,28 @@
         <v>0.49</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.26</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.48</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>-0.68</v>
@@ -2543,31 +2543,31 @@
         <v>-0.76</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.11</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.22</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.21</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.25</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.58</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="27">
@@ -2594,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>25.49</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0</v>
+        <v>7.94</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -2762,64 +2762,64 @@
         <v>30.64</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>42.95</v>
+        <v>41.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>35.42</v>
+        <v>60.4</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>23.37</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>26.95</v>
+        <v>23.03</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>30.12</v>
+        <v>30.06</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>29.85</v>
+        <v>23.97</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>29.72</v>
+        <v>29.73</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>29.65</v>
+        <v>33.04</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>29.41</v>
+        <v>29.49</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>34.53</v>
+        <v>34.6</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.11</v>
+        <v>33.21</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>43.27</v>
+        <v>44.45</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>44.54</v>
+        <v>45.03</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.01</v>
+        <v>50.64</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>44.5</v>
+        <v>54.29</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>44.17</v>
+        <v>44.45</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.41</v>
+        <v>48.33</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>41.24</v>
+        <v>41.37</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>41.45</v>
+        <v>41.37</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.7</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="30">
@@ -2930,64 +2930,64 @@
         <v>0.64</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.26</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0.73</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.7</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.07</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.11</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.98</v>
+        <v>-1.14</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>-1.24</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.11</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="32">
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0</v>
@@ -3182,64 +3182,64 @@
         <v>32.36</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45.65</v>
+        <v>37.9</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>37.74</v>
+        <v>62.48</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>24.32</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>27.99</v>
+        <v>23.75</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>31.9</v>
+        <v>31.83</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>31.66</v>
+        <v>25.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>31.68</v>
+        <v>31.63</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>31.63</v>
+        <v>35.22</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>32.11</v>
+        <v>32.16</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>37.39</v>
+        <v>37.43</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>35.03</v>
+        <v>35.1</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>45.97</v>
+        <v>47.22</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>46.44</v>
+        <v>46.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>49.22</v>
+        <v>52.97</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>46.69</v>
+        <v>56.97</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>46.43</v>
+        <v>46.77</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>47.32</v>
+        <v>51.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>44.07</v>
+        <v>44.16</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>44.98</v>
+        <v>44.84</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>33.28</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="35">
@@ -3350,64 +3350,64 @@
         <v>2.36</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.61</v>
+        <v>2.92</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.01</v>
+        <v>0.74</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.66</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>1.99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>1.19</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="37">
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>0</v>
@@ -3602,64 +3602,64 @@
         <v>30.24</v>
       </c>
       <c r="G39" s="3" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>35.21</v>
-      </c>
       <c r="I39" s="3" t="n">
-        <v>23.21</v>
+        <v>23.23</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>26.79</v>
+        <v>22.87</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>30</v>
+        <v>29.94</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>29.82</v>
+        <v>23.92</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>29.72</v>
+        <v>29.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>29.59</v>
+        <v>32.98</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>29.35</v>
+        <v>29.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>34.37</v>
+        <v>34.43</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>32.95</v>
+        <v>33.01</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>42.98</v>
+        <v>44.19</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>44.5</v>
+        <v>44.94</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>46.87</v>
+        <v>50.39</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>44.32</v>
+        <v>54.03</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>43.91</v>
+        <v>44.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>44.02</v>
+        <v>47.91</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>40.92</v>
+        <v>41</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>41.08</v>
+        <v>41</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>30.25</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="40">
@@ -3770,58 +3770,58 @@
         <v>0.24</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>-0.24</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.31</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>-0.76</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>-0.89</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.33</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.36</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.53</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.82</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>-0.62</v>
@@ -3854,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>25.49</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0</v>
+        <v>7.94</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0</v>
@@ -4022,64 +4022,64 @@
         <v>29.82</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>41.88</v>
+        <v>34.85</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>35</v>
+        <v>59.73</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>23.23</v>
+        <v>23.26</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>26.87</v>
+        <v>22.92</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>30.09</v>
+        <v>30.03</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>30</v>
+        <v>24.04</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>29.96</v>
+        <v>29.94</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>29.7</v>
+        <v>33.04</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>29.56</v>
+        <v>29.55</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>34.47</v>
+        <v>34.54</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.92</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>42.98</v>
+        <v>44.19</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>44.67</v>
+        <v>45.11</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>47.19</v>
+        <v>50.79</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>44.72</v>
+        <v>54.56</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>44.56</v>
+        <v>44.85</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>44.8</v>
+        <v>48.71</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>41.2</v>
+        <v>41.25</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>41.12</v>
+        <v>41.04</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>30.37</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="45">
@@ -4190,64 +4190,64 @@
         <v>-0.18</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.19</v>
       </c>
       <c r="I46" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>-0.09</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>-0.11</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>-0.15</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>-0.3</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.63</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>-0.79</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.99</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.33</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.13</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.96</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.87</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>-0.85</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.73</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.58</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="47">
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -4442,64 +4442,64 @@
         <v>25.93</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>36.92</v>
+        <v>30.55</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>31.12</v>
+        <v>54.32</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>20.72</v>
+        <v>20.64</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>24</v>
+        <v>21.13</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>26.69</v>
+        <v>26.5</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>26.66</v>
+        <v>21.24</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>26.54</v>
+        <v>26.34</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>26.46</v>
+        <v>29.3</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>26.21</v>
+        <v>26.1</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>30.61</v>
+        <v>30.48</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>29.58</v>
+        <v>29.43</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>38.82</v>
+        <v>39.76</v>
       </c>
       <c r="S49" s="3" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="V49" s="3" t="n">
         <v>40.23</v>
       </c>
-      <c r="T49" s="3" t="n">
-        <v>42.44</v>
-      </c>
-      <c r="U49" s="3" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="V49" s="3" t="n">
-        <v>40.18</v>
-      </c>
       <c r="W49" s="3" t="n">
-        <v>40.14</v>
+        <v>43.41</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>36.59</v>
+        <v>36.43</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>36.35</v>
+        <v>36.09</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>27.97</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="50">
@@ -4610,64 +4610,64 @@
         <v>-4.07</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-5.13</v>
+        <v>-4.43</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-4.02</v>
+        <v>-5.6</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.68</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-2.98</v>
+        <v>-1.88</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-3.55</v>
+        <v>-3.68</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-3.55</v>
+        <v>-2.99</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.9</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-3.78</v>
+        <v>-4.37</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-3.91</v>
+        <v>-4.07</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-4.65</v>
+        <v>-4.85</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-4.26</v>
+        <v>-4.47</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-5.36</v>
+        <v>-5.76</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-5.51</v>
+        <v>-5.79</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-5.6</v>
+        <v>-6.28</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.23</v>
+        <v>-6.64</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-5.22</v>
+        <v>-5.47</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.34</v>
+        <v>-6.03</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.2</v>
+        <v>-5.39</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-5.34</v>
+        <v>-5.52</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.88</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="52">
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>0</v>
@@ -4862,64 +4862,64 @@
         <v>29.79</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>41.92</v>
+        <v>34.78</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>35.03</v>
+        <v>59.68</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>22.78</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>26.22</v>
+        <v>22.36</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>29.47</v>
+        <v>29.41</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>29.47</v>
+        <v>23.64</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>30.08</v>
+        <v>30.03</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>30.03</v>
+        <v>33.44</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>29.88</v>
+        <v>29.93</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>35.05</v>
+        <v>35.12</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>33.67</v>
+        <v>33.74</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>43.83</v>
+        <v>45.11</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>44.41</v>
+        <v>44.89</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>46.6</v>
+        <v>50.15</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>43.56</v>
+        <v>53.09</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>43.53</v>
+        <v>43.81</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>44.11</v>
+        <v>47.91</v>
       </c>
       <c r="X54" s="3" t="n">
         <v>41.29</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>41.61</v>
+        <v>41.53</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>30.52</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="55">
@@ -5030,28 +5030,28 @@
         <v>-0.21</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.21</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.24</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>-0.55</v>
       </c>
       <c r="J56" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="K56" s="3" t="n">
         <v>-0.76</v>
       </c>
-      <c r="K56" s="3" t="n">
-        <v>-0.77</v>
-      </c>
       <c r="L56" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.59</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>-0.24</v>
@@ -5063,31 +5063,31 @@
         <v>-0.17</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.41</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.33</v>
+        <v>-1.35</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.6</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.34</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.87</v>
+        <v>-1.88</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.53</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.54</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>-0.08</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="57">
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0</v>
@@ -5282,64 +5282,64 @@
         <v>30.39</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>42.64</v>
+        <v>35.48</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>35.71</v>
+        <v>60.69</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>23.75</v>
+        <v>23.78</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>27.5</v>
+        <v>23.46</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>30.82</v>
+        <v>30.73</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>30.79</v>
+        <v>24.65</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>30.75</v>
+        <v>30.7</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>30.45</v>
+        <v>33.87</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>30.45</v>
+        <v>30.41</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>35.47</v>
+        <v>35.54</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>33.84</v>
+        <v>33.8</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>44.14</v>
+        <v>45.43</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>45.88</v>
+        <v>46.33</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>48.28</v>
+        <v>52.01</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>45.8</v>
+        <v>55.82</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>45.63</v>
+        <v>45.93</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>46.03</v>
+        <v>50.04</v>
       </c>
       <c r="X59" s="3" t="n">
         <v>42.25</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>42.03</v>
+        <v>41.95</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>31.16</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="60">
@@ -5450,58 +5450,58 @@
         <v>0.4</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>0.23</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.34</v>
@@ -5621,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>0</v>
@@ -5702,64 +5702,64 @@
         <v>30.7</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>43.12</v>
+        <v>35.85</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>36.15</v>
+        <v>61.34</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>24.07</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>27.87</v>
+        <v>23.77</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>31.24</v>
+        <v>31.18</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>31.24</v>
+        <v>25.01</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>31.19</v>
+        <v>31.14</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>30.89</v>
+        <v>34.32</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>30.89</v>
+        <v>30.94</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>35.98</v>
+        <v>36.05</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>34.28</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>44.81</v>
+        <v>46.12</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>46.53</v>
+        <v>46.99</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>49.02</v>
+        <v>52.75</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>46.45</v>
+        <v>56.62</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>46.33</v>
+        <v>46.63</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>46.69</v>
+        <v>50.76</v>
       </c>
       <c r="X64" s="3" t="n">
         <v>42.81</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>42.55</v>
+        <v>42.46</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>31.55</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="65">
@@ -5870,25 +5870,25 @@
         <v>0.71</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.08</v>
+        <v>0.86</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>0.75</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>0.65</v>
@@ -5900,28 +5900,28 @@
         <v>0.72</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>0.98</v>
+        <v>1.19</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>0.93</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>0.85</v>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>0</v>
@@ -6122,64 +6122,64 @@
         <v>41.43</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>43.17</v>
+        <v>35.92</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>36.19</v>
+        <v>61.34</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>24.07</v>
+        <v>24.1</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>27.87</v>
+        <v>23.8</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>31.24</v>
+        <v>31.18</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>31.24</v>
+        <v>25.01</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>31.19</v>
+        <v>31.14</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>30.73</v>
+        <v>34.22</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>30.89</v>
+        <v>30.88</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>36.02</v>
+        <v>36.09</v>
       </c>
       <c r="Q69" s="3" t="n">
         <v>34.18</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>44.63</v>
+        <v>45.93</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>46.34</v>
+        <v>46.8</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>48.77</v>
+        <v>52.49</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>46.22</v>
+        <v>56.33</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>46.1</v>
+        <v>46.39</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>46.69</v>
+        <v>50.76</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>42.64</v>
+        <v>42.51</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>31.61</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="70">
@@ -6290,64 +6290,64 @@
         <v>0.8</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1.12</v>
+        <v>0.93</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0.76</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>0.73</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="72">
@@ -6461,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0</v>
@@ -6542,64 +6542,64 @@
         <v>29.85</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>42</v>
+        <v>34.95</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>35.14</v>
+        <v>59.97</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>23.4</v>
+        <v>23.42</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>27.12</v>
+        <v>23.15</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>30.39</v>
+        <v>30.3</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>30.45</v>
+        <v>24.33</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>30.44</v>
+        <v>30.3</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>30.06</v>
+        <v>33.44</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>30.06</v>
+        <v>30.02</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>35.01</v>
+        <v>35.05</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>33.5</v>
+        <v>33.37</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>43.66</v>
+        <v>44.89</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>45.33</v>
+        <v>45.78</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>47.71</v>
+        <v>51.39</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>45.25</v>
+        <v>55.15</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>45.13</v>
+        <v>45.43</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>45.48</v>
+        <v>49.44</v>
       </c>
       <c r="X74" s="3" t="n">
         <v>41.7</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>41.45</v>
+        <v>41.33</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>30.73</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="75">
@@ -6710,49 +6710,49 @@
         <v>-0.15</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.23</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.53</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.63</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.46</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.28</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>-0.27</v>
@@ -6761,13 +6761,13 @@
         <v>0</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.29</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="77">
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>0</v>
@@ -6962,64 +6962,64 @@
         <v>30</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>42.05</v>
+        <v>34.98</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>35.14</v>
+        <v>59.92</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>23.33</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>26.98</v>
+        <v>23.01</v>
       </c>
       <c r="K79" s="3" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="M79" s="3" t="n">
         <v>30.24</v>
       </c>
-      <c r="L79" s="3" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>30.26</v>
-      </c>
       <c r="N79" s="3" t="n">
-        <v>30.24</v>
+        <v>33.67</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>30.12</v>
+        <v>30.17</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>35.26</v>
+        <v>35.33</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>33.84</v>
+        <v>33.9</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>44.18</v>
+        <v>45.52</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>45.74</v>
+        <v>46.24</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>48.04</v>
+        <v>51.75</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>45.48</v>
+        <v>55.43</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>45.41</v>
+        <v>45.7</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>45.48</v>
+        <v>49.44</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>41.78</v>
+        <v>41.82</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>41.7</v>
+        <v>41.61</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>30.85</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="80">
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>0</v>
@@ -7382,64 +7382,64 @@
         <v>30.03</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>42.34</v>
+        <v>35.13</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>35.46</v>
+        <v>60.3</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>22.3</v>
+        <v>22.32</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>25.79</v>
+        <v>21.98</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>29.05</v>
+        <v>28.96</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>29.1</v>
+        <v>23.33</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>30.47</v>
+        <v>30.42</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>30.39</v>
+        <v>33.81</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>30.15</v>
+        <v>30.2</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>35.44</v>
+        <v>35.51</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>34.18</v>
+        <v>34.25</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>44.31</v>
+        <v>45.66</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>43.69</v>
+        <v>44.17</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>45.67</v>
+        <v>49.19</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>41.68</v>
+        <v>50.81</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>41.73</v>
+        <v>42</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>43.56</v>
+        <v>47.31</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>41.7</v>
+        <v>41.74</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>42.12</v>
+        <v>41.99</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>30.91</v>
+        <v>33.97</v>
       </c>
     </row>
     <row r="85">
@@ -7550,28 +7550,28 @@
         <v>0.03</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I86" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J86" s="3" t="n">
         <v>-1.03</v>
       </c>
-      <c r="J86" s="3" t="n">
-        <v>-1.19</v>
-      </c>
       <c r="K86" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.11</v>
+        <v>-0.91</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="O86" s="3" t="n">
         <v>0.03</v>
@@ -7583,31 +7583,31 @@
         <v>0.34</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.05</v>
+        <v>-2.08</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.56</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-3.79</v>
+        <v>-4.62</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-3.67</v>
+        <v>-3.7</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.13</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-0.08</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>0</v>
@@ -7802,64 +7802,64 @@
         <v>30.64</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>42.95</v>
+        <v>41.7</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>35.42</v>
+        <v>60.4</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>23.37</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>26.95</v>
+        <v>23.03</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>30.12</v>
+        <v>30.06</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>29.85</v>
+        <v>23.97</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>29.72</v>
+        <v>29.73</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>29.65</v>
+        <v>33.01</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>29.41</v>
+        <v>29.49</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>34.53</v>
+        <v>34.6</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>33.11</v>
+        <v>33.21</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>43.27</v>
+        <v>44.45</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>44.54</v>
+        <v>45.03</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>47.01</v>
+        <v>50.64</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>44.5</v>
+        <v>54.29</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>44.17</v>
+        <v>44.45</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.41</v>
+        <v>48.33</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>41.24</v>
+        <v>41.37</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>41.45</v>
+        <v>41.37</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>30.7</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="90">
@@ -7970,64 +7970,64 @@
         <v>0.64</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.26</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.66</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="P91" s="3" t="n">
         <v>-0.73</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.7</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.07</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.11</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.98</v>
+        <v>-1.14</v>
       </c>
       <c r="V91" s="3" t="n">
         <v>-1.24</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.11</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="Y91" s="3" t="n">
         <v>-0.25</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="92">
@@ -8054,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0</v>
+        <v>12.19</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-14T17:08:03</t>
+          <t>CreatedAt: 2026-04-14T18:07:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -707,16 +707,16 @@
         <v>137.57</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>134.6</v>
+        <v>107.86</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>328.73</v>
+        <v>122.34</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.82</v>
+        <v>40.35</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>33.41</v>
+        <v>33.08</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>29.47</v>
@@ -875,16 +875,16 @@
         <v>-3.85</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-4.85</v>
+        <v>-3.56</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-3.06</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.85</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.47</v>
@@ -1127,19 +1127,19 @@
         <v>137.04</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>132.42</v>
+        <v>106.42</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>338.62</v>
+        <v>125.65</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>35.09</v>
+        <v>41.48</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>35.06</v>
+        <v>34.4</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>31.09</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="10">
@@ -1295,19 +1295,19 @@
         <v>-4.39</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-7.02</v>
+        <v>-5</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1.02</v>
+        <v>0.25</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.63</v>
+        <v>0.29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.12</v>
+        <v>0.76</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12">
@@ -1547,19 +1547,19 @@
         <v>137.04</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>132.42</v>
+        <v>106.42</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>338.62</v>
+        <v>125.65</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>35.13</v>
+        <v>41.48</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>35.06</v>
+        <v>34.43</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>31.12</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="15">
@@ -1715,19 +1715,19 @@
         <v>-4.39</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-7.02</v>
+        <v>-5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.02</v>
+        <v>0.25</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.67</v>
+        <v>0.29</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.18</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="17">
@@ -1967,19 +1967,19 @@
         <v>138.11</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>134.99</v>
+        <v>108.07</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>330.34</v>
+        <v>123.06</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>33.99</v>
+        <v>40.5</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>33.57</v>
+        <v>33.21</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.76</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="20">
@@ -2135,19 +2135,19 @@
         <v>-3.31</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-4.45</v>
+        <v>-3.35</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-7.27</v>
+        <v>-2.34</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.43</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="22">
@@ -2387,19 +2387,19 @@
         <v>138.11</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>134.99</v>
+        <v>108.07</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>330.34</v>
+        <v>123.06</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>33.99</v>
+        <v>40.5</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>33.57</v>
+        <v>33.21</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>29.76</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="25">
@@ -2555,19 +2555,19 @@
         <v>-3.31</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-4.45</v>
+        <v>-3.35</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-7.27</v>
+        <v>-2.34</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.43</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="27">
@@ -2807,19 +2807,19 @@
         <v>138.65</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>135.64</v>
+        <v>108.59</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>331.64</v>
+        <v>123.79</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>34.09</v>
+        <v>40.66</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>33.67</v>
+        <v>33.31</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.03</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="30">
@@ -2975,19 +2975,19 @@
         <v>-2.77</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-3.8</v>
+        <v>-2.82</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-5.97</v>
+        <v>-1.61</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.53</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.33</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32">
@@ -3227,19 +3227,19 @@
         <v>135.07</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>129.83</v>
+        <v>104.81</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>343.09</v>
+        <v>126.79</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>35.82</v>
+        <v>41.99</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>35.99</v>
+        <v>35.08</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>31.92</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="35">
@@ -3395,19 +3395,19 @@
         <v>-6.35</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-9.609999999999999</v>
+        <v>-6.6</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>5.49</v>
+        <v>1.39</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="37">
@@ -3647,16 +3647,16 @@
         <v>137.57</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>134.6</v>
+        <v>107.86</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>328.73</v>
+        <v>122.34</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>33.82</v>
+        <v>40.35</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>33.41</v>
+        <v>33.08</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>29.47</v>
@@ -3815,16 +3815,16 @@
         <v>-3.85</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-4.85</v>
+        <v>-3.56</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-3.06</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.85</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-0.47</v>
@@ -4067,19 +4067,19 @@
         <v>137.84</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>136.04</v>
+        <v>109.34</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>333.27</v>
+        <v>123.79</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>33.99</v>
+        <v>40.62</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>33.41</v>
+        <v>33.14</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>29.52</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="45">
@@ -4235,19 +4235,19 @@
         <v>-3.58</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-3.4</v>
+        <v>-2.08</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-4.33</v>
+        <v>-1.61</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.57</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="47">
@@ -4487,19 +4487,19 @@
         <v>123.41</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>122.42</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>296.67</v>
+        <v>111.07</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>30.34</v>
+        <v>36.26</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>29.72</v>
+        <v>29.43</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>25.94</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="50">
@@ -4655,19 +4655,19 @@
         <v>-18.02</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-17.02</v>
+        <v>-13.43</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-40.94</v>
+        <v>-14.33</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-4.13</v>
+        <v>-4.93</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-4.22</v>
+        <v>-4.21</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-4</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="52">
@@ -4907,16 +4907,16 @@
         <v>133.92</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>132.67</v>
+        <v>105.61</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>323.38</v>
+        <v>120.58</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.82</v>
+        <v>40.42</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>33.31</v>
+        <v>33.01</v>
       </c>
       <c r="Z54" s="3" t="n">
         <v>29.18</v>
@@ -5075,13 +5075,13 @@
         <v>-7.5</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-6.77</v>
+        <v>-5.81</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-14.23</v>
+        <v>-4.82</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.77</v>
       </c>
       <c r="Y56" s="3" t="n">
         <v>-0.63</v>
@@ -5327,16 +5327,16 @@
         <v>140.58</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>139.16</v>
+        <v>111.98</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>342.05</v>
+        <v>127.05</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>34.81</v>
+        <v>41.61</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>34.18</v>
+        <v>33.88</v>
       </c>
       <c r="Z59" s="3" t="n">
         <v>30.24</v>
@@ -5495,13 +5495,13 @@
         <v>-0.84</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>-0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>4.45</v>
+        <v>1.65</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.24</v>
@@ -5747,19 +5747,19 @@
         <v>142.56</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>140.99</v>
+        <v>113.69</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>347.33</v>
+        <v>128.88</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>35.31</v>
+        <v>42.21</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>34.56</v>
+        <v>34.29</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>30.58</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="65">
@@ -5915,19 +5915,19 @@
         <v>1.14</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.55</v>
+        <v>2.27</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>9.73</v>
+        <v>3.48</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="67">
@@ -6167,16 +6167,16 @@
         <v>141</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>346.97</v>
+        <v>128.75</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>35.31</v>
+        <v>42.21</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>34.63</v>
+        <v>34.36</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>30.67</v>
@@ -6335,16 +6335,16 @@
         <v>-0.42</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>0.74</v>
@@ -6587,16 +6587,16 @@
         <v>138.79</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>137.65</v>
+        <v>110.64</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>337.61</v>
+        <v>125.4</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.36</v>
+        <v>41.07</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>33.64</v>
+        <v>33.37</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>29.76</v>
@@ -6755,16 +6755,16 @@
         <v>-2.64</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>-1.79</v>
+        <v>-0.77</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>-0.18</v>
@@ -7007,16 +7007,16 @@
         <v>141.42</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>139.44</v>
+        <v>111.42</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>337.61</v>
+        <v>125.4</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>34.46</v>
+        <v>41.19</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>33.94</v>
+        <v>33.64</v>
       </c>
       <c r="Z79" s="3" t="n">
         <v>29.94</v>
@@ -7427,16 +7427,16 @@
         <v>127.29</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>126.53</v>
+        <v>100.56</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>318.8</v>
+        <v>118.52</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>34.02</v>
+        <v>40.58</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>33.5</v>
+        <v>33.21</v>
       </c>
       <c r="Z84" s="3" t="n">
         <v>29.35</v>
@@ -7595,16 +7595,16 @@
         <v>-14.13</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-12.91</v>
+        <v>-10.86</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-18.81</v>
+        <v>-6.87</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.61</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>-0.59</v>
@@ -7847,19 +7847,19 @@
         <v>138.65</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>135.64</v>
+        <v>108.59</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>331.64</v>
+        <v>123.79</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>34.09</v>
+        <v>40.66</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.67</v>
+        <v>33.31</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>30.03</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="90">
@@ -8015,19 +8015,19 @@
         <v>-2.77</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-3.8</v>
+        <v>-2.82</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-5.97</v>
+        <v>-1.61</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.53</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.33</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-15T12:09:13</t>
+          <t>CreatedAt: 2026-04-15T14:08:42</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -692,34 +692,34 @@
         <v>54.68</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>45.8</v>
+        <v>44.91</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>32.36</v>
+        <v>63.19</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>74.61</v>
+        <v>115.16</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>60.91</v>
+        <v>52.75</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>71.03</v>
+        <v>65.91</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>224.21</v>
+        <v>126.09</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>44.66</v>
+        <v>33.01</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>32.31</v>
+        <v>29.76</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>41.98</v>
+        <v>32.87</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.64</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="5">
@@ -860,34 +860,34 @@
         <v>-1.26</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.85</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.14</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.84</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.74</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.59</v>
+        <v>-1.89</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.53</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.39</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="7">
@@ -1112,31 +1112,31 @@
         <v>57.31</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>47.62</v>
+        <v>46.46</v>
       </c>
       <c r="R9" s="3" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>126.84</v>
+      </c>
+      <c r="W9" s="3" t="n">
         <v>33.37</v>
       </c>
-      <c r="S9" s="3" t="n">
-        <v>74.17</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="U9" s="3" t="n">
-        <v>71.66</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>225.32</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>45.23</v>
-      </c>
       <c r="X9" s="3" t="n">
-        <v>33.44</v>
+        <v>30.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>44.16</v>
+        <v>34.55</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>34.21</v>
@@ -1280,31 +1280,31 @@
         <v>1.38</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.3</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.58</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2.48</v>
+        <v>-1.14</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.17</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1.57</v>
@@ -1532,31 +1532,31 @@
         <v>57.31</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>47.62</v>
+        <v>46.46</v>
       </c>
       <c r="R14" s="3" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>126.84</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>33.37</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>74.17</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>71.66</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>225.32</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>45.23</v>
-      </c>
       <c r="X14" s="3" t="n">
-        <v>33.44</v>
+        <v>30.73</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>44.16</v>
+        <v>34.58</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>34.21</v>
@@ -1700,31 +1700,31 @@
         <v>1.38</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.3</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.58</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-2.48</v>
+        <v>-1.14</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.17</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1.57</v>
@@ -1952,31 +1952,31 @@
         <v>55</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>46.07</v>
+        <v>45.13</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>32.49</v>
+        <v>76</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>74.83</v>
+        <v>115.38</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>61.09</v>
+        <v>52.85</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>71.17</v>
+        <v>66.11</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>224.66</v>
+        <v>126.34</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>44.7</v>
+        <v>33.04</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>32.44</v>
+        <v>29.88</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>42.23</v>
+        <v>33.07</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>32.87</v>
@@ -2120,31 +2120,31 @@
         <v>-0.93</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.63</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.62</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.63</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.15</v>
+        <v>-1.64</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.23</v>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>55</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>46.07</v>
+        <v>45.13</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>32.49</v>
+        <v>63.57</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>74.83</v>
+        <v>115.38</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>61.09</v>
+        <v>52.85</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>71.17</v>
+        <v>66.11</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>224.66</v>
+        <v>126.34</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>44.7</v>
+        <v>33.04</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>32.44</v>
+        <v>29.88</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>42.23</v>
+        <v>33.07</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>32.87</v>
@@ -2540,31 +2540,31 @@
         <v>-0.93</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.63</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.62</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.63</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.15</v>
+        <v>-1.64</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0.23</v>
@@ -2792,31 +2792,31 @@
         <v>55.16</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>46.21</v>
+        <v>45.22</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>32.52</v>
+        <v>76.31</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>74.97</v>
+        <v>115.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>61.15</v>
+        <v>52.9</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>71.17</v>
+        <v>66.11</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>224.88</v>
+        <v>126.46</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.66</v>
+        <v>32.97</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>32.44</v>
+        <v>29.88</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>42.31</v>
+        <v>33.14</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>33.07</v>
@@ -2960,31 +2960,31 @@
         <v>-0.77</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.54</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.45</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.58</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.92</v>
+        <v>-1.52</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>0.43</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>58.69</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>48.46</v>
+        <v>47.18</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>33.84</v>
+        <v>65.11</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>112.72</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.52</v>
+        <v>53.11</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>72.23999999999999</v>
+        <v>67.17</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>225.99</v>
+        <v>127.34</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>45.73</v>
+        <v>33.74</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>34.03</v>
+        <v>31.21</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>45.39</v>
+        <v>35.54</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>35.02</v>
@@ -3380,31 +3380,31 @@
         <v>2.76</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.54</v>
+        <v>0.78</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-2.3</v>
+        <v>-4.28</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>-0.37</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-1.81</v>
+        <v>-0.64</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>2.38</v>
@@ -3632,34 +3632,34 @@
         <v>54.68</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>45.8</v>
+        <v>44.91</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>32.36</v>
+        <v>63.19</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>74.61</v>
+        <v>115.16</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>60.91</v>
+        <v>52.75</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>71.03</v>
+        <v>65.91</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>224.21</v>
+        <v>126.09</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>44.66</v>
+        <v>33.01</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>32.31</v>
+        <v>29.76</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>41.98</v>
+        <v>32.87</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.64</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="40">
@@ -3800,34 +3800,34 @@
         <v>-1.26</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.85</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.14</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.84</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.74</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.59</v>
+        <v>-1.89</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.53</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.39</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="42">
@@ -4052,34 +4052,34 @@
         <v>54.73</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>45.54</v>
+        <v>44.69</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>32.43</v>
+        <v>63.01</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>74.68000000000001</v>
+        <v>114.93</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>60.97</v>
+        <v>52.8</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>71.03</v>
+        <v>65.98</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>224.88</v>
+        <v>126.34</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>44.92</v>
+        <v>33.1</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>32.15</v>
+        <v>29.61</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>41.69</v>
+        <v>32.65</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="45">
@@ -4220,34 +4220,34 @@
         <v>-1.2</v>
       </c>
       <c r="Q46" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>-1.32</v>
       </c>
-      <c r="R46" s="3" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="S46" s="3" t="n">
-        <v>-1.72</v>
+        <v>-2.07</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.73</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-2.92</v>
+        <v>-1.64</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.43</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.62</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="47">
@@ -4472,31 +4472,31 @@
         <v>48.85</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>40.96</v>
+        <v>39.97</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>29.37</v>
+        <v>56.43</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>67.67</v>
+        <v>103.63</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>54.91</v>
+        <v>47.5</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>64.06</v>
+        <v>59.56</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>200</v>
+        <v>112.96</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>40.34</v>
+        <v>29.7</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>28.78</v>
+        <v>26.53</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>37.07</v>
+        <v>29.03</v>
       </c>
       <c r="Z49" s="3" t="n">
         <v>28.45</v>
@@ -4640,31 +4640,31 @@
         <v>-7.08</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.93</v>
+        <v>-7.9</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-8.73</v>
+        <v>-13.37</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-6.97</v>
+        <v>-5.98</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-7.82</v>
+        <v>-7.15</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-27.8</v>
+        <v>-15.02</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.2</v>
+        <v>-3.83</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-3.86</v>
+        <v>-3.56</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-5.41</v>
+        <v>-4.24</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>-4.18</v>
@@ -4892,31 +4892,31 @@
         <v>55</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>45.89</v>
+        <v>44.82</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>32.17</v>
+        <v>61.8</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>73.81</v>
+        <v>112.39</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>58.94</v>
+        <v>50.7</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>68.26000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>216.13</v>
+        <v>121.42</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>43.67</v>
+        <v>32.15</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>31.38</v>
+        <v>28.9</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>41.61</v>
+        <v>32.58</v>
       </c>
       <c r="Z54" s="3" t="n">
         <v>31.9</v>
@@ -5060,31 +5060,31 @@
         <v>-0.93</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.13</v>
+        <v>-2.53</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-2.58</v>
+        <v>-4.61</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.95</v>
+        <v>-2.79</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-3.62</v>
+        <v>-3.3</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-11.67</v>
+        <v>-6.56</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.88</v>
+        <v>-1.38</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.19</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.68</v>
       </c>
       <c r="Z56" s="3" t="n">
         <v>-0.73</v>
@@ -5312,34 +5312,34 @@
         <v>56.33</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>47</v>
+        <v>46.04</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>33.5</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>77.01000000000001</v>
+        <v>118.3</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>62.57</v>
+        <v>54.19</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>230.8</v>
+        <v>129.66</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>46.1</v>
+        <v>33.94</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>32.9</v>
+        <v>30.33</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>42.74</v>
+        <v>33.47</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>32.97</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="60">
@@ -5480,34 +5480,34 @@
         <v>0.39</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.62</v>
+        <v>1.3</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="U61" s="3" t="n">
         <v>1.02</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="62">
@@ -5732,31 +5732,31 @@
         <v>57.08</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>47.62</v>
+        <v>46.65</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>33.95</v>
+        <v>65.78</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>78.12</v>
+        <v>119.63</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>63.47</v>
+        <v>54.91</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>73.87</v>
+        <v>68.69</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>234.12</v>
+        <v>131.67</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>46.77</v>
+        <v>34.43</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>33.34</v>
+        <v>30.73</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>43.17</v>
+        <v>33.88</v>
       </c>
       <c r="Z64" s="3" t="n">
         <v>33.34</v>
@@ -5900,31 +5900,31 @@
         <v>1.14</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.64</v>
+        <v>1.45</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="U66" s="3" t="n">
         <v>1.99</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>6.32</v>
+        <v>3.69</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.22</v>
+        <v>0.9</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>0.7</v>
@@ -6152,31 +6152,31 @@
         <v>57.13</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>47.72</v>
+        <v>46.7</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>34.01</v>
+        <v>65.78</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>78.2</v>
+        <v>120</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>63.47</v>
+        <v>54.97</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>73.87</v>
+        <v>68.69</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>234.12</v>
+        <v>131.53</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>46.77</v>
+        <v>34.43</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>33.27</v>
+        <v>30.67</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>43.35</v>
+        <v>33.95</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>33.41</v>
@@ -6320,31 +6320,31 @@
         <v>1.2</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.71</v>
+        <v>1.45</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="U71" s="3" t="n">
         <v>1.99</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>6.32</v>
+        <v>3.55</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.22</v>
+        <v>0.9</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="Z71" s="3" t="n">
         <v>0.77</v>
@@ -6572,31 +6572,31 @@
         <v>55.55</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>46.39</v>
+        <v>45.4</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>33.07</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>76.02</v>
+        <v>116.65</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>61.76</v>
+        <v>53.43</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>71.88</v>
+        <v>66.84</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>227.57</v>
+        <v>127.98</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>45.5</v>
+        <v>33.5</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>32.41</v>
+        <v>29.88</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>42.06</v>
+        <v>32.94</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>32.38</v>
@@ -6740,31 +6740,31 @@
         <v>-0.39</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.36</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.32</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.33</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>-0.26</v>
@@ -6992,31 +6992,31 @@
         <v>55.93</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>46.86</v>
+        <v>45.77</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>33.3</v>
+        <v>64.33</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>117</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>61.89</v>
+        <v>53.48</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>71.88</v>
+        <v>66.7</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>227.8</v>
+        <v>127.98</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>45.55</v>
+        <v>33.53</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>32.64</v>
+        <v>30.09</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>42.48</v>
+        <v>33.27</v>
       </c>
       <c r="Z79" s="3" t="n">
         <v>32.64</v>
@@ -7412,31 +7412,31 @@
         <v>55.11</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>46.03</v>
+        <v>44.78</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>31.45</v>
+        <v>60.24</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>72</v>
+        <v>109.65</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>56.06</v>
+        <v>48.27</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>65.05</v>
+        <v>60.42</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>206.34</v>
+        <v>115.82</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>42.85</v>
+        <v>31.55</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>30.67</v>
+        <v>28.25</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>41.69</v>
+        <v>32.65</v>
       </c>
       <c r="Z84" s="3" t="n">
         <v>32.19</v>
@@ -7580,31 +7580,31 @@
         <v>-0.83</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.99</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.86</v>
+        <v>-4.1</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-4.39</v>
+        <v>-7.35</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-5.83</v>
+        <v>-5.21</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.83</v>
+        <v>-6.28</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-21.46</v>
+        <v>-12.16</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.7</v>
+        <v>-1.99</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.84</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.62</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>-0.45</v>
@@ -7832,31 +7832,31 @@
         <v>55.16</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.21</v>
+        <v>45.22</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>32.52</v>
+        <v>76.31</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>74.97</v>
+        <v>115.5</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>61.15</v>
+        <v>52.9</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>71.17</v>
+        <v>66.11</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>224.88</v>
+        <v>126.46</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.66</v>
+        <v>32.97</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>32.44</v>
+        <v>29.88</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>42.31</v>
+        <v>33.14</v>
       </c>
       <c r="Z89" s="3" t="n">
         <v>33.07</v>
@@ -8000,31 +8000,31 @@
         <v>-0.77</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.54</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.45</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.5</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.58</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.92</v>
+        <v>-1.52</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="Z91" s="3" t="n">
         <v>0.43</v>
@@ -8087,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="S92" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-15T14:08:42</t>
+          <t>CreatedAt: 2026-04-15T15:09:22</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -698,28 +698,28 @@
         <v>63.19</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>115.16</v>
+        <v>147.92</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>52.75</v>
+        <v>139.05</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>65.91</v>
+        <v>273.3</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>126.09</v>
+        <v>119.32</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>33.01</v>
+        <v>44.39</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>29.76</v>
+        <v>33.69</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>32.87</v>
+        <v>33.09</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.6</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="5">
@@ -866,28 +866,28 @@
         <v>-1.14</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.37</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1.39</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.79</v>
+        <v>-4.1</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.89</v>
+        <v>-1.91</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.71</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.13</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.23</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="7">
@@ -1118,28 +1118,28 @@
         <v>64.59</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>113.7</v>
+        <v>145.34</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>52.9</v>
+        <v>138.09</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>66.63</v>
+        <v>276.85</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>126.84</v>
+        <v>120.03</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>33.37</v>
+        <v>45.24</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>30.7</v>
+        <v>34.94</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>34.55</v>
+        <v>34.78</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>34.21</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="10">
@@ -1286,28 +1286,28 @@
         <v>0.26</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-3.3</v>
+        <v>-4.94</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.58</v>
+        <v>-2.35</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.2</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.17</v>
+        <v>0.14</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="12">
@@ -1538,28 +1538,28 @@
         <v>64.59</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>113.7</v>
+        <v>145.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>52.9</v>
+        <v>138.09</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>66.63</v>
+        <v>276.85</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>126.84</v>
+        <v>120.03</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>33.37</v>
+        <v>45.24</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>30.73</v>
+        <v>34.98</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>34.58</v>
+        <v>34.78</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>34.21</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="15">
@@ -1706,28 +1706,28 @@
         <v>0.26</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-3.3</v>
+        <v>-5.08</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.58</v>
+        <v>-2.35</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.17</v>
+        <v>0.14</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="17">
@@ -1958,28 +1958,28 @@
         <v>76</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>115.38</v>
+        <v>148.79</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>52.85</v>
+        <v>139.74</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>66.11</v>
+        <v>274.38</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>126.34</v>
+        <v>119.55</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>33.04</v>
+        <v>44.48</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>29.88</v>
+        <v>33.85</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>33.07</v>
+        <v>33.32</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.87</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="20">
@@ -2126,28 +2126,28 @@
         <v>-0.76</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.7</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.59</v>
+        <v>-3.02</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.67</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.21</v>
+        <v>0.03</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22">
@@ -2378,28 +2378,28 @@
         <v>63.57</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>115.38</v>
+        <v>148.79</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>52.85</v>
+        <v>139.74</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>66.11</v>
+        <v>274.38</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>126.34</v>
+        <v>119.55</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>33.04</v>
+        <v>44.48</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>29.88</v>
+        <v>33.85</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>33.07</v>
+        <v>33.32</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.87</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="25">
@@ -2546,28 +2546,28 @@
         <v>-0.76</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.7</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.59</v>
+        <v>-3.02</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.67</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.21</v>
+        <v>0.03</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="27">
@@ -2798,28 +2798,28 @@
         <v>76.31</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>115.5</v>
+        <v>149.68</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>52.9</v>
+        <v>140.3</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>66.11</v>
+        <v>275.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>126.46</v>
+        <v>119.55</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>32.97</v>
+        <v>44.53</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>29.88</v>
+        <v>33.96</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>33.14</v>
+        <v>33.45</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>33.07</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="30">
@@ -2966,28 +2966,28 @@
         <v>-0.45</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="T31" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>-0.58</v>
       </c>
-      <c r="U31" s="3" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
       <c r="X31" s="3" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.13</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
@@ -3218,28 +3218,28 @@
         <v>65.11</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>112.72</v>
+        <v>142.85</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>53.11</v>
+        <v>136.88</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>67.17</v>
+        <v>279.07</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>127.34</v>
+        <v>120.74</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>33.74</v>
+        <v>45.84</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>31.21</v>
+        <v>35.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>35.54</v>
+        <v>35.67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>35.02</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="35">
@@ -3386,28 +3386,28 @@
         <v>0.78</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-4.28</v>
+        <v>-7.43</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.37</v>
+        <v>-3.56</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.47</v>
+        <v>1.67</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.48</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="37">
@@ -3638,28 +3638,28 @@
         <v>63.19</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>115.16</v>
+        <v>147.92</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52.75</v>
+        <v>139.05</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>65.91</v>
+        <v>273.3</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>126.09</v>
+        <v>119.32</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>33.01</v>
+        <v>44.39</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>29.76</v>
+        <v>33.69</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>32.87</v>
+        <v>33.09</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.6</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="40">
@@ -3806,28 +3806,28 @@
         <v>-1.14</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.37</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1.39</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.79</v>
+        <v>-4.1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.89</v>
+        <v>-1.91</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.71</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.13</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.23</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="42">
@@ -4058,28 +4058,28 @@
         <v>63.01</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>114.93</v>
+        <v>145.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>52.8</v>
+        <v>137.14</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>65.98</v>
+        <v>273.57</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>126.34</v>
+        <v>119.67</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>33.1</v>
+        <v>44.48</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>29.61</v>
+        <v>33.35</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>32.65</v>
+        <v>32.73</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>32.28</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="45">
@@ -4226,28 +4226,28 @@
         <v>-1.32</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-2.07</v>
+        <v>-4.38</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.29</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.73</v>
+        <v>-3.83</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.56</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.62</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.59</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="47">
@@ -4478,28 +4478,28 @@
         <v>56.43</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>103.63</v>
+        <v>130</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>47.5</v>
+        <v>121.91</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>59.56</v>
+        <v>242.06</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>112.96</v>
+        <v>106.9</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>29.7</v>
+        <v>39.67</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>26.53</v>
+        <v>29.56</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>29.03</v>
+        <v>28.82</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>28.45</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="50">
@@ -4646,28 +4646,28 @@
         <v>-7.9</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-13.37</v>
+        <v>-20.28</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-5.98</v>
+        <v>-18.53</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-7.15</v>
+        <v>-35.34</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-15.02</v>
+        <v>-14.32</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-3.83</v>
+        <v>-5.43</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-3.56</v>
+        <v>-4.26</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-4.24</v>
+        <v>-4.5</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-4.18</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="52">
@@ -4898,28 +4898,28 @@
         <v>61.8</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>112.39</v>
+        <v>142.45</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>50.7</v>
+        <v>132.74</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>63.4</v>
+        <v>263.44</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>121.42</v>
+        <v>115.02</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>32.15</v>
+        <v>43.25</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>28.9</v>
+        <v>32.36</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>32.58</v>
+        <v>32.44</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>31.9</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="55">
@@ -5066,28 +5066,28 @@
         <v>-2.53</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-4.61</v>
+        <v>-7.83</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.79</v>
+        <v>-7.7</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-3.3</v>
+        <v>-13.96</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-6.56</v>
+        <v>-6.21</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.86</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.46</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.88</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="57">
@@ -5318,28 +5318,28 @@
         <v>64.84999999999999</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>118.3</v>
+        <v>149.53</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>54.19</v>
+        <v>140.16</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>67.72</v>
+        <v>281.05</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>129.66</v>
+        <v>122.82</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>33.94</v>
+        <v>45.65</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>30.33</v>
+        <v>34.09</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>33.47</v>
+        <v>33.52</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>32.93</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="60">
@@ -5486,28 +5486,28 @@
         <v>0.52</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.3</v>
+        <v>-0.75</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="62">
@@ -5738,28 +5738,28 @@
         <v>65.78</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>119.63</v>
+        <v>151.49</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>54.91</v>
+        <v>142</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>68.69</v>
+        <v>285.1</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>131.67</v>
+        <v>124.72</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>34.43</v>
+        <v>46.31</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>30.73</v>
+        <v>34.55</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>33.88</v>
+        <v>33.93</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>33.34</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="65">
@@ -5906,28 +5906,28 @@
         <v>1.45</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.63</v>
+        <v>1.21</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>1.99</v>
+        <v>7.7</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.69</v>
+        <v>3.49</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="Y66" s="3" t="n">
         <v>0.61</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="67">
@@ -6158,28 +6158,28 @@
         <v>65.78</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>120</v>
+        <v>150.13</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>54.97</v>
+        <v>141</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>68.69</v>
+        <v>284.8</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>131.53</v>
+        <v>124.59</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>34.43</v>
+        <v>46.26</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>30.67</v>
+        <v>34.51</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>33.95</v>
+        <v>34</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>33.41</v>
+        <v>30.89</v>
       </c>
     </row>
     <row r="70">
@@ -6326,28 +6326,28 @@
         <v>1.45</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3</v>
+        <v>-0.15</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>1.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>1.99</v>
+        <v>7.4</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="72">
@@ -6578,28 +6578,28 @@
         <v>64.01000000000001</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>116.65</v>
+        <v>147.34</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>53.43</v>
+        <v>138.09</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>66.84</v>
+        <v>276.85</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>127.98</v>
+        <v>121.1</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>33.5</v>
+        <v>45.01</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>29.88</v>
+        <v>33.59</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>32.94</v>
+        <v>32.99</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>32.38</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="75">
@@ -6746,28 +6746,28 @@
         <v>-0.32</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-0.35</v>
+        <v>-2.95</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>-0.05</v>
+        <v>-2.35</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.55</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>-0.33</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="77">
@@ -6998,28 +6998,28 @@
         <v>64.33</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>117</v>
+        <v>150.28</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>53.48</v>
+        <v>140.44</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>66.7</v>
+        <v>277.4</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>127.98</v>
+        <v>121.23</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>33.53</v>
+        <v>45.1</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>30.09</v>
+        <v>33.82</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>33.27</v>
+        <v>33.32</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>32.64</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="80">
@@ -7418,28 +7418,28 @@
         <v>60.24</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>109.65</v>
+        <v>135.88</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>48.27</v>
+        <v>126.52</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>60.42</v>
+        <v>250.81</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>115.82</v>
+        <v>109.81</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>31.55</v>
+        <v>42.43</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>28.25</v>
+        <v>31.64</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>32.65</v>
+        <v>32.57</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>32.19</v>
+        <v>29.62</v>
       </c>
     </row>
     <row r="85">
@@ -7586,28 +7586,28 @@
         <v>-4.1</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-7.35</v>
+        <v>-14.4</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-5.21</v>
+        <v>-13.92</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.28</v>
+        <v>-26.59</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-12.16</v>
+        <v>-11.42</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.67</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.18</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="87">
@@ -7838,28 +7838,28 @@
         <v>76.31</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>115.5</v>
+        <v>149.68</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>52.9</v>
+        <v>140.3</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>66.11</v>
+        <v>275.2</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>126.46</v>
+        <v>119.55</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>32.97</v>
+        <v>44.53</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>29.88</v>
+        <v>33.96</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>33.14</v>
+        <v>33.45</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>33.07</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="90">
@@ -8006,28 +8006,28 @@
         <v>-0.45</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="T91" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="W91" s="3" t="n">
         <v>-0.58</v>
       </c>
-      <c r="U91" s="3" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
       <c r="X91" s="3" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.13</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-19T15:09:23</t>
+          <t>CreatedAt: 2026-04-19T16:08:23</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -701,25 +701,25 @@
         <v>29.66</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>75</v>
+        <v>90.42</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>106.24</v>
+        <v>131.31</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>139.18</v>
+        <v>248.74</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>43.86</v>
+        <v>44.84</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>29.55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>42.19</v>
+        <v>42.53</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>30.34</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="5">
@@ -869,25 +869,25 @@
         <v>-0.59</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.45</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.91</v>
+        <v>-1.97</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.92</v>
+        <v>-5.72</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="7">
@@ -1121,25 +1121,25 @@
         <v>30.11</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>76.66</v>
+        <v>92.42</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>107.93</v>
+        <v>133.55</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>141.96</v>
+        <v>254.46</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>44.73</v>
+        <v>45.79</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>30.11</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>42.87</v>
+        <v>43.18</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>31.12</v>
+        <v>31.02</v>
       </c>
     </row>
     <row r="10">
@@ -1289,25 +1289,25 @@
         <v>-0.15</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.22</v>
+        <v>0.27</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="12">
@@ -1541,25 +1541,25 @@
         <v>3.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>76.66</v>
+        <v>11.72</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>13.4</v>
+        <v>16.84</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>141.96</v>
+        <v>254.46</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>44.73</v>
+        <v>5.63</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>3.5</v>
+        <v>30.11</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>5.63</v>
+        <v>43.18</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>31.12</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="15">
@@ -1625,22 +1625,22 @@
         <v>-27</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>-80.8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-94.54000000000001</v>
+        <v>-116.71</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>0</v>
+        <v>-40.16</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-26.61</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-37.24</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1709,25 +1709,25 @@
         <v>-0.15</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.22</v>
+        <v>0.27</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="17">
@@ -1961,25 +1961,25 @@
         <v>29.72</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>75.3</v>
+        <v>90.78</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>106.55</v>
+        <v>131.96</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>139.59</v>
+        <v>250.21</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>44.12</v>
+        <v>45.11</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>29.66</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>42.36</v>
+        <v>42.7</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>30.55</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="20">
@@ -2129,25 +2129,25 @@
         <v>-0.53</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.09</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.32</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.51</v>
+        <v>-4.25</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
@@ -2381,25 +2381,25 @@
         <v>29.72</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>75.3</v>
+        <v>90.78</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>106.55</v>
+        <v>131.96</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>139.59</v>
+        <v>250.21</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>44.12</v>
+        <v>45.11</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>29.66</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>42.36</v>
+        <v>42.7</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>30.55</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="25">
@@ -2549,25 +2549,25 @@
         <v>-0.53</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.09</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.32</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.51</v>
+        <v>-4.25</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="27">
@@ -2801,25 +2801,25 @@
         <v>29.81</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>75.67</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>107.08</v>
+        <v>132.75</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>140.28</v>
+        <v>251.94</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.42</v>
+        <v>45.47</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>29.81</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>42.48</v>
+        <v>42.83</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.77</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="30">
@@ -2969,25 +2969,25 @@
         <v>-0.45</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.55</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.07</v>
+        <v>-0.53</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.82</v>
+        <v>-2.52</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="32">
@@ -3221,25 +3221,25 @@
         <v>3.26</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>77.28</v>
+        <v>12.47</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>14.48</v>
+        <v>18.05</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>143.54</v>
+        <v>257.29</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>45.05</v>
+        <v>5.95</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>3.74</v>
+        <v>30.35</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>5.9</v>
+        <v>43.45</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>31.47</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="35">
@@ -3305,22 +3305,22 @@
         <v>-27</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>-80.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-94.54000000000001</v>
+        <v>-116.71</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>-40.16</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>-26.61</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-37.24</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3389,25 +3389,25 @@
         <v>0</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.87</v>
+        <v>1.48</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.44</v>
+        <v>2.83</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="37">
@@ -3641,25 +3641,25 @@
         <v>29.66</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>75</v>
+        <v>90.42</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>106.24</v>
+        <v>131.31</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>139.18</v>
+        <v>248.74</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>43.86</v>
+        <v>44.84</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>29.55</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>42.19</v>
+        <v>42.53</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>30.34</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="40">
@@ -3809,25 +3809,25 @@
         <v>-0.59</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.45</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.91</v>
+        <v>-1.97</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.92</v>
+        <v>-5.72</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="42">
@@ -4061,25 +4061,25 @@
         <v>30.41</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>76.89</v>
+        <v>92.42</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>108.8</v>
+        <v>133.55</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>142.53</v>
+        <v>254.72</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>44.78</v>
+        <v>45.79</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>30.14</v>
+        <v>30.17</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>42.65</v>
+        <v>42.88</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>30.52</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="45">
@@ -4229,25 +4229,25 @@
         <v>0.15</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="47">
@@ -4481,25 +4481,25 @@
         <v>27.53</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>83.52</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>97.43000000000001</v>
+        <v>119.86</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>127.56</v>
+        <v>228.22</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>40.48</v>
+        <v>41.54</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>26.95</v>
+        <v>27.12</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>37.94</v>
+        <v>38.35</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>26.95</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="50">
@@ -4649,25 +4649,25 @@
         <v>-2.73</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-6.67</v>
+        <v>-8.35</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-10.72</v>
+        <v>-13.42</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-14.54</v>
+        <v>-26.24</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-4.25</v>
+        <v>-4.2</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-3.07</v>
+        <v>-2.93</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-4.29</v>
+        <v>-4.14</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-3.42</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="52">
@@ -4901,25 +4901,25 @@
         <v>28.09</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>70.16</v>
+        <v>84.36</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>99.68000000000001</v>
+        <v>122.84</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>131.33</v>
+        <v>234.96</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>41.77</v>
+        <v>42.71</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>28.03</v>
+        <v>28.06</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>39.28</v>
+        <v>39.53</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>28.38</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="55">
@@ -5069,25 +5069,25 @@
         <v>-2.16</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-5.96</v>
+        <v>-7.51</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-8.470000000000001</v>
+        <v>-10.44</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-10.77</v>
+        <v>-19.5</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-2.97</v>
+        <v>-3.03</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>-1.99</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-2.95</v>
+        <v>-2.96</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-1.99</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="57">
@@ -5321,25 +5321,25 @@
         <v>31.39</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>79.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>111.96</v>
+        <v>137.12</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>146.65</v>
+        <v>262.33</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>46.07</v>
+        <v>47.11</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>31.04</v>
+        <v>31.07</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>43.81</v>
+        <v>44.03</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>31.37</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="60">
@@ -5489,25 +5489,25 @@
         <v>1.13</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>4.55</v>
+        <v>7.87</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="62">
@@ -5741,25 +5741,25 @@
         <v>31.88</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>80.64</v>
+        <v>96.91</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>113.84</v>
+        <v>139.56</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>148.95</v>
+        <v>266.45</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>46.84</v>
+        <v>47.85</v>
       </c>
       <c r="X64" s="3" t="n">
         <v>31.53</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>44.4</v>
+        <v>44.68</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>31.77</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="65">
@@ -5909,25 +5909,25 @@
         <v>1.63</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>4.52</v>
+        <v>5.04</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5.69</v>
+        <v>6.28</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>6.85</v>
+        <v>11.99</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>2.11</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="67">
@@ -6161,25 +6161,25 @@
         <v>32.26</v>
       </c>
       <c r="T69" s="3" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="U69" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="U69" s="3" t="n">
-        <v>114.69</v>
-      </c>
       <c r="V69" s="3" t="n">
-        <v>149.9</v>
+        <v>268.14</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>47.14</v>
+        <v>48.2</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>31.87</v>
+        <v>31.9</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>45.02</v>
+        <v>2000</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>32.24</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="70">
@@ -6329,25 +6329,25 @@
         <v>2</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>5.29</v>
+        <v>6.18</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>6.54</v>
+        <v>6.72</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>7.79</v>
+        <v>13.67</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>1.85</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="72">
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>58.58</v>
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="Y72" s="3" t="n">
-        <v>0</v>
+        <v>1954.75</v>
       </c>
       <c r="Z72" s="3" t="n">
         <v>0</v>
@@ -6581,25 +6581,25 @@
         <v>30.78</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>77.76000000000001</v>
+        <v>93.55</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>109.8</v>
+        <v>134.49</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>143.68</v>
+        <v>257.03</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>45.18</v>
+        <v>46.2</v>
       </c>
       <c r="X74" s="3" t="n">
         <v>30.41</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>42.83</v>
+        <v>43.05</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
     </row>
     <row r="75">
@@ -6749,25 +6749,25 @@
         <v>0.52</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.58</v>
+        <v>2.57</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="77">
@@ -7001,25 +7001,25 @@
         <v>30.26</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>76.12</v>
+        <v>91.87</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>108.15</v>
+        <v>133.28</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>142.1</v>
+        <v>254.46</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>44.73</v>
+        <v>45.74</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>30.02</v>
+        <v>30.05</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>42.23</v>
+        <v>42.49</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>30.37</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="80">
@@ -7421,25 +7421,25 @@
         <v>27.56</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>67.19</v>
+        <v>80.94</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>95.62</v>
+        <v>117.84</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>126.54</v>
+        <v>226.19</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>41.3</v>
+        <v>42.23</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>27.77</v>
+        <v>27.8</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>38.92</v>
+        <v>39.16</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>28.3</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="85">
@@ -7589,25 +7589,25 @@
         <v>-2.7</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-8.94</v>
+        <v>-10.93</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-12.53</v>
+        <v>-15.44</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-15.56</v>
+        <v>-28.27</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.43</v>
+        <v>-3.51</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-2.25</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3.33</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="87">
@@ -7841,25 +7841,25 @@
         <v>29.81</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>75.67</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>107.08</v>
+        <v>132.75</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>140.28</v>
+        <v>251.94</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.42</v>
+        <v>45.47</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>29.81</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>42.48</v>
+        <v>42.83</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>30.77</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="90">
@@ -8009,25 +8009,25 @@
         <v>-0.45</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.55</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.07</v>
+        <v>-0.53</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.82</v>
+        <v>-2.52</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-20T04:13:23</t>
+          <t>CreatedAt: 2026-04-20T05:13:22</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -668,58 +668,58 @@
         <v>70</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>102</v>
+        <v>138.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>41.48</v>
+        <v>46.59</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>29.78</v>
+        <v>30</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>29.64</v>
+        <v>29.63</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>29.2</v>
+        <v>29.22</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>22.96</v>
+        <v>23.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>23.01</v>
+        <v>23.9</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>23.05</v>
+        <v>25.66</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>29.04</v>
+        <v>29.01</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>32.72</v>
+        <v>31.59</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>29.99</v>
+        <v>29.63</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>36.56</v>
+        <v>36.09</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>47.8</v>
+        <v>47.65</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>75.75</v>
+        <v>104.1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>45.25</v>
+        <v>46.1</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>29.92</v>
+        <v>29.98</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>32.22</v>
+        <v>32.84</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>30.19</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="5">
@@ -836,58 +836,58 @@
         <v>-0.77</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-2.75</v>
+        <v>-3.45</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.75</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>-0.73</v>
       </c>
       <c r="N6" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>-0.67</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.64</v>
-      </c>
       <c r="P6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.67</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.82</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.77</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.33</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.5</v>
+        <v>-3.44</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.24</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="7">
@@ -1088,58 +1088,58 @@
         <v>71.63</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>102.5</v>
+        <v>139.05</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>42.31</v>
+        <v>47.62</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>30.19</v>
+        <v>30.45</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>29.93</v>
+        <v>29.92</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>29.63</v>
+        <v>29.69</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>22.92</v>
+        <v>23.88</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>22.94</v>
+        <v>23.81</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>22.96</v>
+        <v>25.56</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>29.1</v>
+        <v>29.07</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>33.2</v>
+        <v>32.13</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>30.47</v>
+        <v>30.1</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>36.96</v>
+        <v>36.52</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48.85</v>
+        <v>48.55</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>76.79000000000001</v>
+        <v>105.53</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>45.74</v>
+        <v>46.55</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>30.33</v>
+        <v>30.43</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>32.73</v>
+        <v>33.42</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>30.74</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="10">
@@ -1256,58 +1256,58 @@
         <v>0.86</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-2.25</v>
+        <v>-2.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.3</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
       <c r="M11" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-0.37</v>
-      </c>
       <c r="T11" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.44</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.46</v>
+        <v>-2.01</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="12">
@@ -1508,58 +1508,58 @@
         <v>71.63</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>102.5</v>
+        <v>103.63</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>42.31</v>
+        <v>47.62</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>30.19</v>
+        <v>30.45</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>7.44</v>
+        <v>29.95</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>29.63</v>
+        <v>29.69</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>7.23</v>
+        <v>23.88</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>7.25</v>
+        <v>10.04</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>22.96</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>29.1</v>
+        <v>7.1</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>2.55</v>
+        <v>35.59</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>34.4</v>
+        <v>33.92</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>6.37</v>
+        <v>6.32</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>49.73</v>
+        <v>5.7</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>91.67</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>6.94</v>
+        <v>34.57</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>3.94</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="15">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>-35.41</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1601,49 +1601,49 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>-22.49</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-15.68</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-15.69</v>
+        <v>-13.77</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
+        <v>-18.06</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0</v>
+        <v>-21.97</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-30.65</v>
+        <v>3.43</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>-30.59</v>
+        <v>-30.19</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0.88</v>
+        <v>-42.9</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>-66.90000000000001</v>
+        <v>-94.23999999999999</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>45.93</v>
+        <v>45.13</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-23.39</v>
+        <v>4.13</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-28.94</v>
+        <v>-29.57</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>-26.8</v>
+        <v>-28.29</v>
       </c>
     </row>
     <row r="16">
@@ -1676,58 +1676,58 @@
         <v>0.86</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-2.25</v>
+        <v>-2.5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.3</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-0.48</v>
       </c>
       <c r="M16" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="S16" s="3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="N16" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-0.37</v>
-      </c>
       <c r="T16" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.39</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.46</v>
+        <v>-2.01</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="17">
@@ -1928,58 +1928,58 @@
         <v>132.16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>102.4</v>
+        <v>138.91</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>41.73</v>
+        <v>46.87</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>29.86</v>
+        <v>30.06</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>29.25</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>22.96</v>
+        <v>23.9</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>23.01</v>
+        <v>23.9</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>23.07</v>
+        <v>25.69</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>32.78</v>
+        <v>31.69</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>30.05</v>
+        <v>29.69</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>36.52</v>
+        <v>36.09</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>47.75</v>
+        <v>47.6</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>75.68000000000001</v>
+        <v>104</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>45.12</v>
+        <v>45.92</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>29.92</v>
+        <v>29.98</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>32.25</v>
+        <v>32.87</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>30.31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -2096,58 +2096,58 @@
         <v>-0.42</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.64</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.84</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="M21" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="O21" s="3" t="n">
         <v>-0.67</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="O21" s="3" t="n">
+      <c r="P21" s="3" t="n">
         <v>-0.64</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.58</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>-0.64</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.73</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.71</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>-1.38</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.57</v>
+        <v>-3.54</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.42</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="22">
@@ -2348,58 +2348,58 @@
         <v>70.34999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>102.4</v>
+        <v>138.91</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>41.73</v>
+        <v>46.87</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>29.86</v>
+        <v>30.06</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>29.67</v>
+        <v>29.66</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>29.25</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>22.96</v>
+        <v>23.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>23.01</v>
+        <v>23.9</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>23.07</v>
+        <v>25.69</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>32.78</v>
+        <v>31.69</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>30.05</v>
+        <v>29.69</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>36.52</v>
+        <v>36.09</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>47.75</v>
+        <v>47.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>75.68000000000001</v>
+        <v>104</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>45.12</v>
+        <v>45.92</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>29.92</v>
+        <v>29.98</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>32.25</v>
+        <v>32.87</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>30.31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -2516,58 +2516,58 @@
         <v>-0.42</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.64</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.84</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="M26" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="O26" s="3" t="n">
         <v>-0.67</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="O26" s="3" t="n">
+      <c r="P26" s="3" t="n">
         <v>-0.64</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-0.58</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>-0.64</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.73</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.71</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>-1.38</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.57</v>
+        <v>-3.54</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.42</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="27">
@@ -2768,13 +2768,13 @@
         <v>132.58</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>103.21</v>
+        <v>140.15</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>42.02</v>
+        <v>47.24</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>29.95</v>
+        <v>30.15</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>29.72</v>
@@ -2783,43 +2783,43 @@
         <v>29.31</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>23.01</v>
+        <v>23.95</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>23.05</v>
+        <v>23.95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>23.12</v>
+        <v>25.74</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>29.24</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>32.91</v>
+        <v>31.78</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>30.14</v>
+        <v>29.81</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>36.49</v>
+        <v>36.02</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>47.71</v>
+        <v>47.56</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>44.94</v>
+        <v>45.7</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>29.89</v>
+        <v>29.98</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.29</v>
+        <v>32.93</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.49</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="30">
@@ -2936,58 +2936,58 @@
         <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.6</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.71</v>
       </c>
       <c r="M31" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>-0.62</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="P31" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.59</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0.5</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>-1.43</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.65</v>
+        <v>-3.64</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.65</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.51</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="32">
@@ -3188,58 +3188,58 @@
         <v>72.88</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>102.9</v>
+        <v>104.04</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>42.78</v>
+        <v>48.19</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>30.52</v>
+        <v>30.81</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>7.65</v>
+        <v>30.19</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>29.84</v>
+        <v>29.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>7.23</v>
+        <v>23.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>7.25</v>
+        <v>9.99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>22.92</v>
+        <v>7.48</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>29.19</v>
+        <v>7.21</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>2.68</v>
+        <v>35.75</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>34.55</v>
+        <v>34.04</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>6.66</v>
+        <v>6.58</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>50.32</v>
+        <v>6.24</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>10.88</v>
+        <v>12.76</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>92.34999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>7.28</v>
+        <v>34.9</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.31</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="35">
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>-35.41</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -3281,49 +3281,49 @@
         <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-22.49</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-15.68</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-15.69</v>
+        <v>-13.77</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>-18.06</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>-21.97</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-30.65</v>
+        <v>3.43</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>-30.59</v>
+        <v>-30.19</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>0.88</v>
+        <v>-42.9</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>-66.90000000000001</v>
+        <v>-94.23999999999999</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>45.93</v>
+        <v>45.13</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>-23.39</v>
+        <v>4.13</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-28.94</v>
+        <v>-29.57</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-26.8</v>
+        <v>-28.29</v>
       </c>
     </row>
     <row r="36">
@@ -3356,58 +3356,58 @@
         <v>2.11</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-1.85</v>
+        <v>-2.09</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.79</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>-0.55</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.53</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="37">
@@ -3608,58 +3608,58 @@
         <v>70</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>102</v>
+        <v>138.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>41.48</v>
+        <v>46.59</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>29.78</v>
+        <v>30</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>29.64</v>
+        <v>29.63</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>29.2</v>
+        <v>29.22</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>22.96</v>
+        <v>23.9</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>23.01</v>
+        <v>23.9</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>23.05</v>
+        <v>25.66</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.04</v>
+        <v>29.01</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>32.72</v>
+        <v>31.59</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>29.99</v>
+        <v>29.63</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>36.56</v>
+        <v>36.09</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>47.8</v>
+        <v>47.65</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>75.75</v>
+        <v>104.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>45.25</v>
+        <v>46.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>29.92</v>
+        <v>29.98</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>32.22</v>
+        <v>32.84</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>30.19</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="40">
@@ -3776,58 +3776,58 @@
         <v>-0.77</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-2.75</v>
+        <v>-3.45</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.75</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>-0.73</v>
       </c>
       <c r="N41" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="O41" s="3" t="n">
         <v>-0.67</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>-0.64</v>
-      </c>
       <c r="P41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.67</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.82</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.77</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.33</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.5</v>
+        <v>-3.44</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.24</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="42">
@@ -4028,58 +4028,58 @@
         <v>71.05</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>104.65</v>
+        <v>141.13</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>42.4</v>
+        <v>47.71</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>30.4</v>
+        <v>30.72</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>30.35</v>
+        <v>30.34</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>29.93</v>
+        <v>29.96</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>23.63</v>
+        <v>24.57</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>23.6</v>
+        <v>26.25</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>29.65</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>33.6</v>
+        <v>32.48</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.96</v>
+        <v>30.52</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>37.66</v>
+        <v>37.18</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>49.49</v>
+        <v>49.33</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>78.56</v>
+        <v>107.97</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>46.75</v>
+        <v>47.63</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>30.7</v>
+        <v>30.77</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>33.16</v>
+        <v>33.79</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>30.83</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="45">
@@ -4196,58 +4196,58 @@
         <v>0.28</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.42</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>-0.03</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.35</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="47">
@@ -4448,58 +4448,58 @@
         <v>64.98999999999999</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>95.23</v>
+        <v>128.8</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>38.86</v>
+        <v>43.81</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>27.92</v>
+        <v>28.24</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>27.57</v>
+        <v>27.59</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>27.08</v>
+        <v>27.13</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>21.36</v>
+        <v>22.26</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>21.29</v>
+        <v>22.13</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>21.29</v>
+        <v>23.72</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>26.79</v>
+        <v>26.82</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>30.55</v>
+        <v>29.52</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>28.11</v>
+        <v>27.69</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>34.31</v>
+        <v>33.9</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>45.08</v>
+        <v>44.98</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>71.84999999999999</v>
+        <v>98.38</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>42.51</v>
+        <v>43.31</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>27.76</v>
+        <v>27.77</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>29.83</v>
+        <v>30.31</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>27.8</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="50">
@@ -4616,10 +4616,10 @@
         <v>-5.78</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-9.52</v>
+        <v>-12.75</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-3.5</v>
+        <v>-3.9</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>-2.51</v>
@@ -4628,46 +4628,46 @@
         <v>-2.84</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-2.84</v>
+        <v>-2.82</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-2.26</v>
+        <v>-2.34</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.43</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.61</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.95</v>
+        <v>-2.92</v>
       </c>
       <c r="R51" s="3" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="T51" s="3" t="n">
         <v>-3.05</v>
       </c>
-      <c r="S51" s="3" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="T51" s="3" t="n">
-        <v>-3.12</v>
-      </c>
       <c r="U51" s="3" t="n">
-        <v>-4.06</v>
+        <v>-4</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-6.4</v>
+        <v>-9.15</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-3.91</v>
+        <v>-4.03</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-2.69</v>
+        <v>-2.72</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-3.1</v>
+        <v>-3.24</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.75</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="52">
@@ -4868,13 +4868,13 @@
         <v>65.77</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>97.36</v>
+        <v>131.43</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>41.52</v>
+        <v>46.64</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>29.43</v>
+        <v>29.66</v>
       </c>
       <c r="L54" s="3" t="n">
         <v>29.32</v>
@@ -4883,43 +4883,43 @@
         <v>28.89</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>22.74</v>
+        <v>23.67</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>22.83</v>
+        <v>23.72</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>22.87</v>
+        <v>25.46</v>
       </c>
       <c r="Q54" s="3" t="n">
         <v>28.71</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>32.28</v>
+        <v>31.17</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>29.59</v>
+        <v>29.2</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>36.31</v>
+        <v>35.84</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>47.29</v>
+        <v>47.15</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>74.88</v>
+        <v>102.8</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>45.07</v>
+        <v>45.88</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>29.71</v>
+        <v>29.78</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>31.79</v>
+        <v>32.39</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>29.75</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="55">
@@ -5036,58 +5036,58 @@
         <v>-5</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-7.4</v>
+        <v>-10.12</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.07</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-1.08</v>
+        <v>-1.11</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.07</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.85</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.87</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>-1.03</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.25</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.2</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.11</v>
       </c>
       <c r="U56" s="3" t="n">
         <v>-1.84</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-3.37</v>
+        <v>-4.73</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.47</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.71</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.17</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="57">
@@ -5288,58 +5288,58 @@
         <v>73.03</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>107.88</v>
+        <v>145.33</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>43.66</v>
+        <v>49.19</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>31.4</v>
+        <v>31.74</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>31.35</v>
+        <v>31.34</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>30.85</v>
+        <v>30.91</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>24.38</v>
+        <v>25.35</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>24.36</v>
+        <v>25.28</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>24.36</v>
+        <v>27.09</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>30.6</v>
+        <v>30.63</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>34.68</v>
+        <v>33.49</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>31.95</v>
+        <v>31.5</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>38.79</v>
+        <v>38.29</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>50.97</v>
+        <v>50.81</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>81</v>
+        <v>111.32</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>48.11</v>
+        <v>49.06</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>31.56</v>
+        <v>31.63</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>34.16</v>
+        <v>34.77</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>31.73</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="60">
@@ -5456,19 +5456,19 @@
         <v>2.26</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>3.13</v>
+        <v>3.78</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>0.76</v>
@@ -5477,37 +5477,37 @@
         <v>0.71</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>1.07</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.75</v>
+        <v>3.78</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="62">
@@ -5708,58 +5708,58 @@
         <v>74.09999999999999</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>109.69</v>
+        <v>147.75</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>44.4</v>
+        <v>49.96</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>31.9</v>
+        <v>32.24</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>31.84</v>
+        <v>31.87</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>31.34</v>
+        <v>31.37</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>24.74</v>
+        <v>25.75</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>24.71</v>
+        <v>25.65</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>24.71</v>
+        <v>27.48</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>31.08</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>35.22</v>
+        <v>34.01</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>32.49</v>
+        <v>32.04</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>39.41</v>
+        <v>38.94</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>51.78</v>
+        <v>51.62</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>82.37</v>
+        <v>113.19</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>48.87</v>
+        <v>49.83</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>32.06</v>
+        <v>32.1</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>34.63</v>
+        <v>35.29</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>32.16</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="65">
@@ -5876,13 +5876,13 @@
         <v>3.33</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>4.94</v>
+        <v>6.21</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="L66" s="3" t="n">
         <v>1.43</v>
@@ -5891,43 +5891,43 @@
         <v>1.41</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Q66" s="3" t="n">
         <v>1.34</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.12</v>
+        <v>5.66</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="67">
@@ -6128,58 +6128,58 @@
         <v>75.05</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>110.85</v>
+        <v>149</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>44.92</v>
+        <v>50.54</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>32.27</v>
+        <v>32.61</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>31.7</v>
+        <v>31.77</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>25.06</v>
+        <v>26.05</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>25.03</v>
+        <v>25.97</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>25.03</v>
+        <v>27.83</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>35.6</v>
+        <v>34.41</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>32.8</v>
+        <v>32.34</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>39.83</v>
+        <v>39.35</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>52.33</v>
+        <v>52.17</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>83.23999999999999</v>
+        <v>114.4</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>49.44</v>
+        <v>50.42</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>32.4</v>
+        <v>32.47</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>35.11</v>
+        <v>35.74</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>32.57</v>
+        <v>34.39</v>
       </c>
     </row>
     <row r="70">
@@ -6296,58 +6296,58 @@
         <v>4.28</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>6.1</v>
+        <v>7.45</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>4.99</v>
+        <v>6.86</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>2.18</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="72">
@@ -6548,58 +6548,58 @@
         <v>71.63</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>105.81</v>
+        <v>142.55</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>42.91</v>
+        <v>48.34</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>30.83</v>
+        <v>31.16</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>30.78</v>
+        <v>30.77</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>30.26</v>
+        <v>30.32</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>23.91</v>
+        <v>24.87</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>23.89</v>
+        <v>24.79</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>23.87</v>
+        <v>26.57</v>
       </c>
       <c r="Q74" s="3" t="n">
         <v>30.01</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>34.01</v>
+        <v>32.88</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>31.36</v>
+        <v>30.93</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>38.08</v>
+        <v>37.59</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>50.09</v>
+        <v>49.93</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>79.68000000000001</v>
+        <v>109.39</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>47.28</v>
+        <v>48.16</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>30.95</v>
+        <v>30.99</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>33.47</v>
+        <v>34.07</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>31.08</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="75">
@@ -6716,58 +6716,58 @@
         <v>0.86</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="O76" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P76" s="3" t="n">
         <v>0.24</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="Q76" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="S76" s="3" t="n">
         <v>0.53</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="X76" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -6968,58 +6968,58 @@
         <v>70.77</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>104.75</v>
+        <v>141.55</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>42.35</v>
+        <v>47.71</v>
       </c>
       <c r="K79" s="3" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="L79" s="3" t="n">
         <v>30.43</v>
       </c>
-      <c r="L79" s="3" t="n">
-        <v>30.41</v>
-      </c>
       <c r="M79" s="3" t="n">
-        <v>29.93</v>
+        <v>29.96</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>23.63</v>
+        <v>24.59</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>23.65</v>
+        <v>24.57</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>23.65</v>
+        <v>26.33</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>29.74</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>33.6</v>
+        <v>32.42</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>30.83</v>
+        <v>30.4</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>37.44</v>
+        <v>36.95</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>49.14</v>
+        <v>48.98</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>78.25</v>
+        <v>107.53</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>46.42</v>
+        <v>47.34</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>30.46</v>
+        <v>30.49</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>32.93</v>
+        <v>33.56</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>30.55</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="80">
@@ -7388,58 +7388,58 @@
         <v>63.64</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>94.2</v>
+        <v>126.95</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>37.88</v>
+        <v>42.68</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>26.95</v>
+        <v>27.26</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>28.1</v>
+        <v>28.15</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>27.53</v>
+        <v>27.58</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>21.68</v>
+        <v>22.56</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>21.78</v>
+        <v>22.62</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>21.74</v>
+        <v>24.2</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>27.36</v>
+        <v>27.38</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>30.97</v>
+        <v>28.46</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>27.19</v>
+        <v>26.79</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>33.37</v>
+        <v>32.94</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>44.11</v>
+        <v>43.97</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>70.75</v>
+        <v>97.23</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>41.82</v>
+        <v>44.71</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>28.62</v>
+        <v>28.66</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>30.81</v>
+        <v>31.39</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>28.63</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="85">
@@ -7556,58 +7556,58 @@
         <v>-7.13</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-10.55</v>
+        <v>-14.6</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-4.47</v>
+        <v>-5.04</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-3.48</v>
+        <v>-3.49</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.28</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-2.4</v>
+        <v>-2.37</v>
       </c>
       <c r="N86" s="3" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="O86" s="3" t="n">
         <v>-1.95</v>
       </c>
-      <c r="O86" s="3" t="n">
-        <v>-1.87</v>
-      </c>
       <c r="P86" s="3" t="n">
-        <v>-1.91</v>
+        <v>-2.13</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-2.38</v>
+        <v>-2.36</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-2.63</v>
+        <v>-3.96</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-3.64</v>
+        <v>-3.62</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-4.07</v>
+        <v>-4.02</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-5.03</v>
+        <v>-5.01</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-7.5</v>
+        <v>-10.31</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-4.6</v>
+        <v>-2.64</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-1.83</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.17</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="87">
@@ -7808,13 +7808,13 @@
         <v>132.58</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>103.21</v>
+        <v>140.15</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>42.02</v>
+        <v>47.24</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>29.95</v>
+        <v>30.15</v>
       </c>
       <c r="L89" s="3" t="n">
         <v>29.72</v>
@@ -7823,43 +7823,43 @@
         <v>29.31</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>23.01</v>
+        <v>23.95</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>23.05</v>
+        <v>23.95</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>23.12</v>
+        <v>25.74</v>
       </c>
       <c r="Q89" s="3" t="n">
         <v>29.24</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>32.91</v>
+        <v>31.78</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>30.14</v>
+        <v>29.81</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>36.49</v>
+        <v>36.02</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>47.71</v>
+        <v>47.56</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>44.94</v>
+        <v>45.7</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>29.89</v>
+        <v>29.98</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>32.29</v>
+        <v>32.93</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>30.49</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="90">
@@ -7976,58 +7976,58 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.4</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.6</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.71</v>
       </c>
       <c r="M91" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="O91" s="3" t="n">
         <v>-0.62</v>
       </c>
-      <c r="N91" s="3" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="P91" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.59</v>
       </c>
       <c r="Q91" s="3" t="n">
         <v>-0.5</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U91" s="3" t="n">
         <v>-1.43</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.65</v>
+        <v>-3.64</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.65</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.51</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-21T08:10:05</t>
+          <t>CreatedAt: 2026-04-21T09:09:52</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -680,46 +680,46 @@
         <v>26.15</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>54</v>
+        <v>54.81</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>5.7</v>
+        <v>16.52</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>14.36</v>
+        <v>6.26</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>14.58</v>
+        <v>14.35</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>22.57</v>
+        <v>14.68</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>22.52</v>
+        <v>19.77</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>45.56</v>
+        <v>45.66</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>46.2</v>
+        <v>45.84</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>39.31</v>
+        <v>45.74</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>30</v>
+        <v>30.03</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>30.23</v>
+        <v>30.09</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>30.12</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="5">
@@ -848,46 +848,46 @@
         <v>-0.05</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="N6" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="Q6" s="3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="R6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.28</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="7">
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>39.37</v>
+        <v>40.46</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0</v>
@@ -1100,46 +1100,46 @@
         <v>26.71</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>14.91</v>
+        <v>14.58</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>5.84</v>
+        <v>7.43</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>14.44</v>
+        <v>6.34</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>14.74</v>
+        <v>14.48</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>22.77</v>
+        <v>14.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>22.79</v>
+        <v>19.98</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>25.28</v>
+        <v>25.23</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>46.11</v>
+        <v>46.21</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>46.56</v>
+        <v>46.16</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>39.63</v>
+        <v>46.1</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>30.79</v>
+        <v>30.82</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>31.13</v>
+        <v>31.02</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>30.73</v>
+        <v>30.91</v>
       </c>
     </row>
     <row r="10">
@@ -1271,43 +1271,43 @@
         <v>0.22</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.24</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="12">
@@ -1520,46 +1520,46 @@
         <v>26.74</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>14.91</v>
+        <v>14.58</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>5.84</v>
+        <v>7.43</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>14.44</v>
+        <v>6.35</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>14.74</v>
+        <v>14.48</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.77</v>
+        <v>14.8</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>22.79</v>
+        <v>20</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>25.28</v>
+        <v>25.23</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>46.11</v>
+        <v>46.21</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>46.56</v>
+        <v>46.16</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>39.63</v>
+        <v>46.1</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>30.79</v>
+        <v>30.82</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>31.16</v>
+        <v>31.02</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>30.73</v>
+        <v>30.91</v>
       </c>
     </row>
     <row r="15">
@@ -1691,43 +1691,43 @@
         <v>0.22</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.22</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="17">
@@ -1940,46 +1940,46 @@
         <v>26.34</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>14.69</v>
+        <v>14.41</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>14.37</v>
+        <v>6.27</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.6</v>
+        <v>14.35</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>22.59</v>
+        <v>14.68</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>22.57</v>
+        <v>19.81</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>25.08</v>
+        <v>25.06</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>45.61</v>
+        <v>45.7</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>46.2</v>
+        <v>45.79</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>39.27</v>
+        <v>45.69</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>30.18</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>30.47</v>
+        <v>30.33</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>30.27</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="20">
@@ -2108,46 +2108,46 @@
         <v>0.13</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N21" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.11</v>
-      </c>
       <c r="Q21" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>-0.15</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>-0.09</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22">
@@ -2360,46 +2360,46 @@
         <v>26.34</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>54.06</v>
+        <v>54.87</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>5.7</v>
+        <v>16.53</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>14.37</v>
+        <v>6.27</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>14.6</v>
+        <v>14.35</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>22.59</v>
+        <v>14.68</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>22.57</v>
+        <v>19.81</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>25.08</v>
+        <v>25.06</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>45.61</v>
+        <v>45.7</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>46.2</v>
+        <v>45.79</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>39.27</v>
+        <v>45.69</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>30.18</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>30.47</v>
+        <v>30.33</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>30.27</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="25">
@@ -2528,46 +2528,46 @@
         <v>0.13</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N26" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-0.11</v>
-      </c>
       <c r="Q26" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>-0.15</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>-0.09</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27">
@@ -2612,10 +2612,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>39.37</v>
+        <v>40.46</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0</v>
@@ -2780,46 +2780,46 @@
         <v>26.55</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.76</v>
+        <v>14.47</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>5.71</v>
+        <v>7.32</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>14.37</v>
+        <v>6.27</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>14.61</v>
+        <v>14.34</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>22.65</v>
+        <v>14.71</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>22.63</v>
+        <v>19.84</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>25.08</v>
+        <v>25.06</v>
       </c>
       <c r="U29" s="3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>45.65</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>39.27</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>30.36</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>30.75</v>
+        <v>30.64</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.48</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="30">
@@ -2948,46 +2948,46 @@
         <v>0.35</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.55</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.78</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="32">
@@ -3200,46 +3200,46 @@
         <v>26.88</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>15.01</v>
+        <v>14.64</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>5.92</v>
+        <v>7.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>14.43</v>
+        <v>6.38</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>14.82</v>
+        <v>14.56</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>22.77</v>
+        <v>14.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>22.81</v>
+        <v>20.02</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25.43</v>
+        <v>25.38</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>46.48</v>
+        <v>46.58</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>46.94</v>
+        <v>46.52</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>39.98</v>
+        <v>46.52</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>31.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>31.52</v>
+        <v>31.4</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>31.07</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="35">
@@ -3368,46 +3368,46 @@
         <v>0.67</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="R36" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="S36" s="3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>-0.14</v>
-      </c>
       <c r="T36" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="W36" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3620,46 +3620,46 @@
         <v>26.15</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>54</v>
+        <v>54.81</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>5.7</v>
+        <v>16.52</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.36</v>
+        <v>6.26</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>14.58</v>
+        <v>14.35</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>22.57</v>
+        <v>14.68</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.52</v>
+        <v>19.77</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>45.56</v>
+        <v>45.66</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>46.2</v>
+        <v>45.84</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>39.31</v>
+        <v>45.74</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>30</v>
+        <v>30.03</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>30.23</v>
+        <v>30.09</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>30.12</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="40">
@@ -3788,46 +3788,46 @@
         <v>-0.05</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="N41" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="n">
         <v>-0.05</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="P41" s="3" t="n">
+      <c r="Q41" s="3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="R41" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.28</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="42">
@@ -3872,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>39.37</v>
+        <v>40.46</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>0</v>
@@ -4040,46 +4040,46 @@
         <v>26.39</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>14.82</v>
+        <v>14.47</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>5.79</v>
+        <v>7.37</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>14.59</v>
+        <v>6.36</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>14.85</v>
+        <v>14.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>23.16</v>
+        <v>15.07</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>23.13</v>
+        <v>20.38</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>25.74</v>
+        <v>25.69</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>46.76</v>
+        <v>46.86</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>47.36</v>
+        <v>46.99</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>40.23</v>
+        <v>46.8</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>30.51</v>
+        <v>30.57</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>30.56</v>
+        <v>30.45</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>30.73</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="45">
@@ -4208,43 +4208,43 @@
         <v>0.18</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>0.4</v>
@@ -4460,46 +4460,46 @@
         <v>24.04</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>13.46</v>
+        <v>13.17</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>5.19</v>
+        <v>6.57</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>13.03</v>
+        <v>5.68</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>13.32</v>
+        <v>13.08</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>20.88</v>
+        <v>13.6</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>20.94</v>
+        <v>18.45</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>23.34</v>
+        <v>23.29</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>42.46</v>
+        <v>42.59</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>36.41</v>
+        <v>42.4</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>27.54</v>
+        <v>27.6</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>27.34</v>
+        <v>27.24</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>27.55</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="50">
@@ -4628,46 +4628,46 @@
         <v>-2.16</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-1.23</v>
+        <v>-1.2</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.46</v>
+        <v>-0.64</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.4</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.09</v>
+        <v>-1.36</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-2.01</v>
+        <v>-1.77</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.15</v>
+        <v>-2.12</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.65</v>
+        <v>-3.66</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.84</v>
+        <v>-3.77</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-3.46</v>
+        <v>-4.03</v>
       </c>
       <c r="X51" s="3" t="n">
         <v>-2.73</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-3.01</v>
+        <v>-2.97</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.78</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="52">
@@ -4880,46 +4880,46 @@
         <v>26.21</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>14.69</v>
+        <v>14.37</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>5.74</v>
+        <v>7.28</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="P54" s="3" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="Q54" s="3" t="n">
         <v>14.48</v>
       </c>
-      <c r="Q54" s="3" t="n">
-        <v>14.74</v>
-      </c>
       <c r="R54" s="3" t="n">
-        <v>22.97</v>
+        <v>14.96</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>22.95</v>
+        <v>20.22</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>25.48</v>
+        <v>25.41</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>46.11</v>
+        <v>46.25</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>46.94</v>
+        <v>46.57</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>39.86</v>
+        <v>46.42</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>30.27</v>
+        <v>30.33</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>30.35</v>
+        <v>30.21</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>30.33</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="55">
@@ -5300,46 +5300,46 @@
         <v>27.16</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>15.25</v>
+        <v>14.89</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>5.96</v>
+        <v>7.57</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>15.01</v>
+        <v>6.54</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>15.28</v>
+        <v>15.02</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>23.85</v>
+        <v>15.54</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>23.86</v>
+        <v>21.02</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>26.49</v>
+        <v>26.44</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>48.03</v>
+        <v>48.18</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>48.74</v>
+        <v>48.36</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>41.4</v>
+        <v>48.16</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>31.37</v>
+        <v>31.43</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>31.39</v>
+        <v>31.24</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>31.66</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="60">
@@ -5468,43 +5468,43 @@
         <v>0.95</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.53</v>
+        <v>0.23</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>1.33</v>
@@ -5720,46 +5720,46 @@
         <v>27.56</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>15.46</v>
+        <v>15.09</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>6.05</v>
+        <v>7.68</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>15.23</v>
+        <v>6.64</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>15.52</v>
+        <v>15.25</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>24.23</v>
+        <v>15.78</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>24.23</v>
+        <v>21.38</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>26.91</v>
+        <v>26.83</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>48.84</v>
+        <v>49</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>49.56</v>
+        <v>49.13</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>42.05</v>
+        <v>48.92</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>31.79</v>
+        <v>31.86</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>31.81</v>
+        <v>31.63</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>32.09</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="65">
@@ -5888,43 +5888,43 @@
         <v>1.35</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.26</v>
+        <v>0.82</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U66" s="3" t="n">
         <v>2.74</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>1.53</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>1.77</v>
@@ -6140,46 +6140,46 @@
         <v>27.88</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>15.66</v>
+        <v>15.28</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>6.12</v>
+        <v>7.78</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>15.41</v>
+        <v>6.72</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>15.7</v>
+        <v>15.42</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>24.52</v>
+        <v>15.95</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>24.52</v>
+        <v>21.6</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>27.2</v>
+        <v>27.14</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>49.31</v>
+        <v>49.47</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>50.04</v>
+        <v>49.65</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>42.5</v>
+        <v>49.49</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>32.2</v>
+        <v>32.26</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>32.22</v>
+        <v>32.07</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>32.51</v>
+        <v>32.63</v>
       </c>
     </row>
     <row r="70">
@@ -6308,46 +6308,46 @@
         <v>1.67</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.92</v>
+        <v>0.4</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.54</v>
+        <v>0.99</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.63</v>
+        <v>3.07</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="72">
@@ -6560,46 +6560,46 @@
         <v>26.69</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>14.99</v>
+        <v>14.63</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>5.85</v>
+        <v>7.43</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>14.72</v>
+        <v>6.41</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>15</v>
+        <v>14.73</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>23.44</v>
+        <v>15.27</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>23.47</v>
+        <v>20.68</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>26.06</v>
+        <v>25.98</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>47.24</v>
+        <v>47.39</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>47.99</v>
+        <v>47.57</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>40.72</v>
+        <v>47.42</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>30.82</v>
+        <v>30.88</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>30.78</v>
+        <v>30.67</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>31.07</v>
+        <v>31.16</v>
       </c>
     </row>
     <row r="75">
@@ -6728,43 +6728,43 @@
         <v>0.48</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="Q76" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>0.57</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>0.75</v>
@@ -6980,46 +6980,46 @@
         <v>26.21</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>14.69</v>
+        <v>14.37</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>5.74</v>
+        <v>7.28</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="P79" s="3" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="Q79" s="3" t="n">
         <v>14.48</v>
       </c>
-      <c r="Q79" s="3" t="n">
-        <v>14.74</v>
-      </c>
       <c r="R79" s="3" t="n">
-        <v>22.97</v>
+        <v>14.96</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>22.95</v>
+        <v>20.22</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>25.48</v>
+        <v>25.41</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>46.11</v>
+        <v>46.25</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>46.94</v>
+        <v>46.57</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>39.86</v>
+        <v>46.42</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>30.27</v>
+        <v>30.33</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>30.35</v>
+        <v>30.21</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>30.33</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="80">
@@ -7400,46 +7400,46 @@
         <v>23.25</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>13</v>
+        <v>12.66</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>5.4</v>
+        <v>6.38</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>12.65</v>
+        <v>5.59</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>12.84</v>
+        <v>12.61</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>20.17</v>
+        <v>13.14</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>20.2</v>
+        <v>17.78</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>22.67</v>
+        <v>22.62</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>41.46</v>
+        <v>41.59</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>42.4</v>
+        <v>42.07</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>36.94</v>
+        <v>43.71</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>28.88</v>
+        <v>28.94</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>27.22</v>
+        <v>27.12</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>27.22</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="85">
@@ -7568,46 +7568,46 @@
         <v>-2.95</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.71</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.89</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="P86" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="R86" s="3" t="n">
         <v>-1.83</v>
       </c>
-      <c r="Q86" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>-2.8</v>
-      </c>
       <c r="S86" s="3" t="n">
-        <v>-2.75</v>
+        <v>-2.44</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-2.81</v>
+        <v>-2.78</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-4.64</v>
+        <v>-4.66</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-4.54</v>
+        <v>-4.5</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.92</v>
+        <v>-2.71</v>
       </c>
       <c r="X86" s="3" t="n">
         <v>-1.39</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.09</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-3.1</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="87">
@@ -7820,46 +7820,46 @@
         <v>26.55</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>14.76</v>
+        <v>14.47</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>5.71</v>
+        <v>7.32</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>14.37</v>
+        <v>6.27</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>14.61</v>
+        <v>14.34</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>22.65</v>
+        <v>14.71</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>22.63</v>
+        <v>19.84</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>25.08</v>
+        <v>25.06</v>
       </c>
       <c r="U89" s="3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="W89" s="3" t="n">
         <v>45.65</v>
-      </c>
-      <c r="V89" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="W89" s="3" t="n">
-        <v>39.27</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>30.36</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>30.75</v>
+        <v>30.64</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>30.48</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="90">
@@ -7988,46 +7988,46 @@
         <v>0.35</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.55</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.78</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="92">

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-22T06:11:13</t>
+          <t>CreatedAt: 2026-04-22T07:10:32</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -674,10 +674,10 @@
         <v>45.13</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>40.92</v>
+        <v>42.55</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>30.36</v>
+        <v>30.26</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>325</v>
@@ -686,10 +686,10 @@
         <v>23.69</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>19.82</v>
+        <v>19.68</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>325</v>
@@ -698,22 +698,22 @@
         <v>30.05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>185.85</v>
+        <v>31.83</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>38</v>
+        <v>34.01</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>47.73</v>
+        <v>46.19</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>214.79</v>
+        <v>210.28</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>46.28</v>
+        <v>46.19</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>50.1</v>
+        <v>44.58</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>25.15</v>
@@ -842,10 +842,10 @@
         <v>-0.27</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.09</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>-0.06</v>
@@ -854,34 +854,34 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="O6" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="Q6" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.51</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.01</v>
+        <v>-2.94</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0.13</v>
@@ -944,13 +944,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>298.99</v>
+        <v>301.17</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>152.48</v>
+        <v>0</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>0</v>
@@ -1094,10 +1094,10 @@
         <v>45.95</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>41.8</v>
+        <v>43.55</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>30.39</v>
@@ -1106,34 +1106,34 @@
         <v>23.95</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>20.1</v>
+        <v>19.96</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>26.6</v>
+        <v>24.37</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>30.48</v>
+        <v>30.51</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>33.84</v>
+        <v>32.38</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>38.5</v>
+        <v>34.53</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48.25</v>
+        <v>46.75</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>217.14</v>
+        <v>212.58</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>47.26</v>
+        <v>47.17</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>51.33</v>
+        <v>45.72</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>25.9</v>
@@ -1262,10 +1262,10 @@
         <v>0.55</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>0.64</v>
@@ -1274,34 +1274,34 @@
         <v>0.19</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>0.88</v>
@@ -1514,49 +1514,49 @@
         <v>14.31</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>41.8</v>
+        <v>13.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>30.42</v>
+        <v>6.86</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>23.95</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>20.1</v>
+        <v>19.96</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>26.6</v>
+        <v>24.37</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>30.48</v>
+        <v>30.51</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>33.84</v>
+        <v>32.38</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>38.5</v>
+        <v>11.43</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>13.52</v>
+        <v>13.38</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>217.14</v>
+        <v>36.91</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>13.14</v>
+        <v>47.17</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>7.47</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>25.9</v>
+        <v>6.67</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>32.08</v>
@@ -1598,13 +1598,13 @@
         <v>-31.64</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>-29.85</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>-20.15</v>
+        <v>-19.94</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0</v>
+        <v>-23.55</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
@@ -1625,22 +1625,22 @@
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>-23.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-34.73</v>
+        <v>-33.36</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>-175.67</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-34.13</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-42.73</v>
+        <v>-38.25</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>-19.26</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
         <v>0.55</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0.67</v>
@@ -1694,37 +1694,37 @@
         <v>0.19</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1.12</v>
@@ -1934,52 +1934,52 @@
         <v>45.22</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>41.13</v>
+        <v>42.8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>30.54</v>
+        <v>30.45</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>29.9</v>
+        <v>29.87</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>23.83</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>19.92</v>
+        <v>19.88</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>19.94</v>
+        <v>19.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>26.25</v>
+        <v>24.05</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>30.26</v>
+        <v>30.29</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>33.51</v>
+        <v>32.02</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>38.11</v>
+        <v>34.15</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>47.77</v>
+        <v>46.28</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>215</v>
+        <v>210.48</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>46.37</v>
+        <v>46.28</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>50.4</v>
+        <v>44.89</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>25.43</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>31.36</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="20">
@@ -2102,52 +2102,52 @@
         <v>-0.18</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="O21" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>0.08</v>
-      </c>
       <c r="Q21" s="3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.74</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.46</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="22">
@@ -2354,52 +2354,52 @@
         <v>45.22</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>41.13</v>
+        <v>42.8</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>30.54</v>
+        <v>30.45</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>325.21</v>
+        <v>325.18</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>23.83</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>19.92</v>
+        <v>19.88</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>19.94</v>
+        <v>19.8</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>325.24</v>
+        <v>325.22</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>30.26</v>
+        <v>30.29</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>185.98</v>
+        <v>32.02</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>38.11</v>
+        <v>34.15</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>47.77</v>
+        <v>46.28</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>215</v>
+        <v>210.48</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>46.37</v>
+        <v>46.28</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>50.4</v>
+        <v>44.89</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>25.43</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>31.36</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="25">
@@ -2522,52 +2522,52 @@
         <v>-0.18</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>0.08</v>
-      </c>
       <c r="Q26" s="3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.74</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.46</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="27">
@@ -2624,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>298.99</v>
+        <v>301.17</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>152.48</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>0</v>
@@ -2774,10 +2774,10 @@
         <v>45.26</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>41.38</v>
+        <v>43.06</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>30.69</v>
+        <v>30.66</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>30.11</v>
@@ -2786,34 +2786,34 @@
         <v>24</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>20.04</v>
+        <v>20.02</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>20.08</v>
+        <v>19.94</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>26.49</v>
+        <v>24.27</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>30.54</v>
+        <v>30.57</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.67</v>
+        <v>32.28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>38.23</v>
+        <v>34.32</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>47.87</v>
+        <v>46.38</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>215.21</v>
+        <v>210.69</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>46.42</v>
+        <v>46.37</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>50.81</v>
+        <v>45.26</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>25.8</v>
@@ -2942,10 +2942,10 @@
         <v>-0.14</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>0.36</v>
@@ -2954,34 +2954,34 @@
         <v>0.24</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.14</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.32</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.58</v>
+        <v>-2.53</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.37</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>0.77</v>
@@ -3194,13 +3194,13 @@
         <v>14.73</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>42.14</v>
+        <v>14.06</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>11.14</v>
+        <v>11.26</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>30.67</v>
+        <v>7.11</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>24.1</v>
@@ -3209,34 +3209,34 @@
         <v>19.94</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>20.14</v>
+        <v>20.02</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26.82</v>
+        <v>24.57</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>30.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>34.02</v>
+        <v>32.48</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>38.77</v>
+        <v>11.64</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>14.01</v>
+        <v>13.81</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>219.33</v>
+        <v>39.05</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>13.81</v>
+        <v>47.85</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>9.19</v>
+        <v>7.94</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>26.12</v>
+        <v>6.86</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>32.41</v>
@@ -3278,13 +3278,13 @@
         <v>-31.64</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>-29.85</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-20.15</v>
+        <v>-19.94</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>-23.55</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>-23.1</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-34.73</v>
+        <v>-33.36</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>-175.67</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-34.13</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>-42.73</v>
+        <v>-38.25</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>-19.26</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0.97</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.92</v>
@@ -3380,28 +3380,28 @@
         <v>0.28</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0.55</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="T36" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>0.44</v>
-      </c>
       <c r="V36" s="3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>1.1</v>
@@ -3614,10 +3614,10 @@
         <v>45.13</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>40.92</v>
+        <v>42.55</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>30.36</v>
+        <v>30.26</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>325</v>
@@ -3626,10 +3626,10 @@
         <v>23.69</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>19.82</v>
+        <v>19.68</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>325</v>
@@ -3638,22 +3638,22 @@
         <v>30.05</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>185.85</v>
+        <v>31.83</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>38</v>
+        <v>34.01</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>47.73</v>
+        <v>46.19</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>214.79</v>
+        <v>210.28</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>46.28</v>
+        <v>46.19</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>50.1</v>
+        <v>44.58</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>25.15</v>
@@ -3782,10 +3782,10 @@
         <v>-0.27</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.09</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>-0.06</v>
@@ -3794,34 +3794,34 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="O41" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="P41" s="3" t="n">
         <v>-0.06</v>
       </c>
-      <c r="P41" s="3" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="Q41" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.51</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.01</v>
+        <v>-2.94</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>0.13</v>
@@ -3884,13 +3884,13 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>298.99</v>
+        <v>301.17</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>152.48</v>
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>45.85</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>41.42</v>
+        <v>42.98</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>30.72</v>
+        <v>30.57</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>29.93</v>
@@ -4046,34 +4046,34 @@
         <v>23.88</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>19.98</v>
+        <v>19.96</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>19.98</v>
+        <v>19.86</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>26.09</v>
+        <v>23.93</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>30.26</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>33.81</v>
+        <v>32.12</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>38.77</v>
+        <v>34.6</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>48.84</v>
+        <v>47.22</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>219.55</v>
+        <v>215.16</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>47.41</v>
+        <v>47.27</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>50.66</v>
+        <v>45.07</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>25.28</v>
@@ -4202,10 +4202,10 @@
         <v>0.46</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>0.18</v>
@@ -4214,34 +4214,34 @@
         <v>0.12</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.12</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0.52</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>0.25</v>
@@ -4454,10 +4454,10 @@
         <v>41.69</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>37.08</v>
+        <v>38.87</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>27.41</v>
+        <v>27.25</v>
       </c>
       <c r="M49" s="3" t="n">
         <v>26.54</v>
@@ -4469,37 +4469,37 @@
         <v>17.65</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>17.59</v>
+        <v>17.48</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>23.01</v>
+        <v>21.08</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>30.1</v>
+        <v>28.59</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>34.7</v>
+        <v>30.96</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>43.99</v>
+        <v>42.53</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>195.86</v>
+        <v>191.92</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>42.31</v>
+        <v>42.19</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>45.09</v>
+        <v>40.12</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>22.22</v>
+        <v>22.24</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>27.71</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="50">
@@ -4622,10 +4622,10 @@
         <v>-3.71</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-4</v>
+        <v>-3.85</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.11</v>
       </c>
       <c r="M51" s="3" t="n">
         <v>-3.21</v>
@@ -4637,37 +4637,37 @@
         <v>-2.21</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.26</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.92</v>
+        <v>-2.68</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>-3.24</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.2</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.61</v>
+        <v>-3.22</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-4.31</v>
+        <v>-4.17</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-21.94</v>
+        <v>-21.3</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-4.57</v>
+        <v>-4.56</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.01</v>
+        <v>-4.41</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-2.8</v>
+        <v>-2.78</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-3.24</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="52">
@@ -4874,10 +4874,10 @@
         <v>45.4</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>41.09</v>
+        <v>42.72</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>30.54</v>
+        <v>30.35</v>
       </c>
       <c r="M54" s="3" t="n">
         <v>29.75</v>
@@ -4889,31 +4889,31 @@
         <v>19.86</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>19.86</v>
+        <v>19.74</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.93</v>
+        <v>23.76</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>30.05</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>33.47</v>
+        <v>31.8</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>38.3</v>
+        <v>34.18</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>217.79</v>
+        <v>213.22</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>46.88</v>
+        <v>46.75</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>50.1</v>
+        <v>44.53</v>
       </c>
       <c r="Y54" s="3" t="n">
         <v>25.02</v>
@@ -5294,46 +5294,46 @@
         <v>47.09</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>42.53</v>
+        <v>44.13</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>31.58</v>
+        <v>31.39</v>
       </c>
       <c r="M59" s="3" t="n">
         <v>30.73</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>24.57</v>
+        <v>24.55</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>20.54</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>20.54</v>
+        <v>20.41</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>26.79</v>
+        <v>24.55</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>31.07</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>34.76</v>
+        <v>32.98</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>39.82</v>
+        <v>35.49</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>50.15</v>
+        <v>48.49</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>225.46</v>
+        <v>221.18</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>48.74</v>
+        <v>48.59</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>51.97</v>
+        <v>46.19</v>
       </c>
       <c r="Y59" s="3" t="n">
         <v>25.9</v>
@@ -5462,7 +5462,7 @@
         <v>1.7</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>1.04</v>
@@ -5471,37 +5471,37 @@
         <v>0.98</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>1.03</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>7.67</v>
+        <v>7.96</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>1.85</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Y61" s="3" t="n">
         <v>0.88</v>
@@ -5714,10 +5714,10 @@
         <v>47.79</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>43.11</v>
+        <v>44.78</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>32.01</v>
+        <v>31.82</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>31.15</v>
@@ -5729,37 +5729,37 @@
         <v>20.82</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>20.82</v>
+        <v>20.69</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>27.12</v>
+        <v>24.88</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>31.53</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>35.27</v>
+        <v>33.51</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>40.41</v>
+        <v>36.05</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>50.95</v>
+        <v>49.26</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>228.3</v>
+        <v>224.21</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>49.46</v>
+        <v>49.26</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>52.68</v>
+        <v>46.83</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>26.2</v>
+        <v>26.23</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>32.59</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="65">
@@ -5882,10 +5882,10 @@
         <v>2.39</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M66" s="3" t="n">
         <v>1.4</v>
@@ -5897,34 +5897,34 @@
         <v>0.96</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>1.48</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>10.5</v>
+        <v>10.99</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>1.63</v>
@@ -6134,10 +6134,10 @@
         <v>48.35</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>43.66</v>
+        <v>45.35</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>32.42</v>
+        <v>32.26</v>
       </c>
       <c r="M69" s="3" t="n">
         <v>31.58</v>
@@ -6146,34 +6146,34 @@
         <v>25.22</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>21.11</v>
+        <v>21.1</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>21.1</v>
+        <v>20.96</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>27.5</v>
+        <v>25.2</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>31.93</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>35.69</v>
+        <v>33.86</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>40.92</v>
+        <v>36.44</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>51.49</v>
+        <v>49.79</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>230.96</v>
+        <v>226.83</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>50.04</v>
+        <v>49.89</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>53.35</v>
+        <v>47.42</v>
       </c>
       <c r="Y69" s="3" t="n">
         <v>26.59</v>
@@ -6302,10 +6302,10 @@
         <v>2.95</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>1.83</v>
@@ -6317,31 +6317,31 @@
         <v>1.25</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>1.88</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>13.16</v>
+        <v>13.61</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>1.57</v>
@@ -6554,10 +6554,10 @@
         <v>46.23</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>41.71</v>
+        <v>43.33</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>30.94</v>
+        <v>30.79</v>
       </c>
       <c r="M74" s="3" t="n">
         <v>30.11</v>
@@ -6566,34 +6566,34 @@
         <v>24.05</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>20.12</v>
+        <v>20.1</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>20.1</v>
+        <v>19.98</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>26.22</v>
+        <v>24.03</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>30.44</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>34.09</v>
+        <v>32.35</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>39.09</v>
+        <v>34.81</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>49.23</v>
+        <v>47.6</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>221.11</v>
+        <v>216.91</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>47.79</v>
+        <v>47.65</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>50.91</v>
+        <v>45.26</v>
       </c>
       <c r="Y74" s="3" t="n">
         <v>25.35</v>
@@ -6722,10 +6722,10 @@
         <v>0.83</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="M76" s="3" t="n">
         <v>0.36</v>
@@ -6734,34 +6734,34 @@
         <v>0.29</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="P76" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.32</v>
+        <v>3.69</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0.91</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>0.33</v>
@@ -6974,10 +6974,10 @@
         <v>45.4</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>41.09</v>
+        <v>42.72</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>30.54</v>
+        <v>30.35</v>
       </c>
       <c r="M79" s="3" t="n">
         <v>29.75</v>
@@ -6989,31 +6989,31 @@
         <v>19.86</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>19.86</v>
+        <v>19.74</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>25.93</v>
+        <v>23.76</v>
       </c>
       <c r="R79" s="3" t="n">
         <v>30.05</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>33.47</v>
+        <v>31.8</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>38.3</v>
+        <v>34.18</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>217.79</v>
+        <v>213.22</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>46.88</v>
+        <v>46.75</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>50.1</v>
+        <v>44.53</v>
       </c>
       <c r="Y79" s="3" t="n">
         <v>25.02</v>
@@ -7394,46 +7394,46 @@
         <v>40.07</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>35.85</v>
+        <v>37.28</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>26.3</v>
+        <v>26.12</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>25.54</v>
+        <v>25.49</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>20.45</v>
+        <v>20.41</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>17.06</v>
+        <v>17.03</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>17.08</v>
+        <v>16.93</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>22.37</v>
+        <v>20.43</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>25.93</v>
+        <v>25.55</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>28.81</v>
+        <v>26.99</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>33.31</v>
+        <v>29.34</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>42.55</v>
+        <v>40.57</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>192.57</v>
+        <v>186.22</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>43.09</v>
+        <v>41.85</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>44.49</v>
+        <v>38.96</v>
       </c>
       <c r="Y84" s="3" t="n">
         <v>21.99</v>
@@ -7562,46 +7562,46 @@
         <v>-5.33</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-5.23</v>
+        <v>-5.44</v>
       </c>
       <c r="L86" s="3" t="n">
         <v>-4.23</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-4.21</v>
+        <v>-4.26</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3.35</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-2.8</v>
+        <v>-2.83</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-2.78</v>
+        <v>-2.81</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-3.56</v>
+        <v>-3.33</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-4.12</v>
+        <v>-4.5</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-4.67</v>
+        <v>-4.8</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-5</v>
+        <v>-4.84</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-5.74</v>
+        <v>-6.13</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-25.23</v>
+        <v>-27</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.79</v>
+        <v>-4.9</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-5.61</v>
+        <v>-5.57</v>
       </c>
       <c r="Y86" s="3" t="n">
         <v>-3.03</v>
@@ -7814,10 +7814,10 @@
         <v>45.26</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>41.38</v>
+        <v>43.06</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>30.69</v>
+        <v>30.66</v>
       </c>
       <c r="M89" s="3" t="n">
         <v>30.11</v>
@@ -7826,34 +7826,34 @@
         <v>24</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>20.04</v>
+        <v>20.02</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>20.08</v>
+        <v>19.94</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>26.49</v>
+        <v>24.27</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>30.54</v>
+        <v>30.57</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>33.67</v>
+        <v>32.28</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>38.23</v>
+        <v>34.32</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>47.87</v>
+        <v>46.38</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>215.21</v>
+        <v>210.69</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>46.42</v>
+        <v>46.37</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>50.81</v>
+        <v>45.26</v>
       </c>
       <c r="Y89" s="3" t="n">
         <v>25.8</v>
@@ -7982,10 +7982,10 @@
         <v>-0.14</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="M91" s="3" t="n">
         <v>0.36</v>
@@ -7994,34 +7994,34 @@
         <v>0.24</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.14</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.32</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.58</v>
+        <v>-2.53</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.37</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="Y91" s="3" t="n">
         <v>0.77</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-24T10:09:44</t>
+          <t>CreatedAt: 2026-04-24T11:09:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -686,40 +686,40 @@
         <v>24.26</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>28.22</v>
+        <v>23.23</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>14.3</v>
+        <v>31.4</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>19.61</v>
+        <v>14.32</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>24.81</v>
+        <v>24.76</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>34.3</v>
+        <v>33.51</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>46.87</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>54.06</v>
+        <v>53.47</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>59.41</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>46.54</v>
+        <v>44.97</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>34.15</v>
+        <v>38.48</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>29.84</v>
+        <v>29.34</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>31.36</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="5">
@@ -854,40 +854,40 @@
         <v>0.19</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.31</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.36</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.13</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="7">
@@ -1106,40 +1106,40 @@
         <v>23.93</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>27.98</v>
+        <v>23.93</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>14.24</v>
+        <v>31.25</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>19.4</v>
+        <v>14.15</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.69</v>
+        <v>24.56</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>34.13</v>
+        <v>33.28</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>46.54</v>
+        <v>46.49</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>54.06</v>
+        <v>53.41</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>72.52</v>
+        <v>59.53</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>47.01</v>
+        <v>45.33</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>34.4</v>
+        <v>38.75</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>30.37</v>
+        <v>29.82</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.14</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="10">
@@ -1274,40 +1274,40 @@
         <v>-0.14</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="V11" s="3" t="n">
-        <v>-1.67</v>
+        <v>-0.24</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="12">
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.02</v>
+        <v>0.98</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -1526,40 +1526,40 @@
         <v>23.93</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>27.98</v>
+        <v>23.93</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>14.24</v>
+        <v>31.22</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>19.4</v>
+        <v>14.14</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>24.69</v>
+        <v>24.56</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>34.13</v>
+        <v>33.28</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>46.54</v>
+        <v>46.49</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>54.06</v>
+        <v>53.41</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>72.52</v>
+        <v>59.53</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>47.01</v>
+        <v>45.33</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>34.4</v>
+        <v>38.75</v>
       </c>
       <c r="Y14" s="3" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="Z14" s="3" t="n">
         <v>30.4</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>32.14</v>
       </c>
     </row>
     <row r="15">
@@ -1694,40 +1694,40 @@
         <v>-0.14</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-0.16</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.37</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.37</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.67</v>
+        <v>-0.24</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="17">
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.02</v>
+        <v>0.98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
@@ -1946,40 +1946,40 @@
         <v>73.45999999999999</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>101.04</v>
+        <v>101.08</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>14.36</v>
+        <v>100.79</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>19.67</v>
+        <v>14.35</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>24.91</v>
+        <v>24.83</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>34.43</v>
+        <v>33.61</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>46.87</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>55.5</v>
+        <v>55.43</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>126.02</v>
+        <v>135.5</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>46.97</v>
+        <v>45.32</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>34.26</v>
+        <v>38.63</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.92</v>
+        <v>81.37</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>31.61</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="20">
@@ -2114,19 +2114,19 @@
         <v>0.24</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>0</v>
@@ -2135,19 +2135,19 @@
         <v>-0.05</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.36</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="22">
@@ -2198,10 +2198,10 @@
         <v>49.15</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>72.77</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>69.36</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
@@ -2216,19 +2216,19 @@
         <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>52.42</v>
+        <v>76.09</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>51.9</v>
+        <v>51.88</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>0</v>
@@ -2366,40 +2366,40 @@
         <v>24.31</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>28.28</v>
+        <v>23.25</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>14.36</v>
+        <v>31.43</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>19.67</v>
+        <v>14.35</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>24.91</v>
+        <v>24.83</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>34.43</v>
+        <v>33.61</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>46.87</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>54.06</v>
+        <v>53.52</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>59.41</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>46.63</v>
+        <v>45.05</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>34.26</v>
+        <v>38.63</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>30.03</v>
+        <v>29.49</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>31.61</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="25">
@@ -2534,19 +2534,19 @@
         <v>0.24</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>0</v>
@@ -2555,19 +2555,19 @@
         <v>-0.05</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.36</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="27">
@@ -2789,37 +2789,37 @@
         <v>101.1</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>14.42</v>
+        <v>100.76</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>19.73</v>
+        <v>14.39</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>25.01</v>
+        <v>24.94</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>34.57</v>
+        <v>33.75</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>46.82</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>55.45</v>
+        <v>55.38</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>125.95</v>
+        <v>135.44</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>47.02</v>
+        <v>45.41</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>34.33</v>
+        <v>38.79</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>82.08</v>
+        <v>81.55</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>31.88</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="30">
@@ -2954,19 +2954,19 @@
         <v>0.27</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="P31" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>0.18</v>
-      </c>
       <c r="R31" s="3" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>-0.05</v>
@@ -2975,19 +2975,19 @@
         <v>-0.11</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.42</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="32">
@@ -3038,10 +3038,10 @@
         <v>49.15</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>72.77</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>69.36</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>0</v>
@@ -3056,19 +3056,19 @@
         <v>0</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>52.42</v>
+        <v>76.09</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>51.9</v>
+        <v>51.88</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>0</v>
@@ -3206,40 +3206,40 @@
         <v>27.89</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>29.17</v>
+        <v>29.27</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>14.1</v>
+        <v>39.16</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>19.17</v>
+        <v>13.99</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>24.49</v>
+        <v>24.35</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>33.86</v>
+        <v>32.99</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>46.27</v>
+        <v>46.17</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>53.95</v>
+        <v>53.31</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>59.59</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>47.1</v>
+        <v>45.42</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>34.4</v>
+        <v>38.67</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>30.52</v>
+        <v>29.95</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>32.38</v>
+        <v>30.59</v>
       </c>
     </row>
     <row r="35">
@@ -3374,40 +3374,40 @@
         <v>-0.45</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.34</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.31</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.41</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.66</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.27</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-2.09</v>
+        <v>-0.18</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="37">
@@ -3458,10 +3458,10 @@
         <v>4.27</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1.53</v>
+        <v>6.59</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>8.42</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>0</v>
@@ -3626,40 +3626,40 @@
         <v>24.26</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>28.22</v>
+        <v>23.23</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.3</v>
+        <v>31.4</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>19.61</v>
+        <v>14.32</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>24.81</v>
+        <v>24.76</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>34.3</v>
+        <v>33.51</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>46.87</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>54.06</v>
+        <v>53.47</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>59.41</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>46.54</v>
+        <v>44.97</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>34.15</v>
+        <v>38.48</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>29.84</v>
+        <v>29.34</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>31.36</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="40">
@@ -3794,40 +3794,40 @@
         <v>0.19</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.31</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.36</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.13</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="42">
@@ -4046,40 +4046,40 @@
         <v>24.05</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>27.91</v>
+        <v>23.05</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>14.26</v>
+        <v>31.05</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>19.51</v>
+        <v>14.27</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>24.76</v>
+        <v>24.74</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>34.47</v>
+        <v>33.68</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>47.05</v>
+        <v>47.1</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>54.44</v>
+        <v>53.95</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>74.48999999999999</v>
+        <v>60.07</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>46.87</v>
+        <v>45.24</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>34.19</v>
+        <v>38.48</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>29.69</v>
+        <v>29.19</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>31.01</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="45">
@@ -4214,13 +4214,13 @@
         <v>-0.02</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>-0.02</v>
@@ -4229,10 +4229,10 @@
         <v>0.03</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.3</v>
@@ -4241,13 +4241,13 @@
         <v>0.14</v>
       </c>
       <c r="X46" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
         <v>0.24</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>0.19</v>
       </c>
     </row>
     <row r="47">
@@ -4466,40 +4466,40 @@
         <v>21.08</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>24.23</v>
+        <v>20.09</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>12.44</v>
+        <v>27</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>16.97</v>
+        <v>12.41</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>21.67</v>
+        <v>21.64</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>30.31</v>
+        <v>29.62</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>41.44</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>48.06</v>
+        <v>47.58</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>65.89</v>
+        <v>53.08</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>41.39</v>
+        <v>39.95</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>29.89</v>
+        <v>33.6</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>25.75</v>
+        <v>25.32</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>26.99</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="50">
@@ -4634,40 +4634,40 @@
         <v>-2.99</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-3.73</v>
+        <v>-2.95</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.88</v>
+        <v>-4.08</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.58</v>
+        <v>-1.89</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>-3.12</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-4.12</v>
+        <v>-4.03</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>-5.43</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-6.06</v>
+        <v>-6</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.69</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-5.34</v>
+        <v>-5.15</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-4.06</v>
+        <v>-4.6</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-3.73</v>
+        <v>-3.67</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-3.83</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="52">
@@ -4886,40 +4886,40 @@
         <v>24.07</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>27.97</v>
+        <v>23.05</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>14.31</v>
+        <v>31.08</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>19.55</v>
+        <v>14.29</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>24.79</v>
+        <v>24.76</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>34.43</v>
+        <v>33.65</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>46.87</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>54.12</v>
+        <v>53.57</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>74.19</v>
+        <v>59.77</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>46.73</v>
+        <v>45.1</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.95</v>
+        <v>38.21</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>29.49</v>
+        <v>28.99</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>30.82</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="55">
@@ -5306,40 +5306,40 @@
         <v>24.74</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>28.68</v>
+        <v>23.71</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>14.68</v>
+        <v>31.88</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>20.09</v>
+        <v>14.69</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>25.47</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>35.46</v>
+        <v>34.69</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>48.27</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>55.85</v>
+        <v>55.29</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>76.48999999999999</v>
+        <v>61.62</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>48.12</v>
+        <v>46.45</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>35.07</v>
+        <v>39.43</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>30.43</v>
+        <v>29.89</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>31.68</v>
+        <v>30.09</v>
       </c>
     </row>
     <row r="60">
@@ -5474,40 +5474,40 @@
         <v>0.67</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.37</v>
+        <v>0.8</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="62">
@@ -5726,40 +5726,40 @@
         <v>25.02</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>29.04</v>
+        <v>23.98</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>14.86</v>
+        <v>32.28</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>20.37</v>
+        <v>14.87</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>25.79</v>
+        <v>25.77</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>35.98</v>
+        <v>35.16</v>
       </c>
       <c r="T64" s="3" t="n">
         <v>48.92</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>56.67</v>
+        <v>56.1</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>77.61</v>
+        <v>62.52</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>48.78</v>
+        <v>47.08</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>35.55</v>
+        <v>39.97</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>30.81</v>
+        <v>30.26</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>32.04</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="65">
@@ -5894,37 +5894,37 @@
         <v>0.95</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.55</v>
+        <v>1.19</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>2.05</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.41</v>
+        <v>2.75</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>1.22</v>
@@ -6146,40 +6146,40 @@
         <v>27.85</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>30.01</v>
+        <v>24.95</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>15.1</v>
+        <v>145</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>20.64</v>
+        <v>15.09</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>26.17</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>36.44</v>
+        <v>35.64</v>
       </c>
       <c r="T69" s="3" t="n">
         <v>49.59</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>57.33</v>
+        <v>56.75</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>78.51000000000001</v>
+        <v>63.31</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>49.39</v>
+        <v>47.67</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>36</v>
+        <v>40.47</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>31.24</v>
+        <v>30.68</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>32.38</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="70">
@@ -6314,16 +6314,16 @@
         <v>1.35</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.79</v>
+        <v>1.67</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.09</v>
+        <v>0.8</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S71" s="3" t="n">
         <v>2</v>
@@ -6332,22 +6332,22 @@
         <v>2.73</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>4.32</v>
+        <v>3.55</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="72">
@@ -6398,10 +6398,10 @@
         <v>2.43</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>0</v>
+        <v>112.25</v>
       </c>
       <c r="Q72" s="3" t="n">
         <v>0</v>
@@ -6566,40 +6566,40 @@
         <v>24.17</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>28.02</v>
+        <v>23.16</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>14.36</v>
+        <v>31.14</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>19.65</v>
+        <v>14.35</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>24.91</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>34.75</v>
+        <v>33.95</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>47.24</v>
+        <v>47.29</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>54.66</v>
+        <v>54.17</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>74.94</v>
+        <v>60.37</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>47.1</v>
+        <v>45.46</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.29</v>
+        <v>38.55</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>29.72</v>
+        <v>29.19</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>30.92</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="75">
@@ -6734,40 +6734,40 @@
         <v>0.1</v>
       </c>
       <c r="O76" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P76" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="P76" s="3" t="n">
-        <v>0.04</v>
-      </c>
       <c r="Q76" s="3" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="S76" s="3" t="n">
         <v>0.31</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="77">
@@ -6986,40 +6986,40 @@
         <v>24.07</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>27.97</v>
+        <v>23.05</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>14.31</v>
+        <v>31.08</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>19.55</v>
+        <v>14.29</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>24.79</v>
+        <v>24.76</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>34.43</v>
+        <v>33.65</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>46.87</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>54.12</v>
+        <v>53.57</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>74.19</v>
+        <v>59.77</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>46.73</v>
+        <v>45.1</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>33.95</v>
+        <v>38.21</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>29.49</v>
+        <v>28.99</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>30.82</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="80">
@@ -7406,40 +7406,40 @@
         <v>20.28</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>23.48</v>
+        <v>19.37</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>12.02</v>
+        <v>26.14</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>16.48</v>
+        <v>12.04</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>20.9</v>
+        <v>20.89</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>29.33</v>
+        <v>28.66</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>40.37</v>
+        <v>40.33</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>47.1</v>
+        <v>46.59</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>52.24</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>40.88</v>
+        <v>39.42</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>29.55</v>
+        <v>33.22</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>25.8</v>
+        <v>25.32</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>26.73</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="85">
@@ -7574,40 +7574,40 @@
         <v>-3.79</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-4.48</v>
+        <v>-3.68</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-2.3</v>
+        <v>-4.94</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-3.07</v>
+        <v>-2.25</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-3.89</v>
+        <v>-3.87</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-5.1</v>
+        <v>-4.99</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-6.5</v>
+        <v>-6.53</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-7.02</v>
+        <v>-6.99</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-9.34</v>
+        <v>-7.52</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-5.85</v>
+        <v>-5.68</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-4.4</v>
+        <v>-4.98</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-3.69</v>
+        <v>-3.67</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-4.09</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="87">
@@ -7829,37 +7829,37 @@
         <v>101.1</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>14.42</v>
+        <v>100.73</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>19.73</v>
+        <v>14.39</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>25.01</v>
+        <v>24.94</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>34.57</v>
+        <v>33.75</v>
       </c>
       <c r="T89" s="3" t="n">
         <v>46.82</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>55.45</v>
+        <v>55.38</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>125.95</v>
+        <v>135.44</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>47.02</v>
+        <v>45.41</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>34.33</v>
+        <v>38.79</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>82.08</v>
+        <v>81.55</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>31.88</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="90">
@@ -7994,19 +7994,19 @@
         <v>0.27</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="P91" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Q91" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q91" s="3" t="n">
-        <v>0.18</v>
-      </c>
       <c r="R91" s="3" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="T91" s="3" t="n">
         <v>-0.05</v>
@@ -8015,19 +8015,19 @@
         <v>-0.11</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.42</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="92">
@@ -8078,10 +8078,10 @@
         <v>49.15</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>72.77</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>69.36</v>
       </c>
       <c r="Q92" s="3" t="n">
         <v>0</v>
@@ -8096,19 +8096,19 @@
         <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>52.42</v>
+        <v>76.09</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="X92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>51.9</v>
+        <v>51.88</v>
       </c>
       <c r="Z92" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-25T21:12:46</t>
+          <t>CreatedAt: 2026-04-26T00:12:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>29.18</v>
+        <v>66.73</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>29.4</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>28</v>
+        <v>77.06</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>30</v>
+        <v>-68.97</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>37.52</v>
+        <v>32.48</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>41.68</v>
+        <v>33.73</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>32.13</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>28.71</v>
+        <v>34.69</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.39</v>
+        <v>14.44</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>7.81</v>
+        <v>25.22</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>21.45</v>
+        <v>40.08</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>16</v>
+        <v>29.22</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>7.7</v>
+        <v>14.45</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>14.45</v>
+        <v>7.66</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>17.57</v>
+        <v>27.52</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>39.69</v>
+        <v>33.53</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>28.92</v>
+        <v>14.42</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>29.06</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>44.24</v>
+        <v>41.94</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>54.41</v>
+        <v>44.33</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>29.35</v>
+        <v>29.32</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>40.7</v>
+        <v>34.34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>29.34</v>
+        <v>28.79</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>14.56</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="5">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.22</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.06</v>
@@ -845,49 +845,49 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.26</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>-0.78</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.96</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.11</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.52</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="7">
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>29.75</v>
+        <v>66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>29.73</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>28.34</v>
+        <v>76.33</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>30.4</v>
+        <v>-68.62</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>37.67</v>
+        <v>32.68</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>42.02</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>31.97</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>28.48</v>
+        <v>34.38</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>14.42</v>
+        <v>14.47</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>7.9</v>
+        <v>25.45</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>21.86</v>
+        <v>40.77</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>16.28</v>
+        <v>29.61</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>7.79</v>
+        <v>14.65</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>14.73</v>
+        <v>7.81</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>17.78</v>
+        <v>27.86</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>39.57</v>
+        <v>33.57</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>28.55</v>
+        <v>14.27</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>28.73</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>43.94</v>
+        <v>41.61</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>54.09</v>
+        <v>44.07</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>29.41</v>
+        <v>29.38</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>40.42</v>
+        <v>34.24</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>29.22</v>
+        <v>28.65</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>14.68</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="10">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.48</v>
+        <v>-1.25</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.57</v>
+        <v>-0.66</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.3</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.41</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>-1.12</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.29</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.37</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>-0.62</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.62</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>-0.29</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>29.75</v>
+        <v>66</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>29.73</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>28.34</v>
+        <v>76.27</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>30.4</v>
+        <v>-68.62</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>37.67</v>
+        <v>32.68</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>42.02</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>31.97</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>28.48</v>
+        <v>34.38</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>14.42</v>
+        <v>14.47</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>7.9</v>
+        <v>25.45</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>21.86</v>
+        <v>40.77</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16.28</v>
+        <v>29.61</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>7.79</v>
+        <v>14.65</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>14.73</v>
+        <v>7.81</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>17.78</v>
+        <v>27.86</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>39.57</v>
+        <v>33.57</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28.55</v>
+        <v>14.27</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>28.73</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>43.9</v>
+        <v>41.57</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>54.09</v>
+        <v>44.07</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>29.41</v>
+        <v>29.38</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>40.42</v>
+        <v>34.21</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>29.22</v>
+        <v>28.65</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>14.68</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="15">
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.48</v>
+        <v>-1.25</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.57</v>
+        <v>-0.72</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.41</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>-1.12</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.33</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.37</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>-0.62</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.65</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>-0.29</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="17">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>29.42</v>
+        <v>66.8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>29.64</v>
+        <v>67.41</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>28.26</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>30.27</v>
+        <v>-68.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>37.78</v>
+        <v>32.71</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>41.98</v>
+        <v>33.97</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>32.39</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>28.94</v>
+        <v>34.94</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.55</v>
+        <v>14.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>7.91</v>
+        <v>25.53</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>21.71</v>
+        <v>40.53</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>16.18</v>
+        <v>29.49</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>7.79</v>
+        <v>14.61</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>14.63</v>
+        <v>7.75</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>17.76</v>
+        <v>27.83</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>39.96</v>
+        <v>33.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>29.06</v>
+        <v>14.51</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>29.15</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>44.5</v>
+        <v>42.14</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>54.68</v>
+        <v>44.55</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>29.53</v>
+        <v>29.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>40.86</v>
+        <v>34.48</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>29.48</v>
+        <v>28.97</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.68</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="20">
@@ -2078,55 +2078,55 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.48</v>
+        <v>0.18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0.32</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0.16</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.19</v>
-      </c>
       <c r="Q21" s="3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.17</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>-0.7</v>
@@ -2135,16 +2135,16 @@
         <v>-0.76</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.89</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>-0.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.19</v>
@@ -2246,16 +2246,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>29.42</v>
+        <v>66.8</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>29.64</v>
+        <v>67.41</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>28.26</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>30.27</v>
+        <v>-68.7</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>37.78</v>
+        <v>32.71</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>41.98</v>
+        <v>33.97</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>32.39</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>28.94</v>
+        <v>34.94</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>14.55</v>
+        <v>14.6</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>7.91</v>
+        <v>25.53</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>21.71</v>
+        <v>40.53</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>16.18</v>
+        <v>29.49</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>7.79</v>
+        <v>14.61</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>14.63</v>
+        <v>7.75</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>17.76</v>
+        <v>27.83</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>39.96</v>
+        <v>33.8</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.06</v>
+        <v>14.51</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>29.15</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>44.5</v>
+        <v>42.14</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>54.68</v>
+        <v>44.55</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>29.53</v>
+        <v>29.5</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>40.86</v>
+        <v>34.48</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>29.48</v>
+        <v>28.97</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>14.68</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="25">
@@ -2498,55 +2498,55 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.48</v>
+        <v>0.18</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.32</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.16</v>
       </c>
       <c r="L26" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.19</v>
-      </c>
       <c r="Q26" s="3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.17</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>-0.7</v>
@@ -2555,16 +2555,16 @@
         <v>-0.76</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.89</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>-0.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0.19</v>
@@ -2666,16 +2666,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>29.63</v>
+        <v>66.73</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.82</v>
+        <v>67.41</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>28.49</v>
+        <v>77.3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.52</v>
+        <v>-68.47</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>38.01</v>
+        <v>32.91</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>42.23</v>
+        <v>34.21</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>32.65</v>
+        <v>32.68</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>29.2</v>
+        <v>35.22</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>14.73</v>
+        <v>14.78</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.01</v>
+        <v>25.84</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>22</v>
+        <v>40.98</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.34</v>
+        <v>29.73</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>7.88</v>
+        <v>14.8</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>14.81</v>
+        <v>7.85</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>18</v>
+        <v>28.17</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>40.28</v>
+        <v>34.07</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>29.23</v>
+        <v>14.62</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.29</v>
+        <v>29.26</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>44.77</v>
+        <v>42.39</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>55</v>
+        <v>44.81</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>29.73</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>41.03</v>
+        <v>34.68</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>29.69</v>
+        <v>29.17</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>14.82</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="30">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.51</v>
+        <v>0.13</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.71</v>
+        <v>0.31</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0.76</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.34</v>
       </c>
       <c r="L31" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="Q31" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z31" s="3" t="n">
         <v>0.31</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>0.33</v>
       </c>
     </row>
     <row r="32">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>29.87</v>
+        <v>65.94</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>29.76</v>
+        <v>65.7</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>28.34</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>30.4</v>
+        <v>-68.62</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>37.59</v>
+        <v>32.58</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>42.02</v>
+        <v>34</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>31.71</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>28.11</v>
+        <v>33.91</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>14.25</v>
+        <v>14.3</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>7.88</v>
+        <v>25.32</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.84</v>
+        <v>40.69</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>16.24</v>
+        <v>29.58</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>7.78</v>
+        <v>14.63</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>14.72</v>
+        <v>7.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>17.73</v>
+        <v>27.77</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>39.18</v>
+        <v>33.3</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>28.31</v>
+        <v>14.14</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>28.53</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>43.73</v>
+        <v>41.41</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>53.88</v>
+        <v>43.94</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>29.35</v>
+        <v>29.32</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>40.19</v>
+        <v>34.1</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>29.08</v>
+        <v>28.48</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>14.65</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="35">
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.66</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.51</v>
+        <v>-1.51</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.57</v>
+        <v>-0.84</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>-0.35</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.78</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>-0.14</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="P36" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>0.16</v>
-      </c>
       <c r="R36" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-1.22</v>
+        <v>-0.54</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>-1.31</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.49</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.49</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.75</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
@@ -3506,16 +3506,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>29.18</v>
+        <v>66.73</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>29.4</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>28</v>
+        <v>77.06</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>30</v>
+        <v>-68.97</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>37.52</v>
+        <v>32.48</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>41.68</v>
+        <v>33.73</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>32.13</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>28.71</v>
+        <v>34.69</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>14.39</v>
+        <v>14.44</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>7.81</v>
+        <v>25.22</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>21.45</v>
+        <v>40.08</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>16</v>
+        <v>29.22</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>7.7</v>
+        <v>14.45</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14.45</v>
+        <v>7.66</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>17.57</v>
+        <v>27.52</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>39.69</v>
+        <v>33.53</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>28.92</v>
+        <v>14.42</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>29.06</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>44.24</v>
+        <v>41.94</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>54.41</v>
+        <v>44.33</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>29.35</v>
+        <v>29.32</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>40.7</v>
+        <v>34.34</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>29.34</v>
+        <v>28.79</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>14.56</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="40">
@@ -3758,22 +3758,22 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0.22</v>
-      </c>
       <c r="F41" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.06</v>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.26</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>-0.78</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.96</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.11</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.52</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="42">
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>28.58</v>
+        <v>66.86</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>28.85</v>
+        <v>67.41</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>27.39</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>29.35</v>
+        <v>-69.59</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>36.67</v>
+        <v>31.81</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>40.9</v>
+        <v>33.13</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>31.47</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>28.06</v>
+        <v>33.91</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>14.01</v>
+        <v>14.06</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>7.6</v>
+        <v>24.54</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>20.87</v>
+        <v>38.99</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>15.61</v>
+        <v>28.43</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>7.51</v>
+        <v>14.09</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>14.08</v>
+        <v>7.45</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>17.16</v>
+        <v>26.82</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>39.49</v>
+        <v>33.08</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>29.03</v>
+        <v>14.39</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>29.38</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>44.24</v>
+        <v>41.94</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>54.36</v>
+        <v>44.33</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>29.33</v>
+        <v>29.3</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>40.74</v>
+        <v>34.41</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>29.16</v>
+        <v>28.62</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>14.42</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="45">
@@ -4178,73 +4178,73 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-0.55</v>
+        <v>0.27</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.48</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.46</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>-0.6</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.78</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>-0.38</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.66</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.61</v>
+        <v>-1.09</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.77</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.41</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.67</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.79</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.29</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.96</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.11</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>-0.7</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.45</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -4346,16 +4346,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>24.97</v>
+        <v>57.76</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>25.13</v>
+        <v>58.19</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>23.86</v>
+        <v>68.72</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>25.54</v>
+        <v>-73.25</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>32.11</v>
+        <v>27.88</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>35.91</v>
+        <v>29.11</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>27.83</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>24.92</v>
+        <v>30.14</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>12.42</v>
+        <v>12.48</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>6.73</v>
+        <v>21.72</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>18.45</v>
+        <v>34.43</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>13.75</v>
+        <v>25.02</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>6.63</v>
+        <v>12.44</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>12.46</v>
+        <v>6.6</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>15.14</v>
+        <v>23.7</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>35.24</v>
+        <v>29.55</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>25.88</v>
+        <v>12.86</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>26.25</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>39.74</v>
+        <v>37.66</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>48.87</v>
+        <v>39.93</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>26.34</v>
+        <v>26.29</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>35.89</v>
+        <v>30.47</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>25.55</v>
+        <v>25.14</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>12.48</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>-4.15</v>
+        <v>-8.84</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-4.12</v>
+        <v>-9.02</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-3.91</v>
+        <v>-8.27</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-4.21</v>
+        <v>-4.02</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>-5.11</v>
+        <v>-4.41</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-5.57</v>
+        <v>-4.48</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>-4.23</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-3.79</v>
+        <v>-4.55</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>-1.96</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-1.08</v>
+        <v>-3.48</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-3.03</v>
+        <v>-5.65</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-2.28</v>
+        <v>-4.18</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-1.09</v>
+        <v>-2.05</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-1.98</v>
+        <v>-1.06</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-2.42</v>
+        <v>-3.79</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-5.08</v>
+        <v>-4.31</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.65</v>
+        <v>-1.83</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>-3.6</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.52</v>
+        <v>-5.24</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-6.79</v>
+        <v>-5.51</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>-3.69</v>
+        <v>-3.71</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>-5.38</v>
+        <v>-4.39</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-3.96</v>
+        <v>-3.8</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-2.01</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="52">
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>29.12</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>29.25</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>27.78</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>29.76</v>
+        <v>-69.23</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>37.22</v>
+        <v>32.29</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>41.47</v>
+        <v>33.59</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>32.06</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>28.71</v>
+        <v>34.69</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>14.39</v>
+        <v>14.44</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>7.81</v>
+        <v>25.2</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>21.47</v>
+        <v>40.08</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>16.03</v>
+        <v>29.19</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>7.72</v>
+        <v>14.49</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>14.44</v>
+        <v>7.65</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>17.57</v>
+        <v>27.49</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>40.32</v>
+        <v>33.87</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>29.52</v>
+        <v>14.68</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>29.85</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>45.26</v>
+        <v>42.9</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>55.66</v>
+        <v>45.44</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>30.03</v>
+        <v>30</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>41.27</v>
+        <v>34.86</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>29.51</v>
+        <v>28.94</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>14.49</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="55">
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>29.03</v>
+        <v>68.66</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>29.31</v>
+        <v>69.22</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>27.86</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>29.82</v>
+        <v>-69.14</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>37.22</v>
+        <v>32.29</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>41.6</v>
+        <v>33.69</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>31.94</v>
+        <v>31.9</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>28.51</v>
+        <v>34.45</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>14.25</v>
+        <v>14.3</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>7.73</v>
+        <v>24.92</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>21.22</v>
+        <v>39.64</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>15.89</v>
+        <v>28.91</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>7.64</v>
+        <v>14.32</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>14.32</v>
+        <v>7.57</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>17.45</v>
+        <v>27.25</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>40.32</v>
+        <v>33.7</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>29.61</v>
+        <v>14.68</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>30.09</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>45.03</v>
+        <v>42.69</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>55.27</v>
+        <v>45.12</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>29.85</v>
+        <v>29.82</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>41.56</v>
+        <v>35.1</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>29.69</v>
+        <v>29.14</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>14.59</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="60">
@@ -5438,73 +5438,73 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>-0.09</v>
+        <v>2.06</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.06</v>
+        <v>2.01</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.08</v>
+        <v>1.5</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>-0.14</v>
       </c>
       <c r="L61" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="P61" s="3" t="n">
         <v>-0.08</v>
       </c>
-      <c r="M61" s="3" t="n">
+      <c r="Q61" s="3" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N61" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="R61" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>-0.18</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>0.1</v>
@@ -5606,16 +5606,16 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>29.33</v>
+        <v>69.44</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>29.61</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>28.11</v>
+        <v>79.2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>30.12</v>
+        <v>-68.84999999999999</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>37.59</v>
+        <v>32.62</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>42.06</v>
+        <v>34.04</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>32.22</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>28.79</v>
+        <v>34.8</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>14.39</v>
+        <v>14.44</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>7.81</v>
+        <v>25.17</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>21.43</v>
+        <v>40.04</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>16.03</v>
+        <v>29.17</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>7.71</v>
+        <v>14.46</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>14.47</v>
+        <v>7.65</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>17.6</v>
+        <v>27.52</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>40.85</v>
+        <v>34.11</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>30</v>
+        <v>14.86</v>
       </c>
       <c r="T64" s="3" t="n">
         <v>30.49</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>45.67</v>
+        <v>43.29</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>56.05</v>
+        <v>45.76</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>30.27</v>
+        <v>30.24</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>42.12</v>
+        <v>35.57</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>30.05</v>
+        <v>29.5</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>14.74</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="65">
@@ -5858,73 +5858,73 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.21</v>
+        <v>2.85</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.36</v>
+        <v>2.8</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.34</v>
+        <v>2.21</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>0.16</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="M66" s="3" t="n">
         <v>-0.04</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="O66" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="P66" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="P66" s="3" t="n">
+      <c r="Q66" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q66" s="3" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R66" s="3" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.48</v>
+        <v>0.18</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>0.64</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>0.25</v>
@@ -6026,16 +6026,16 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>29.09</v>
+        <v>70.47</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>29.49</v>
+        <v>71.05</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>30</v>
+        <v>-69</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>37.33</v>
+        <v>32.39</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>41.85</v>
+        <v>33.9</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>31.94</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>28.53</v>
+        <v>34.48</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>14.26</v>
+        <v>14.31</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>7.74</v>
+        <v>24.97</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>21.26</v>
+        <v>39.68</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>15.92</v>
+        <v>28.93</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>7.66</v>
+        <v>14.34</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>14.35</v>
+        <v>7.58</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>17.46</v>
+        <v>27.3</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>40.6</v>
+        <v>33.9</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>29.82</v>
+        <v>14.77</v>
       </c>
       <c r="T69" s="3" t="n">
         <v>30.43</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>45.12</v>
+        <v>42.77</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>55.33</v>
+        <v>45.17</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>29.94</v>
+        <v>29.91</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>42.03</v>
+        <v>35.49</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>30.02</v>
+        <v>29.47</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>14.67</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>-0.03</v>
+        <v>3.88</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.24</v>
+        <v>3.84</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.22</v>
+        <v>3.01</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.22</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.4</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.28</v>
+        <v>0.03</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>0.58</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="W71" s="3" t="n">
         <v>-0.09</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="72">
@@ -6446,16 +6446,16 @@
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>28.3</v>
+        <v>66.8</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>28.57</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>27.12</v>
+        <v>76.81</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>29.03</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>36.27</v>
+        <v>31.47</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>40.54</v>
+        <v>32.84</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>31.16</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>27.82</v>
+        <v>33.62</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>13.91</v>
+        <v>13.97</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>7.54</v>
+        <v>24.35</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20.73</v>
+        <v>38.69</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>15.5</v>
+        <v>28.18</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>7.46</v>
+        <v>13.99</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>13.98</v>
+        <v>7.39</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>17.02</v>
+        <v>26.62</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>39.45</v>
+        <v>32.98</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>29</v>
+        <v>14.37</v>
       </c>
       <c r="T74" s="3" t="n">
         <v>29.44</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>44.11</v>
+        <v>41.81</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>54.14</v>
+        <v>44.2</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>29.24</v>
+        <v>29.21</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>40.62</v>
+        <v>34.31</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>28.99</v>
+        <v>28.46</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>-0.83</v>
+        <v>0.2</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.18</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.82</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.76</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>-0.9</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.08</v>
       </c>
       <c r="K76" s="3" t="n">
         <v>-0.47</v>
       </c>
       <c r="L76" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P76" s="3" t="n">
         <v>-0.26</v>
       </c>
-      <c r="M76" s="3" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>-0.46</v>
-      </c>
       <c r="Q76" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.88</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.89</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.32</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>-0.41</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.09</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.24</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>-0.79</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.55</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.48</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="77">
@@ -6866,16 +6866,16 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>29.12</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>29.25</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>27.78</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>29.76</v>
+        <v>-69.23</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>37.22</v>
+        <v>32.29</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>41.47</v>
+        <v>33.59</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>32.06</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>28.71</v>
+        <v>34.69</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>14.39</v>
+        <v>14.44</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>7.81</v>
+        <v>25.2</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>21.47</v>
+        <v>40.08</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>16.03</v>
+        <v>29.19</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>7.72</v>
+        <v>14.49</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>14.44</v>
+        <v>7.65</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>17.57</v>
+        <v>27.49</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>40.32</v>
+        <v>33.87</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>29.52</v>
+        <v>14.68</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>29.85</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>45.26</v>
+        <v>42.9</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>55.66</v>
+        <v>45.44</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>30.03</v>
+        <v>30</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>41.27</v>
+        <v>34.86</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>29.51</v>
+        <v>28.94</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>14.49</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="80">
@@ -7286,16 +7286,16 @@
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>26.53</v>
+        <v>60.71</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>26.62</v>
+        <v>61.38</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>25.3</v>
+        <v>71.5</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>27.08</v>
+        <v>-73</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>32.39</v>
+        <v>28.13</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>36.19</v>
+        <v>29.31</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>28</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>24.9</v>
+        <v>30.11</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>12.41</v>
+        <v>12.46</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>6.67</v>
+        <v>21.52</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>18.43</v>
+        <v>34.4</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>13.76</v>
+        <v>25.04</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>6.6</v>
+        <v>12.99</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>12.3</v>
+        <v>6.83</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>14.96</v>
+        <v>23.42</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>33.88</v>
+        <v>28.51</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>24.87</v>
+        <v>12.38</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>25.47</v>
+        <v>25.49</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>38.85</v>
+        <v>36.79</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>47.98</v>
+        <v>39.17</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>25.95</v>
+        <v>25.86</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>35.49</v>
+        <v>31.49</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>26.71</v>
+        <v>26.19</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>13.02</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="85">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>-2.59</v>
+        <v>-5.89</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-2.64</v>
+        <v>-5.83</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-2.48</v>
+        <v>-5.49</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>-2.68</v>
+        <v>-3.77</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>-4.83</v>
+        <v>-4.16</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-5.28</v>
+        <v>-4.28</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>-4.06</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-3.81</v>
+        <v>-4.58</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-1.97</v>
+        <v>-1.98</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.14</v>
+        <v>-3.68</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-3.04</v>
+        <v>-5.68</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-2.27</v>
+        <v>-4.16</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.51</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-2.14</v>
+        <v>-0.82</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-2.6</v>
+        <v>-4.08</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-6.44</v>
+        <v>-5.36</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-4.65</v>
+        <v>-2.3</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-4.38</v>
+        <v>-4.36</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.41</v>
+        <v>-6.11</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-7.68</v>
+        <v>-6.27</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-4.07</v>
+        <v>-4.14</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-5.78</v>
+        <v>-3.37</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-2.8</v>
+        <v>-2.75</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-1.47</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="87">
@@ -7706,16 +7706,16 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0</v>
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>29.63</v>
+        <v>66.73</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>29.82</v>
+        <v>67.41</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>28.49</v>
+        <v>77.3</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>30.55</v>
+        <v>-68.47</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>38.01</v>
+        <v>32.91</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>42.23</v>
+        <v>34.21</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>32.65</v>
+        <v>32.68</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>29.2</v>
+        <v>35.22</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>14.73</v>
+        <v>14.78</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>8.01</v>
+        <v>25.84</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>22</v>
+        <v>40.98</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>16.34</v>
+        <v>29.73</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>7.88</v>
+        <v>14.8</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>14.81</v>
+        <v>7.85</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>18</v>
+        <v>28.17</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>40.28</v>
+        <v>34.11</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>29.23</v>
+        <v>14.62</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>29.29</v>
+        <v>29.26</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>44.77</v>
+        <v>42.39</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>55.05</v>
+        <v>44.81</v>
       </c>
       <c r="W89" s="3" t="n">
         <v>29.73</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>41.03</v>
+        <v>34.68</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>29.69</v>
+        <v>29.17</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>14.82</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="90">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0.51</v>
+        <v>0.13</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0.71</v>
+        <v>0.31</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>0.34</v>
       </c>
       <c r="L91" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P91" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="M91" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N91" s="3" t="n">
+      <c r="Q91" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z91" s="3" t="n">
         <v>0.31</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="X91" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Y91" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="Z91" s="3" t="n">
-        <v>0.33</v>
       </c>
     </row>
     <row r="92">
@@ -8126,16 +8126,16 @@
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>0</v>
+        <v>16.06</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-04-26T03:10:42</t>
+          <t>CreatedAt: 2026-04-26T04:10:32</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -665,61 +665,61 @@
         <v>76</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>102.83</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-34.82</v>
+        <v>93</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>24.07</v>
+        <v>-69.34999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.38</v>
+        <v>14.44</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>25.3</v>
+        <v>14.44</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>31.98</v>
+        <v>29.09</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>38.72</v>
+        <v>28.7</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>28.64</v>
+        <v>14.51</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>25.86</v>
+        <v>25.81</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>29.22</v>
+        <v>28.59</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>29.52</v>
+        <v>40.46</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>14.4</v>
+        <v>29.02</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>32.08</v>
+        <v>29.62</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>44.46</v>
+        <v>42.14</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>47.43</v>
+        <v>44.28</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>29.41</v>
+        <v>29.38</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>39.76</v>
+        <v>33.07</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>14.73</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="5">
@@ -833,28 +833,28 @@
         <v>0.04</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>-0.01</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.06</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>-0.03</v>
@@ -863,31 +863,31 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.57</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.58</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.77</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.07</v>
+        <v>-0.88</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.19</v>
+        <v>-0.97</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1001,13 +1001,13 @@
         <v>31.38</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>73.98</v>
+        <v>40.58</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-75.02</v>
+        <v>57.96</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>-98.29000000000001</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1085,61 +1085,61 @@
         <v>76.36</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>102.86</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-34.49</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>23.9</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>14.44</v>
+        <v>14.62</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>25.5</v>
+        <v>14.71</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.5</v>
+        <v>29.9</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>39.23</v>
+        <v>29.5</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>28.93</v>
+        <v>14.85</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>26.33</v>
+        <v>26.58</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>29.43</v>
+        <v>29.23</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>29.49</v>
+        <v>41.03</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>14.26</v>
+        <v>29.11</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>31.8</v>
+        <v>29.73</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>43.86</v>
+        <v>42.22</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>47.01</v>
+        <v>44.37</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>29.56</v>
+        <v>29.85</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>39.65</v>
+        <v>33.43</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14.7</v>
+        <v>14.89</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>14.58</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="10">
@@ -1253,61 +1253,61 @@
         <v>0.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.21</v>
+        <v>0.64</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.65</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.67</v>
+        <v>-0.8</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.6</v>
+        <v>-0.89</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.15</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.13</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.25</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="12">
@@ -1421,13 +1421,13 @@
         <v>31.38</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>73.98</v>
+        <v>40.58</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-75.02</v>
+        <v>57.96</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>-98.29000000000001</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1505,61 +1505,61 @@
         <v>76.36</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>102.86</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-34.49</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>23.9</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>14.43</v>
+        <v>14.62</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>25.5</v>
+        <v>14.71</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>32.5</v>
+        <v>29.9</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>39.23</v>
+        <v>29.5</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>28.9</v>
+        <v>14.85</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>26.33</v>
+        <v>26.61</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>29.43</v>
+        <v>29.23</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>29.49</v>
+        <v>41.03</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>14.26</v>
+        <v>29.11</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>31.8</v>
+        <v>29.73</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>43.86</v>
+        <v>42.22</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>47.01</v>
+        <v>44.37</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>29.56</v>
+        <v>29.85</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>39.65</v>
+        <v>33.43</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>14.7</v>
+        <v>14.89</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>14.58</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="15">
@@ -1673,61 +1673,61 @@
         <v>0.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.21</v>
+        <v>0.64</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.65</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.67</v>
+        <v>-0.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.6</v>
+        <v>-0.89</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.15</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.13</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.25</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="17">
@@ -1841,13 +1841,13 @@
         <v>31.38</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>73.98</v>
+        <v>40.58</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-75.02</v>
+        <v>57.96</v>
       </c>
       <c r="J18" s=